--- a/data/dividend_calendar.xlsx
+++ b/data/dividend_calendar.xlsx
@@ -575,7 +575,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Estimated Dividend Calendar: Anticipated Announcements - 09/07/2026</t>
+          <t>Estimated Dividend Calendar: Anticipated Announcements - 09/14/2026</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
         <v>46048</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>-224</v>
+        <v>-231</v>
       </c>
       <c r="J6" s="10" t="n">
         <v>46413</v>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0.06045694038225009</v>
+        <v>0.0618816332174422</v>
       </c>
     </row>
     <row r="7">
@@ -726,7 +726,7 @@
         <v>46263</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>-9</v>
+        <v>-16</v>
       </c>
       <c r="J7" s="10" t="n">
         <v>46662</v>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0.03239186184874104</v>
+        <v>0.03249306950164277</v>
       </c>
     </row>
     <row r="8">
@@ -771,11 +771,11 @@
       <c r="H8" s="10" t="n">
         <v>46278</v>
       </c>
-      <c r="I8" s="13" t="n">
-        <v>6</v>
+      <c r="I8" s="11" t="n">
+        <v>-1</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>46344</v>
+        <v>46709</v>
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="L8" s="9" t="n">
-        <v>0.007284370444425581</v>
+        <v>0.007252874320868801</v>
       </c>
     </row>
     <row r="9">
@@ -818,7 +818,7 @@
         <v>46280</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J9" s="10" t="n">
         <v>46668</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="L9" s="9" t="n">
-        <v>0.05648185150526099</v>
+        <v>0.05532352119915055</v>
       </c>
     </row>
     <row r="10">
@@ -864,7 +864,7 @@
         <v>46285</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J10" s="10" t="n">
         <v>46325</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0.0219780217704021</v>
+        <v>0.02153962736846832</v>
       </c>
     </row>
     <row r="11">
@@ -910,7 +910,7 @@
         <v>46305</v>
       </c>
       <c r="I11" s="14" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J11" s="10" t="n">
         <v>46339</v>
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0.02866320644948689</v>
+        <v>0.028948135474036</v>
       </c>
     </row>
     <row r="12">
@@ -956,7 +956,7 @@
         <v>46311</v>
       </c>
       <c r="I12" s="14" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="J12" s="10" t="n">
         <v>46386</v>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="L12" s="9" t="n">
-        <v>0.01143105184521834</v>
+        <v>0.0127142515706196</v>
       </c>
     </row>
     <row r="13">
@@ -1002,7 +1002,7 @@
         <v>46318</v>
       </c>
       <c r="I13" s="14" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="J13" s="10" t="n">
         <v>46352</v>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="L13" s="9" t="n">
-        <v>0.01930542489909123</v>
+        <v>0.01974143087025879</v>
       </c>
     </row>
     <row r="14">
@@ -1048,7 +1048,7 @@
         <v>46322</v>
       </c>
       <c r="I14" s="14" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="J14" s="10" t="n">
         <v>46338</v>
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="L14" s="9" t="n">
-        <v>0.0238650142641304</v>
+        <v>0.02491484184914842</v>
       </c>
     </row>
     <row r="15">
@@ -1094,7 +1094,7 @@
         <v>46329</v>
       </c>
       <c r="I15" s="14" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="J15" s="10" t="n">
         <v>46338</v>
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="L15" s="9" t="n">
-        <v>0.007251850465255884</v>
+        <v>0.007397361552028218</v>
       </c>
     </row>
     <row r="16">
@@ -1140,7 +1140,7 @@
         <v>46332</v>
       </c>
       <c r="I16" s="14" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="J16" s="10" t="n">
         <v>46346</v>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0.02548302872062663</v>
+        <v>0.02583787857341831</v>
       </c>
     </row>
     <row r="17">
@@ -1186,7 +1186,7 @@
         <v>46341</v>
       </c>
       <c r="I17" s="14" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="J17" s="10" t="n">
         <v>46340</v>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.02583558016217738</v>
+        <v>0.02451651249736115</v>
       </c>
     </row>
     <row r="18">
@@ -1232,7 +1232,7 @@
         <v>46344</v>
       </c>
       <c r="I18" s="14" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="J18" s="10" t="n">
         <v>46385</v>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0.03686635815083875</v>
+        <v>0.03748535638894003</v>
       </c>
     </row>
     <row r="19">
@@ -1278,7 +1278,7 @@
         <v>46347</v>
       </c>
       <c r="I19" s="14" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="J19" s="10" t="n">
         <v>46358</v>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="L19" s="9" t="n">
-        <v>0.04270833163625671</v>
+        <v>0.04430037762617224</v>
       </c>
     </row>
     <row r="20">
@@ -1324,7 +1324,7 @@
         <v>46352</v>
       </c>
       <c r="I20" s="14" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="J20" s="10" t="n">
         <v>46400</v>
@@ -1335,7 +1335,7 @@
         </is>
       </c>
       <c r="L20" s="9" t="n">
-        <v>0.05441039694455867</v>
+        <v>0.05595607625096392</v>
       </c>
     </row>
     <row r="21">
@@ -1370,7 +1370,7 @@
         <v>46360</v>
       </c>
       <c r="I21" s="14" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="J21" s="10" t="n">
         <v>46371</v>
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="L21" s="9" t="n">
-        <v>0.04719763849938742</v>
+        <v>0.04971885038416789</v>
       </c>
     </row>
     <row r="22">
@@ -1416,7 +1416,7 @@
         <v>46366</v>
       </c>
       <c r="I22" s="14" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="J22" s="10" t="n">
         <v>46432</v>
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="L22" s="9" t="n">
-        <v>0.02305422717269788</v>
+        <v>0.02668498548328576</v>
       </c>
     </row>
     <row r="23">
@@ -1462,7 +1462,7 @@
         <v>46380</v>
       </c>
       <c r="I23" s="14" t="n">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="J23" s="10" t="n">
         <v>46436</v>
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0.02419964820546709</v>
+        <v>0.02463433333150609</v>
       </c>
     </row>
     <row r="24">
@@ -1508,7 +1508,7 @@
         <v>46383</v>
       </c>
       <c r="I24" s="21" t="n">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="J24" s="20" t="n">
         <v>46404</v>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="L24" s="19" t="n">
-        <v>0.01515151568586133</v>
+        <v>0.01539665983034154</v>
       </c>
     </row>
     <row r="25">
@@ -1554,7 +1554,7 @@
         <v>46402</v>
       </c>
       <c r="I25" s="14" t="n">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="J25" s="10" t="n">
         <v>46483</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="L25" s="9" t="n">
-        <v>0.014506198907202</v>
+        <v>0.01446715458684541</v>
       </c>
     </row>
     <row r="26">
@@ -1600,7 +1600,7 @@
         <v>46411</v>
       </c>
       <c r="I26" s="14" t="n">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="J26" s="10" t="n">
         <v>46435</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="L26" s="9" t="n">
-        <v>0.03841005375174777</v>
+        <v>0.03957219387294963</v>
       </c>
     </row>
     <row r="27">
@@ -1646,7 +1646,7 @@
         <v>46417</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="J27" s="10" t="n">
         <v>46433</v>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="L27" s="9" t="n">
-        <v>0.03413230964368608</v>
+        <v>0.03291115891894363</v>
       </c>
     </row>
     <row r="28">
@@ -1692,7 +1692,7 @@
         <v>46423</v>
       </c>
       <c r="I28" s="14" t="n">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="J28" s="10" t="n">
         <v>46473</v>
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="L28" s="9" t="n">
-        <v>0.02484978622141126</v>
+        <v>0.02673438847314084</v>
       </c>
     </row>
     <row r="29">
@@ -1738,7 +1738,7 @@
         <v>46428</v>
       </c>
       <c r="I29" s="14" t="n">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="J29" s="10" t="n">
         <v>46452</v>
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="L29" s="9" t="n">
-        <v>0.01473074142109956</v>
+        <v>0.01462479053918474</v>
       </c>
     </row>
     <row r="30">
@@ -1784,7 +1784,7 @@
         <v>46428</v>
       </c>
       <c r="I30" s="14" t="n">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="J30" s="10" t="n">
         <v>46460</v>
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="L30" s="9" t="n">
-        <v>0.04736746272382592</v>
+        <v>0.04881483149978388</v>
       </c>
     </row>
     <row r="31">
@@ -1830,7 +1830,7 @@
         <v>46429</v>
       </c>
       <c r="I31" s="21" t="n">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="J31" s="20" t="n">
         <v>46450</v>
@@ -1841,7 +1841,7 @@
         </is>
       </c>
       <c r="L31" s="19" t="n">
-        <v>0.02637130929027715</v>
+        <v>0.02641310047223251</v>
       </c>
     </row>
     <row r="32">
@@ -1876,7 +1876,7 @@
         <v>46431</v>
       </c>
       <c r="I32" s="14" t="n">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="J32" s="10" t="n">
         <v>46480</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="L32" s="9" t="n">
-        <v>0.01538461581456155</v>
+        <v>0.01520224384693243</v>
       </c>
     </row>
     <row r="33">
@@ -1922,7 +1922,7 @@
         <v>46432</v>
       </c>
       <c r="I33" s="14" t="n">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="J33" s="10" t="n">
         <v>46455</v>
@@ -1933,7 +1933,7 @@
         </is>
       </c>
       <c r="L33" s="9" t="n">
-        <v>0.03636363786937607</v>
+        <v>0.03727399086403899</v>
       </c>
     </row>
     <row r="34">
@@ -1968,7 +1968,7 @@
         <v>46433</v>
       </c>
       <c r="I34" s="14" t="n">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="J34" s="10" t="n">
         <v>46425</v>
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="L34" s="9" t="n">
-        <v>0.004986937847341924</v>
+        <v>0.005338793701200471</v>
       </c>
     </row>
     <row r="35">
@@ -2014,7 +2014,7 @@
         <v>46433</v>
       </c>
       <c r="I35" s="14" t="n">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="J35" s="10" t="n">
         <v>46383</v>
@@ -2025,7 +2025,7 @@
         </is>
       </c>
       <c r="L35" s="9" t="n">
-        <v>0.0184862591703806</v>
+        <v>0.0186580544393274</v>
       </c>
     </row>
     <row r="36">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D36" s="7" t="n">
@@ -2060,10 +2060,10 @@
         <v>46433</v>
       </c>
       <c r="I36" s="14" t="n">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>46368</v>
+        <v>46458</v>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="L36" s="9" t="n">
-        <v>0.02663337418694604</v>
+        <v>0.02508574153301707</v>
       </c>
     </row>
     <row r="37">
@@ -2106,7 +2106,7 @@
         <v>46433</v>
       </c>
       <c r="I37" s="14" t="n">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="J37" s="10" t="n">
         <v>46634</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="L37" s="9" t="n">
-        <v>0.02879670887223125</v>
+        <v>0.02863412689310154</v>
       </c>
     </row>
     <row r="38">
@@ -2152,7 +2152,7 @@
         <v>46433</v>
       </c>
       <c r="I38" s="14" t="n">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="J38" s="10" t="n">
         <v>46608</v>
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="L38" s="9" t="n">
-        <v>0.03308411372219163</v>
+        <v>0.03364219619018467</v>
       </c>
     </row>
     <row r="39">
@@ -2198,7 +2198,7 @@
         <v>46440</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="J39" s="10" t="n">
         <v>46450</v>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="L39" s="9" t="n">
-        <v>0.00883876829813468</v>
+        <v>0.00946320755973527</v>
       </c>
     </row>
     <row r="40">
@@ -2244,7 +2244,7 @@
         <v>46441</v>
       </c>
       <c r="I40" s="14" t="n">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="J40" s="10" t="n">
         <v>46456</v>
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="L40" s="9" t="n">
-        <v>0.02902974724923542</v>
+        <v>0.03000740561476674</v>
       </c>
     </row>
     <row r="41">
@@ -2290,7 +2290,7 @@
         <v>46452</v>
       </c>
       <c r="I41" s="14" t="n">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="J41" s="10" t="n">
         <v>46487</v>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="L41" s="9" t="n">
-        <v>0.01769665194015332</v>
+        <v>0.01779070791836802</v>
       </c>
     </row>
     <row r="42">
@@ -2336,7 +2336,7 @@
         <v>46461</v>
       </c>
       <c r="I42" s="14" t="n">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="J42" s="10" t="n">
         <v>46300</v>
@@ -2347,7 +2347,7 @@
         </is>
       </c>
       <c r="L42" s="9" t="n">
-        <v>0.01672986770838049</v>
+        <v>0.01699235314722998</v>
       </c>
     </row>
     <row r="43">
@@ -2382,7 +2382,7 @@
         <v>46461</v>
       </c>
       <c r="I43" s="14" t="n">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="J43" s="10" t="n">
         <v>46386</v>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="L43" s="9" t="n">
-        <v>0.05309387755102041</v>
+        <v>0.05447236111291268</v>
       </c>
     </row>
     <row r="44">
@@ -2428,7 +2428,7 @@
         <v>46488</v>
       </c>
       <c r="I44" s="14" t="n">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="J44" s="10" t="n">
         <v>46498</v>
@@ -2439,7 +2439,7 @@
         </is>
       </c>
       <c r="L44" s="9" t="n">
-        <v>0.02974597055024585</v>
+        <v>0.02964170822323141</v>
       </c>
     </row>
     <row r="45">
@@ -2474,7 +2474,7 @@
         <v>46492</v>
       </c>
       <c r="I45" s="14" t="n">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="J45" s="10" t="n">
         <v>46501</v>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="L45" s="9" t="n">
-        <v>0.02008928571428572</v>
+        <v>0.0204202028393521</v>
       </c>
     </row>
     <row r="46">
@@ -2520,7 +2520,7 @@
         <v>46492</v>
       </c>
       <c r="I46" s="14" t="n">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="J46" s="10" t="n">
         <v>46376</v>
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="L46" s="9" t="n">
-        <v>0.04397787742467318</v>
+        <v>0.04231333292565891</v>
       </c>
     </row>
     <row r="47">
@@ -2566,7 +2566,7 @@
         <v>46493</v>
       </c>
       <c r="I47" s="14" t="n">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="J47" s="10" t="n">
         <v>46531</v>
@@ -2577,7 +2577,7 @@
         </is>
       </c>
       <c r="L47" s="9" t="n">
-        <v>0.01947462044851735</v>
+        <v>0.01990567170011602</v>
       </c>
     </row>
     <row r="48">
@@ -2612,7 +2612,7 @@
         <v>46499</v>
       </c>
       <c r="I48" s="14" t="n">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="J48" s="10" t="n">
         <v>46526</v>
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="L48" s="9" t="n">
-        <v>0.01991454025218246</v>
+        <v>0.01924971624665003</v>
       </c>
     </row>
     <row r="49">
@@ -2658,7 +2658,7 @@
         <v>46504</v>
       </c>
       <c r="I49" s="14" t="n">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="J49" s="10" t="n">
         <v>46562</v>
@@ -2669,7 +2669,7 @@
         </is>
       </c>
       <c r="L49" s="9" t="n">
-        <v>0.04520098596940841</v>
+        <v>0.04570717428878286</v>
       </c>
     </row>
     <row r="50">
@@ -2704,7 +2704,7 @@
         <v>46508</v>
       </c>
       <c r="I50" s="14" t="n">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="J50" s="10" t="n">
         <v>46518</v>
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="L50" s="9" t="n">
-        <v>0.03910935860492718</v>
+        <v>0.04061086969695727</v>
       </c>
     </row>
     <row r="51">
@@ -2750,7 +2750,7 @@
         <v>46515</v>
       </c>
       <c r="I51" s="14" t="n">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="J51" s="10" t="n">
         <v>46542</v>
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="L51" s="9" t="n">
-        <v>0.0430138762622343</v>
+        <v>0.04294834704934376</v>
       </c>
     </row>
     <row r="52">
@@ -2796,7 +2796,7 @@
         <v>46532</v>
       </c>
       <c r="I52" s="14" t="n">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="J52" s="10" t="n">
         <v>46563</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="L52" s="9" t="n">
-        <v>0.03058298880746655</v>
+        <v>0.03080872803355954</v>
       </c>
     </row>
     <row r="53">
@@ -2842,7 +2842,7 @@
         <v>46589</v>
       </c>
       <c r="I53" s="14" t="n">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="J53" s="10" t="n">
         <v>46629</v>
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="L53" s="9" t="n">
-        <v>0.01961190558580643</v>
+        <v>0.0199424192610679</v>
       </c>
     </row>
     <row r="54">
@@ -2873,25 +2873,25 @@
         </is>
       </c>
       <c r="D54" s="7" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E54" s="7" t="n">
         <v>0.83</v>
       </c>
-      <c r="E54" s="7" t="n">
-        <v>0.82</v>
-      </c>
       <c r="F54" s="8" t="n">
-        <v>0.01219512195121952</v>
+        <v>0.01204819277108435</v>
       </c>
       <c r="G54" s="9" t="n">
         <v>0.04</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>46592</v>
+        <v>46591</v>
       </c>
       <c r="I54" s="14" t="n">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>46632</v>
+        <v>46633</v>
       </c>
       <c r="K54" s="12" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="L54" s="9" t="n">
-        <v>0.03410024629403103</v>
+        <v>0.03791041525582833</v>
       </c>
     </row>
     <row r="55">
@@ -2934,7 +2934,7 @@
         <v>46594</v>
       </c>
       <c r="I55" s="14" t="n">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J55" s="10" t="n">
         <v>46613</v>
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="L55" s="9" t="n">
-        <v>0.01547755333783219</v>
+        <v>0.01568376395018629</v>
       </c>
     </row>
     <row r="56">
@@ -2980,7 +2980,7 @@
         <v>46595</v>
       </c>
       <c r="I56" s="14" t="n">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="J56" s="10" t="n">
         <v>46614</v>
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="L56" s="9" t="n">
-        <v>0.02466960386438792</v>
+        <v>0.0250789461211513</v>
       </c>
     </row>
     <row r="57">
@@ -3026,7 +3026,7 @@
         <v>46597</v>
       </c>
       <c r="I57" s="14" t="n">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="J57" s="10" t="n">
         <v>46611</v>
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="L57" s="9" t="n">
-        <v>0.05372877854259377</v>
+        <v>0.05629362775477879</v>
       </c>
     </row>
     <row r="58">
@@ -3072,7 +3072,7 @@
         <v>46598</v>
       </c>
       <c r="I58" s="14" t="n">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="J58" s="10" t="n">
         <v>46629</v>
@@ -3083,7 +3083,7 @@
         </is>
       </c>
       <c r="L58" s="9" t="n">
-        <v>0.02533513789021478</v>
+        <v>0.02503037574256811</v>
       </c>
     </row>
   </sheetData>
@@ -3118,7 +3118,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Expected Increase Announcements by Month - 09/07/2026</t>
+          <t>Expected Increase Announcements by Month - 09/14/2026</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3297,7 @@
         <v>46278</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>46344</v>
+        <v>46709</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>0.91</v>
@@ -4164,7 +4164,7 @@
         <v>46433</v>
       </c>
       <c r="C57" s="10" t="n">
-        <v>46368</v>
+        <v>46458</v>
       </c>
       <c r="D57" s="7" t="n">
         <v>0.32</v>
@@ -4749,16 +4749,16 @@
         </is>
       </c>
       <c r="B87" s="10" t="n">
-        <v>46592</v>
+        <v>46591</v>
       </c>
       <c r="C87" s="10" t="n">
-        <v>46632</v>
+        <v>46633</v>
       </c>
       <c r="D87" s="7" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>0.01219512195121952</v>
+        <v>0.01204819277108435</v>
       </c>
       <c r="F87" s="12" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Complete Holdings Dividend Summary - 09/07/2026</t>
+          <t>Complete Holdings Dividend Summary - 09/14/2026</t>
         </is>
       </c>
     </row>
@@ -5005,7 +5005,7 @@
         <v>1.16</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.00883876829813468</v>
+        <v>0.00946320755973527</v>
       </c>
       <c r="I5" s="10" t="n">
         <v>46255</v>
@@ -5058,7 +5058,7 @@
         <v>10.08</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.02305422717269788</v>
+        <v>0.02668498548328576</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>46255</v>
@@ -5111,7 +5111,7 @@
         <v>8.552</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.004986937847341924</v>
+        <v>0.005338793701200471</v>
       </c>
       <c r="I7" s="10" t="n">
         <v>46231</v>
@@ -5164,7 +5164,7 @@
         <v>2.184</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>0.02466960386438792</v>
+        <v>0.0250789461211513</v>
       </c>
       <c r="I8" s="10" t="n">
         <v>46251</v>
@@ -5217,7 +5217,7 @@
         <v>2.812</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.03841005375174777</v>
+        <v>0.03957219387294963</v>
       </c>
       <c r="I9" s="10" t="n">
         <v>46251</v>
@@ -5270,7 +5270,7 @@
         <v>4.12</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.02533513789021478</v>
+        <v>0.02503037574256811</v>
       </c>
       <c r="I10" s="10" t="n">
         <v>46265</v>
@@ -5323,7 +5323,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.05372877854259377</v>
+        <v>0.05629362775477879</v>
       </c>
       <c r="I11" s="10" t="n">
         <v>46246</v>
@@ -5376,10 +5376,10 @@
         <v>5.2</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0.0184862591703806</v>
+        <v>0.0186580544393274</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>46182</v>
+        <v>46274</v>
       </c>
       <c r="J12" s="8" t="n">
         <v>4.96</v>
@@ -5429,7 +5429,7 @@
         <v>0.96</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0.02419964820546709</v>
+        <v>0.02463433333150609</v>
       </c>
       <c r="I13" s="10" t="n">
         <v>46254</v>
@@ -5482,7 +5482,7 @@
         <v>2.4</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>0.007251850465255884</v>
+        <v>0.007397361552028218</v>
       </c>
       <c r="I14" s="10" t="n">
         <v>46248</v>
@@ -5535,7 +5535,7 @@
         <v>1.68</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0.01538461581456155</v>
+        <v>0.01520224384693243</v>
       </c>
       <c r="I15" s="10" t="n">
         <v>46209</v>
@@ -5588,7 +5588,7 @@
         <v>7.12</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>0.03413230964368608</v>
+        <v>0.03291115891894363</v>
       </c>
       <c r="I16" s="10" t="n">
         <v>46253</v>
@@ -5641,7 +5641,7 @@
         <v>3.44</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0.014506198907202</v>
+        <v>0.01446715458684541</v>
       </c>
       <c r="I17" s="10" t="n">
         <v>46211</v>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="F18" s="7" t="n">
@@ -5694,7 +5694,7 @@
         <v>1.28</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0.02663337418694604</v>
+        <v>0.02508574153301707</v>
       </c>
       <c r="I18" s="10" t="n">
         <v>46188</v>
@@ -5706,7 +5706,7 @@
         <v>46433</v>
       </c>
       <c r="L18" s="10" t="n">
-        <v>46368</v>
+        <v>46458</v>
       </c>
       <c r="M18" s="12" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>3.36</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0.04719763849938742</v>
+        <v>0.04971885038416789</v>
       </c>
       <c r="I19" s="10" t="n">
         <v>46188</v>
@@ -5800,7 +5800,7 @@
         <v>2.56</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0.0238650142641304</v>
+        <v>0.02491484184914842</v>
       </c>
       <c r="I20" s="10" t="n">
         <v>46247</v>
@@ -5853,7 +5853,7 @@
         <v>6.36</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0.01769665194015332</v>
+        <v>0.01779070791836802</v>
       </c>
       <c r="I21" s="10" t="n">
         <v>46205</v>
@@ -5906,7 +5906,7 @@
         <v>1.18</v>
       </c>
       <c r="H22" s="19" t="n">
-        <v>0.01515151568586133</v>
+        <v>0.01539665983034154</v>
       </c>
       <c r="I22" s="20" t="n">
         <v>46223</v>
@@ -5959,7 +5959,7 @@
         <v>9.32</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>0.02902974724923542</v>
+        <v>0.03000740561476674</v>
       </c>
       <c r="I23" s="10" t="n">
         <v>46268</v>
@@ -6012,7 +6012,7 @@
         <v>5.52</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>0.01930542489909123</v>
+        <v>0.01974143087025879</v>
       </c>
       <c r="I24" s="10" t="n">
         <v>46262</v>
@@ -6065,7 +6065,7 @@
         <v>1.172</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0.05441039694455867</v>
+        <v>0.05595607625096392</v>
       </c>
       <c r="I25" s="10" t="n">
         <v>46216</v>
@@ -6118,7 +6118,7 @@
         <v>2</v>
       </c>
       <c r="H26" s="19" t="n">
-        <v>0.02637130929027715</v>
+        <v>0.02641310047223251</v>
       </c>
       <c r="I26" s="20" t="n">
         <v>46269</v>
@@ -6171,7 +6171,7 @@
         <v>3.28</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0.03239186184874104</v>
+        <v>0.03249306950164277</v>
       </c>
       <c r="I27" s="10" t="n">
         <v>46204</v>
@@ -6224,7 +6224,7 @@
         <v>2.44</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>0.01473074142109956</v>
+        <v>0.01462479053918474</v>
       </c>
       <c r="I28" s="10" t="n">
         <v>46269</v>
@@ -6277,7 +6277,7 @@
         <v>5.36</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.01947462044851735</v>
+        <v>0.01990567170011602</v>
       </c>
       <c r="I29" s="10" t="n">
         <v>46259</v>
@@ -6330,7 +6330,7 @@
         <v>6</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>0.01672986770838049</v>
+        <v>0.01699235314722998</v>
       </c>
       <c r="I30" s="10" t="n">
         <v>46209</v>
@@ -6383,7 +6383,7 @@
         <v>2.25</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0.02008928571428572</v>
+        <v>0.0204202028393521</v>
       </c>
       <c r="I31" s="10" t="n">
         <v>46216</v>
@@ -6436,7 +6436,7 @@
         <v>3.16</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>0.01143105184521834</v>
+        <v>0.0127142515706196</v>
       </c>
       <c r="I32" s="10" t="n">
         <v>46203</v>
@@ -6489,7 +6489,7 @@
         <v>2.88</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0.03058298880746655</v>
+        <v>0.03080872803355954</v>
       </c>
       <c r="I33" s="10" t="n">
         <v>46199</v>
@@ -6542,7 +6542,7 @@
         <v>1.92</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0.03686635815083875</v>
+        <v>0.03748535638894003</v>
       </c>
       <c r="I34" s="10" t="n">
         <v>46209</v>
@@ -6595,7 +6595,7 @@
         <v>3.64</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>0.007284370444425581</v>
+        <v>0.007252874320868801</v>
       </c>
       <c r="I35" s="10" t="n">
         <v>46254</v>
@@ -6607,7 +6607,7 @@
         <v>46278</v>
       </c>
       <c r="L35" s="10" t="n">
-        <v>46344</v>
+        <v>46709</v>
       </c>
       <c r="M35" s="12" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>3.48</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>0.02866320644948689</v>
+        <v>0.028948135474036</v>
       </c>
       <c r="I36" s="10" t="n">
         <v>46211</v>
@@ -6701,7 +6701,7 @@
         <v>1.64</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>0.04270833163625671</v>
+        <v>0.04430037762617224</v>
       </c>
       <c r="I37" s="10" t="n">
         <v>46266</v>
@@ -6754,7 +6754,7 @@
         <v>1.158</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0.02484978622141126</v>
+        <v>0.02673438847314084</v>
       </c>
       <c r="I38" s="10" t="n">
         <v>46251</v>
@@ -6807,7 +6807,7 @@
         <v>3.252</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>0.05309387755102041</v>
+        <v>0.05447236111291268</v>
       </c>
       <c r="I39" s="10" t="n">
         <v>46265</v>
@@ -6860,7 +6860,7 @@
         <v>4.76</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0.03910935860492718</v>
+        <v>0.04061086969695727</v>
       </c>
       <c r="I40" s="10" t="n">
         <v>46231</v>
@@ -6913,10 +6913,10 @@
         <v>2.68</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>0.03636363786937607</v>
+        <v>0.03727399086403899</v>
       </c>
       <c r="I41" s="10" t="n">
-        <v>46182</v>
+        <v>46274</v>
       </c>
       <c r="J41" s="8" t="n">
         <v>0.06349206349206354</v>
@@ -6966,7 +6966,7 @@
         <v>5.92</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>0.0430138762622343</v>
+        <v>0.04294834704934376</v>
       </c>
       <c r="I42" s="10" t="n">
         <v>46269</v>
@@ -7019,7 +7019,7 @@
         <v>1.72</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>0.06045694038225009</v>
+        <v>0.0618816332174422</v>
       </c>
       <c r="I43" s="10" t="n">
         <v>46227</v>
@@ -7072,7 +7072,7 @@
         <v>3.36</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>0.02879670887223125</v>
+        <v>0.02863412689310154</v>
       </c>
       <c r="I44" s="10" t="n">
         <v>46268</v>
@@ -7125,7 +7125,7 @@
         <v>4.356</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>0.02974597055024585</v>
+        <v>0.02964170822323141</v>
       </c>
       <c r="I45" s="10" t="n">
         <v>46227</v>
@@ -7178,7 +7178,7 @@
         <v>2.204</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>0.04520098596940841</v>
+        <v>0.04570717428878286</v>
       </c>
       <c r="I46" s="10" t="n">
         <v>46198</v>
@@ -7231,7 +7231,7 @@
         <v>5.08</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>0.01991454025218246</v>
+        <v>0.01924971624665003</v>
       </c>
       <c r="I47" s="10" t="n">
         <v>46252</v>
@@ -7284,7 +7284,7 @@
         <v>3.92</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>0.01547755333783219</v>
+        <v>0.01568376395018629</v>
       </c>
       <c r="I48" s="10" t="n">
         <v>46252</v>
@@ -7337,7 +7337,7 @@
         <v>9.76</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>0.02548302872062663</v>
+        <v>0.02583787857341831</v>
       </c>
       <c r="I49" s="10" t="n">
         <v>46253</v>
@@ -7384,25 +7384,25 @@
         </is>
       </c>
       <c r="F50" s="7" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="G50" s="25" t="n">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>0.03410024629403103</v>
+        <v>0.03791041525582833</v>
       </c>
       <c r="I50" s="10" t="n">
-        <v>46181</v>
+        <v>46273</v>
       </c>
       <c r="J50" s="8" t="n">
-        <v>0.01219512195121952</v>
+        <v>0.01204819277108435</v>
       </c>
       <c r="K50" s="10" t="n">
-        <v>46592</v>
+        <v>46591</v>
       </c>
       <c r="L50" s="10" t="n">
-        <v>46632</v>
+        <v>46633</v>
       </c>
       <c r="M50" s="12" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>5.2</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>0.04736746272382592</v>
+        <v>0.04881483149978388</v>
       </c>
       <c r="I51" s="10" t="n">
         <v>46188</v>
@@ -7496,7 +7496,7 @@
         <v>3.896</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>0.04397787742467318</v>
+        <v>0.04231333292565891</v>
       </c>
       <c r="I52" s="10" t="n">
         <v>46112</v>
@@ -7549,7 +7549,7 @@
         <v>5.68</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>0.0219780217704021</v>
+        <v>0.02153962736846832</v>
       </c>
       <c r="I53" s="10" t="n">
         <v>46234</v>
@@ -7602,7 +7602,7 @@
         <v>2.124</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>0.03308411372219163</v>
+        <v>0.03364219619018467</v>
       </c>
       <c r="I54" s="10" t="n">
         <v>46241</v>
@@ -7655,7 +7655,7 @@
         <v>5.68</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>0.01961190558580643</v>
+        <v>0.0199424192610679</v>
       </c>
       <c r="I55" s="10" t="n">
         <v>46265</v>
@@ -7708,7 +7708,7 @@
         <v>2.832</v>
       </c>
       <c r="H56" s="9" t="n">
-        <v>0.05648185150526099</v>
+        <v>0.05532352119915055</v>
       </c>
       <c r="I56" s="10" t="n">
         <v>46213</v>
@@ -7761,7 +7761,7 @@
         <v>4.12</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>0.02583558016217738</v>
+        <v>0.02451651249736115</v>
       </c>
       <c r="I57" s="10" t="n">
         <v>46251</v>

--- a/data/dividend_calendar.xlsx
+++ b/data/dividend_calendar.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="167" formatCode="MM/DD/YYYY"/>
     <numFmt numFmtId="168" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -84,12 +84,6 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00856404"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <color rgb="001a3a5c"/>
       <sz val="12"/>
     </font>
@@ -100,7 +94,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -122,11 +116,6 @@
         <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -145,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -163,9 +152,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -179,8 +165,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -575,7 +561,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Estimated Dividend Calendar: Anticipated Announcements - 09/14/2026</t>
+          <t>Estimated Dividend Calendar: Anticipated Announcements - 09/21/2026</t>
         </is>
       </c>
     </row>
@@ -680,7 +666,7 @@
         <v>46048</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>-231</v>
+        <v>-238</v>
       </c>
       <c r="J6" s="10" t="n">
         <v>46413</v>
@@ -691,13 +677,13 @@
         </is>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0.0618816332174422</v>
+        <v>0.06210507380223738</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -711,25 +697,25 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>0.82</v>
+        <v>1.5</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.07142857142857149</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>46263</v>
+        <v>46284</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>-16</v>
+        <v>-2</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>46662</v>
+        <v>46665</v>
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
@@ -737,13 +723,13 @@
         </is>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0.03249306950164277</v>
+        <v>0.017034323631875</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -757,25 +743,25 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.09638554216867479</v>
+        <v>0.0235294117647059</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>46278</v>
-      </c>
-      <c r="I8" s="11" t="n">
-        <v>-1</v>
+        <v>46305</v>
+      </c>
+      <c r="I8" s="13" t="n">
+        <v>19</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>46709</v>
+        <v>46339</v>
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
@@ -783,13 +769,13 @@
         </is>
       </c>
       <c r="L8" s="9" t="n">
-        <v>0.007252874320868801</v>
+        <v>0.02857260193208257</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -799,29 +785,29 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>0.708</v>
+        <v>0.79</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>0.02608695652173916</v>
+        <v>0.05333333333333338</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>46280</v>
+        <v>46311</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>46668</v>
+        <v>46386</v>
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
@@ -829,13 +815,13 @@
         </is>
       </c>
       <c r="L9" s="9" t="n">
-        <v>0.05532352119915055</v>
+        <v>0.0122511718530932</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>HII</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -845,29 +831,29 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.0441176470588234</v>
+        <v>0.02222222222222208</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>46285</v>
+        <v>46318</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>46325</v>
+        <v>46352</v>
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
@@ -875,13 +861,13 @@
         </is>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0.02153962736846832</v>
+        <v>0.02022274389215184</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -895,25 +881,25 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.87</v>
+        <v>0.64</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>0.0235294117647059</v>
+        <v>0.06666666666666674</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>46305</v>
-      </c>
-      <c r="I11" s="14" t="n">
-        <v>26</v>
+        <v>46322</v>
+      </c>
+      <c r="I11" s="13" t="n">
+        <v>36</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>46339</v>
+        <v>46338</v>
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
@@ -921,13 +907,13 @@
         </is>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0.028948135474036</v>
+        <v>0.02523905638405114</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -937,29 +923,29 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.79</v>
+        <v>0.6</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>0.75</v>
+        <v>0.55</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.05333333333333338</v>
+        <v>0.09090909090909079</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>46311</v>
-      </c>
-      <c r="I12" s="14" t="n">
-        <v>32</v>
+        <v>46329</v>
+      </c>
+      <c r="I12" s="13" t="n">
+        <v>43</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>46386</v>
+        <v>46338</v>
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
@@ -967,13 +953,13 @@
         </is>
       </c>
       <c r="L12" s="9" t="n">
-        <v>0.0127142515706196</v>
+        <v>0.007728721893003816</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -987,25 +973,25 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1.38</v>
+        <v>2.44</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>1.35</v>
+        <v>2.14</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0.02222222222222208</v>
+        <v>0.1401869158878504</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>46318</v>
-      </c>
-      <c r="I13" s="14" t="n">
-        <v>39</v>
+        <v>46332</v>
+      </c>
+      <c r="I13" s="13" t="n">
+        <v>46</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>46352</v>
+        <v>46346</v>
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
@@ -1013,13 +999,13 @@
         </is>
       </c>
       <c r="L13" s="9" t="n">
-        <v>0.01974143087025879</v>
+        <v>0.02634704658156829</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -1033,25 +1019,25 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.64</v>
+        <v>1.03</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>0.6</v>
+        <v>0.99</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.06666666666666674</v>
+        <v>0.04040404040404044</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>46322</v>
-      </c>
-      <c r="I14" s="14" t="n">
-        <v>43</v>
+        <v>46341</v>
+      </c>
+      <c r="I14" s="13" t="n">
+        <v>55</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>46338</v>
+        <v>46340</v>
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
@@ -1059,13 +1045,13 @@
         </is>
       </c>
       <c r="L14" s="9" t="n">
-        <v>0.02491484184914842</v>
+        <v>0.02579191096983098</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -1075,29 +1061,29 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.6</v>
+        <v>0.48</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>0.55</v>
+        <v>0.45</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0.09090909090909079</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>46329</v>
-      </c>
-      <c r="I15" s="14" t="n">
-        <v>50</v>
+        <v>46344</v>
+      </c>
+      <c r="I15" s="13" t="n">
+        <v>58</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>46338</v>
+        <v>46385</v>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
@@ -1105,13 +1091,13 @@
         </is>
       </c>
       <c r="L15" s="9" t="n">
-        <v>0.007397361552028218</v>
+        <v>0.03923571975309979</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -1121,29 +1107,29 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>2.44</v>
+        <v>0.41</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>2.14</v>
+        <v>0.4</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0.1401869158878504</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="G16" s="9" t="n">
         <v>0.08</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>46332</v>
-      </c>
-      <c r="I16" s="14" t="n">
-        <v>53</v>
+        <v>46347</v>
+      </c>
+      <c r="I16" s="13" t="n">
+        <v>61</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>46346</v>
+        <v>46358</v>
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
@@ -1151,13 +1137,13 @@
         </is>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0.02583787857341831</v>
+        <v>0.04623560300134034</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -1167,29 +1153,29 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>1.03</v>
+        <v>0.293</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>0.99</v>
+        <v>0.29</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0.04040404040404044</v>
+        <v>0.01034482758620691</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>0.04</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>46341</v>
-      </c>
-      <c r="I17" s="14" t="n">
-        <v>62</v>
+        <v>46352</v>
+      </c>
+      <c r="I17" s="13" t="n">
+        <v>66</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>46340</v>
+        <v>46400</v>
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
@@ -1197,13 +1183,13 @@
         </is>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.02451651249736115</v>
+        <v>0.05678294741557949</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>EMN</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -1217,25 +1203,25 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.48</v>
+        <v>0.84</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>0.45</v>
+        <v>0.83</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.01204819277108435</v>
       </c>
       <c r="G18" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>46344</v>
-      </c>
-      <c r="I18" s="14" t="n">
-        <v>65</v>
+        <v>46360</v>
+      </c>
+      <c r="I18" s="13" t="n">
+        <v>74</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>46385</v>
+        <v>46371</v>
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
@@ -1243,13 +1229,13 @@
         </is>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0.03748535638894003</v>
+        <v>0.05154560291238409</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -1259,29 +1245,29 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.41</v>
+        <v>2.52</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>0.4</v>
+        <v>2.38</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.05882352941176476</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>0.08</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>46347</v>
-      </c>
-      <c r="I19" s="14" t="n">
-        <v>68</v>
+        <v>46366</v>
+      </c>
+      <c r="I19" s="13" t="n">
+        <v>80</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>46358</v>
+        <v>46432</v>
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
@@ -1289,13 +1275,13 @@
         </is>
       </c>
       <c r="L19" s="9" t="n">
-        <v>0.04430037762617224</v>
+        <v>0.02574909946756583</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -1305,29 +1291,29 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.293</v>
+        <v>0.24</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>0.29</v>
+        <v>0.23</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>0.01034482758620691</v>
+        <v>0.04347826086956513</v>
       </c>
       <c r="G20" s="9" t="n">
         <v>0.04</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>46352</v>
-      </c>
-      <c r="I20" s="14" t="n">
-        <v>73</v>
+        <v>46380</v>
+      </c>
+      <c r="I20" s="13" t="n">
+        <v>94</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>46400</v>
+        <v>46436</v>
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
@@ -1335,59 +1321,59 @@
         </is>
       </c>
       <c r="L20" s="9" t="n">
-        <v>0.05595607625096392</v>
+        <v>0.02520677492654566</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>EMN</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="F21" s="8" t="n">
-        <v>0.01204819277108435</v>
-      </c>
-      <c r="G21" s="9" t="n">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>GGG</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="F21" s="17" t="n">
+        <v>0.07272727272727258</v>
+      </c>
+      <c r="G21" s="18" t="n">
         <v>0.06</v>
       </c>
-      <c r="H21" s="10" t="n">
-        <v>46360</v>
-      </c>
-      <c r="I21" s="14" t="n">
-        <v>81</v>
-      </c>
-      <c r="J21" s="10" t="n">
-        <v>46371</v>
-      </c>
-      <c r="K21" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L21" s="9" t="n">
-        <v>0.04971885038416789</v>
+      <c r="H21" s="19" t="n">
+        <v>46383</v>
+      </c>
+      <c r="I21" s="20" t="n">
+        <v>97</v>
+      </c>
+      <c r="J21" s="19" t="n">
+        <v>46404</v>
+      </c>
+      <c r="K21" s="21" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="L21" s="18" t="n">
+        <v>0.01548353253084369</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -1397,29 +1383,29 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>2.52</v>
+        <v>0.86</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>2.38</v>
+        <v>0.8</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>0.05882352941176476</v>
+        <v>0.07499999999999993</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>46366</v>
-      </c>
-      <c r="I22" s="14" t="n">
-        <v>87</v>
+        <v>46402</v>
+      </c>
+      <c r="I22" s="13" t="n">
+        <v>116</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>46432</v>
+        <v>46483</v>
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
@@ -1427,13 +1413,13 @@
         </is>
       </c>
       <c r="L22" s="9" t="n">
-        <v>0.02668498548328576</v>
+        <v>0.01387936217586079</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>CNP</t>
+          <t>BKH</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -1447,25 +1433,25 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.24</v>
+        <v>0.703</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>0.23</v>
+        <v>0.676</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>0.04347826086956513</v>
+        <v>0.03994082840236673</v>
       </c>
       <c r="G23" s="9" t="n">
         <v>0.04</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>46380</v>
-      </c>
-      <c r="I23" s="14" t="n">
-        <v>101</v>
+        <v>46411</v>
+      </c>
+      <c r="I23" s="13" t="n">
+        <v>125</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>46436</v>
+        <v>46435</v>
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
@@ -1473,91 +1459,91 @@
         </is>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0.02463433333150609</v>
+        <v>0.03886124898121857</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>GGG</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>Jan</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E24" s="17" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="F24" s="18" t="n">
-        <v>0.07272727272727258</v>
-      </c>
-      <c r="G24" s="19" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="H24" s="20" t="n">
-        <v>46383</v>
-      </c>
-      <c r="I24" s="21" t="n">
-        <v>104</v>
-      </c>
-      <c r="J24" s="20" t="n">
-        <v>46404</v>
-      </c>
-      <c r="K24" s="22" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
-      <c r="L24" s="19" t="n">
-        <v>0.01539665983034154</v>
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>CVX</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>0.04093567251461992</v>
+      </c>
+      <c r="G24" s="9" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H24" s="10" t="n">
+        <v>46417</v>
+      </c>
+      <c r="I24" s="13" t="n">
+        <v>131</v>
+      </c>
+      <c r="J24" s="10" t="n">
+        <v>46433</v>
+      </c>
+      <c r="K24" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+      <c r="L24" s="9" t="n">
+        <v>0.03451117291578592</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>0.86</v>
+        <v>0.579</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>0.8</v>
+        <v>0.584</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>0.07499999999999993</v>
+        <v>1.183219178082192</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>46402</v>
-      </c>
-      <c r="I25" s="14" t="n">
-        <v>123</v>
+        <v>46423</v>
+      </c>
+      <c r="I25" s="13" t="n">
+        <v>137</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>46483</v>
+        <v>46473</v>
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
@@ -1565,13 +1551,13 @@
         </is>
       </c>
       <c r="L25" s="9" t="n">
-        <v>0.01446715458684541</v>
+        <v>0.02892830465433105</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>BKH</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -1581,29 +1567,29 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>0.703</v>
+        <v>0.61</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>0.676</v>
+        <v>0.58</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>0.03994082840236673</v>
+        <v>0.05172413793103453</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>46411</v>
-      </c>
-      <c r="I26" s="14" t="n">
-        <v>132</v>
+        <v>46428</v>
+      </c>
+      <c r="I26" s="13" t="n">
+        <v>142</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>46435</v>
+        <v>46452</v>
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
@@ -1611,13 +1597,13 @@
         </is>
       </c>
       <c r="L26" s="9" t="n">
-        <v>0.03957219387294963</v>
+        <v>0.01583901299359408</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -1627,29 +1613,29 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>1.78</v>
+        <v>1.3</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>1.71</v>
+        <v>1.27</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>0.04093567251461992</v>
+        <v>0.02362204724409451</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>46417</v>
-      </c>
-      <c r="I27" s="14" t="n">
-        <v>138</v>
+        <v>46428</v>
+      </c>
+      <c r="I27" s="13" t="n">
+        <v>142</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>46433</v>
+        <v>46460</v>
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
@@ -1657,59 +1643,59 @@
         </is>
       </c>
       <c r="L27" s="9" t="n">
-        <v>0.03291115891894363</v>
+        <v>0.05013256280063842</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>NVO</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>Semi-Annual</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>HWC</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="D28" s="7" t="n">
-        <v>0.579</v>
-      </c>
-      <c r="E28" s="7" t="n">
-        <v>0.584</v>
-      </c>
-      <c r="F28" s="8" t="n">
-        <v>1.183219178082192</v>
-      </c>
-      <c r="G28" s="9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="H28" s="10" t="n">
-        <v>46423</v>
-      </c>
-      <c r="I28" s="14" t="n">
-        <v>144</v>
-      </c>
-      <c r="J28" s="10" t="n">
-        <v>46473</v>
-      </c>
-      <c r="K28" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L28" s="9" t="n">
-        <v>0.02673438847314084</v>
+      <c r="D28" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E28" s="16" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F28" s="17" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="G28" s="18" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H28" s="19" t="n">
+        <v>46429</v>
+      </c>
+      <c r="I28" s="20" t="n">
+        <v>143</v>
+      </c>
+      <c r="J28" s="19" t="n">
+        <v>46450</v>
+      </c>
+      <c r="K28" s="21" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="L28" s="18" t="n">
+        <v>0.02664889964922068</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -1719,29 +1705,29 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>0.61</v>
+        <v>0.42</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>0.58</v>
+        <v>0.41</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>0.05172413793103453</v>
+        <v>0.02439024390243905</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>46428</v>
-      </c>
-      <c r="I29" s="14" t="n">
-        <v>149</v>
+        <v>46431</v>
+      </c>
+      <c r="I29" s="13" t="n">
+        <v>145</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>46452</v>
+        <v>46480</v>
       </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
@@ -1749,13 +1735,13 @@
         </is>
       </c>
       <c r="L29" s="9" t="n">
-        <v>0.01462479053918474</v>
+        <v>0.01533966445849374</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>PEG</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -1769,25 +1755,25 @@
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>1.3</v>
+        <v>0.67</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>1.27</v>
+        <v>0.63</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>0.02362204724409451</v>
+        <v>0.06349206349206354</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>46428</v>
-      </c>
-      <c r="I30" s="14" t="n">
-        <v>149</v>
+        <v>46432</v>
+      </c>
+      <c r="I30" s="13" t="n">
+        <v>146</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>46460</v>
+        <v>46455</v>
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
@@ -1795,59 +1781,59 @@
         </is>
       </c>
       <c r="L30" s="9" t="n">
-        <v>0.04881483149978388</v>
+        <v>0.03862784817086413</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
-        <is>
-          <t>HWC</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E31" s="17" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="F31" s="18" t="n">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="G31" s="19" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H31" s="20" t="n">
-        <v>46429</v>
-      </c>
-      <c r="I31" s="21" t="n">
-        <v>150</v>
-      </c>
-      <c r="J31" s="20" t="n">
-        <v>46450</v>
-      </c>
-      <c r="K31" s="22" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
-      <c r="L31" s="19" t="n">
-        <v>0.02641310047223251</v>
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>2.138</v>
+      </c>
+      <c r="E31" s="7" t="n">
+        <v>1.883</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>0.6872012745618694</v>
+      </c>
+      <c r="G31" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H31" s="10" t="n">
+        <v>46433</v>
+      </c>
+      <c r="I31" s="13" t="n">
+        <v>147</v>
+      </c>
+      <c r="J31" s="10" t="n">
+        <v>46425</v>
+      </c>
+      <c r="K31" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+      <c r="L31" s="9" t="n">
+        <v>0.005078776879924646</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -1857,29 +1843,29 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>0.42</v>
+        <v>1.3</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>0.41</v>
+        <v>1.25</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>0.02439024390243905</v>
+        <v>4.96</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>46431</v>
-      </c>
-      <c r="I32" s="14" t="n">
-        <v>152</v>
+        <v>46433</v>
+      </c>
+      <c r="I32" s="13" t="n">
+        <v>147</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>46480</v>
+        <v>46383</v>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
@@ -1887,13 +1873,13 @@
         </is>
       </c>
       <c r="L32" s="9" t="n">
-        <v>0.01520224384693243</v>
+        <v>0.01892595187562783</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -1907,25 +1893,25 @@
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>0.67</v>
+        <v>0.32</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>0.63</v>
+        <v>0.24</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>0.06349206349206354</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>46432</v>
-      </c>
-      <c r="I33" s="14" t="n">
-        <v>153</v>
+        <v>46433</v>
+      </c>
+      <c r="I33" s="13" t="n">
+        <v>147</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>46455</v>
+        <v>46458</v>
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
@@ -1933,13 +1919,13 @@
         </is>
       </c>
       <c r="L33" s="9" t="n">
-        <v>0.03727399086403899</v>
+        <v>0.02686253848921341</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -1949,29 +1935,29 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>2.138</v>
+        <v>0.84</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>1.883</v>
+        <v>0.82</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>0.6872012745618694</v>
+        <v>0.02439024390243905</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="H34" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I34" s="14" t="n">
-        <v>154</v>
+      <c r="I34" s="13" t="n">
+        <v>147</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>46425</v>
+        <v>46634</v>
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
@@ -1979,13 +1965,13 @@
         </is>
       </c>
       <c r="L34" s="9" t="n">
-        <v>0.005338793701200471</v>
+        <v>0.0286225403992658</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -1995,29 +1981,29 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>1.3</v>
+        <v>0.531</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>1.25</v>
+        <v>0.588964</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>4.96</v>
+        <v>0.005735494868956323</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H35" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I35" s="14" t="n">
-        <v>154</v>
+      <c r="I35" s="13" t="n">
+        <v>147</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>46383</v>
+        <v>46608</v>
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
@@ -2025,13 +2011,13 @@
         </is>
       </c>
       <c r="L35" s="9" t="n">
-        <v>0.0186580544393274</v>
+        <v>0.03425806451612903</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -2045,25 +2031,25 @@
         </is>
       </c>
       <c r="D36" s="7" t="n">
-        <v>0.32</v>
+        <v>0.29</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.07407407407407393</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="I36" s="14" t="n">
+        <v>46440</v>
+      </c>
+      <c r="I36" s="13" t="n">
         <v>154</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>46458</v>
+        <v>46450</v>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
@@ -2071,13 +2057,13 @@
         </is>
       </c>
       <c r="L36" s="9" t="n">
-        <v>0.02508574153301707</v>
+        <v>0.00978737793499475</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -2087,29 +2073,29 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>0.84</v>
+        <v>2.33</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>0.82</v>
+        <v>2.3</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>0.02439024390243905</v>
+        <v>0.01304347826086967</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="I37" s="14" t="n">
-        <v>154</v>
+        <v>46441</v>
+      </c>
+      <c r="I37" s="13" t="n">
+        <v>155</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>46634</v>
+        <v>46456</v>
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
@@ -2117,13 +2103,13 @@
         </is>
       </c>
       <c r="L37" s="9" t="n">
-        <v>0.02863412689310154</v>
+        <v>0.03142279099194371</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -2133,29 +2119,29 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D38" s="7" t="n">
-        <v>0.531</v>
+        <v>1.59</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>0.588964</v>
+        <v>1.5</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>0.005735494868956323</v>
+        <v>0.06000000000000005</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="I38" s="14" t="n">
-        <v>154</v>
+        <v>46452</v>
+      </c>
+      <c r="I38" s="13" t="n">
+        <v>166</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>46608</v>
+        <v>46487</v>
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
@@ -2163,45 +2149,45 @@
         </is>
       </c>
       <c r="L38" s="9" t="n">
-        <v>0.03364219619018467</v>
+        <v>0.01805945923134389</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>0.29</v>
+        <v>0.271</v>
       </c>
       <c r="E39" s="7" t="n">
         <v>0.27</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>0.07407407407407393</v>
+        <v>0.003703703703703707</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>46440</v>
-      </c>
-      <c r="I39" s="14" t="n">
-        <v>161</v>
+        <v>46461</v>
+      </c>
+      <c r="I39" s="13" t="n">
+        <v>175</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>46450</v>
+        <v>46386</v>
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
@@ -2209,13 +2195,13 @@
         </is>
       </c>
       <c r="L39" s="9" t="n">
-        <v>0.00946320755973527</v>
+        <v>0.05709770688176589</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -2225,29 +2211,29 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D40" s="7" t="n">
-        <v>2.33</v>
+        <v>1.089</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>2.3</v>
+        <v>1.057</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>0.01304347826086967</v>
+        <v>0.03027436140018924</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>46441</v>
-      </c>
-      <c r="I40" s="14" t="n">
-        <v>162</v>
+        <v>46488</v>
+      </c>
+      <c r="I40" s="13" t="n">
+        <v>202</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>46456</v>
+        <v>46498</v>
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
@@ -2255,18 +2241,18 @@
         </is>
       </c>
       <c r="L40" s="9" t="n">
-        <v>0.03000740561476674</v>
+        <v>0.0298213170506069</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -2275,25 +2261,25 @@
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>1.59</v>
+        <v>1.125</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>1.5</v>
+        <v>1.087</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>0.06000000000000005</v>
+        <v>0.03495860165593379</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>46452</v>
-      </c>
-      <c r="I41" s="14" t="n">
-        <v>173</v>
+        <v>46492</v>
+      </c>
+      <c r="I41" s="13" t="n">
+        <v>206</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>46487</v>
+        <v>46501</v>
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
@@ -2301,13 +2287,13 @@
         </is>
       </c>
       <c r="L41" s="9" t="n">
-        <v>0.01779070791836802</v>
+        <v>0.02042298300259235</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
@@ -2317,29 +2303,29 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D42" s="7" t="n">
-        <v>1.5</v>
+        <v>0.974</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>1.4</v>
+        <v>0.994</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>0.07142857142857149</v>
+        <v>0.001006036217303824</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>46461</v>
-      </c>
-      <c r="I42" s="14" t="n">
-        <v>182</v>
+        <v>46492</v>
+      </c>
+      <c r="I42" s="13" t="n">
+        <v>206</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>46300</v>
+        <v>46376</v>
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
@@ -2347,45 +2333,45 @@
         </is>
       </c>
       <c r="L42" s="9" t="n">
-        <v>0.01699235314722998</v>
+        <v>0.04302120257323579</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>0.271</v>
+        <v>1.34</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>0.27</v>
+        <v>1.3</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>0.003703703703703707</v>
+        <v>0.0307692307692308</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>46461</v>
-      </c>
-      <c r="I43" s="14" t="n">
-        <v>182</v>
+        <v>46493</v>
+      </c>
+      <c r="I43" s="13" t="n">
+        <v>207</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>46386</v>
+        <v>46531</v>
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
@@ -2393,13 +2379,13 @@
         </is>
       </c>
       <c r="L43" s="9" t="n">
-        <v>0.05447236111291268</v>
+        <v>0.01961789025712752</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
@@ -2409,29 +2395,29 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D44" s="7" t="n">
-        <v>1.089</v>
+        <v>1.27</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>1.057</v>
+        <v>1.2</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>0.03027436140018924</v>
+        <v>0.05833333333333339</v>
       </c>
       <c r="G44" s="9" t="n">
         <v>0.04</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>46488</v>
-      </c>
-      <c r="I44" s="14" t="n">
-        <v>209</v>
+        <v>46499</v>
+      </c>
+      <c r="I44" s="13" t="n">
+        <v>213</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>46498</v>
+        <v>46526</v>
       </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
@@ -2439,45 +2425,45 @@
         </is>
       </c>
       <c r="L44" s="9" t="n">
-        <v>0.02964170822323141</v>
+        <v>0.01878350811872483</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Semi-Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>1.125</v>
+        <v>0.551</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>1.087</v>
+        <v>0.525</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>0.03495860165593379</v>
+        <v>0.04952380952380957</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>46492</v>
-      </c>
-      <c r="I45" s="14" t="n">
-        <v>213</v>
+        <v>46504</v>
+      </c>
+      <c r="I45" s="13" t="n">
+        <v>218</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>46501</v>
+        <v>46562</v>
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
@@ -2485,13 +2471,13 @@
         </is>
       </c>
       <c r="L45" s="9" t="n">
-        <v>0.0204202028393521</v>
+        <v>0.04648317953059956</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
@@ -2501,29 +2487,29 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>0.974</v>
+        <v>1.19</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>0.994</v>
+        <v>1.08</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>0.001006036217303824</v>
+        <v>0.1018518518518517</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>46492</v>
-      </c>
-      <c r="I46" s="14" t="n">
-        <v>213</v>
+        <v>46508</v>
+      </c>
+      <c r="I46" s="13" t="n">
+        <v>222</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>46376</v>
+        <v>46518</v>
       </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
@@ -2531,13 +2517,13 @@
         </is>
       </c>
       <c r="L46" s="9" t="n">
-        <v>0.04231333292565891</v>
+        <v>0.04153940267145332</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
@@ -2547,29 +2533,29 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>1.3</v>
+        <v>1.423</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>0.0307692307692308</v>
+        <v>0.04005621925509482</v>
       </c>
       <c r="G47" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>46493</v>
-      </c>
-      <c r="I47" s="14" t="n">
-        <v>214</v>
+        <v>46515</v>
+      </c>
+      <c r="I47" s="13" t="n">
+        <v>229</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>46531</v>
+        <v>46542</v>
       </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
@@ -2577,13 +2563,13 @@
         </is>
       </c>
       <c r="L47" s="9" t="n">
-        <v>0.01990567170011602</v>
+        <v>0.04612387782222198</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
@@ -2593,29 +2579,29 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D48" s="7" t="n">
-        <v>1.27</v>
+        <v>0.72</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>1.2</v>
+        <v>0.71</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>0.05833333333333339</v>
+        <v>0.01408450704225353</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>46499</v>
-      </c>
-      <c r="I48" s="14" t="n">
-        <v>220</v>
+        <v>46532</v>
+      </c>
+      <c r="I48" s="13" t="n">
+        <v>246</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>46526</v>
+        <v>46563</v>
       </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
@@ -2623,13 +2609,13 @@
         </is>
       </c>
       <c r="L48" s="9" t="n">
-        <v>0.01924971624665003</v>
+        <v>0.03129414362926066</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
@@ -2639,29 +2625,29 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>0.551</v>
+        <v>1.42</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>0.525</v>
+        <v>1.38</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>0.04952380952380957</v>
+        <v>0.02898550724637684</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>46504</v>
-      </c>
-      <c r="I49" s="14" t="n">
-        <v>225</v>
+        <v>46589</v>
+      </c>
+      <c r="I49" s="13" t="n">
+        <v>303</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>46562</v>
+        <v>46629</v>
       </c>
       <c r="K49" s="12" t="inlineStr">
         <is>
@@ -2669,13 +2655,13 @@
         </is>
       </c>
       <c r="L49" s="9" t="n">
-        <v>0.04570717428878286</v>
+        <v>0.02079215225231083</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
@@ -2685,29 +2671,29 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="D50" s="7" t="n">
-        <v>1.19</v>
+        <v>0.84</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>1.08</v>
+        <v>0.83</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>0.1018518518518517</v>
+        <v>0.01204819277108435</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>46508</v>
-      </c>
-      <c r="I50" s="14" t="n">
-        <v>229</v>
+        <v>46591</v>
+      </c>
+      <c r="I50" s="13" t="n">
+        <v>305</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>46518</v>
+        <v>46633</v>
       </c>
       <c r="K50" s="12" t="inlineStr">
         <is>
@@ -2715,13 +2701,13 @@
         </is>
       </c>
       <c r="L50" s="9" t="n">
-        <v>0.04061086969695727</v>
+        <v>0.03791041525582833</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -2731,29 +2717,29 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>1.48</v>
+        <v>0.98</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>1.423</v>
+        <v>0.93</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>0.04005621925509482</v>
+        <v>0.05376344086021498</v>
       </c>
       <c r="G51" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>46515</v>
-      </c>
-      <c r="I51" s="14" t="n">
-        <v>236</v>
+        <v>46594</v>
+      </c>
+      <c r="I51" s="13" t="n">
+        <v>308</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>46542</v>
+        <v>46613</v>
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
@@ -2761,13 +2747,13 @@
         </is>
       </c>
       <c r="L51" s="9" t="n">
-        <v>0.04294834704934376</v>
+        <v>0.01592201481961874</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>AWR</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -2777,29 +2763,29 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D52" s="7" t="n">
-        <v>0.72</v>
+        <v>0.546</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>0.71</v>
+        <v>0.504</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>0.01408450704225353</v>
+        <v>0.08333333333333341</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>46532</v>
-      </c>
-      <c r="I52" s="14" t="n">
-        <v>253</v>
+        <v>46595</v>
+      </c>
+      <c r="I52" s="13" t="n">
+        <v>309</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>46563</v>
+        <v>46614</v>
       </c>
       <c r="K52" s="12" t="inlineStr">
         <is>
@@ -2807,13 +2793,13 @@
         </is>
       </c>
       <c r="L52" s="9" t="n">
-        <v>0.03080872803355954</v>
+        <v>0.02551849066264972</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -2827,25 +2813,25 @@
         </is>
       </c>
       <c r="D53" s="7" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>0.02898550724637684</v>
+        <v>0.008064516129032265</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>46589</v>
-      </c>
-      <c r="I53" s="14" t="n">
-        <v>310</v>
+        <v>46597</v>
+      </c>
+      <c r="I53" s="13" t="n">
+        <v>311</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>46629</v>
+        <v>46611</v>
       </c>
       <c r="K53" s="12" t="inlineStr">
         <is>
@@ -2853,13 +2839,13 @@
         </is>
       </c>
       <c r="L53" s="9" t="n">
-        <v>0.0199424192610679</v>
+        <v>0.06040099158048739</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>CFR</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -2869,29 +2855,29 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D54" s="7" t="n">
-        <v>0.84</v>
+        <v>1.03</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>0.01204819277108435</v>
+        <v>0.03000000000000003</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>46591</v>
-      </c>
-      <c r="I54" s="14" t="n">
+        <v>46598</v>
+      </c>
+      <c r="I54" s="13" t="n">
         <v>312</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>46633</v>
+        <v>46629</v>
       </c>
       <c r="K54" s="12" t="inlineStr">
         <is>
@@ -2899,13 +2885,13 @@
         </is>
       </c>
       <c r="L54" s="9" t="n">
-        <v>0.03791041525582833</v>
+        <v>0.0258234356907714</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -2915,29 +2901,29 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D55" s="7" t="n">
-        <v>0.98</v>
+        <v>0.82</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>0.05376344086021498</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>46594</v>
-      </c>
-      <c r="I55" s="14" t="n">
-        <v>315</v>
+        <v>46628</v>
+      </c>
+      <c r="I55" s="13" t="n">
+        <v>342</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>46613</v>
+        <v>46662</v>
       </c>
       <c r="K55" s="12" t="inlineStr">
         <is>
@@ -2945,13 +2931,13 @@
         </is>
       </c>
       <c r="L55" s="9" t="n">
-        <v>0.01568376395018629</v>
+        <v>0.03369112923733877</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>AWR</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
@@ -2961,29 +2947,29 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D56" s="7" t="n">
-        <v>0.546</v>
+        <v>0.91</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>0.504</v>
+        <v>0.83</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>0.08333333333333341</v>
+        <v>0.09638554216867479</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>46595</v>
-      </c>
-      <c r="I56" s="14" t="n">
-        <v>316</v>
+        <v>46643</v>
+      </c>
+      <c r="I56" s="13" t="n">
+        <v>357</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>46614</v>
+        <v>46709</v>
       </c>
       <c r="K56" s="12" t="inlineStr">
         <is>
@@ -2991,13 +2977,13 @@
         </is>
       </c>
       <c r="L56" s="9" t="n">
-        <v>0.0250789461211513</v>
+        <v>0.007345385769172313</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
@@ -3007,29 +2993,29 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D57" s="7" t="n">
-        <v>1.25</v>
+        <v>0.708</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>1.24</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>0.008064516129032265</v>
+        <v>0.02608695652173916</v>
       </c>
       <c r="G57" s="9" t="n">
         <v>0.02</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>46597</v>
-      </c>
-      <c r="I57" s="14" t="n">
-        <v>318</v>
+        <v>46645</v>
+      </c>
+      <c r="I57" s="13" t="n">
+        <v>359</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>46611</v>
+        <v>46668</v>
       </c>
       <c r="K57" s="12" t="inlineStr">
         <is>
@@ -3037,13 +3023,13 @@
         </is>
       </c>
       <c r="L57" s="9" t="n">
-        <v>0.05629362775477879</v>
+        <v>0.05928406893158691</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>CFR</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
@@ -3053,29 +3039,29 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D58" s="7" t="n">
-        <v>1.03</v>
+        <v>1.42</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>0.03000000000000003</v>
+        <v>0.0441176470588234</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>46598</v>
-      </c>
-      <c r="I58" s="14" t="n">
-        <v>319</v>
+        <v>46650</v>
+      </c>
+      <c r="I58" s="13" t="n">
+        <v>364</v>
       </c>
       <c r="J58" s="10" t="n">
-        <v>46629</v>
+        <v>46690</v>
       </c>
       <c r="K58" s="12" t="inlineStr">
         <is>
@@ -3083,7 +3069,7 @@
         </is>
       </c>
       <c r="L58" s="9" t="n">
-        <v>0.02503037574256811</v>
+        <v>0.02139359698681732</v>
       </c>
     </row>
   </sheetData>
@@ -3097,7 +3083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3118,44 +3104,44 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Expected Increase Announcements by Month - 09/14/2026</t>
+          <t>Expected Increase Announcements by Month - 09/21/2026</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>January 2026</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C5" s="24" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D5" s="24" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E5" s="24" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F5" s="24" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3186,39 +3172,39 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="inlineStr">
-        <is>
-          <t>August 2026</t>
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>September 2026</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D9" s="24" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F9" s="24" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3227,20 +3213,20 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>46263</v>
+        <v>46284</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>46662</v>
+        <v>46665</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>0.82</v>
+        <v>1.5</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.07142857142857149</v>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
@@ -3249,39 +3235,39 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="inlineStr">
-        <is>
-          <t>September 2026</t>
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>October 2026</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D13" s="24" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E13" s="24" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F13" s="24" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3290,20 +3276,20 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="B14" s="10" t="n">
-        <v>46278</v>
+        <v>46305</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>46709</v>
+        <v>46339</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>0.09638554216867479</v>
+        <v>0.0235294117647059</v>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
@@ -3314,20 +3300,20 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="B15" s="10" t="n">
-        <v>46280</v>
+        <v>46311</v>
       </c>
       <c r="C15" s="10" t="n">
-        <v>46668</v>
+        <v>46386</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.708</v>
+        <v>0.79</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>0.02608695652173916</v>
+        <v>0.05333333333333338</v>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
@@ -3338,20 +3324,20 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>HII</t>
         </is>
       </c>
       <c r="B16" s="10" t="n">
-        <v>46285</v>
+        <v>46318</v>
       </c>
       <c r="C16" s="10" t="n">
-        <v>46325</v>
+        <v>46352</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>0.0441176470588234</v>
+        <v>0.02222222222222208</v>
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
@@ -3359,86 +3345,86 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="23" t="inlineStr">
-        <is>
-          <t>October 2026</t>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>ETR</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C17" s="10" t="n">
+        <v>46338</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>0.06666666666666674</v>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="24" t="inlineStr">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>November 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="23" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D19" s="24" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E19" s="24" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F19" s="24" t="inlineStr">
+      <c r="F20" s="23" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>MSM</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="n">
-        <v>46305</v>
-      </c>
-      <c r="C20" s="10" t="n">
-        <v>46339</v>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>0.0235294117647059</v>
-      </c>
-      <c r="F20" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B21" s="10" t="n">
-        <v>46311</v>
+        <v>46329</v>
       </c>
       <c r="C21" s="10" t="n">
-        <v>46386</v>
+        <v>46338</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.79</v>
+        <v>0.6</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>0.05333333333333338</v>
+        <v>0.09090909090909079</v>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
@@ -3449,20 +3435,20 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B22" s="10" t="n">
-        <v>46318</v>
+        <v>46332</v>
       </c>
       <c r="C22" s="10" t="n">
-        <v>46352</v>
+        <v>46346</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>1.38</v>
+        <v>2.44</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>0.02222222222222208</v>
+        <v>0.1401869158878504</v>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
@@ -3473,20 +3459,20 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B23" s="10" t="n">
-        <v>46322</v>
+        <v>46341</v>
       </c>
       <c r="C23" s="10" t="n">
-        <v>46338</v>
+        <v>46340</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.64</v>
+        <v>1.03</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>0.06666666666666674</v>
+        <v>0.04040404040404044</v>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
@@ -3494,134 +3480,134 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>MKC</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="n">
+        <v>46344</v>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>46385</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>0.0666666666666666</v>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="25">
-      <c r="A25" s="23" t="inlineStr">
-        <is>
-          <t>November 2026</t>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>NKE</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="n">
+        <v>46347</v>
+      </c>
+      <c r="C25" s="10" t="n">
+        <v>46358</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>0.02499999999999988</v>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="24" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>HRL</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n">
+        <v>46352</v>
+      </c>
+      <c r="C26" s="10" t="n">
+        <v>46400</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>0.01034482758620691</v>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>December 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B26" s="24" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C26" s="24" t="inlineStr">
+      <c r="C29" s="23" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D26" s="24" t="inlineStr">
+      <c r="D29" s="23" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E26" s="24" t="inlineStr">
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F26" s="24" t="inlineStr">
+      <c r="F29" s="23" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>COR</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="n">
-        <v>46329</v>
-      </c>
-      <c r="C27" s="10" t="n">
-        <v>46338</v>
-      </c>
-      <c r="D27" s="7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E27" s="8" t="n">
-        <v>0.09090909090909079</v>
-      </c>
-      <c r="F27" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>SNA</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="n">
-        <v>46332</v>
-      </c>
-      <c r="C28" s="10" t="n">
-        <v>46346</v>
-      </c>
-      <c r="D28" s="7" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>0.1401869158878504</v>
-      </c>
-      <c r="F28" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="n">
-        <v>46341</v>
-      </c>
-      <c r="C29" s="10" t="n">
-        <v>46340</v>
-      </c>
-      <c r="D29" s="7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E29" s="8" t="n">
-        <v>0.04040404040404044</v>
-      </c>
-      <c r="F29" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>EMN</t>
         </is>
       </c>
       <c r="B30" s="10" t="n">
-        <v>46344</v>
+        <v>46360</v>
       </c>
       <c r="C30" s="10" t="n">
-        <v>46385</v>
+        <v>46371</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>0.48</v>
+        <v>0.84</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.01204819277108435</v>
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
@@ -3632,20 +3618,20 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B31" s="10" t="n">
-        <v>46347</v>
+        <v>46366</v>
       </c>
       <c r="C31" s="10" t="n">
-        <v>46358</v>
+        <v>46432</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>0.41</v>
+        <v>2.52</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.05882352941176476</v>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
@@ -3656,20 +3642,20 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="B32" s="10" t="n">
-        <v>46352</v>
+        <v>46380</v>
       </c>
       <c r="C32" s="10" t="n">
-        <v>46400</v>
+        <v>46436</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>0.293</v>
+        <v>0.24</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>0.01034482758620691</v>
+        <v>0.04347826086956513</v>
       </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
@@ -3677,86 +3663,86 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="23" t="inlineStr">
-        <is>
-          <t>December 2026</t>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>GGG</t>
+        </is>
+      </c>
+      <c r="B33" s="19" t="n">
+        <v>46383</v>
+      </c>
+      <c r="C33" s="19" t="n">
+        <v>46404</v>
+      </c>
+      <c r="D33" s="16" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="E33" s="17" t="n">
+        <v>0.07272727272727258</v>
+      </c>
+      <c r="F33" s="21" t="inlineStr">
+        <is>
+          <t>yfinance</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="24" t="inlineStr">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>January 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="23" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B35" s="24" t="inlineStr">
+      <c r="B36" s="23" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C35" s="24" t="inlineStr">
+      <c r="C36" s="23" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D35" s="24" t="inlineStr">
+      <c r="D36" s="23" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E35" s="24" t="inlineStr">
+      <c r="E36" s="23" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F35" s="24" t="inlineStr">
+      <c r="F36" s="23" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>EMN</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="n">
-        <v>46360</v>
-      </c>
-      <c r="C36" s="10" t="n">
-        <v>46371</v>
-      </c>
-      <c r="D36" s="7" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E36" s="8" t="n">
-        <v>0.01204819277108435</v>
-      </c>
-      <c r="F36" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="B37" s="10" t="n">
-        <v>46366</v>
+        <v>46402</v>
       </c>
       <c r="C37" s="10" t="n">
-        <v>46432</v>
+        <v>46483</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>2.52</v>
+        <v>0.86</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>0.05882352941176476</v>
+        <v>0.07499999999999993</v>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
@@ -3767,20 +3753,20 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>CNP</t>
+          <t>BKH</t>
         </is>
       </c>
       <c r="B38" s="10" t="n">
-        <v>46380</v>
+        <v>46411</v>
       </c>
       <c r="C38" s="10" t="n">
-        <v>46436</v>
+        <v>46435</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>0.24</v>
+        <v>0.703</v>
       </c>
       <c r="E38" s="8" t="n">
-        <v>0.04347826086956513</v>
+        <v>0.03994082840236673</v>
       </c>
       <c r="F38" s="12" t="inlineStr">
         <is>
@@ -3789,63 +3775,63 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
-        <is>
-          <t>GGG</t>
-        </is>
-      </c>
-      <c r="B39" s="20" t="n">
-        <v>46383</v>
-      </c>
-      <c r="C39" s="20" t="n">
-        <v>46404</v>
-      </c>
-      <c r="D39" s="17" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E39" s="18" t="n">
-        <v>0.07272727272727258</v>
-      </c>
-      <c r="F39" s="22" t="inlineStr">
-        <is>
-          <t>yfinance</t>
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>CVX</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="n">
+        <v>46417</v>
+      </c>
+      <c r="C39" s="10" t="n">
+        <v>46433</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>0.04093567251461992</v>
+      </c>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="23" t="inlineStr">
-        <is>
-          <t>January 2027</t>
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t>February 2027</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="24" t="inlineStr">
+      <c r="A42" s="23" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B42" s="24" t="inlineStr">
+      <c r="B42" s="23" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C42" s="24" t="inlineStr">
+      <c r="C42" s="23" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D42" s="24" t="inlineStr">
+      <c r="D42" s="23" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E42" s="24" t="inlineStr">
+      <c r="E42" s="23" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F42" s="24" t="inlineStr">
+      <c r="F42" s="23" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3854,20 +3840,20 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B43" s="10" t="n">
-        <v>46402</v>
+        <v>46423</v>
       </c>
       <c r="C43" s="10" t="n">
-        <v>46483</v>
+        <v>46473</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>0.86</v>
+        <v>0.579</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>0.07499999999999993</v>
+        <v>1.183219178082192</v>
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
@@ -3878,20 +3864,20 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>BKH</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B44" s="10" t="n">
-        <v>46411</v>
+        <v>46428</v>
       </c>
       <c r="C44" s="10" t="n">
-        <v>46435</v>
+        <v>46452</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>0.703</v>
+        <v>0.61</v>
       </c>
       <c r="E44" s="8" t="n">
-        <v>0.03994082840236673</v>
+        <v>0.05172413793103453</v>
       </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
@@ -3902,20 +3888,20 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B45" s="10" t="n">
-        <v>46417</v>
+        <v>46428</v>
       </c>
       <c r="C45" s="10" t="n">
-        <v>46433</v>
+        <v>46460</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>1.78</v>
+        <v>1.3</v>
       </c>
       <c r="E45" s="8" t="n">
-        <v>0.04093567251461992</v>
+        <v>0.02362204724409451</v>
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
@@ -3923,62 +3909,95 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t>HWC</t>
+        </is>
+      </c>
+      <c r="B46" s="19" t="n">
+        <v>46429</v>
+      </c>
+      <c r="C46" s="19" t="n">
+        <v>46450</v>
+      </c>
+      <c r="D46" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E46" s="17" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="F46" s="21" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="47">
-      <c r="A47" s="23" t="inlineStr">
-        <is>
-          <t>February 2027</t>
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>CSCO</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="n">
+        <v>46431</v>
+      </c>
+      <c r="C47" s="10" t="n">
+        <v>46480</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>0.02439024390243905</v>
+      </c>
+      <c r="F47" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="24" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B48" s="24" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C48" s="24" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D48" s="24" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E48" s="24" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F48" s="24" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>PEG</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="n">
+        <v>46432</v>
+      </c>
+      <c r="C48" s="10" t="n">
+        <v>46455</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>0.06349206349206354</v>
+      </c>
+      <c r="F48" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B49" s="10" t="n">
-        <v>46423</v>
+        <v>46433</v>
       </c>
       <c r="C49" s="10" t="n">
-        <v>46473</v>
+        <v>46425</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>0.579</v>
+        <v>2.138</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>1.183219178082192</v>
+        <v>0.6872012745618694</v>
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
@@ -3989,20 +4008,20 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B50" s="10" t="n">
-        <v>46428</v>
+        <v>46433</v>
       </c>
       <c r="C50" s="10" t="n">
-        <v>46452</v>
+        <v>46383</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>0.61</v>
+        <v>1.3</v>
       </c>
       <c r="E50" s="8" t="n">
-        <v>0.05172413793103453</v>
+        <v>4.96</v>
       </c>
       <c r="F50" s="12" t="inlineStr">
         <is>
@@ -4013,20 +4032,20 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B51" s="10" t="n">
-        <v>46428</v>
+        <v>46433</v>
       </c>
       <c r="C51" s="10" t="n">
-        <v>46460</v>
+        <v>46458</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>1.3</v>
+        <v>0.32</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>0.02362204724409451</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="F51" s="12" t="inlineStr">
         <is>
@@ -4035,46 +4054,46 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="15" t="inlineStr">
-        <is>
-          <t>HWC</t>
-        </is>
-      </c>
-      <c r="B52" s="20" t="n">
-        <v>46429</v>
-      </c>
-      <c r="C52" s="20" t="n">
-        <v>46450</v>
-      </c>
-      <c r="D52" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E52" s="18" t="n">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="F52" s="22" t="inlineStr">
-        <is>
-          <t>yfinance</t>
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>PFG</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="n">
+        <v>46433</v>
+      </c>
+      <c r="C52" s="10" t="n">
+        <v>46634</v>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>0.02439024390243905</v>
+      </c>
+      <c r="F52" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B53" s="10" t="n">
-        <v>46431</v>
+        <v>46433</v>
       </c>
       <c r="C53" s="10" t="n">
-        <v>46480</v>
+        <v>46608</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>0.42</v>
+        <v>0.531</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>0.02439024390243905</v>
+        <v>0.005735494868956323</v>
       </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
@@ -4085,20 +4104,20 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="B54" s="10" t="n">
-        <v>46432</v>
+        <v>46440</v>
       </c>
       <c r="C54" s="10" t="n">
-        <v>46455</v>
+        <v>46450</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>0.67</v>
+        <v>0.29</v>
       </c>
       <c r="E54" s="8" t="n">
-        <v>0.06349206349206354</v>
+        <v>0.07407407407407393</v>
       </c>
       <c r="F54" s="12" t="inlineStr">
         <is>
@@ -4109,20 +4128,20 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B55" s="10" t="n">
-        <v>46433</v>
+        <v>46441</v>
       </c>
       <c r="C55" s="10" t="n">
-        <v>46425</v>
+        <v>46456</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>2.138</v>
+        <v>2.33</v>
       </c>
       <c r="E55" s="8" t="n">
-        <v>0.6872012745618694</v>
+        <v>0.01304347826086967</v>
       </c>
       <c r="F55" s="12" t="inlineStr">
         <is>
@@ -4130,95 +4149,62 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>CME</t>
-        </is>
-      </c>
-      <c r="B56" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="C56" s="10" t="n">
-        <v>46383</v>
-      </c>
-      <c r="D56" s="7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E56" s="8" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="F56" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>DVN</t>
-        </is>
-      </c>
-      <c r="B57" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="C57" s="10" t="n">
-        <v>46458</v>
-      </c>
-      <c r="D57" s="7" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E57" s="8" t="n">
-        <v>0.3333333333333334</v>
-      </c>
-      <c r="F57" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A57" s="22" t="inlineStr">
+        <is>
+          <t>March 2027</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>PFG</t>
-        </is>
-      </c>
-      <c r="B58" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="C58" s="10" t="n">
-        <v>46634</v>
-      </c>
-      <c r="D58" s="7" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E58" s="8" t="n">
-        <v>0.02439024390243905</v>
-      </c>
-      <c r="F58" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A58" s="23" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B58" s="23" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C58" s="23" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D58" s="23" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E58" s="23" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F58" s="23" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="B59" s="10" t="n">
-        <v>46433</v>
+        <v>46452</v>
       </c>
       <c r="C59" s="10" t="n">
-        <v>46608</v>
+        <v>46487</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>0.531</v>
+        <v>1.59</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>0.005735494868956323</v>
+        <v>0.06000000000000005</v>
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
@@ -4229,20 +4215,20 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B60" s="10" t="n">
-        <v>46440</v>
+        <v>46461</v>
       </c>
       <c r="C60" s="10" t="n">
-        <v>46450</v>
+        <v>46386</v>
       </c>
       <c r="D60" s="7" t="n">
-        <v>0.29</v>
+        <v>0.271</v>
       </c>
       <c r="E60" s="8" t="n">
-        <v>0.07407407407407393</v>
+        <v>0.003703703703703707</v>
       </c>
       <c r="F60" s="12" t="inlineStr">
         <is>
@@ -4250,86 +4236,86 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>HD</t>
-        </is>
-      </c>
-      <c r="B61" s="10" t="n">
-        <v>46441</v>
-      </c>
-      <c r="C61" s="10" t="n">
-        <v>46456</v>
-      </c>
-      <c r="D61" s="7" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="E61" s="8" t="n">
-        <v>0.01304347826086967</v>
-      </c>
-      <c r="F61" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="62">
+      <c r="A62" s="22" t="inlineStr">
+        <is>
+          <t>April 2027</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="23" t="inlineStr">
         <is>
-          <t>March 2027</t>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B63" s="23" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C63" s="23" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D63" s="23" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E63" s="23" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F63" s="23" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="24" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B64" s="24" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C64" s="24" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D64" s="24" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E64" s="24" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F64" s="24" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="n">
+        <v>46488</v>
+      </c>
+      <c r="C64" s="10" t="n">
+        <v>46498</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="E64" s="8" t="n">
+        <v>0.03027436140018924</v>
+      </c>
+      <c r="F64" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="B65" s="10" t="n">
-        <v>46452</v>
+        <v>46492</v>
       </c>
       <c r="C65" s="10" t="n">
-        <v>46487</v>
+        <v>46501</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>1.59</v>
+        <v>1.125</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>0.06000000000000005</v>
+        <v>0.03495860165593379</v>
       </c>
       <c r="F65" s="12" t="inlineStr">
         <is>
@@ -4340,20 +4326,20 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B66" s="10" t="n">
-        <v>46461</v>
+        <v>46492</v>
       </c>
       <c r="C66" s="10" t="n">
-        <v>46300</v>
+        <v>46376</v>
       </c>
       <c r="D66" s="7" t="n">
-        <v>1.5</v>
+        <v>0.974</v>
       </c>
       <c r="E66" s="8" t="n">
-        <v>0.07142857142857149</v>
+        <v>0.001006036217303824</v>
       </c>
       <c r="F66" s="12" t="inlineStr">
         <is>
@@ -4364,20 +4350,20 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B67" s="10" t="n">
-        <v>46461</v>
+        <v>46493</v>
       </c>
       <c r="C67" s="10" t="n">
-        <v>46386</v>
+        <v>46531</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>0.271</v>
+        <v>1.34</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>0.003703703703703707</v>
+        <v>0.0307692307692308</v>
       </c>
       <c r="F67" s="12" t="inlineStr">
         <is>
@@ -4385,110 +4371,110 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>PSX</t>
+        </is>
+      </c>
+      <c r="B68" s="10" t="n">
+        <v>46499</v>
+      </c>
+      <c r="C68" s="10" t="n">
+        <v>46526</v>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E68" s="8" t="n">
+        <v>0.05833333333333339</v>
+      </c>
+      <c r="F68" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="23" t="inlineStr">
-        <is>
-          <t>April 2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="24" t="inlineStr">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
+      <c r="B69" s="10" t="n">
+        <v>46504</v>
+      </c>
+      <c r="C69" s="10" t="n">
+        <v>46562</v>
+      </c>
+      <c r="D69" s="7" t="n">
+        <v>0.551</v>
+      </c>
+      <c r="E69" s="8" t="n">
+        <v>0.04952380952380957</v>
+      </c>
+      <c r="F69" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="22" t="inlineStr">
+        <is>
+          <t>May 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="23" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B70" s="24" t="inlineStr">
+      <c r="B72" s="23" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C70" s="24" t="inlineStr">
+      <c r="C72" s="23" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D70" s="24" t="inlineStr">
+      <c r="D72" s="23" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E70" s="24" t="inlineStr">
+      <c r="E72" s="23" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F70" s="24" t="inlineStr">
+      <c r="F72" s="23" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>PG</t>
-        </is>
-      </c>
-      <c r="B71" s="10" t="n">
-        <v>46488</v>
-      </c>
-      <c r="C71" s="10" t="n">
-        <v>46498</v>
-      </c>
-      <c r="D71" s="7" t="n">
-        <v>1.089</v>
-      </c>
-      <c r="E71" s="8" t="n">
-        <v>0.03027436140018924</v>
-      </c>
-      <c r="F71" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>KOF</t>
-        </is>
-      </c>
-      <c r="B72" s="10" t="n">
-        <v>46492</v>
-      </c>
-      <c r="C72" s="10" t="n">
-        <v>46501</v>
-      </c>
-      <c r="D72" s="7" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="E72" s="8" t="n">
-        <v>0.03495860165593379</v>
-      </c>
-      <c r="F72" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="B73" s="10" t="n">
-        <v>46492</v>
+        <v>46508</v>
       </c>
       <c r="C73" s="10" t="n">
-        <v>46376</v>
+        <v>46518</v>
       </c>
       <c r="D73" s="7" t="n">
-        <v>0.974</v>
+        <v>1.19</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>0.001006036217303824</v>
+        <v>0.1018518518518517</v>
       </c>
       <c r="F73" s="12" t="inlineStr">
         <is>
@@ -4499,20 +4485,20 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B74" s="10" t="n">
-        <v>46493</v>
+        <v>46515</v>
       </c>
       <c r="C74" s="10" t="n">
-        <v>46531</v>
+        <v>46542</v>
       </c>
       <c r="D74" s="7" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="E74" s="8" t="n">
-        <v>0.0307692307692308</v>
+        <v>0.04005621925509482</v>
       </c>
       <c r="F74" s="12" t="inlineStr">
         <is>
@@ -4523,20 +4509,20 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B75" s="10" t="n">
-        <v>46499</v>
+        <v>46532</v>
       </c>
       <c r="C75" s="10" t="n">
-        <v>46526</v>
+        <v>46563</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>1.27</v>
+        <v>0.72</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>0.05833333333333339</v>
+        <v>0.01408450704225353</v>
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
@@ -4544,86 +4530,86 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
-      </c>
-      <c r="B76" s="10" t="n">
-        <v>46504</v>
-      </c>
-      <c r="C76" s="10" t="n">
-        <v>46562</v>
-      </c>
-      <c r="D76" s="7" t="n">
-        <v>0.551</v>
-      </c>
-      <c r="E76" s="8" t="n">
-        <v>0.04952380952380957</v>
-      </c>
-      <c r="F76" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="77">
+      <c r="A77" s="22" t="inlineStr">
+        <is>
+          <t>July 2027</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="23" t="inlineStr">
         <is>
-          <t>May 2027</t>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B78" s="23" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C78" s="23" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D78" s="23" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E78" s="23" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F78" s="23" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="24" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B79" s="24" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C79" s="24" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D79" s="24" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E79" s="24" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F79" s="24" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>UNP</t>
+        </is>
+      </c>
+      <c r="B79" s="10" t="n">
+        <v>46589</v>
+      </c>
+      <c r="C79" s="10" t="n">
+        <v>46629</v>
+      </c>
+      <c r="D79" s="7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="E79" s="8" t="n">
+        <v>0.02898550724637684</v>
+      </c>
+      <c r="F79" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="B80" s="10" t="n">
-        <v>46508</v>
+        <v>46591</v>
       </c>
       <c r="C80" s="10" t="n">
-        <v>46518</v>
+        <v>46633</v>
       </c>
       <c r="D80" s="7" t="n">
-        <v>1.19</v>
+        <v>0.84</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>0.1018518518518517</v>
+        <v>0.01204819277108435</v>
       </c>
       <c r="F80" s="12" t="inlineStr">
         <is>
@@ -4634,20 +4620,20 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="B81" s="10" t="n">
-        <v>46515</v>
+        <v>46594</v>
       </c>
       <c r="C81" s="10" t="n">
-        <v>46542</v>
+        <v>46613</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>1.48</v>
+        <v>0.98</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>0.04005621925509482</v>
+        <v>0.05376344086021498</v>
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
@@ -4658,20 +4644,20 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>AWR</t>
         </is>
       </c>
       <c r="B82" s="10" t="n">
-        <v>46532</v>
+        <v>46595</v>
       </c>
       <c r="C82" s="10" t="n">
-        <v>46563</v>
+        <v>46614</v>
       </c>
       <c r="D82" s="7" t="n">
-        <v>0.72</v>
+        <v>0.546</v>
       </c>
       <c r="E82" s="8" t="n">
-        <v>0.01408450704225353</v>
+        <v>0.08333333333333341</v>
       </c>
       <c r="F82" s="12" t="inlineStr">
         <is>
@@ -4679,110 +4665,110 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>CLX</t>
+        </is>
+      </c>
+      <c r="B83" s="10" t="n">
+        <v>46597</v>
+      </c>
+      <c r="C83" s="10" t="n">
+        <v>46611</v>
+      </c>
+      <c r="D83" s="7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E83" s="8" t="n">
+        <v>0.008064516129032265</v>
+      </c>
+      <c r="F83" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="84">
-      <c r="A84" s="23" t="inlineStr">
-        <is>
-          <t>July 2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="24" t="inlineStr">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>CFR</t>
+        </is>
+      </c>
+      <c r="B84" s="10" t="n">
+        <v>46598</v>
+      </c>
+      <c r="C84" s="10" t="n">
+        <v>46629</v>
+      </c>
+      <c r="D84" s="7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E84" s="8" t="n">
+        <v>0.03000000000000003</v>
+      </c>
+      <c r="F84" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="22" t="inlineStr">
+        <is>
+          <t>August 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="23" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B85" s="24" t="inlineStr">
+      <c r="B87" s="23" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C85" s="24" t="inlineStr">
+      <c r="C87" s="23" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D85" s="24" t="inlineStr">
+      <c r="D87" s="23" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E85" s="24" t="inlineStr">
+      <c r="E87" s="23" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F85" s="24" t="inlineStr">
+      <c r="F87" s="23" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
-          <t>UNP</t>
-        </is>
-      </c>
-      <c r="B86" s="10" t="n">
-        <v>46589</v>
-      </c>
-      <c r="C86" s="10" t="n">
-        <v>46629</v>
-      </c>
-      <c r="D86" s="7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="E86" s="8" t="n">
-        <v>0.02898550724637684</v>
-      </c>
-      <c r="F86" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>SWK</t>
-        </is>
-      </c>
-      <c r="B87" s="10" t="n">
-        <v>46591</v>
-      </c>
-      <c r="C87" s="10" t="n">
-        <v>46633</v>
-      </c>
-      <c r="D87" s="7" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E87" s="8" t="n">
-        <v>0.01204819277108435</v>
-      </c>
-      <c r="F87" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="B88" s="10" t="n">
-        <v>46594</v>
+        <v>46628</v>
       </c>
       <c r="C88" s="10" t="n">
-        <v>46613</v>
+        <v>46662</v>
       </c>
       <c r="D88" s="7" t="n">
-        <v>0.98</v>
+        <v>0.82</v>
       </c>
       <c r="E88" s="8" t="n">
-        <v>0.05376344086021498</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="F88" s="12" t="inlineStr">
         <is>
@@ -4790,73 +4776,112 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="5" t="inlineStr">
-        <is>
-          <t>AWR</t>
-        </is>
-      </c>
-      <c r="B89" s="10" t="n">
-        <v>46595</v>
-      </c>
-      <c r="C89" s="10" t="n">
-        <v>46614</v>
-      </c>
-      <c r="D89" s="7" t="n">
-        <v>0.546</v>
-      </c>
-      <c r="E89" s="8" t="n">
-        <v>0.08333333333333341</v>
-      </c>
-      <c r="F89" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
     <row r="90">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>CLX</t>
-        </is>
-      </c>
-      <c r="B90" s="10" t="n">
-        <v>46597</v>
-      </c>
-      <c r="C90" s="10" t="n">
-        <v>46611</v>
-      </c>
-      <c r="D90" s="7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E90" s="8" t="n">
-        <v>0.008064516129032265</v>
-      </c>
-      <c r="F90" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A90" s="22" t="inlineStr">
+        <is>
+          <t>September 2027</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="inlineStr">
-        <is>
-          <t>CFR</t>
-        </is>
-      </c>
-      <c r="B91" s="10" t="n">
-        <v>46598</v>
-      </c>
-      <c r="C91" s="10" t="n">
-        <v>46629</v>
-      </c>
-      <c r="D91" s="7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E91" s="8" t="n">
-        <v>0.03000000000000003</v>
-      </c>
-      <c r="F91" s="12" t="inlineStr">
+      <c r="A91" s="23" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B91" s="23" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C91" s="23" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D91" s="23" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E91" s="23" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F91" s="23" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B92" s="10" t="n">
+        <v>46643</v>
+      </c>
+      <c r="C92" s="10" t="n">
+        <v>46709</v>
+      </c>
+      <c r="D92" s="7" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E92" s="8" t="n">
+        <v>0.09638554216867479</v>
+      </c>
+      <c r="F92" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>VZ</t>
+        </is>
+      </c>
+      <c r="B93" s="10" t="n">
+        <v>46645</v>
+      </c>
+      <c r="C93" s="10" t="n">
+        <v>46668</v>
+      </c>
+      <c r="D93" s="7" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="E93" s="8" t="n">
+        <v>0.02608695652173916</v>
+      </c>
+      <c r="F93" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="B94" s="10" t="n">
+        <v>46650</v>
+      </c>
+      <c r="C94" s="10" t="n">
+        <v>46690</v>
+      </c>
+      <c r="D94" s="7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="E94" s="8" t="n">
+        <v>0.0441176470588234</v>
+      </c>
+      <c r="F94" s="12" t="inlineStr">
         <is>
           <t>Notion + yfinance</t>
         </is>
@@ -4901,7 +4926,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Complete Holdings Dividend Summary - 09/14/2026</t>
+          <t>Complete Holdings Dividend Summary - 09/21/2026</t>
         </is>
       </c>
     </row>
@@ -5001,11 +5026,11 @@
       <c r="F5" s="7" t="n">
         <v>0.29</v>
       </c>
-      <c r="G5" s="25" t="n">
+      <c r="G5" s="24" t="n">
         <v>1.16</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.00946320755973527</v>
+        <v>0.00978737793499475</v>
       </c>
       <c r="I5" s="10" t="n">
         <v>46255</v>
@@ -5054,11 +5079,11 @@
       <c r="F6" s="7" t="n">
         <v>2.52</v>
       </c>
-      <c r="G6" s="25" t="n">
+      <c r="G6" s="24" t="n">
         <v>10.08</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.02668498548328576</v>
+        <v>0.02574909946756583</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>46255</v>
@@ -5107,11 +5132,11 @@
       <c r="F7" s="7" t="n">
         <v>2.138</v>
       </c>
-      <c r="G7" s="25" t="n">
+      <c r="G7" s="24" t="n">
         <v>8.552</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.005338793701200471</v>
+        <v>0.005078776879924646</v>
       </c>
       <c r="I7" s="10" t="n">
         <v>46231</v>
@@ -5160,11 +5185,11 @@
       <c r="F8" s="7" t="n">
         <v>0.546</v>
       </c>
-      <c r="G8" s="25" t="n">
+      <c r="G8" s="24" t="n">
         <v>2.184</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>0.0250789461211513</v>
+        <v>0.02551849066264972</v>
       </c>
       <c r="I8" s="10" t="n">
         <v>46251</v>
@@ -5213,11 +5238,11 @@
       <c r="F9" s="7" t="n">
         <v>0.703</v>
       </c>
-      <c r="G9" s="25" t="n">
+      <c r="G9" s="24" t="n">
         <v>2.812</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.03957219387294963</v>
+        <v>0.03886124898121857</v>
       </c>
       <c r="I9" s="10" t="n">
         <v>46251</v>
@@ -5266,11 +5291,11 @@
       <c r="F10" s="7" t="n">
         <v>1.03</v>
       </c>
-      <c r="G10" s="25" t="n">
+      <c r="G10" s="24" t="n">
         <v>4.12</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.02503037574256811</v>
+        <v>0.0258234356907714</v>
       </c>
       <c r="I10" s="10" t="n">
         <v>46265</v>
@@ -5319,11 +5344,11 @@
       <c r="F11" s="7" t="n">
         <v>1.25</v>
       </c>
-      <c r="G11" s="25" t="n">
+      <c r="G11" s="24" t="n">
         <v>5</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.05629362775477879</v>
+        <v>0.06040099158048739</v>
       </c>
       <c r="I11" s="10" t="n">
         <v>46246</v>
@@ -5372,11 +5397,11 @@
       <c r="F12" s="7" t="n">
         <v>1.3</v>
       </c>
-      <c r="G12" s="25" t="n">
+      <c r="G12" s="24" t="n">
         <v>5.2</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0.0186580544393274</v>
+        <v>0.01892595187562783</v>
       </c>
       <c r="I12" s="10" t="n">
         <v>46274</v>
@@ -5425,11 +5450,11 @@
       <c r="F13" s="7" t="n">
         <v>0.24</v>
       </c>
-      <c r="G13" s="25" t="n">
+      <c r="G13" s="24" t="n">
         <v>0.96</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0.02463433333150609</v>
+        <v>0.02520677492654566</v>
       </c>
       <c r="I13" s="10" t="n">
         <v>46254</v>
@@ -5478,11 +5503,11 @@
       <c r="F14" s="7" t="n">
         <v>0.6</v>
       </c>
-      <c r="G14" s="25" t="n">
+      <c r="G14" s="24" t="n">
         <v>2.4</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>0.007397361552028218</v>
+        <v>0.007728721893003816</v>
       </c>
       <c r="I14" s="10" t="n">
         <v>46248</v>
@@ -5531,11 +5556,11 @@
       <c r="F15" s="7" t="n">
         <v>0.42</v>
       </c>
-      <c r="G15" s="25" t="n">
+      <c r="G15" s="24" t="n">
         <v>1.68</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0.01520224384693243</v>
+        <v>0.01533966445849374</v>
       </c>
       <c r="I15" s="10" t="n">
         <v>46209</v>
@@ -5584,11 +5609,11 @@
       <c r="F16" s="7" t="n">
         <v>1.78</v>
       </c>
-      <c r="G16" s="25" t="n">
+      <c r="G16" s="24" t="n">
         <v>7.12</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>0.03291115891894363</v>
+        <v>0.03451117291578592</v>
       </c>
       <c r="I16" s="10" t="n">
         <v>46253</v>
@@ -5637,11 +5662,11 @@
       <c r="F17" s="7" t="n">
         <v>0.86</v>
       </c>
-      <c r="G17" s="25" t="n">
+      <c r="G17" s="24" t="n">
         <v>3.44</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0.01446715458684541</v>
+        <v>0.01387936217586079</v>
       </c>
       <c r="I17" s="10" t="n">
         <v>46211</v>
@@ -5690,14 +5715,14 @@
       <c r="F18" s="7" t="n">
         <v>0.32</v>
       </c>
-      <c r="G18" s="25" t="n">
+      <c r="G18" s="24" t="n">
         <v>1.28</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0.02508574153301707</v>
+        <v>0.02686253848921341</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>46188</v>
+        <v>46280</v>
       </c>
       <c r="J18" s="8" t="n">
         <v>0.3333333333333334</v>
@@ -5743,14 +5768,14 @@
       <c r="F19" s="7" t="n">
         <v>0.84</v>
       </c>
-      <c r="G19" s="25" t="n">
+      <c r="G19" s="24" t="n">
         <v>3.36</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0.04971885038416789</v>
+        <v>0.05154560291238409</v>
       </c>
       <c r="I19" s="10" t="n">
-        <v>46188</v>
+        <v>46280</v>
       </c>
       <c r="J19" s="8" t="n">
         <v>0.01204819277108435</v>
@@ -5796,11 +5821,11 @@
       <c r="F20" s="7" t="n">
         <v>0.64</v>
       </c>
-      <c r="G20" s="25" t="n">
+      <c r="G20" s="24" t="n">
         <v>2.56</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0.02491484184914842</v>
+        <v>0.02523905638405114</v>
       </c>
       <c r="I20" s="10" t="n">
         <v>46247</v>
@@ -5849,11 +5874,11 @@
       <c r="F21" s="7" t="n">
         <v>1.59</v>
       </c>
-      <c r="G21" s="25" t="n">
+      <c r="G21" s="24" t="n">
         <v>6.36</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0.01779070791836802</v>
+        <v>0.01805945923134389</v>
       </c>
       <c r="I21" s="10" t="n">
         <v>46205</v>
@@ -5874,53 +5899,53 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>GGG</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>SMID/DAC</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
         <is>
           <t>Jan/Apr/Jul/Oct</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E22" s="15" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="F22" s="17" t="n">
+      <c r="F22" s="16" t="n">
         <v>0.295</v>
       </c>
-      <c r="G22" s="26" t="n">
+      <c r="G22" s="25" t="n">
         <v>1.18</v>
       </c>
-      <c r="H22" s="19" t="n">
-        <v>0.01539665983034154</v>
-      </c>
-      <c r="I22" s="20" t="n">
+      <c r="H22" s="18" t="n">
+        <v>0.01548353253084369</v>
+      </c>
+      <c r="I22" s="19" t="n">
         <v>46223</v>
       </c>
-      <c r="J22" s="18" t="n">
+      <c r="J22" s="17" t="n">
         <v>0.07272727272727258</v>
       </c>
-      <c r="K22" s="20" t="n">
+      <c r="K22" s="19" t="n">
         <v>46383</v>
       </c>
-      <c r="L22" s="20" t="n">
+      <c r="L22" s="19" t="n">
         <v>46404</v>
       </c>
-      <c r="M22" s="22" t="inlineStr">
+      <c r="M22" s="21" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
@@ -5955,11 +5980,11 @@
       <c r="F23" s="7" t="n">
         <v>2.33</v>
       </c>
-      <c r="G23" s="25" t="n">
+      <c r="G23" s="24" t="n">
         <v>9.32</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>0.03000740561476674</v>
+        <v>0.03142279099194371</v>
       </c>
       <c r="I23" s="10" t="n">
         <v>46268</v>
@@ -6008,11 +6033,11 @@
       <c r="F24" s="7" t="n">
         <v>1.38</v>
       </c>
-      <c r="G24" s="25" t="n">
+      <c r="G24" s="24" t="n">
         <v>5.52</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>0.01974143087025879</v>
+        <v>0.02022274389215184</v>
       </c>
       <c r="I24" s="10" t="n">
         <v>46262</v>
@@ -6061,11 +6086,11 @@
       <c r="F25" s="7" t="n">
         <v>0.293</v>
       </c>
-      <c r="G25" s="25" t="n">
+      <c r="G25" s="24" t="n">
         <v>1.172</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0.05595607625096392</v>
+        <v>0.05678294741557949</v>
       </c>
       <c r="I25" s="10" t="n">
         <v>46216</v>
@@ -6086,53 +6111,53 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>HWC</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>SMID/DAC</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
         <is>
           <t>Mar/Jun/Sep/Dec</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E26" s="15" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="F26" s="17" t="n">
+      <c r="F26" s="16" t="n">
         <v>0.5</v>
       </c>
-      <c r="G26" s="26" t="n">
+      <c r="G26" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="H26" s="19" t="n">
-        <v>0.02641310047223251</v>
-      </c>
-      <c r="I26" s="20" t="n">
+      <c r="H26" s="18" t="n">
+        <v>0.02664889964922068</v>
+      </c>
+      <c r="I26" s="19" t="n">
         <v>46269</v>
       </c>
-      <c r="J26" s="18" t="n">
+      <c r="J26" s="17" t="n">
         <v>0.1111111111111111</v>
       </c>
-      <c r="K26" s="20" t="n">
+      <c r="K26" s="19" t="n">
         <v>46429</v>
       </c>
-      <c r="L26" s="20" t="n">
+      <c r="L26" s="19" t="n">
         <v>46450</v>
       </c>
-      <c r="M26" s="22" t="inlineStr">
+      <c r="M26" s="21" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
@@ -6167,11 +6192,11 @@
       <c r="F27" s="7" t="n">
         <v>0.82</v>
       </c>
-      <c r="G27" s="25" t="n">
+      <c r="G27" s="24" t="n">
         <v>3.28</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0.03249306950164277</v>
+        <v>0.03369112923733877</v>
       </c>
       <c r="I27" s="10" t="n">
         <v>46204</v>
@@ -6180,7 +6205,7 @@
         <v>0.02499999999999988</v>
       </c>
       <c r="K27" s="10" t="n">
-        <v>46263</v>
+        <v>46628</v>
       </c>
       <c r="L27" s="10" t="n">
         <v>46662</v>
@@ -6220,11 +6245,11 @@
       <c r="F28" s="7" t="n">
         <v>0.61</v>
       </c>
-      <c r="G28" s="25" t="n">
+      <c r="G28" s="24" t="n">
         <v>2.44</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>0.01462479053918474</v>
+        <v>0.01583901299359408</v>
       </c>
       <c r="I28" s="10" t="n">
         <v>46269</v>
@@ -6273,11 +6298,11 @@
       <c r="F29" s="7" t="n">
         <v>1.34</v>
       </c>
-      <c r="G29" s="25" t="n">
+      <c r="G29" s="24" t="n">
         <v>5.36</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.01990567170011602</v>
+        <v>0.01961789025712752</v>
       </c>
       <c r="I29" s="10" t="n">
         <v>46259</v>
@@ -6326,11 +6351,11 @@
       <c r="F30" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="G30" s="25" t="n">
+      <c r="G30" s="24" t="n">
         <v>6</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>0.01699235314722998</v>
+        <v>0.017034323631875</v>
       </c>
       <c r="I30" s="10" t="n">
         <v>46209</v>
@@ -6339,10 +6364,10 @@
         <v>0.07142857142857149</v>
       </c>
       <c r="K30" s="10" t="n">
-        <v>46461</v>
+        <v>46284</v>
       </c>
       <c r="L30" s="10" t="n">
-        <v>46300</v>
+        <v>46665</v>
       </c>
       <c r="M30" s="12" t="inlineStr">
         <is>
@@ -6379,11 +6404,11 @@
       <c r="F31" s="7" t="n">
         <v>1.125</v>
       </c>
-      <c r="G31" s="25" t="n">
+      <c r="G31" s="24" t="n">
         <v>2.25</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0.0204202028393521</v>
+        <v>0.02042298300259235</v>
       </c>
       <c r="I31" s="10" t="n">
         <v>46216</v>
@@ -6432,11 +6457,11 @@
       <c r="F32" s="7" t="n">
         <v>0.79</v>
       </c>
-      <c r="G32" s="25" t="n">
+      <c r="G32" s="24" t="n">
         <v>3.16</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>0.0127142515706196</v>
+        <v>0.0122511718530932</v>
       </c>
       <c r="I32" s="10" t="n">
         <v>46203</v>
@@ -6485,11 +6510,11 @@
       <c r="F33" s="7" t="n">
         <v>0.72</v>
       </c>
-      <c r="G33" s="25" t="n">
+      <c r="G33" s="24" t="n">
         <v>2.88</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0.03080872803355954</v>
+        <v>0.03129414362926066</v>
       </c>
       <c r="I33" s="10" t="n">
         <v>46199</v>
@@ -6538,11 +6563,11 @@
       <c r="F34" s="7" t="n">
         <v>0.48</v>
       </c>
-      <c r="G34" s="25" t="n">
+      <c r="G34" s="24" t="n">
         <v>1.92</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0.03748535638894003</v>
+        <v>0.03923571975309979</v>
       </c>
       <c r="I34" s="10" t="n">
         <v>46209</v>
@@ -6591,11 +6616,11 @@
       <c r="F35" s="7" t="n">
         <v>0.91</v>
       </c>
-      <c r="G35" s="25" t="n">
+      <c r="G35" s="24" t="n">
         <v>3.64</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>0.007252874320868801</v>
+        <v>0.007345385769172313</v>
       </c>
       <c r="I35" s="10" t="n">
         <v>46254</v>
@@ -6604,7 +6629,7 @@
         <v>0.09638554216867479</v>
       </c>
       <c r="K35" s="10" t="n">
-        <v>46278</v>
+        <v>46643</v>
       </c>
       <c r="L35" s="10" t="n">
         <v>46709</v>
@@ -6644,11 +6669,11 @@
       <c r="F36" s="7" t="n">
         <v>0.87</v>
       </c>
-      <c r="G36" s="25" t="n">
+      <c r="G36" s="24" t="n">
         <v>3.48</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>0.028948135474036</v>
+        <v>0.02857260193208257</v>
       </c>
       <c r="I36" s="10" t="n">
         <v>46211</v>
@@ -6697,11 +6722,11 @@
       <c r="F37" s="7" t="n">
         <v>0.41</v>
       </c>
-      <c r="G37" s="25" t="n">
+      <c r="G37" s="24" t="n">
         <v>1.64</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>0.04430037762617224</v>
+        <v>0.04623560300134034</v>
       </c>
       <c r="I37" s="10" t="n">
         <v>46266</v>
@@ -6750,11 +6775,11 @@
       <c r="F38" s="7" t="n">
         <v>0.579</v>
       </c>
-      <c r="G38" s="25" t="n">
+      <c r="G38" s="24" t="n">
         <v>1.158</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0.02673438847314084</v>
+        <v>0.02892830465433105</v>
       </c>
       <c r="I38" s="10" t="n">
         <v>46251</v>
@@ -6803,11 +6828,11 @@
       <c r="F39" s="7" t="n">
         <v>0.271</v>
       </c>
-      <c r="G39" s="25" t="n">
+      <c r="G39" s="24" t="n">
         <v>3.252</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>0.05447236111291268</v>
+        <v>0.05709770688176589</v>
       </c>
       <c r="I39" s="10" t="n">
         <v>46265</v>
@@ -6856,11 +6881,11 @@
       <c r="F40" s="7" t="n">
         <v>1.19</v>
       </c>
-      <c r="G40" s="25" t="n">
+      <c r="G40" s="24" t="n">
         <v>4.76</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0.04061086969695727</v>
+        <v>0.04153940267145332</v>
       </c>
       <c r="I40" s="10" t="n">
         <v>46231</v>
@@ -6909,11 +6934,11 @@
       <c r="F41" s="7" t="n">
         <v>0.67</v>
       </c>
-      <c r="G41" s="25" t="n">
+      <c r="G41" s="24" t="n">
         <v>2.68</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>0.03727399086403899</v>
+        <v>0.03862784817086413</v>
       </c>
       <c r="I41" s="10" t="n">
         <v>46274</v>
@@ -6962,11 +6987,11 @@
       <c r="F42" s="7" t="n">
         <v>1.48</v>
       </c>
-      <c r="G42" s="25" t="n">
+      <c r="G42" s="24" t="n">
         <v>5.92</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>0.04294834704934376</v>
+        <v>0.04612387782222198</v>
       </c>
       <c r="I42" s="10" t="n">
         <v>46269</v>
@@ -7015,11 +7040,11 @@
       <c r="F43" s="7" t="n">
         <v>0.43</v>
       </c>
-      <c r="G43" s="25" t="n">
+      <c r="G43" s="24" t="n">
         <v>1.72</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>0.0618816332174422</v>
+        <v>0.06210507380223738</v>
       </c>
       <c r="I43" s="10" t="n">
         <v>46227</v>
@@ -7068,11 +7093,11 @@
       <c r="F44" s="7" t="n">
         <v>0.84</v>
       </c>
-      <c r="G44" s="25" t="n">
+      <c r="G44" s="24" t="n">
         <v>3.36</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>0.02863412689310154</v>
+        <v>0.0286225403992658</v>
       </c>
       <c r="I44" s="10" t="n">
         <v>46268</v>
@@ -7121,11 +7146,11 @@
       <c r="F45" s="7" t="n">
         <v>1.089</v>
       </c>
-      <c r="G45" s="25" t="n">
+      <c r="G45" s="24" t="n">
         <v>4.356</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>0.02964170822323141</v>
+        <v>0.0298213170506069</v>
       </c>
       <c r="I45" s="10" t="n">
         <v>46227</v>
@@ -7174,11 +7199,11 @@
       <c r="F46" s="7" t="n">
         <v>0.551</v>
       </c>
-      <c r="G46" s="25" t="n">
+      <c r="G46" s="24" t="n">
         <v>2.204</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>0.04570717428878286</v>
+        <v>0.04648317953059956</v>
       </c>
       <c r="I46" s="10" t="n">
         <v>46198</v>
@@ -7227,11 +7252,11 @@
       <c r="F47" s="7" t="n">
         <v>1.27</v>
       </c>
-      <c r="G47" s="25" t="n">
+      <c r="G47" s="24" t="n">
         <v>5.08</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>0.01924971624665003</v>
+        <v>0.01878350811872483</v>
       </c>
       <c r="I47" s="10" t="n">
         <v>46252</v>
@@ -7280,11 +7305,11 @@
       <c r="F48" s="7" t="n">
         <v>0.98</v>
       </c>
-      <c r="G48" s="25" t="n">
+      <c r="G48" s="24" t="n">
         <v>3.92</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>0.01568376395018629</v>
+        <v>0.01592201481961874</v>
       </c>
       <c r="I48" s="10" t="n">
         <v>46252</v>
@@ -7333,11 +7358,11 @@
       <c r="F49" s="7" t="n">
         <v>2.44</v>
       </c>
-      <c r="G49" s="25" t="n">
+      <c r="G49" s="24" t="n">
         <v>9.76</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>0.02583787857341831</v>
+        <v>0.02634704658156829</v>
       </c>
       <c r="I49" s="10" t="n">
         <v>46253</v>
@@ -7386,7 +7411,7 @@
       <c r="F50" s="7" t="n">
         <v>0.84</v>
       </c>
-      <c r="G50" s="25" t="n">
+      <c r="G50" s="24" t="n">
         <v>3.36</v>
       </c>
       <c r="H50" s="9" t="n">
@@ -7439,14 +7464,14 @@
       <c r="F51" s="7" t="n">
         <v>1.3</v>
       </c>
-      <c r="G51" s="25" t="n">
+      <c r="G51" s="24" t="n">
         <v>5.2</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>0.04881483149978388</v>
+        <v>0.05013256280063842</v>
       </c>
       <c r="I51" s="10" t="n">
-        <v>46188</v>
+        <v>46280</v>
       </c>
       <c r="J51" s="8" t="n">
         <v>0.02362204724409451</v>
@@ -7492,11 +7517,11 @@
       <c r="F52" s="7" t="n">
         <v>0.974</v>
       </c>
-      <c r="G52" s="25" t="n">
+      <c r="G52" s="24" t="n">
         <v>3.896</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>0.04231333292565891</v>
+        <v>0.04302120257323579</v>
       </c>
       <c r="I52" s="10" t="n">
         <v>46112</v>
@@ -7545,11 +7570,11 @@
       <c r="F53" s="7" t="n">
         <v>1.42</v>
       </c>
-      <c r="G53" s="25" t="n">
+      <c r="G53" s="24" t="n">
         <v>5.68</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>0.02153962736846832</v>
+        <v>0.02139359698681732</v>
       </c>
       <c r="I53" s="10" t="n">
         <v>46234</v>
@@ -7558,10 +7583,10 @@
         <v>0.0441176470588234</v>
       </c>
       <c r="K53" s="10" t="n">
-        <v>46285</v>
+        <v>46650</v>
       </c>
       <c r="L53" s="10" t="n">
-        <v>46325</v>
+        <v>46690</v>
       </c>
       <c r="M53" s="12" t="inlineStr">
         <is>
@@ -7598,11 +7623,11 @@
       <c r="F54" s="7" t="n">
         <v>0.531</v>
       </c>
-      <c r="G54" s="25" t="n">
+      <c r="G54" s="24" t="n">
         <v>2.124</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>0.03364219619018467</v>
+        <v>0.03425806451612903</v>
       </c>
       <c r="I54" s="10" t="n">
         <v>46241</v>
@@ -7651,11 +7676,11 @@
       <c r="F55" s="7" t="n">
         <v>1.42</v>
       </c>
-      <c r="G55" s="25" t="n">
+      <c r="G55" s="24" t="n">
         <v>5.68</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>0.0199424192610679</v>
+        <v>0.02079215225231083</v>
       </c>
       <c r="I55" s="10" t="n">
         <v>46265</v>
@@ -7704,11 +7729,11 @@
       <c r="F56" s="7" t="n">
         <v>0.708</v>
       </c>
-      <c r="G56" s="25" t="n">
+      <c r="G56" s="24" t="n">
         <v>2.832</v>
       </c>
       <c r="H56" s="9" t="n">
-        <v>0.05532352119915055</v>
+        <v>0.05928406893158691</v>
       </c>
       <c r="I56" s="10" t="n">
         <v>46213</v>
@@ -7717,7 +7742,7 @@
         <v>0.02608695652173916</v>
       </c>
       <c r="K56" s="10" t="n">
-        <v>46280</v>
+        <v>46645</v>
       </c>
       <c r="L56" s="10" t="n">
         <v>46668</v>
@@ -7757,11 +7782,11 @@
       <c r="F57" s="7" t="n">
         <v>1.03</v>
       </c>
-      <c r="G57" s="25" t="n">
+      <c r="G57" s="24" t="n">
         <v>4.12</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>0.02451651249736115</v>
+        <v>0.02579191096983098</v>
       </c>
       <c r="I57" s="10" t="n">
         <v>46251</v>

--- a/data/dividend_calendar.xlsx
+++ b/data/dividend_calendar.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="167" formatCode="MM/DD/YYYY"/>
     <numFmt numFmtId="168" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -84,6 +84,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00856404"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="001a3a5c"/>
       <sz val="12"/>
     </font>
@@ -94,7 +100,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -116,6 +122,11 @@
         <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -134,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -152,6 +163,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -165,8 +179,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -561,7 +576,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Estimated Dividend Calendar: Anticipated Announcements - 09/21/2026</t>
+          <t>Estimated Dividend Calendar: Anticipated Announcements - 09/28/2026</t>
         </is>
       </c>
     </row>
@@ -666,7 +681,7 @@
         <v>46048</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>-238</v>
+        <v>-245</v>
       </c>
       <c r="J6" s="10" t="n">
         <v>46413</v>
@@ -677,13 +692,13 @@
         </is>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0.06210507380223738</v>
+        <v>0.06040386222854276</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -693,29 +708,29 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>1.5</v>
+        <v>0.87</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1.4</v>
+        <v>0.85</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>0.07142857142857149</v>
+        <v>0.0235294117647059</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>46284</v>
-      </c>
-      <c r="I7" s="11" t="n">
-        <v>-2</v>
+        <v>46305</v>
+      </c>
+      <c r="I7" s="13" t="n">
+        <v>12</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>46665</v>
+        <v>46339</v>
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
@@ -723,13 +738,13 @@
         </is>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0.017034323631875</v>
+        <v>0.02871523995292049</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -739,29 +754,29 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>0.87</v>
+        <v>0.79</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.0235294117647059</v>
+        <v>0.05333333333333338</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>46305</v>
-      </c>
-      <c r="I8" s="13" t="n">
-        <v>19</v>
+        <v>46311</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>18</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>46339</v>
+        <v>46386</v>
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
@@ -769,13 +784,13 @@
         </is>
       </c>
       <c r="L8" s="9" t="n">
-        <v>0.02857260193208257</v>
+        <v>0.01157763600694031</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>HII</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -785,29 +800,29 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>0.79</v>
+        <v>1.38</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>0.75</v>
+        <v>1.35</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>0.05333333333333338</v>
+        <v>0.02222222222222208</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>46311</v>
-      </c>
-      <c r="I9" s="13" t="n">
+        <v>46318</v>
+      </c>
+      <c r="I9" s="14" t="n">
         <v>25</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>46386</v>
+        <v>46352</v>
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
@@ -815,13 +830,13 @@
         </is>
       </c>
       <c r="L9" s="9" t="n">
-        <v>0.0122511718530932</v>
+        <v>0.02119327413458831</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -835,25 +850,25 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>1.38</v>
+        <v>0.64</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1.35</v>
+        <v>0.6</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.02222222222222208</v>
+        <v>0.06666666666666674</v>
       </c>
       <c r="G10" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>46318</v>
-      </c>
-      <c r="I10" s="13" t="n">
-        <v>32</v>
+        <v>46322</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>29</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>46352</v>
+        <v>46338</v>
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
@@ -861,13 +876,13 @@
         </is>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0.02022274389215184</v>
+        <v>0.02619193836660545</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -881,21 +896,21 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>0.06666666666666674</v>
+        <v>0.09090909090909079</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>46322</v>
-      </c>
-      <c r="I11" s="13" t="n">
+        <v>46329</v>
+      </c>
+      <c r="I11" s="14" t="n">
         <v>36</v>
       </c>
       <c r="J11" s="10" t="n">
@@ -907,13 +922,13 @@
         </is>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0.02523905638405114</v>
+        <v>0.00785828876337411</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -927,25 +942,25 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.6</v>
+        <v>2.44</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>0.55</v>
+        <v>2.14</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.09090909090909079</v>
+        <v>0.1401869158878504</v>
       </c>
       <c r="G12" s="9" t="n">
         <v>0.08</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>46329</v>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>43</v>
+        <v>46332</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>39</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>46338</v>
+        <v>46346</v>
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
@@ -953,13 +968,13 @@
         </is>
       </c>
       <c r="L12" s="9" t="n">
-        <v>0.007728721893003816</v>
+        <v>0.02629593680273037</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -973,25 +988,25 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>2.44</v>
+        <v>1.03</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>2.14</v>
+        <v>0.99</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0.1401869158878504</v>
+        <v>0.04040404040404044</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>46332</v>
-      </c>
-      <c r="I13" s="13" t="n">
-        <v>46</v>
+        <v>46341</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>48</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>46346</v>
+        <v>46340</v>
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
@@ -999,13 +1014,13 @@
         </is>
       </c>
       <c r="L13" s="9" t="n">
-        <v>0.02634704658156829</v>
+        <v>0.02525206111259398</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -1015,29 +1030,29 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>1.03</v>
+        <v>0.48</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>0.99</v>
+        <v>0.45</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.04040404040404044</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>46341</v>
-      </c>
-      <c r="I14" s="13" t="n">
-        <v>55</v>
+        <v>46344</v>
+      </c>
+      <c r="I14" s="14" t="n">
+        <v>51</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>46340</v>
+        <v>46385</v>
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
@@ -1045,13 +1060,13 @@
         </is>
       </c>
       <c r="L14" s="9" t="n">
-        <v>0.02579191096983098</v>
+        <v>0.03987953020551666</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -1065,25 +1080,25 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.48</v>
+        <v>0.41</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>46344</v>
-      </c>
-      <c r="I15" s="13" t="n">
-        <v>58</v>
+        <v>46347</v>
+      </c>
+      <c r="I15" s="14" t="n">
+        <v>54</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>46385</v>
+        <v>46358</v>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
@@ -1091,13 +1106,13 @@
         </is>
       </c>
       <c r="L15" s="9" t="n">
-        <v>0.03923571975309979</v>
+        <v>0.04558087884561619</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -1107,29 +1122,29 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.41</v>
+        <v>0.293</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>0.4</v>
+        <v>0.29</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.01034482758620691</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>46347</v>
-      </c>
-      <c r="I16" s="13" t="n">
-        <v>61</v>
+        <v>46352</v>
+      </c>
+      <c r="I16" s="14" t="n">
+        <v>59</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>46358</v>
+        <v>46400</v>
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
@@ -1137,13 +1152,13 @@
         </is>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0.04623560300134034</v>
+        <v>0.05962859115015496</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>EMN</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -1153,29 +1168,29 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.293</v>
+        <v>0.84</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>0.29</v>
+        <v>0.83</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0.01034482758620691</v>
+        <v>0.01204819277108435</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>46352</v>
-      </c>
-      <c r="I17" s="13" t="n">
-        <v>66</v>
+        <v>46360</v>
+      </c>
+      <c r="I17" s="14" t="n">
+        <v>67</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>46400</v>
+        <v>46371</v>
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
@@ -1183,13 +1198,13 @@
         </is>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.05678294741557949</v>
+        <v>0.05089367117307898</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>EMN</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -1199,29 +1214,29 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.84</v>
+        <v>2.52</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>0.83</v>
+        <v>2.38</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0.01204819277108435</v>
+        <v>0.05882352941176476</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>46360</v>
-      </c>
-      <c r="I18" s="13" t="n">
-        <v>74</v>
+        <v>46366</v>
+      </c>
+      <c r="I18" s="14" t="n">
+        <v>73</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>46371</v>
+        <v>46432</v>
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
@@ -1229,13 +1244,13 @@
         </is>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0.05154560291238409</v>
+        <v>0.02434900172108285</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -1249,25 +1264,25 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>2.52</v>
+        <v>0.24</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>2.38</v>
+        <v>0.23</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>0.05882352941176476</v>
+        <v>0.04347826086956513</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>46366</v>
-      </c>
-      <c r="I19" s="13" t="n">
-        <v>80</v>
+        <v>46380</v>
+      </c>
+      <c r="I19" s="14" t="n">
+        <v>87</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>46432</v>
+        <v>46436</v>
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
@@ -1275,105 +1290,105 @@
         </is>
       </c>
       <c r="L19" s="9" t="n">
-        <v>0.02574909946756583</v>
+        <v>0.026044492243725</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>CNP</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E20" s="7" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>0.04347826086956513</v>
-      </c>
-      <c r="G20" s="9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H20" s="10" t="n">
-        <v>46380</v>
-      </c>
-      <c r="I20" s="13" t="n">
-        <v>94</v>
-      </c>
-      <c r="J20" s="10" t="n">
-        <v>46436</v>
-      </c>
-      <c r="K20" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L20" s="9" t="n">
-        <v>0.02520677492654566</v>
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>GGG</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="F20" s="18" t="n">
+        <v>0.07272727272727258</v>
+      </c>
+      <c r="G20" s="19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H20" s="20" t="n">
+        <v>46383</v>
+      </c>
+      <c r="I20" s="21" t="n">
+        <v>90</v>
+      </c>
+      <c r="J20" s="20" t="n">
+        <v>46404</v>
+      </c>
+      <c r="K20" s="22" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="L20" s="19" t="n">
+        <v>0.01510303393679408</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>GGG</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>Jan</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E21" s="16" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="F21" s="17" t="n">
-        <v>0.07272727272727258</v>
-      </c>
-      <c r="G21" s="18" t="n">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>0.07499999999999993</v>
+      </c>
+      <c r="G21" s="9" t="n">
         <v>0.06</v>
       </c>
-      <c r="H21" s="19" t="n">
-        <v>46383</v>
-      </c>
-      <c r="I21" s="20" t="n">
-        <v>97</v>
-      </c>
-      <c r="J21" s="19" t="n">
-        <v>46404</v>
-      </c>
-      <c r="K21" s="21" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
-      <c r="L21" s="18" t="n">
-        <v>0.01548353253084369</v>
+      <c r="H21" s="10" t="n">
+        <v>46402</v>
+      </c>
+      <c r="I21" s="14" t="n">
+        <v>109</v>
+      </c>
+      <c r="J21" s="10" t="n">
+        <v>46483</v>
+      </c>
+      <c r="K21" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="n">
+        <v>0.01466044423432771</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>BKH</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -1383,29 +1398,29 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.86</v>
+        <v>0.703</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>0.8</v>
+        <v>0.676</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>0.07499999999999993</v>
+        <v>0.03994082840236673</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>46402</v>
-      </c>
-      <c r="I22" s="13" t="n">
-        <v>116</v>
+        <v>46411</v>
+      </c>
+      <c r="I22" s="14" t="n">
+        <v>118</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>46483</v>
+        <v>46435</v>
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
@@ -1413,13 +1428,13 @@
         </is>
       </c>
       <c r="L22" s="9" t="n">
-        <v>0.01387936217586079</v>
+        <v>0.04049539028131194</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>BKH</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -1433,25 +1448,25 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.703</v>
+        <v>1.78</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>0.676</v>
+        <v>1.71</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>0.03994082840236673</v>
+        <v>0.04093567251461992</v>
       </c>
       <c r="G23" s="9" t="n">
         <v>0.04</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>46411</v>
-      </c>
-      <c r="I23" s="13" t="n">
-        <v>125</v>
+        <v>46417</v>
+      </c>
+      <c r="I23" s="14" t="n">
+        <v>124</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>46435</v>
+        <v>46433</v>
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
@@ -1459,45 +1474,45 @@
         </is>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0.03886124898121857</v>
+        <v>0.03436293486905094</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>1.78</v>
+        <v>0.579</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>1.71</v>
+        <v>0.584</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>0.04093567251461992</v>
+        <v>1.183219178082192</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>46417</v>
-      </c>
-      <c r="I24" s="13" t="n">
-        <v>131</v>
+        <v>46423</v>
+      </c>
+      <c r="I24" s="14" t="n">
+        <v>130</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>46433</v>
+        <v>46473</v>
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
@@ -1505,18 +1520,18 @@
         </is>
       </c>
       <c r="L24" s="9" t="n">
-        <v>0.03451117291578592</v>
+        <v>0.03028242544905738</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Semi-Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -1525,25 +1540,25 @@
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>0.579</v>
+        <v>0.61</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>0.584</v>
+        <v>0.58</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>1.183219178082192</v>
+        <v>0.05172413793103453</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>46423</v>
-      </c>
-      <c r="I25" s="13" t="n">
-        <v>137</v>
+        <v>46428</v>
+      </c>
+      <c r="I25" s="14" t="n">
+        <v>135</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>46473</v>
+        <v>46452</v>
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
@@ -1551,13 +1566,13 @@
         </is>
       </c>
       <c r="L25" s="9" t="n">
-        <v>0.02892830465433105</v>
+        <v>0.01661898840947346</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -1571,25 +1586,25 @@
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>0.61</v>
+        <v>1.3</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>0.58</v>
+        <v>1.27</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>0.05172413793103453</v>
+        <v>0.02362204724409451</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H26" s="10" t="n">
         <v>46428</v>
       </c>
-      <c r="I26" s="13" t="n">
-        <v>142</v>
+      <c r="I26" s="14" t="n">
+        <v>135</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>46452</v>
+        <v>46460</v>
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
@@ -1597,105 +1612,105 @@
         </is>
       </c>
       <c r="L26" s="9" t="n">
-        <v>0.01583901299359408</v>
+        <v>0.04955920751734383</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>TROW</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>HWC</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="D27" s="7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E27" s="7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="F27" s="8" t="n">
-        <v>0.02362204724409451</v>
-      </c>
-      <c r="G27" s="9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="H27" s="10" t="n">
-        <v>46428</v>
-      </c>
-      <c r="I27" s="13" t="n">
-        <v>142</v>
-      </c>
-      <c r="J27" s="10" t="n">
-        <v>46460</v>
-      </c>
-      <c r="K27" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L27" s="9" t="n">
-        <v>0.05013256280063842</v>
+      <c r="D27" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F27" s="18" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="G27" s="19" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H27" s="20" t="n">
+        <v>46429</v>
+      </c>
+      <c r="I27" s="21" t="n">
+        <v>136</v>
+      </c>
+      <c r="J27" s="20" t="n">
+        <v>46450</v>
+      </c>
+      <c r="K27" s="22" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="L27" s="19" t="n">
+        <v>0.02734481838515112</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="inlineStr">
-        <is>
-          <t>HWC</t>
-        </is>
-      </c>
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C28" s="15" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E28" s="16" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="F28" s="17" t="n">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="G28" s="18" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H28" s="19" t="n">
-        <v>46429</v>
-      </c>
-      <c r="I28" s="20" t="n">
-        <v>143</v>
-      </c>
-      <c r="J28" s="19" t="n">
-        <v>46450</v>
-      </c>
-      <c r="K28" s="21" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
-      <c r="L28" s="18" t="n">
-        <v>0.02664889964922068</v>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>CSCO</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>0.02439024390243905</v>
+      </c>
+      <c r="G28" s="9" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H28" s="10" t="n">
+        <v>46431</v>
+      </c>
+      <c r="I28" s="14" t="n">
+        <v>138</v>
+      </c>
+      <c r="J28" s="10" t="n">
+        <v>46480</v>
+      </c>
+      <c r="K28" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+      <c r="L28" s="9" t="n">
+        <v>0.01573991652591106</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>PEG</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -1705,29 +1720,29 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>0.42</v>
+        <v>0.67</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>0.41</v>
+        <v>0.63</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>0.02439024390243905</v>
+        <v>0.06349206349206354</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>0.04</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>46431</v>
-      </c>
-      <c r="I29" s="13" t="n">
-        <v>145</v>
+        <v>46432</v>
+      </c>
+      <c r="I29" s="14" t="n">
+        <v>139</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>46480</v>
+        <v>46455</v>
       </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
@@ -1735,13 +1750,13 @@
         </is>
       </c>
       <c r="L29" s="9" t="n">
-        <v>0.01533966445849374</v>
+        <v>0.04014379739729774</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -1751,29 +1766,29 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>0.67</v>
+        <v>2.138</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>0.63</v>
+        <v>1.883</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>0.06349206349206354</v>
+        <v>0.6872012745618694</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>46432</v>
-      </c>
-      <c r="I30" s="13" t="n">
-        <v>146</v>
+        <v>46433</v>
+      </c>
+      <c r="I30" s="14" t="n">
+        <v>140</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>46455</v>
+        <v>46425</v>
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
@@ -1781,13 +1796,13 @@
         </is>
       </c>
       <c r="L30" s="9" t="n">
-        <v>0.03862784817086413</v>
+        <v>0.004863235712254763</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -1797,29 +1812,29 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>2.138</v>
+        <v>1.3</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>1.883</v>
+        <v>1.25</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>0.6872012745618694</v>
+        <v>4.96</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="H31" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I31" s="13" t="n">
-        <v>147</v>
+      <c r="I31" s="14" t="n">
+        <v>140</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>46425</v>
+        <v>46383</v>
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
@@ -1827,13 +1842,13 @@
         </is>
       </c>
       <c r="L31" s="9" t="n">
-        <v>0.005078776879924646</v>
+        <v>0.01946180602749289</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -1843,17 +1858,17 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>1.3</v>
+        <v>0.32</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>1.25</v>
+        <v>0.24</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>4.96</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="G32" s="9" t="n">
         <v>0.06</v>
@@ -1861,11 +1876,11 @@
       <c r="H32" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I32" s="13" t="n">
-        <v>147</v>
+      <c r="I32" s="14" t="n">
+        <v>140</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>46383</v>
+        <v>46458</v>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
@@ -1873,13 +1888,13 @@
         </is>
       </c>
       <c r="L32" s="9" t="n">
-        <v>0.01892595187562783</v>
+        <v>0.02705845030636119</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -1889,29 +1904,29 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>0.32</v>
+        <v>0.84</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>0.24</v>
+        <v>0.82</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.02439024390243905</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H33" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I33" s="13" t="n">
-        <v>147</v>
+      <c r="I33" s="14" t="n">
+        <v>140</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>46458</v>
+        <v>46634</v>
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
@@ -1919,13 +1934,13 @@
         </is>
       </c>
       <c r="L33" s="9" t="n">
-        <v>0.02686253848921341</v>
+        <v>0.0289443082784107</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -1935,17 +1950,17 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>0.84</v>
+        <v>0.531</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>0.82</v>
+        <v>0.588964</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>0.02439024390243905</v>
+        <v>0.005735494868956323</v>
       </c>
       <c r="G34" s="9" t="n">
         <v>0.04</v>
@@ -1953,11 +1968,11 @@
       <c r="H34" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I34" s="13" t="n">
-        <v>147</v>
+      <c r="I34" s="14" t="n">
+        <v>140</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>46634</v>
+        <v>46608</v>
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
@@ -1965,13 +1980,13 @@
         </is>
       </c>
       <c r="L34" s="9" t="n">
-        <v>0.0286225403992658</v>
+        <v>0.03422494284562026</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -1981,29 +1996,29 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>0.531</v>
+        <v>0.29</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>0.588964</v>
+        <v>0.27</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>0.005735494868956323</v>
+        <v>0.07407407407407393</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="I35" s="13" t="n">
+        <v>46440</v>
+      </c>
+      <c r="I35" s="14" t="n">
         <v>147</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>46608</v>
+        <v>46450</v>
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
@@ -2011,13 +2026,13 @@
         </is>
       </c>
       <c r="L35" s="9" t="n">
-        <v>0.03425806451612903</v>
+        <v>0.01017633144783744</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -2031,25 +2046,25 @@
         </is>
       </c>
       <c r="D36" s="7" t="n">
-        <v>0.29</v>
+        <v>2.33</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>0.27</v>
+        <v>2.3</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>0.07407407407407393</v>
+        <v>0.01304347826086967</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>46440</v>
-      </c>
-      <c r="I36" s="13" t="n">
-        <v>154</v>
+        <v>46441</v>
+      </c>
+      <c r="I36" s="14" t="n">
+        <v>148</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>46450</v>
+        <v>46456</v>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
@@ -2057,13 +2072,13 @@
         </is>
       </c>
       <c r="L36" s="9" t="n">
-        <v>0.00978737793499475</v>
+        <v>0.03197583639308245</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -2073,29 +2088,29 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>2.33</v>
+        <v>1.59</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>0.01304347826086967</v>
+        <v>0.06000000000000005</v>
       </c>
       <c r="G37" s="9" t="n">
         <v>0.08</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>46441</v>
-      </c>
-      <c r="I37" s="13" t="n">
-        <v>155</v>
+        <v>46452</v>
+      </c>
+      <c r="I37" s="14" t="n">
+        <v>159</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>46456</v>
+        <v>46487</v>
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
@@ -2103,13 +2118,13 @@
         </is>
       </c>
       <c r="L37" s="9" t="n">
-        <v>0.03142279099194371</v>
+        <v>0.018949438093953</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -2119,29 +2134,29 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D38" s="7" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>0.06000000000000005</v>
+        <v>0.07142857142857149</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>46452</v>
-      </c>
-      <c r="I38" s="13" t="n">
-        <v>166</v>
+        <v>46461</v>
+      </c>
+      <c r="I38" s="14" t="n">
+        <v>168</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>46487</v>
+        <v>46665</v>
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
@@ -2149,7 +2164,7 @@
         </is>
       </c>
       <c r="L38" s="9" t="n">
-        <v>0.01805945923134389</v>
+        <v>0.01768920061562391</v>
       </c>
     </row>
     <row r="39">
@@ -2183,8 +2198,8 @@
       <c r="H39" s="10" t="n">
         <v>46461</v>
       </c>
-      <c r="I39" s="13" t="n">
-        <v>175</v>
+      <c r="I39" s="14" t="n">
+        <v>168</v>
       </c>
       <c r="J39" s="10" t="n">
         <v>46386</v>
@@ -2195,7 +2210,7 @@
         </is>
       </c>
       <c r="L39" s="9" t="n">
-        <v>0.05709770688176589</v>
+        <v>0.05867388443418352</v>
       </c>
     </row>
     <row r="40">
@@ -2229,8 +2244,8 @@
       <c r="H40" s="10" t="n">
         <v>46488</v>
       </c>
-      <c r="I40" s="13" t="n">
-        <v>202</v>
+      <c r="I40" s="14" t="n">
+        <v>195</v>
       </c>
       <c r="J40" s="10" t="n">
         <v>46498</v>
@@ -2241,7 +2256,7 @@
         </is>
       </c>
       <c r="L40" s="9" t="n">
-        <v>0.0298213170506069</v>
+        <v>0.02960948806953896</v>
       </c>
     </row>
     <row r="41">
@@ -2275,8 +2290,8 @@
       <c r="H41" s="10" t="n">
         <v>46492</v>
       </c>
-      <c r="I41" s="13" t="n">
-        <v>206</v>
+      <c r="I41" s="14" t="n">
+        <v>199</v>
       </c>
       <c r="J41" s="10" t="n">
         <v>46501</v>
@@ -2287,7 +2302,7 @@
         </is>
       </c>
       <c r="L41" s="9" t="n">
-        <v>0.02042298300259235</v>
+        <v>0.02055733268831431</v>
       </c>
     </row>
     <row r="42">
@@ -2321,8 +2336,8 @@
       <c r="H42" s="10" t="n">
         <v>46492</v>
       </c>
-      <c r="I42" s="13" t="n">
-        <v>206</v>
+      <c r="I42" s="14" t="n">
+        <v>199</v>
       </c>
       <c r="J42" s="10" t="n">
         <v>46376</v>
@@ -2333,7 +2348,7 @@
         </is>
       </c>
       <c r="L42" s="9" t="n">
-        <v>0.04302120257323579</v>
+        <v>0.04263981485045694</v>
       </c>
     </row>
     <row r="43">
@@ -2367,8 +2382,8 @@
       <c r="H43" s="10" t="n">
         <v>46493</v>
       </c>
-      <c r="I43" s="13" t="n">
-        <v>207</v>
+      <c r="I43" s="14" t="n">
+        <v>200</v>
       </c>
       <c r="J43" s="10" t="n">
         <v>46531</v>
@@ -2379,13 +2394,13 @@
         </is>
       </c>
       <c r="L43" s="9" t="n">
-        <v>0.01961789025712752</v>
+        <v>0.01969936444610691</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
@@ -2395,83 +2410,81 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D44" s="7" t="n">
-        <v>1.27</v>
+        <v>0.551</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>1.2</v>
+        <v>0.525</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>0.05833333333333339</v>
+        <v>0.04952380952380957</v>
       </c>
       <c r="G44" s="9" t="n">
         <v>0.04</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>46499</v>
-      </c>
-      <c r="I44" s="13" t="n">
-        <v>213</v>
+        <v>46504</v>
+      </c>
+      <c r="I44" s="14" t="n">
+        <v>211</v>
       </c>
       <c r="J44" s="10" t="n">
+        <v>46562</v>
+      </c>
+      <c r="K44" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+      <c r="L44" s="9" t="n">
+        <v>0.04796517874658265</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>PSX</t>
+        </is>
+      </c>
+      <c r="B45" s="16" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="D45" s="17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F45" s="18" t="n">
+        <v>0.05833333333333339</v>
+      </c>
+      <c r="G45" s="23" t="n"/>
+      <c r="H45" s="20" t="n">
+        <v>46505</v>
+      </c>
+      <c r="I45" s="21" t="n">
+        <v>212</v>
+      </c>
+      <c r="J45" s="20" t="n">
         <v>46526</v>
       </c>
-      <c r="K44" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L44" s="9" t="n">
-        <v>0.01878350811872483</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="n">
-        <v>0.551</v>
-      </c>
-      <c r="E45" s="7" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="F45" s="8" t="n">
-        <v>0.04952380952380957</v>
-      </c>
-      <c r="G45" s="9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H45" s="10" t="n">
-        <v>46504</v>
-      </c>
-      <c r="I45" s="13" t="n">
-        <v>218</v>
-      </c>
-      <c r="J45" s="10" t="n">
-        <v>46562</v>
-      </c>
-      <c r="K45" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L45" s="9" t="n">
-        <v>0.04648317953059956</v>
+      <c r="K45" s="22" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="L45" s="19" t="n">
+        <v>0.01969831987068282</v>
       </c>
     </row>
     <row r="46">
@@ -2505,8 +2518,8 @@
       <c r="H46" s="10" t="n">
         <v>46508</v>
       </c>
-      <c r="I46" s="13" t="n">
-        <v>222</v>
+      <c r="I46" s="14" t="n">
+        <v>215</v>
       </c>
       <c r="J46" s="10" t="n">
         <v>46518</v>
@@ -2517,7 +2530,7 @@
         </is>
       </c>
       <c r="L46" s="9" t="n">
-        <v>0.04153940267145332</v>
+        <v>0.04749076963560451</v>
       </c>
     </row>
     <row r="47">
@@ -2551,8 +2564,8 @@
       <c r="H47" s="10" t="n">
         <v>46515</v>
       </c>
-      <c r="I47" s="13" t="n">
-        <v>229</v>
+      <c r="I47" s="14" t="n">
+        <v>222</v>
       </c>
       <c r="J47" s="10" t="n">
         <v>46542</v>
@@ -2563,7 +2576,7 @@
         </is>
       </c>
       <c r="L47" s="9" t="n">
-        <v>0.04612387782222198</v>
+        <v>0.04644933337595475</v>
       </c>
     </row>
     <row r="48">
@@ -2597,8 +2610,8 @@
       <c r="H48" s="10" t="n">
         <v>46532</v>
       </c>
-      <c r="I48" s="13" t="n">
-        <v>246</v>
+      <c r="I48" s="14" t="n">
+        <v>239</v>
       </c>
       <c r="J48" s="10" t="n">
         <v>46563</v>
@@ -2609,7 +2622,7 @@
         </is>
       </c>
       <c r="L48" s="9" t="n">
-        <v>0.03129414362926066</v>
+        <v>0.03276637021439819</v>
       </c>
     </row>
     <row r="49">
@@ -2643,8 +2656,8 @@
       <c r="H49" s="10" t="n">
         <v>46589</v>
       </c>
-      <c r="I49" s="13" t="n">
-        <v>303</v>
+      <c r="I49" s="14" t="n">
+        <v>296</v>
       </c>
       <c r="J49" s="10" t="n">
         <v>46629</v>
@@ -2655,7 +2668,7 @@
         </is>
       </c>
       <c r="L49" s="9" t="n">
-        <v>0.02079215225231083</v>
+        <v>0.02066506695303406</v>
       </c>
     </row>
     <row r="50">
@@ -2689,8 +2702,8 @@
       <c r="H50" s="10" t="n">
         <v>46591</v>
       </c>
-      <c r="I50" s="13" t="n">
-        <v>305</v>
+      <c r="I50" s="14" t="n">
+        <v>298</v>
       </c>
       <c r="J50" s="10" t="n">
         <v>46633</v>
@@ -2701,7 +2714,7 @@
         </is>
       </c>
       <c r="L50" s="9" t="n">
-        <v>0.03791041525582833</v>
+        <v>0.03726707923163132</v>
       </c>
     </row>
     <row r="51">
@@ -2735,8 +2748,8 @@
       <c r="H51" s="10" t="n">
         <v>46594</v>
       </c>
-      <c r="I51" s="13" t="n">
-        <v>308</v>
+      <c r="I51" s="14" t="n">
+        <v>301</v>
       </c>
       <c r="J51" s="10" t="n">
         <v>46613</v>
@@ -2747,7 +2760,7 @@
         </is>
       </c>
       <c r="L51" s="9" t="n">
-        <v>0.01592201481961874</v>
+        <v>0.01576354660457816</v>
       </c>
     </row>
     <row r="52">
@@ -2781,8 +2794,8 @@
       <c r="H52" s="10" t="n">
         <v>46595</v>
       </c>
-      <c r="I52" s="13" t="n">
-        <v>309</v>
+      <c r="I52" s="14" t="n">
+        <v>302</v>
       </c>
       <c r="J52" s="10" t="n">
         <v>46614</v>
@@ -2793,7 +2806,7 @@
         </is>
       </c>
       <c r="L52" s="9" t="n">
-        <v>0.02551849066264972</v>
+        <v>0.0264903876291373</v>
       </c>
     </row>
     <row r="53">
@@ -2827,8 +2840,8 @@
       <c r="H53" s="10" t="n">
         <v>46597</v>
       </c>
-      <c r="I53" s="13" t="n">
-        <v>311</v>
+      <c r="I53" s="14" t="n">
+        <v>304</v>
       </c>
       <c r="J53" s="10" t="n">
         <v>46611</v>
@@ -2839,7 +2852,7 @@
         </is>
       </c>
       <c r="L53" s="9" t="n">
-        <v>0.06040099158048739</v>
+        <v>0.06110975334452722</v>
       </c>
     </row>
     <row r="54">
@@ -2873,8 +2886,8 @@
       <c r="H54" s="10" t="n">
         <v>46598</v>
       </c>
-      <c r="I54" s="13" t="n">
-        <v>312</v>
+      <c r="I54" s="14" t="n">
+        <v>305</v>
       </c>
       <c r="J54" s="10" t="n">
         <v>46629</v>
@@ -2885,7 +2898,7 @@
         </is>
       </c>
       <c r="L54" s="9" t="n">
-        <v>0.0258234356907714</v>
+        <v>0.02627132204797521</v>
       </c>
     </row>
     <row r="55">
@@ -2919,8 +2932,8 @@
       <c r="H55" s="10" t="n">
         <v>46628</v>
       </c>
-      <c r="I55" s="13" t="n">
-        <v>342</v>
+      <c r="I55" s="14" t="n">
+        <v>335</v>
       </c>
       <c r="J55" s="10" t="n">
         <v>46662</v>
@@ -2931,7 +2944,7 @@
         </is>
       </c>
       <c r="L55" s="9" t="n">
-        <v>0.03369112923733877</v>
+        <v>0.03395269278011557</v>
       </c>
     </row>
     <row r="56">
@@ -2965,8 +2978,8 @@
       <c r="H56" s="10" t="n">
         <v>46643</v>
       </c>
-      <c r="I56" s="13" t="n">
-        <v>357</v>
+      <c r="I56" s="14" t="n">
+        <v>350</v>
       </c>
       <c r="J56" s="10" t="n">
         <v>46709</v>
@@ -2977,7 +2990,7 @@
         </is>
       </c>
       <c r="L56" s="9" t="n">
-        <v>0.007345385769172313</v>
+        <v>0.007144434529232485</v>
       </c>
     </row>
     <row r="57">
@@ -3011,8 +3024,8 @@
       <c r="H57" s="10" t="n">
         <v>46645</v>
       </c>
-      <c r="I57" s="13" t="n">
-        <v>359</v>
+      <c r="I57" s="14" t="n">
+        <v>352</v>
       </c>
       <c r="J57" s="10" t="n">
         <v>46668</v>
@@ -3023,7 +3036,7 @@
         </is>
       </c>
       <c r="L57" s="9" t="n">
-        <v>0.05928406893158691</v>
+        <v>0.06022328353230328</v>
       </c>
     </row>
     <row r="58">
@@ -3057,8 +3070,8 @@
       <c r="H58" s="10" t="n">
         <v>46650</v>
       </c>
-      <c r="I58" s="13" t="n">
-        <v>364</v>
+      <c r="I58" s="14" t="n">
+        <v>357</v>
       </c>
       <c r="J58" s="10" t="n">
         <v>46690</v>
@@ -3069,7 +3082,7 @@
         </is>
       </c>
       <c r="L58" s="9" t="n">
-        <v>0.02139359698681732</v>
+        <v>0.0205462099807986</v>
       </c>
     </row>
   </sheetData>
@@ -3083,7 +3096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F94"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3104,44 +3117,44 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Expected Increase Announcements by Month - 09/21/2026</t>
+          <t>Expected Increase Announcements by Month - 09/28/2026</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>January 2026</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F5" s="23" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3172,39 +3185,39 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="inlineStr">
-        <is>
-          <t>September 2026</t>
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>October 2026</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="25" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F9" s="25" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3213,20 +3226,20 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>46284</v>
+        <v>46305</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>46665</v>
+        <v>46339</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>1.5</v>
+        <v>0.87</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>0.07142857142857149</v>
+        <v>0.0235294117647059</v>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
@@ -3234,134 +3247,134 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>LECO</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>46386</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>0.05333333333333338</v>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
-      <c r="A12" s="22" t="inlineStr">
-        <is>
-          <t>October 2026</t>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>HII</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n">
+        <v>46318</v>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v>46352</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>0.02222222222222208</v>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="23" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>ETR</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>46338</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>0.06666666666666674</v>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>November 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C16" s="25" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D16" s="25" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E16" s="25" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F13" s="23" t="inlineStr">
+      <c r="F16" s="25" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>MSM</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="n">
-        <v>46305</v>
-      </c>
-      <c r="C14" s="10" t="n">
-        <v>46339</v>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>0.0235294117647059</v>
-      </c>
-      <c r="F14" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>LECO</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="n">
-        <v>46311</v>
-      </c>
-      <c r="C15" s="10" t="n">
-        <v>46386</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>0.05333333333333338</v>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>HII</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="n">
-        <v>46318</v>
-      </c>
-      <c r="C16" s="10" t="n">
-        <v>46352</v>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>0.02222222222222208</v>
-      </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B17" s="10" t="n">
-        <v>46322</v>
+        <v>46329</v>
       </c>
       <c r="C17" s="10" t="n">
         <v>46338</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>0.06666666666666674</v>
+        <v>0.09090909090909079</v>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
@@ -3369,62 +3382,95 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>SNA</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n">
+        <v>46332</v>
+      </c>
+      <c r="C18" s="10" t="n">
+        <v>46346</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>0.1401869158878504</v>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="19">
-      <c r="A19" s="22" t="inlineStr">
-        <is>
-          <t>November 2026</t>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n">
+        <v>46341</v>
+      </c>
+      <c r="C19" s="10" t="n">
+        <v>46340</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>0.04040404040404044</v>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="23" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B20" s="23" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C20" s="23" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D20" s="23" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E20" s="23" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F20" s="23" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>MKC</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="n">
+        <v>46344</v>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>46385</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>0.0666666666666666</v>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B21" s="10" t="n">
-        <v>46329</v>
+        <v>46347</v>
       </c>
       <c r="C21" s="10" t="n">
-        <v>46338</v>
+        <v>46358</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.6</v>
+        <v>0.41</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>0.09090909090909079</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
@@ -3435,20 +3481,20 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="B22" s="10" t="n">
-        <v>46332</v>
+        <v>46352</v>
       </c>
       <c r="C22" s="10" t="n">
-        <v>46346</v>
+        <v>46400</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>2.44</v>
+        <v>0.293</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>0.1401869158878504</v>
+        <v>0.01034482758620691</v>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
@@ -3456,95 +3502,62 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="n">
-        <v>46341</v>
-      </c>
-      <c r="C23" s="10" t="n">
-        <v>46340</v>
-      </c>
-      <c r="D23" s="7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E23" s="8" t="n">
-        <v>0.04040404040404044</v>
-      </c>
-      <c r="F23" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>MKC</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="n">
-        <v>46344</v>
-      </c>
-      <c r="C24" s="10" t="n">
-        <v>46385</v>
-      </c>
-      <c r="D24" s="7" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E24" s="8" t="n">
-        <v>0.0666666666666666</v>
-      </c>
-      <c r="F24" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>December 2026</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>NKE</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="n">
-        <v>46347</v>
-      </c>
-      <c r="C25" s="10" t="n">
-        <v>46358</v>
-      </c>
-      <c r="D25" s="7" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E25" s="8" t="n">
-        <v>0.02499999999999988</v>
-      </c>
-      <c r="F25" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C25" s="25" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D25" s="25" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E25" s="25" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F25" s="25" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>EMN</t>
         </is>
       </c>
       <c r="B26" s="10" t="n">
-        <v>46352</v>
+        <v>46360</v>
       </c>
       <c r="C26" s="10" t="n">
-        <v>46400</v>
+        <v>46371</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>0.293</v>
+        <v>0.84</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>0.01034482758620691</v>
+        <v>0.01204819277108435</v>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
@@ -3552,245 +3565,245 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>AMGN</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="n">
+        <v>46366</v>
+      </c>
+      <c r="C27" s="10" t="n">
+        <v>46432</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>0.05882352941176476</v>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="28">
-      <c r="A28" s="22" t="inlineStr">
-        <is>
-          <t>December 2026</t>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>CNP</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="n">
+        <v>46380</v>
+      </c>
+      <c r="C28" s="10" t="n">
+        <v>46436</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>0.04347826086956513</v>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="23" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>GGG</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="n">
+        <v>46383</v>
+      </c>
+      <c r="C29" s="20" t="n">
+        <v>46404</v>
+      </c>
+      <c r="D29" s="17" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="E29" s="18" t="n">
+        <v>0.07272727272727258</v>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>January 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="25" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B29" s="23" t="inlineStr">
+      <c r="B32" s="25" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C29" s="23" t="inlineStr">
+      <c r="C32" s="25" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D29" s="23" t="inlineStr">
+      <c r="D32" s="25" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E29" s="23" t="inlineStr">
+      <c r="E32" s="25" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F29" s="23" t="inlineStr">
+      <c r="F32" s="25" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>EMN</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="n">
-        <v>46360</v>
-      </c>
-      <c r="C30" s="10" t="n">
-        <v>46371</v>
-      </c>
-      <c r="D30" s="7" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E30" s="8" t="n">
-        <v>0.01204819277108435</v>
-      </c>
-      <c r="F30" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>AMGN</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="n">
-        <v>46366</v>
-      </c>
-      <c r="C31" s="10" t="n">
-        <v>46432</v>
-      </c>
-      <c r="D31" s="7" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="E31" s="8" t="n">
-        <v>0.05882352941176476</v>
-      </c>
-      <c r="F31" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>CNP</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="n">
-        <v>46380</v>
-      </c>
-      <c r="C32" s="10" t="n">
-        <v>46436</v>
-      </c>
-      <c r="D32" s="7" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>0.04347826086956513</v>
-      </c>
-      <c r="F32" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
     <row r="33">
-      <c r="A33" s="14" t="inlineStr">
-        <is>
-          <t>GGG</t>
-        </is>
-      </c>
-      <c r="B33" s="19" t="n">
-        <v>46383</v>
-      </c>
-      <c r="C33" s="19" t="n">
-        <v>46404</v>
-      </c>
-      <c r="D33" s="16" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E33" s="17" t="n">
-        <v>0.07272727272727258</v>
-      </c>
-      <c r="F33" s="21" t="inlineStr">
-        <is>
-          <t>yfinance</t>
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="n">
+        <v>46402</v>
+      </c>
+      <c r="C33" s="10" t="n">
+        <v>46483</v>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>0.07499999999999993</v>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>BKH</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="n">
+        <v>46411</v>
+      </c>
+      <c r="C34" s="10" t="n">
+        <v>46435</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>0.03994082840236673</v>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="22" t="inlineStr">
-        <is>
-          <t>January 2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="23" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>CVX</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="n">
+        <v>46417</v>
+      </c>
+      <c r="C35" s="10" t="n">
+        <v>46433</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>0.04093567251461992</v>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>February 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="25" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B36" s="23" t="inlineStr">
+      <c r="B38" s="25" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C36" s="23" t="inlineStr">
+      <c r="C38" s="25" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D36" s="23" t="inlineStr">
+      <c r="D38" s="25" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E36" s="23" t="inlineStr">
+      <c r="E38" s="25" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F36" s="23" t="inlineStr">
+      <c r="F38" s="25" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>DGX</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="n">
-        <v>46402</v>
-      </c>
-      <c r="C37" s="10" t="n">
-        <v>46483</v>
-      </c>
-      <c r="D37" s="7" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="E37" s="8" t="n">
-        <v>0.07499999999999993</v>
-      </c>
-      <c r="F37" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>BKH</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="n">
-        <v>46411</v>
-      </c>
-      <c r="C38" s="10" t="n">
-        <v>46435</v>
-      </c>
-      <c r="D38" s="7" t="n">
-        <v>0.703</v>
-      </c>
-      <c r="E38" s="8" t="n">
-        <v>0.03994082840236673</v>
-      </c>
-      <c r="F38" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B39" s="10" t="n">
-        <v>46417</v>
+        <v>46423</v>
       </c>
       <c r="C39" s="10" t="n">
-        <v>46433</v>
+        <v>46473</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>1.78</v>
+        <v>0.579</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>0.04093567251461992</v>
+        <v>1.183219178082192</v>
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
@@ -3798,62 +3811,95 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>JKHY</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="n">
+        <v>46428</v>
+      </c>
+      <c r="C40" s="10" t="n">
+        <v>46452</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>0.05172413793103453</v>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="41">
-      <c r="A41" s="22" t="inlineStr">
-        <is>
-          <t>February 2027</t>
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>TROW</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="n">
+        <v>46428</v>
+      </c>
+      <c r="C41" s="10" t="n">
+        <v>46460</v>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>0.02362204724409451</v>
+      </c>
+      <c r="F41" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="23" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B42" s="23" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C42" s="23" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D42" s="23" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E42" s="23" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F42" s="23" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>HWC</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="n">
+        <v>46429</v>
+      </c>
+      <c r="C42" s="20" t="n">
+        <v>46450</v>
+      </c>
+      <c r="D42" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E42" s="18" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="F42" s="22" t="inlineStr">
+        <is>
+          <t>yfinance</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B43" s="10" t="n">
-        <v>46423</v>
+        <v>46431</v>
       </c>
       <c r="C43" s="10" t="n">
-        <v>46473</v>
+        <v>46480</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>0.579</v>
+        <v>0.42</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>1.183219178082192</v>
+        <v>0.02439024390243905</v>
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
@@ -3864,20 +3910,20 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>PEG</t>
         </is>
       </c>
       <c r="B44" s="10" t="n">
-        <v>46428</v>
+        <v>46432</v>
       </c>
       <c r="C44" s="10" t="n">
-        <v>46452</v>
+        <v>46455</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="E44" s="8" t="n">
-        <v>0.05172413793103453</v>
+        <v>0.06349206349206354</v>
       </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
@@ -3888,68 +3934,68 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B45" s="10" t="n">
-        <v>46428</v>
+        <v>46433</v>
       </c>
       <c r="C45" s="10" t="n">
-        <v>46460</v>
+        <v>46425</v>
       </c>
       <c r="D45" s="7" t="n">
+        <v>2.138</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>0.6872012745618694</v>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>CME</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="n">
+        <v>46433</v>
+      </c>
+      <c r="C46" s="10" t="n">
+        <v>46383</v>
+      </c>
+      <c r="D46" s="7" t="n">
         <v>1.3</v>
       </c>
-      <c r="E45" s="8" t="n">
-        <v>0.02362204724409451</v>
-      </c>
-      <c r="F45" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="14" t="inlineStr">
-        <is>
-          <t>HWC</t>
-        </is>
-      </c>
-      <c r="B46" s="19" t="n">
-        <v>46429</v>
-      </c>
-      <c r="C46" s="19" t="n">
-        <v>46450</v>
-      </c>
-      <c r="D46" s="16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E46" s="17" t="n">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="F46" s="21" t="inlineStr">
-        <is>
-          <t>yfinance</t>
+      <c r="E46" s="8" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="F46" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B47" s="10" t="n">
-        <v>46431</v>
+        <v>46433</v>
       </c>
       <c r="C47" s="10" t="n">
-        <v>46480</v>
+        <v>46458</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>0.42</v>
+        <v>0.32</v>
       </c>
       <c r="E47" s="8" t="n">
-        <v>0.02439024390243905</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
@@ -3960,20 +4006,20 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B48" s="10" t="n">
-        <v>46432</v>
+        <v>46433</v>
       </c>
       <c r="C48" s="10" t="n">
-        <v>46455</v>
+        <v>46634</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>0.67</v>
+        <v>0.84</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>0.06349206349206354</v>
+        <v>0.02439024390243905</v>
       </c>
       <c r="F48" s="12" t="inlineStr">
         <is>
@@ -3984,20 +4030,20 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B49" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C49" s="10" t="n">
-        <v>46425</v>
+        <v>46608</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>2.138</v>
+        <v>0.531</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>0.6872012745618694</v>
+        <v>0.005735494868956323</v>
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
@@ -4008,20 +4054,20 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="B50" s="10" t="n">
-        <v>46433</v>
+        <v>46440</v>
       </c>
       <c r="C50" s="10" t="n">
-        <v>46383</v>
+        <v>46450</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>1.3</v>
+        <v>0.29</v>
       </c>
       <c r="E50" s="8" t="n">
-        <v>4.96</v>
+        <v>0.07407407407407393</v>
       </c>
       <c r="F50" s="12" t="inlineStr">
         <is>
@@ -4032,20 +4078,20 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B51" s="10" t="n">
-        <v>46433</v>
+        <v>46441</v>
       </c>
       <c r="C51" s="10" t="n">
-        <v>46458</v>
+        <v>46456</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>0.32</v>
+        <v>2.33</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.01304347826086967</v>
       </c>
       <c r="F51" s="12" t="inlineStr">
         <is>
@@ -4053,95 +4099,62 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>PFG</t>
-        </is>
-      </c>
-      <c r="B52" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="C52" s="10" t="n">
-        <v>46634</v>
-      </c>
-      <c r="D52" s="7" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E52" s="8" t="n">
-        <v>0.02439024390243905</v>
-      </c>
-      <c r="F52" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>UL</t>
-        </is>
-      </c>
-      <c r="B53" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="C53" s="10" t="n">
-        <v>46608</v>
-      </c>
-      <c r="D53" s="7" t="n">
-        <v>0.531</v>
-      </c>
-      <c r="E53" s="8" t="n">
-        <v>0.005735494868956323</v>
-      </c>
-      <c r="F53" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A53" s="24" t="inlineStr">
+        <is>
+          <t>March 2027</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>ALSN</t>
-        </is>
-      </c>
-      <c r="B54" s="10" t="n">
-        <v>46440</v>
-      </c>
-      <c r="C54" s="10" t="n">
-        <v>46450</v>
-      </c>
-      <c r="D54" s="7" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E54" s="8" t="n">
-        <v>0.07407407407407393</v>
-      </c>
-      <c r="F54" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A54" s="25" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B54" s="25" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C54" s="25" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D54" s="25" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E54" s="25" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F54" s="25" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="B55" s="10" t="n">
-        <v>46441</v>
+        <v>46452</v>
       </c>
       <c r="C55" s="10" t="n">
-        <v>46456</v>
+        <v>46487</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>2.33</v>
+        <v>1.59</v>
       </c>
       <c r="E55" s="8" t="n">
-        <v>0.01304347826086967</v>
+        <v>0.06000000000000005</v>
       </c>
       <c r="F55" s="12" t="inlineStr">
         <is>
@@ -4149,149 +4162,182 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="n">
+        <v>46461</v>
+      </c>
+      <c r="C56" s="10" t="n">
+        <v>46665</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E56" s="8" t="n">
+        <v>0.07142857142857149</v>
+      </c>
+      <c r="F56" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="57">
-      <c r="A57" s="22" t="inlineStr">
-        <is>
-          <t>March 2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="23" t="inlineStr">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="n">
+        <v>46461</v>
+      </c>
+      <c r="C57" s="10" t="n">
+        <v>46386</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="E57" s="8" t="n">
+        <v>0.003703703703703707</v>
+      </c>
+      <c r="F57" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="24" t="inlineStr">
+        <is>
+          <t>April 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="25" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B58" s="23" t="inlineStr">
+      <c r="B60" s="25" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C58" s="23" t="inlineStr">
+      <c r="C60" s="25" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D58" s="23" t="inlineStr">
+      <c r="D60" s="25" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E58" s="23" t="inlineStr">
+      <c r="E60" s="25" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F58" s="23" t="inlineStr">
+      <c r="F60" s="25" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>GD</t>
-        </is>
-      </c>
-      <c r="B59" s="10" t="n">
-        <v>46452</v>
-      </c>
-      <c r="C59" s="10" t="n">
-        <v>46487</v>
-      </c>
-      <c r="D59" s="7" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="E59" s="8" t="n">
-        <v>0.06000000000000005</v>
-      </c>
-      <c r="F59" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B60" s="10" t="n">
-        <v>46461</v>
-      </c>
-      <c r="C60" s="10" t="n">
-        <v>46386</v>
-      </c>
-      <c r="D60" s="7" t="n">
-        <v>0.271</v>
-      </c>
-      <c r="E60" s="8" t="n">
-        <v>0.003703703703703707</v>
-      </c>
-      <c r="F60" s="12" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="n">
+        <v>46488</v>
+      </c>
+      <c r="C61" s="10" t="n">
+        <v>46498</v>
+      </c>
+      <c r="D61" s="7" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>0.03027436140018924</v>
+      </c>
+      <c r="F61" s="12" t="inlineStr">
         <is>
           <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="22" t="inlineStr">
-        <is>
-          <t>April 2027</t>
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>KOF</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="n">
+        <v>46492</v>
+      </c>
+      <c r="C62" s="10" t="n">
+        <v>46501</v>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="E62" s="8" t="n">
+        <v>0.03495860165593379</v>
+      </c>
+      <c r="F62" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="23" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B63" s="23" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C63" s="23" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D63" s="23" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E63" s="23" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F63" s="23" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>TTE</t>
+        </is>
+      </c>
+      <c r="B63" s="10" t="n">
+        <v>46492</v>
+      </c>
+      <c r="C63" s="10" t="n">
+        <v>46376</v>
+      </c>
+      <c r="D63" s="7" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="E63" s="8" t="n">
+        <v>0.001006036217303824</v>
+      </c>
+      <c r="F63" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B64" s="10" t="n">
-        <v>46488</v>
+        <v>46493</v>
       </c>
       <c r="C64" s="10" t="n">
-        <v>46498</v>
+        <v>46531</v>
       </c>
       <c r="D64" s="7" t="n">
-        <v>1.089</v>
+        <v>1.34</v>
       </c>
       <c r="E64" s="8" t="n">
-        <v>0.03027436140018924</v>
+        <v>0.0307692307692308</v>
       </c>
       <c r="F64" s="12" t="inlineStr">
         <is>
@@ -4302,20 +4348,20 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B65" s="10" t="n">
-        <v>46492</v>
+        <v>46504</v>
       </c>
       <c r="C65" s="10" t="n">
-        <v>46501</v>
+        <v>46562</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>1.125</v>
+        <v>0.551</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>0.03495860165593379</v>
+        <v>0.04952380952380957</v>
       </c>
       <c r="F65" s="12" t="inlineStr">
         <is>
@@ -4324,268 +4370,268 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>TTE</t>
-        </is>
-      </c>
-      <c r="B66" s="10" t="n">
-        <v>46492</v>
-      </c>
-      <c r="C66" s="10" t="n">
-        <v>46376</v>
-      </c>
-      <c r="D66" s="7" t="n">
-        <v>0.974</v>
-      </c>
-      <c r="E66" s="8" t="n">
-        <v>0.001006036217303824</v>
-      </c>
-      <c r="F66" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>JNJ</t>
-        </is>
-      </c>
-      <c r="B67" s="10" t="n">
-        <v>46493</v>
-      </c>
-      <c r="C67" s="10" t="n">
-        <v>46531</v>
-      </c>
-      <c r="D67" s="7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="E67" s="8" t="n">
-        <v>0.0307692307692308</v>
-      </c>
-      <c r="F67" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A66" s="15" t="inlineStr">
+        <is>
+          <t>PSX</t>
+        </is>
+      </c>
+      <c r="B66" s="20" t="n">
+        <v>46505</v>
+      </c>
+      <c r="C66" s="20" t="n">
+        <v>46526</v>
+      </c>
+      <c r="D66" s="17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E66" s="18" t="n">
+        <v>0.05833333333333339</v>
+      </c>
+      <c r="F66" s="22" t="inlineStr">
+        <is>
+          <t>yfinance</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>PSX</t>
-        </is>
-      </c>
-      <c r="B68" s="10" t="n">
-        <v>46499</v>
-      </c>
-      <c r="C68" s="10" t="n">
-        <v>46526</v>
-      </c>
-      <c r="D68" s="7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E68" s="8" t="n">
-        <v>0.05833333333333339</v>
-      </c>
-      <c r="F68" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A68" s="24" t="inlineStr">
+        <is>
+          <t>May 2027</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
-      </c>
-      <c r="B69" s="10" t="n">
-        <v>46504</v>
-      </c>
-      <c r="C69" s="10" t="n">
-        <v>46562</v>
-      </c>
-      <c r="D69" s="7" t="n">
-        <v>0.551</v>
-      </c>
-      <c r="E69" s="8" t="n">
-        <v>0.04952380952380957</v>
-      </c>
-      <c r="F69" s="12" t="inlineStr">
+      <c r="A69" s="25" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B69" s="25" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C69" s="25" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D69" s="25" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E69" s="25" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F69" s="25" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>PAYX</t>
+        </is>
+      </c>
+      <c r="B70" s="10" t="n">
+        <v>46508</v>
+      </c>
+      <c r="C70" s="10" t="n">
+        <v>46518</v>
+      </c>
+      <c r="D70" s="7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E70" s="8" t="n">
+        <v>0.1018518518518517</v>
+      </c>
+      <c r="F70" s="12" t="inlineStr">
         <is>
           <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="22" t="inlineStr">
-        <is>
-          <t>May 2027</t>
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="B71" s="10" t="n">
+        <v>46515</v>
+      </c>
+      <c r="C71" s="10" t="n">
+        <v>46542</v>
+      </c>
+      <c r="D71" s="7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="E71" s="8" t="n">
+        <v>0.04005621925509482</v>
+      </c>
+      <c r="F71" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="23" t="inlineStr">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>MDT</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="n">
+        <v>46532</v>
+      </c>
+      <c r="C72" s="10" t="n">
+        <v>46563</v>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E72" s="8" t="n">
+        <v>0.01408450704225353</v>
+      </c>
+      <c r="F72" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="24" t="inlineStr">
+        <is>
+          <t>July 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="25" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B72" s="23" t="inlineStr">
+      <c r="B75" s="25" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C72" s="23" t="inlineStr">
+      <c r="C75" s="25" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D72" s="23" t="inlineStr">
+      <c r="D75" s="25" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E72" s="23" t="inlineStr">
+      <c r="E75" s="25" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F72" s="23" t="inlineStr">
+      <c r="F75" s="25" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>PAYX</t>
-        </is>
-      </c>
-      <c r="B73" s="10" t="n">
-        <v>46508</v>
-      </c>
-      <c r="C73" s="10" t="n">
-        <v>46518</v>
-      </c>
-      <c r="D73" s="7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E73" s="8" t="n">
-        <v>0.1018518518518517</v>
-      </c>
-      <c r="F73" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>PEP</t>
-        </is>
-      </c>
-      <c r="B74" s="10" t="n">
-        <v>46515</v>
-      </c>
-      <c r="C74" s="10" t="n">
-        <v>46542</v>
-      </c>
-      <c r="D74" s="7" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="E74" s="8" t="n">
-        <v>0.04005621925509482</v>
-      </c>
-      <c r="F74" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>MDT</t>
-        </is>
-      </c>
-      <c r="B75" s="10" t="n">
-        <v>46532</v>
-      </c>
-      <c r="C75" s="10" t="n">
-        <v>46563</v>
-      </c>
-      <c r="D75" s="7" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E75" s="8" t="n">
-        <v>0.01408450704225353</v>
-      </c>
-      <c r="F75" s="12" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>UNP</t>
+        </is>
+      </c>
+      <c r="B76" s="10" t="n">
+        <v>46589</v>
+      </c>
+      <c r="C76" s="10" t="n">
+        <v>46629</v>
+      </c>
+      <c r="D76" s="7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="E76" s="8" t="n">
+        <v>0.02898550724637684</v>
+      </c>
+      <c r="F76" s="12" t="inlineStr">
         <is>
           <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="22" t="inlineStr">
-        <is>
-          <t>July 2027</t>
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>SWK</t>
+        </is>
+      </c>
+      <c r="B77" s="10" t="n">
+        <v>46591</v>
+      </c>
+      <c r="C77" s="10" t="n">
+        <v>46633</v>
+      </c>
+      <c r="D77" s="7" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E77" s="8" t="n">
+        <v>0.01204819277108435</v>
+      </c>
+      <c r="F77" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="23" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B78" s="23" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C78" s="23" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D78" s="23" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E78" s="23" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F78" s="23" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>RGA</t>
+        </is>
+      </c>
+      <c r="B78" s="10" t="n">
+        <v>46594</v>
+      </c>
+      <c r="C78" s="10" t="n">
+        <v>46613</v>
+      </c>
+      <c r="D78" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="E78" s="8" t="n">
+        <v>0.05376344086021498</v>
+      </c>
+      <c r="F78" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>AWR</t>
         </is>
       </c>
       <c r="B79" s="10" t="n">
-        <v>46589</v>
+        <v>46595</v>
       </c>
       <c r="C79" s="10" t="n">
-        <v>46629</v>
+        <v>46614</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>1.42</v>
+        <v>0.546</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>0.02898550724637684</v>
+        <v>0.08333333333333341</v>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
@@ -4596,20 +4642,20 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="B80" s="10" t="n">
-        <v>46591</v>
+        <v>46597</v>
       </c>
       <c r="C80" s="10" t="n">
-        <v>46633</v>
+        <v>46611</v>
       </c>
       <c r="D80" s="7" t="n">
-        <v>0.84</v>
+        <v>1.25</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>0.01204819277108435</v>
+        <v>0.008064516129032265</v>
       </c>
       <c r="F80" s="12" t="inlineStr">
         <is>
@@ -4620,20 +4666,20 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>CFR</t>
         </is>
       </c>
       <c r="B81" s="10" t="n">
-        <v>46594</v>
+        <v>46598</v>
       </c>
       <c r="C81" s="10" t="n">
-        <v>46613</v>
+        <v>46629</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>0.98</v>
+        <v>1.03</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>0.05376344086021498</v>
+        <v>0.03000000000000003</v>
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
@@ -4641,247 +4687,175 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>AWR</t>
-        </is>
-      </c>
-      <c r="B82" s="10" t="n">
-        <v>46595</v>
-      </c>
-      <c r="C82" s="10" t="n">
-        <v>46614</v>
-      </c>
-      <c r="D82" s="7" t="n">
-        <v>0.546</v>
-      </c>
-      <c r="E82" s="8" t="n">
-        <v>0.08333333333333341</v>
-      </c>
-      <c r="F82" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
     <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>CLX</t>
-        </is>
-      </c>
-      <c r="B83" s="10" t="n">
-        <v>46597</v>
-      </c>
-      <c r="C83" s="10" t="n">
-        <v>46611</v>
-      </c>
-      <c r="D83" s="7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E83" s="8" t="n">
-        <v>0.008064516129032265</v>
-      </c>
-      <c r="F83" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A83" s="24" t="inlineStr">
+        <is>
+          <t>August 2027</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>CFR</t>
-        </is>
-      </c>
-      <c r="B84" s="10" t="n">
-        <v>46598</v>
-      </c>
-      <c r="C84" s="10" t="n">
-        <v>46629</v>
-      </c>
-      <c r="D84" s="7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E84" s="8" t="n">
-        <v>0.03000000000000003</v>
-      </c>
-      <c r="F84" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="22" t="inlineStr">
-        <is>
-          <t>August 2027</t>
+      <c r="A84" s="25" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B84" s="25" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C84" s="25" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D84" s="25" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E84" s="25" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F84" s="25" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>INGR</t>
+        </is>
+      </c>
+      <c r="B85" s="10" t="n">
+        <v>46628</v>
+      </c>
+      <c r="C85" s="10" t="n">
+        <v>46662</v>
+      </c>
+      <c r="D85" s="7" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E85" s="8" t="n">
+        <v>0.02499999999999988</v>
+      </c>
+      <c r="F85" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="23" t="inlineStr">
+      <c r="A87" s="24" t="inlineStr">
+        <is>
+          <t>September 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="25" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B87" s="23" t="inlineStr">
+      <c r="B88" s="25" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C87" s="23" t="inlineStr">
+      <c r="C88" s="25" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D87" s="23" t="inlineStr">
+      <c r="D88" s="25" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E87" s="23" t="inlineStr">
+      <c r="E88" s="25" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F87" s="23" t="inlineStr">
+      <c r="F88" s="25" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t>INGR</t>
-        </is>
-      </c>
-      <c r="B88" s="10" t="n">
-        <v>46628</v>
-      </c>
-      <c r="C88" s="10" t="n">
-        <v>46662</v>
-      </c>
-      <c r="D88" s="7" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E88" s="8" t="n">
-        <v>0.02499999999999988</v>
-      </c>
-      <c r="F88" s="12" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B89" s="10" t="n">
+        <v>46643</v>
+      </c>
+      <c r="C89" s="10" t="n">
+        <v>46709</v>
+      </c>
+      <c r="D89" s="7" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E89" s="8" t="n">
+        <v>0.09638554216867479</v>
+      </c>
+      <c r="F89" s="12" t="inlineStr">
         <is>
           <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="22" t="inlineStr">
-        <is>
-          <t>September 2027</t>
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>VZ</t>
+        </is>
+      </c>
+      <c r="B90" s="10" t="n">
+        <v>46645</v>
+      </c>
+      <c r="C90" s="10" t="n">
+        <v>46668</v>
+      </c>
+      <c r="D90" s="7" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="E90" s="8" t="n">
+        <v>0.02608695652173916</v>
+      </c>
+      <c r="F90" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="23" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B91" s="23" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C91" s="23" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D91" s="23" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E91" s="23" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F91" s="23" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="5" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="B92" s="10" t="n">
-        <v>46643</v>
-      </c>
-      <c r="C92" s="10" t="n">
-        <v>46709</v>
-      </c>
-      <c r="D92" s="7" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E92" s="8" t="n">
-        <v>0.09638554216867479</v>
-      </c>
-      <c r="F92" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>VZ</t>
-        </is>
-      </c>
-      <c r="B93" s="10" t="n">
-        <v>46645</v>
-      </c>
-      <c r="C93" s="10" t="n">
-        <v>46668</v>
-      </c>
-      <c r="D93" s="7" t="n">
-        <v>0.708</v>
-      </c>
-      <c r="E93" s="8" t="n">
-        <v>0.02608695652173916</v>
-      </c>
-      <c r="F93" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="5" t="inlineStr">
+      <c r="A91" s="5" t="inlineStr">
         <is>
           <t>TXN</t>
         </is>
       </c>
-      <c r="B94" s="10" t="n">
+      <c r="B91" s="10" t="n">
         <v>46650</v>
       </c>
-      <c r="C94" s="10" t="n">
+      <c r="C91" s="10" t="n">
         <v>46690</v>
       </c>
-      <c r="D94" s="7" t="n">
+      <c r="D91" s="7" t="n">
         <v>1.42</v>
       </c>
-      <c r="E94" s="8" t="n">
+      <c r="E91" s="8" t="n">
         <v>0.0441176470588234</v>
       </c>
-      <c r="F94" s="12" t="inlineStr">
+      <c r="F91" s="12" t="inlineStr">
         <is>
           <t>Notion + yfinance</t>
         </is>
@@ -4926,7 +4900,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Complete Holdings Dividend Summary - 09/21/2026</t>
+          <t>Complete Holdings Dividend Summary - 09/28/2026</t>
         </is>
       </c>
     </row>
@@ -5026,11 +5000,11 @@
       <c r="F5" s="7" t="n">
         <v>0.29</v>
       </c>
-      <c r="G5" s="24" t="n">
+      <c r="G5" s="26" t="n">
         <v>1.16</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.00978737793499475</v>
+        <v>0.01017633144783744</v>
       </c>
       <c r="I5" s="10" t="n">
         <v>46255</v>
@@ -5079,11 +5053,11 @@
       <c r="F6" s="7" t="n">
         <v>2.52</v>
       </c>
-      <c r="G6" s="24" t="n">
+      <c r="G6" s="26" t="n">
         <v>10.08</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.02574909946756583</v>
+        <v>0.02434900172108285</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>46255</v>
@@ -5132,11 +5106,11 @@
       <c r="F7" s="7" t="n">
         <v>2.138</v>
       </c>
-      <c r="G7" s="24" t="n">
+      <c r="G7" s="26" t="n">
         <v>8.552</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.005078776879924646</v>
+        <v>0.004863235712254763</v>
       </c>
       <c r="I7" s="10" t="n">
         <v>46231</v>
@@ -5185,11 +5159,11 @@
       <c r="F8" s="7" t="n">
         <v>0.546</v>
       </c>
-      <c r="G8" s="24" t="n">
+      <c r="G8" s="26" t="n">
         <v>2.184</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>0.02551849066264972</v>
+        <v>0.0264903876291373</v>
       </c>
       <c r="I8" s="10" t="n">
         <v>46251</v>
@@ -5238,11 +5212,11 @@
       <c r="F9" s="7" t="n">
         <v>0.703</v>
       </c>
-      <c r="G9" s="24" t="n">
+      <c r="G9" s="26" t="n">
         <v>2.812</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.03886124898121857</v>
+        <v>0.04049539028131194</v>
       </c>
       <c r="I9" s="10" t="n">
         <v>46251</v>
@@ -5291,11 +5265,11 @@
       <c r="F10" s="7" t="n">
         <v>1.03</v>
       </c>
-      <c r="G10" s="24" t="n">
+      <c r="G10" s="26" t="n">
         <v>4.12</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.0258234356907714</v>
+        <v>0.02627132204797521</v>
       </c>
       <c r="I10" s="10" t="n">
         <v>46265</v>
@@ -5344,11 +5318,11 @@
       <c r="F11" s="7" t="n">
         <v>1.25</v>
       </c>
-      <c r="G11" s="24" t="n">
+      <c r="G11" s="26" t="n">
         <v>5</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.06040099158048739</v>
+        <v>0.06110975334452722</v>
       </c>
       <c r="I11" s="10" t="n">
         <v>46246</v>
@@ -5397,11 +5371,11 @@
       <c r="F12" s="7" t="n">
         <v>1.3</v>
       </c>
-      <c r="G12" s="24" t="n">
+      <c r="G12" s="26" t="n">
         <v>5.2</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0.01892595187562783</v>
+        <v>0.01946180602749289</v>
       </c>
       <c r="I12" s="10" t="n">
         <v>46274</v>
@@ -5450,11 +5424,11 @@
       <c r="F13" s="7" t="n">
         <v>0.24</v>
       </c>
-      <c r="G13" s="24" t="n">
+      <c r="G13" s="26" t="n">
         <v>0.96</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0.02520677492654566</v>
+        <v>0.026044492243725</v>
       </c>
       <c r="I13" s="10" t="n">
         <v>46254</v>
@@ -5503,11 +5477,11 @@
       <c r="F14" s="7" t="n">
         <v>0.6</v>
       </c>
-      <c r="G14" s="24" t="n">
+      <c r="G14" s="26" t="n">
         <v>2.4</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>0.007728721893003816</v>
+        <v>0.00785828876337411</v>
       </c>
       <c r="I14" s="10" t="n">
         <v>46248</v>
@@ -5556,11 +5530,11 @@
       <c r="F15" s="7" t="n">
         <v>0.42</v>
       </c>
-      <c r="G15" s="24" t="n">
+      <c r="G15" s="26" t="n">
         <v>1.68</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0.01533966445849374</v>
+        <v>0.01573991652591106</v>
       </c>
       <c r="I15" s="10" t="n">
         <v>46209</v>
@@ -5609,11 +5583,11 @@
       <c r="F16" s="7" t="n">
         <v>1.78</v>
       </c>
-      <c r="G16" s="24" t="n">
+      <c r="G16" s="26" t="n">
         <v>7.12</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>0.03451117291578592</v>
+        <v>0.03436293486905094</v>
       </c>
       <c r="I16" s="10" t="n">
         <v>46253</v>
@@ -5662,11 +5636,11 @@
       <c r="F17" s="7" t="n">
         <v>0.86</v>
       </c>
-      <c r="G17" s="24" t="n">
+      <c r="G17" s="26" t="n">
         <v>3.44</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0.01387936217586079</v>
+        <v>0.01466044423432771</v>
       </c>
       <c r="I17" s="10" t="n">
         <v>46211</v>
@@ -5715,11 +5689,11 @@
       <c r="F18" s="7" t="n">
         <v>0.32</v>
       </c>
-      <c r="G18" s="24" t="n">
+      <c r="G18" s="26" t="n">
         <v>1.28</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0.02686253848921341</v>
+        <v>0.02705845030636119</v>
       </c>
       <c r="I18" s="10" t="n">
         <v>46280</v>
@@ -5768,11 +5742,11 @@
       <c r="F19" s="7" t="n">
         <v>0.84</v>
       </c>
-      <c r="G19" s="24" t="n">
+      <c r="G19" s="26" t="n">
         <v>3.36</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0.05154560291238409</v>
+        <v>0.05089367117307898</v>
       </c>
       <c r="I19" s="10" t="n">
         <v>46280</v>
@@ -5821,11 +5795,11 @@
       <c r="F20" s="7" t="n">
         <v>0.64</v>
       </c>
-      <c r="G20" s="24" t="n">
+      <c r="G20" s="26" t="n">
         <v>2.56</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0.02523905638405114</v>
+        <v>0.02619193836660545</v>
       </c>
       <c r="I20" s="10" t="n">
         <v>46247</v>
@@ -5874,11 +5848,11 @@
       <c r="F21" s="7" t="n">
         <v>1.59</v>
       </c>
-      <c r="G21" s="24" t="n">
+      <c r="G21" s="26" t="n">
         <v>6.36</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0.01805945923134389</v>
+        <v>0.018949438093953</v>
       </c>
       <c r="I21" s="10" t="n">
         <v>46205</v>
@@ -5899,53 +5873,53 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>GGG</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>SMID/DAC</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D22" s="15" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>Jan/Apr/Jul/Oct</t>
         </is>
       </c>
-      <c r="E22" s="15" t="inlineStr">
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="F22" s="16" t="n">
+      <c r="F22" s="17" t="n">
         <v>0.295</v>
       </c>
-      <c r="G22" s="25" t="n">
+      <c r="G22" s="27" t="n">
         <v>1.18</v>
       </c>
-      <c r="H22" s="18" t="n">
-        <v>0.01548353253084369</v>
-      </c>
-      <c r="I22" s="19" t="n">
+      <c r="H22" s="19" t="n">
+        <v>0.01510303393679408</v>
+      </c>
+      <c r="I22" s="20" t="n">
         <v>46223</v>
       </c>
-      <c r="J22" s="17" t="n">
+      <c r="J22" s="18" t="n">
         <v>0.07272727272727258</v>
       </c>
-      <c r="K22" s="19" t="n">
+      <c r="K22" s="20" t="n">
         <v>46383</v>
       </c>
-      <c r="L22" s="19" t="n">
+      <c r="L22" s="20" t="n">
         <v>46404</v>
       </c>
-      <c r="M22" s="21" t="inlineStr">
+      <c r="M22" s="22" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
@@ -5980,11 +5954,11 @@
       <c r="F23" s="7" t="n">
         <v>2.33</v>
       </c>
-      <c r="G23" s="24" t="n">
+      <c r="G23" s="26" t="n">
         <v>9.32</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>0.03142279099194371</v>
+        <v>0.03197583639308245</v>
       </c>
       <c r="I23" s="10" t="n">
         <v>46268</v>
@@ -6033,11 +6007,11 @@
       <c r="F24" s="7" t="n">
         <v>1.38</v>
       </c>
-      <c r="G24" s="24" t="n">
+      <c r="G24" s="26" t="n">
         <v>5.52</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>0.02022274389215184</v>
+        <v>0.02119327413458831</v>
       </c>
       <c r="I24" s="10" t="n">
         <v>46262</v>
@@ -6086,11 +6060,11 @@
       <c r="F25" s="7" t="n">
         <v>0.293</v>
       </c>
-      <c r="G25" s="24" t="n">
+      <c r="G25" s="26" t="n">
         <v>1.172</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0.05678294741557949</v>
+        <v>0.05962859115015496</v>
       </c>
       <c r="I25" s="10" t="n">
         <v>46216</v>
@@ -6111,53 +6085,53 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>HWC</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>SMID/DAC</t>
         </is>
       </c>
-      <c r="C26" s="15" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D26" s="15" t="inlineStr">
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>Mar/Jun/Sep/Dec</t>
         </is>
       </c>
-      <c r="E26" s="15" t="inlineStr">
+      <c r="E26" s="16" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="F26" s="16" t="n">
+      <c r="F26" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="G26" s="25" t="n">
+      <c r="G26" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="H26" s="18" t="n">
-        <v>0.02664889964922068</v>
-      </c>
-      <c r="I26" s="19" t="n">
+      <c r="H26" s="19" t="n">
+        <v>0.02734481838515112</v>
+      </c>
+      <c r="I26" s="20" t="n">
         <v>46269</v>
       </c>
-      <c r="J26" s="17" t="n">
+      <c r="J26" s="18" t="n">
         <v>0.1111111111111111</v>
       </c>
-      <c r="K26" s="19" t="n">
+      <c r="K26" s="20" t="n">
         <v>46429</v>
       </c>
-      <c r="L26" s="19" t="n">
+      <c r="L26" s="20" t="n">
         <v>46450</v>
       </c>
-      <c r="M26" s="21" t="inlineStr">
+      <c r="M26" s="22" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
@@ -6192,11 +6166,11 @@
       <c r="F27" s="7" t="n">
         <v>0.82</v>
       </c>
-      <c r="G27" s="24" t="n">
+      <c r="G27" s="26" t="n">
         <v>3.28</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0.03369112923733877</v>
+        <v>0.03395269278011557</v>
       </c>
       <c r="I27" s="10" t="n">
         <v>46204</v>
@@ -6245,11 +6219,11 @@
       <c r="F28" s="7" t="n">
         <v>0.61</v>
       </c>
-      <c r="G28" s="24" t="n">
+      <c r="G28" s="26" t="n">
         <v>2.44</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>0.01583901299359408</v>
+        <v>0.01661898840947346</v>
       </c>
       <c r="I28" s="10" t="n">
         <v>46269</v>
@@ -6298,11 +6272,11 @@
       <c r="F29" s="7" t="n">
         <v>1.34</v>
       </c>
-      <c r="G29" s="24" t="n">
+      <c r="G29" s="26" t="n">
         <v>5.36</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.01961789025712752</v>
+        <v>0.01969936444610691</v>
       </c>
       <c r="I29" s="10" t="n">
         <v>46259</v>
@@ -6351,11 +6325,11 @@
       <c r="F30" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="G30" s="24" t="n">
+      <c r="G30" s="26" t="n">
         <v>6</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>0.017034323631875</v>
+        <v>0.01768920061562391</v>
       </c>
       <c r="I30" s="10" t="n">
         <v>46209</v>
@@ -6364,7 +6338,7 @@
         <v>0.07142857142857149</v>
       </c>
       <c r="K30" s="10" t="n">
-        <v>46284</v>
+        <v>46461</v>
       </c>
       <c r="L30" s="10" t="n">
         <v>46665</v>
@@ -6404,11 +6378,11 @@
       <c r="F31" s="7" t="n">
         <v>1.125</v>
       </c>
-      <c r="G31" s="24" t="n">
+      <c r="G31" s="26" t="n">
         <v>2.25</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0.02042298300259235</v>
+        <v>0.02055733268831431</v>
       </c>
       <c r="I31" s="10" t="n">
         <v>46216</v>
@@ -6457,11 +6431,11 @@
       <c r="F32" s="7" t="n">
         <v>0.79</v>
       </c>
-      <c r="G32" s="24" t="n">
+      <c r="G32" s="26" t="n">
         <v>3.16</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>0.0122511718530932</v>
+        <v>0.01157763600694031</v>
       </c>
       <c r="I32" s="10" t="n">
         <v>46203</v>
@@ -6510,14 +6484,14 @@
       <c r="F33" s="7" t="n">
         <v>0.72</v>
       </c>
-      <c r="G33" s="24" t="n">
+      <c r="G33" s="26" t="n">
         <v>2.88</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0.03129414362926066</v>
+        <v>0.03276637021439819</v>
       </c>
       <c r="I33" s="10" t="n">
-        <v>46199</v>
+        <v>46290</v>
       </c>
       <c r="J33" s="8" t="n">
         <v>0.01408450704225353</v>
@@ -6563,11 +6537,11 @@
       <c r="F34" s="7" t="n">
         <v>0.48</v>
       </c>
-      <c r="G34" s="24" t="n">
+      <c r="G34" s="26" t="n">
         <v>1.92</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0.03923571975309979</v>
+        <v>0.03987953020551666</v>
       </c>
       <c r="I34" s="10" t="n">
         <v>46209</v>
@@ -6616,11 +6590,11 @@
       <c r="F35" s="7" t="n">
         <v>0.91</v>
       </c>
-      <c r="G35" s="24" t="n">
+      <c r="G35" s="26" t="n">
         <v>3.64</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>0.007345385769172313</v>
+        <v>0.007144434529232485</v>
       </c>
       <c r="I35" s="10" t="n">
         <v>46254</v>
@@ -6669,11 +6643,11 @@
       <c r="F36" s="7" t="n">
         <v>0.87</v>
       </c>
-      <c r="G36" s="24" t="n">
+      <c r="G36" s="26" t="n">
         <v>3.48</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>0.02857260193208257</v>
+        <v>0.02871523995292049</v>
       </c>
       <c r="I36" s="10" t="n">
         <v>46211</v>
@@ -6722,11 +6696,11 @@
       <c r="F37" s="7" t="n">
         <v>0.41</v>
       </c>
-      <c r="G37" s="24" t="n">
+      <c r="G37" s="26" t="n">
         <v>1.64</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>0.04623560300134034</v>
+        <v>0.04558087884561619</v>
       </c>
       <c r="I37" s="10" t="n">
         <v>46266</v>
@@ -6775,11 +6749,11 @@
       <c r="F38" s="7" t="n">
         <v>0.579</v>
       </c>
-      <c r="G38" s="24" t="n">
+      <c r="G38" s="26" t="n">
         <v>1.158</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0.02892830465433105</v>
+        <v>0.03028242544905738</v>
       </c>
       <c r="I38" s="10" t="n">
         <v>46251</v>
@@ -6828,11 +6802,11 @@
       <c r="F39" s="7" t="n">
         <v>0.271</v>
       </c>
-      <c r="G39" s="24" t="n">
+      <c r="G39" s="26" t="n">
         <v>3.252</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>0.05709770688176589</v>
+        <v>0.05867388443418352</v>
       </c>
       <c r="I39" s="10" t="n">
         <v>46265</v>
@@ -6881,11 +6855,11 @@
       <c r="F40" s="7" t="n">
         <v>1.19</v>
       </c>
-      <c r="G40" s="24" t="n">
+      <c r="G40" s="26" t="n">
         <v>4.76</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0.04153940267145332</v>
+        <v>0.04749076963560451</v>
       </c>
       <c r="I40" s="10" t="n">
         <v>46231</v>
@@ -6934,11 +6908,11 @@
       <c r="F41" s="7" t="n">
         <v>0.67</v>
       </c>
-      <c r="G41" s="24" t="n">
+      <c r="G41" s="26" t="n">
         <v>2.68</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>0.03862784817086413</v>
+        <v>0.04014379739729774</v>
       </c>
       <c r="I41" s="10" t="n">
         <v>46274</v>
@@ -6987,11 +6961,11 @@
       <c r="F42" s="7" t="n">
         <v>1.48</v>
       </c>
-      <c r="G42" s="24" t="n">
+      <c r="G42" s="26" t="n">
         <v>5.92</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>0.04612387782222198</v>
+        <v>0.04644933337595475</v>
       </c>
       <c r="I42" s="10" t="n">
         <v>46269</v>
@@ -7040,11 +7014,11 @@
       <c r="F43" s="7" t="n">
         <v>0.43</v>
       </c>
-      <c r="G43" s="24" t="n">
+      <c r="G43" s="26" t="n">
         <v>1.72</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>0.06210507380223738</v>
+        <v>0.06040386222854276</v>
       </c>
       <c r="I43" s="10" t="n">
         <v>46227</v>
@@ -7093,11 +7067,11 @@
       <c r="F44" s="7" t="n">
         <v>0.84</v>
       </c>
-      <c r="G44" s="24" t="n">
+      <c r="G44" s="26" t="n">
         <v>3.36</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>0.0286225403992658</v>
+        <v>0.0289443082784107</v>
       </c>
       <c r="I44" s="10" t="n">
         <v>46268</v>
@@ -7146,11 +7120,11 @@
       <c r="F45" s="7" t="n">
         <v>1.089</v>
       </c>
-      <c r="G45" s="24" t="n">
+      <c r="G45" s="26" t="n">
         <v>4.356</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>0.0298213170506069</v>
+        <v>0.02960948806953896</v>
       </c>
       <c r="I45" s="10" t="n">
         <v>46227</v>
@@ -7199,14 +7173,14 @@
       <c r="F46" s="7" t="n">
         <v>0.551</v>
       </c>
-      <c r="G46" s="24" t="n">
+      <c r="G46" s="26" t="n">
         <v>2.204</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>0.04648317953059956</v>
+        <v>0.04796517874658265</v>
       </c>
       <c r="I46" s="10" t="n">
-        <v>46198</v>
+        <v>46290</v>
       </c>
       <c r="J46" s="8" t="n">
         <v>0.04952380952380957</v>
@@ -7224,55 +7198,55 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" s="15" t="inlineStr">
         <is>
           <t>PSX</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B47" s="16" t="inlineStr">
         <is>
           <t>QDVD/DAC</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="C47" s="16" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D47" s="16" t="inlineStr">
         <is>
           <t>Feb/May/Aug/Nov</t>
         </is>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="E47" s="16" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="F47" s="7" t="n">
+      <c r="F47" s="17" t="n">
         <v>1.27</v>
       </c>
-      <c r="G47" s="24" t="n">
+      <c r="G47" s="27" t="n">
         <v>5.08</v>
       </c>
-      <c r="H47" s="9" t="n">
-        <v>0.01878350811872483</v>
-      </c>
-      <c r="I47" s="10" t="n">
+      <c r="H47" s="19" t="n">
+        <v>0.01969831987068282</v>
+      </c>
+      <c r="I47" s="20" t="n">
         <v>46252</v>
       </c>
-      <c r="J47" s="8" t="n">
+      <c r="J47" s="18" t="n">
         <v>0.05833333333333339</v>
       </c>
-      <c r="K47" s="10" t="n">
-        <v>46499</v>
-      </c>
-      <c r="L47" s="10" t="n">
+      <c r="K47" s="20" t="n">
+        <v>46505</v>
+      </c>
+      <c r="L47" s="20" t="n">
         <v>46526</v>
       </c>
-      <c r="M47" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="M47" s="22" t="inlineStr">
+        <is>
+          <t>yfinance</t>
         </is>
       </c>
     </row>
@@ -7305,11 +7279,11 @@
       <c r="F48" s="7" t="n">
         <v>0.98</v>
       </c>
-      <c r="G48" s="24" t="n">
+      <c r="G48" s="26" t="n">
         <v>3.92</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>0.01592201481961874</v>
+        <v>0.01576354660457816</v>
       </c>
       <c r="I48" s="10" t="n">
         <v>46252</v>
@@ -7358,11 +7332,11 @@
       <c r="F49" s="7" t="n">
         <v>2.44</v>
       </c>
-      <c r="G49" s="24" t="n">
+      <c r="G49" s="26" t="n">
         <v>9.76</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>0.02634704658156829</v>
+        <v>0.02629593680273037</v>
       </c>
       <c r="I49" s="10" t="n">
         <v>46253</v>
@@ -7411,11 +7385,11 @@
       <c r="F50" s="7" t="n">
         <v>0.84</v>
       </c>
-      <c r="G50" s="24" t="n">
+      <c r="G50" s="26" t="n">
         <v>3.36</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>0.03791041525582833</v>
+        <v>0.03726707923163132</v>
       </c>
       <c r="I50" s="10" t="n">
         <v>46273</v>
@@ -7464,11 +7438,11 @@
       <c r="F51" s="7" t="n">
         <v>1.3</v>
       </c>
-      <c r="G51" s="24" t="n">
+      <c r="G51" s="26" t="n">
         <v>5.2</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>0.05013256280063842</v>
+        <v>0.04955920751734383</v>
       </c>
       <c r="I51" s="10" t="n">
         <v>46280</v>
@@ -7517,11 +7491,11 @@
       <c r="F52" s="7" t="n">
         <v>0.974</v>
       </c>
-      <c r="G52" s="24" t="n">
+      <c r="G52" s="26" t="n">
         <v>3.896</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>0.04302120257323579</v>
+        <v>0.04263981485045694</v>
       </c>
       <c r="I52" s="10" t="n">
         <v>46112</v>
@@ -7570,11 +7544,11 @@
       <c r="F53" s="7" t="n">
         <v>1.42</v>
       </c>
-      <c r="G53" s="24" t="n">
+      <c r="G53" s="26" t="n">
         <v>5.68</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>0.02139359698681732</v>
+        <v>0.0205462099807986</v>
       </c>
       <c r="I53" s="10" t="n">
         <v>46234</v>
@@ -7623,11 +7597,11 @@
       <c r="F54" s="7" t="n">
         <v>0.531</v>
       </c>
-      <c r="G54" s="24" t="n">
+      <c r="G54" s="26" t="n">
         <v>2.124</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>0.03425806451612903</v>
+        <v>0.03422494284562026</v>
       </c>
       <c r="I54" s="10" t="n">
         <v>46241</v>
@@ -7676,11 +7650,11 @@
       <c r="F55" s="7" t="n">
         <v>1.42</v>
       </c>
-      <c r="G55" s="24" t="n">
+      <c r="G55" s="26" t="n">
         <v>5.68</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>0.02079215225231083</v>
+        <v>0.02066506695303406</v>
       </c>
       <c r="I55" s="10" t="n">
         <v>46265</v>
@@ -7729,11 +7703,11 @@
       <c r="F56" s="7" t="n">
         <v>0.708</v>
       </c>
-      <c r="G56" s="24" t="n">
+      <c r="G56" s="26" t="n">
         <v>2.832</v>
       </c>
       <c r="H56" s="9" t="n">
-        <v>0.05928406893158691</v>
+        <v>0.06022328353230328</v>
       </c>
       <c r="I56" s="10" t="n">
         <v>46213</v>
@@ -7782,11 +7756,11 @@
       <c r="F57" s="7" t="n">
         <v>1.03</v>
       </c>
-      <c r="G57" s="24" t="n">
+      <c r="G57" s="26" t="n">
         <v>4.12</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>0.02579191096983098</v>
+        <v>0.02525206111259398</v>
       </c>
       <c r="I57" s="10" t="n">
         <v>46251</v>

--- a/data/dividend_calendar.xlsx
+++ b/data/dividend_calendar.xlsx
@@ -576,7 +576,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Estimated Dividend Calendar: Anticipated Announcements - 09/28/2026</t>
+          <t>Estimated Dividend Calendar: Anticipated Announcements - 10/05/2026</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
         <v>46048</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>-245</v>
+        <v>-252</v>
       </c>
       <c r="J6" s="10" t="n">
         <v>46413</v>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0.06040386222854276</v>
+        <v>0.06260236491789237</v>
       </c>
     </row>
     <row r="7">
@@ -727,7 +727,7 @@
         <v>46305</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J7" s="10" t="n">
         <v>46339</v>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0.02871523995292049</v>
+        <v>0.0269120722736316</v>
       </c>
     </row>
     <row r="8">
@@ -772,8 +772,8 @@
       <c r="H8" s="10" t="n">
         <v>46311</v>
       </c>
-      <c r="I8" s="14" t="n">
-        <v>18</v>
+      <c r="I8" s="13" t="n">
+        <v>11</v>
       </c>
       <c r="J8" s="10" t="n">
         <v>46386</v>
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L8" s="9" t="n">
-        <v>0.01157763600694031</v>
+        <v>0.0116302613355222</v>
       </c>
     </row>
     <row r="9">
@@ -819,7 +819,7 @@
         <v>46318</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J9" s="10" t="n">
         <v>46352</v>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="L9" s="9" t="n">
-        <v>0.02119327413458831</v>
+        <v>0.02049834685596653</v>
       </c>
     </row>
     <row r="10">
@@ -865,7 +865,7 @@
         <v>46322</v>
       </c>
       <c r="I10" s="14" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J10" s="10" t="n">
         <v>46338</v>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0.02619193836660545</v>
+        <v>0.02542835780877885</v>
       </c>
     </row>
     <row r="11">
@@ -911,7 +911,7 @@
         <v>46329</v>
       </c>
       <c r="I11" s="14" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J11" s="10" t="n">
         <v>46338</v>
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0.00785828876337411</v>
+        <v>0.007742684745454336</v>
       </c>
     </row>
     <row r="12">
@@ -957,7 +957,7 @@
         <v>46332</v>
       </c>
       <c r="I12" s="14" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="J12" s="10" t="n">
         <v>46346</v>
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="L12" s="9" t="n">
-        <v>0.02629593680273037</v>
+        <v>0.02675878779765391</v>
       </c>
     </row>
     <row r="13">
@@ -1003,7 +1003,7 @@
         <v>46341</v>
       </c>
       <c r="I13" s="14" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J13" s="10" t="n">
         <v>46340</v>
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="L13" s="9" t="n">
-        <v>0.02525206111259398</v>
+        <v>0.025221915188599</v>
       </c>
     </row>
     <row r="14">
@@ -1049,7 +1049,7 @@
         <v>46344</v>
       </c>
       <c r="I14" s="14" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="J14" s="10" t="n">
         <v>46385</v>
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="L14" s="9" t="n">
-        <v>0.03987953020551666</v>
+        <v>0.04340945104841216</v>
       </c>
     </row>
     <row r="15">
@@ -1095,7 +1095,7 @@
         <v>46347</v>
       </c>
       <c r="I15" s="14" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="J15" s="10" t="n">
         <v>46358</v>
@@ -1106,7 +1106,7 @@
         </is>
       </c>
       <c r="L15" s="9" t="n">
-        <v>0.04558087884561619</v>
+        <v>0.0497045022909573</v>
       </c>
     </row>
     <row r="16">
@@ -1141,7 +1141,7 @@
         <v>46352</v>
       </c>
       <c r="I16" s="14" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J16" s="10" t="n">
         <v>46400</v>
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0.05962859115015496</v>
+        <v>0.05796241542035767</v>
       </c>
     </row>
     <row r="17">
@@ -1187,7 +1187,7 @@
         <v>46360</v>
       </c>
       <c r="I17" s="14" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="J17" s="10" t="n">
         <v>46371</v>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.05089367117307898</v>
+        <v>0.05169230769230769</v>
       </c>
     </row>
     <row r="18">
@@ -1233,7 +1233,7 @@
         <v>46366</v>
       </c>
       <c r="I18" s="14" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="J18" s="10" t="n">
         <v>46432</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0.02434900172108285</v>
+        <v>0.0250733801190597</v>
       </c>
     </row>
     <row r="19">
@@ -1279,7 +1279,7 @@
         <v>46380</v>
       </c>
       <c r="I19" s="14" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="J19" s="10" t="n">
         <v>46436</v>
@@ -1290,7 +1290,7 @@
         </is>
       </c>
       <c r="L19" s="9" t="n">
-        <v>0.026044492243725</v>
+        <v>0.02546081297917674</v>
       </c>
     </row>
     <row r="20">
@@ -1325,7 +1325,7 @@
         <v>46383</v>
       </c>
       <c r="I20" s="21" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="J20" s="20" t="n">
         <v>46404</v>
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="L20" s="19" t="n">
-        <v>0.01510303393679408</v>
+        <v>0.0152012882447665</v>
       </c>
     </row>
     <row r="21">
@@ -1371,7 +1371,7 @@
         <v>46402</v>
       </c>
       <c r="I21" s="14" t="n">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="J21" s="10" t="n">
         <v>46483</v>
@@ -1382,7 +1382,7 @@
         </is>
       </c>
       <c r="L21" s="9" t="n">
-        <v>0.01466044423432771</v>
+        <v>0.01482915257546235</v>
       </c>
     </row>
     <row r="22">
@@ -1417,7 +1417,7 @@
         <v>46411</v>
       </c>
       <c r="I22" s="14" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="J22" s="10" t="n">
         <v>46435</v>
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="L22" s="9" t="n">
-        <v>0.04049539028131194</v>
+        <v>0.03974558303886926</v>
       </c>
     </row>
     <row r="23">
@@ -1463,7 +1463,7 @@
         <v>46417</v>
       </c>
       <c r="I23" s="14" t="n">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="J23" s="10" t="n">
         <v>46433</v>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0.03436293486905094</v>
+        <v>0.03491993354817895</v>
       </c>
     </row>
     <row r="24">
@@ -1509,7 +1509,7 @@
         <v>46423</v>
       </c>
       <c r="I24" s="14" t="n">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="J24" s="10" t="n">
         <v>46473</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="L24" s="9" t="n">
-        <v>0.03028242544905738</v>
+        <v>0.03123398452246422</v>
       </c>
     </row>
     <row r="25">
@@ -1555,7 +1555,7 @@
         <v>46428</v>
       </c>
       <c r="I25" s="14" t="n">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="J25" s="10" t="n">
         <v>46452</v>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="L25" s="9" t="n">
-        <v>0.01661898840947346</v>
+        <v>0.01707069676200025</v>
       </c>
     </row>
     <row r="26">
@@ -1601,7 +1601,7 @@
         <v>46428</v>
       </c>
       <c r="I26" s="14" t="n">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="J26" s="10" t="n">
         <v>46460</v>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="L26" s="9" t="n">
-        <v>0.04955920751734383</v>
+        <v>0.05039736368113923</v>
       </c>
     </row>
     <row r="27">
@@ -1647,7 +1647,7 @@
         <v>46429</v>
       </c>
       <c r="I27" s="21" t="n">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="J27" s="20" t="n">
         <v>46450</v>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="L27" s="19" t="n">
-        <v>0.02734481838515112</v>
+        <v>0.0275824016146412</v>
       </c>
     </row>
     <row r="28">
@@ -1693,7 +1693,7 @@
         <v>46431</v>
       </c>
       <c r="I28" s="14" t="n">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="J28" s="10" t="n">
         <v>46480</v>
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="L28" s="9" t="n">
-        <v>0.01573991652591106</v>
+        <v>0.01496259367888212</v>
       </c>
     </row>
     <row r="29">
@@ -1739,7 +1739,7 @@
         <v>46432</v>
       </c>
       <c r="I29" s="14" t="n">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="J29" s="10" t="n">
         <v>46455</v>
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="L29" s="9" t="n">
-        <v>0.04014379739729774</v>
+        <v>0.03948725344843111</v>
       </c>
     </row>
     <row r="30">
@@ -1785,7 +1785,7 @@
         <v>46433</v>
       </c>
       <c r="I30" s="14" t="n">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="J30" s="10" t="n">
         <v>46425</v>
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="L30" s="9" t="n">
-        <v>0.004863235712254763</v>
+        <v>0.004618563878007072</v>
       </c>
     </row>
     <row r="31">
@@ -1831,7 +1831,7 @@
         <v>46433</v>
       </c>
       <c r="I31" s="14" t="n">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="J31" s="10" t="n">
         <v>46383</v>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="L31" s="9" t="n">
-        <v>0.01946180602749289</v>
+        <v>0.01960488686266767</v>
       </c>
     </row>
     <row r="32">
@@ -1877,7 +1877,7 @@
         <v>46433</v>
       </c>
       <c r="I32" s="14" t="n">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="J32" s="10" t="n">
         <v>46458</v>
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="L32" s="9" t="n">
-        <v>0.02705845030636119</v>
+        <v>0.02692469447517261</v>
       </c>
     </row>
     <row r="33">
@@ -1923,7 +1923,7 @@
         <v>46433</v>
       </c>
       <c r="I33" s="14" t="n">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="J33" s="10" t="n">
         <v>46634</v>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="L33" s="9" t="n">
-        <v>0.0289443082784107</v>
+        <v>0.02993185232025556</v>
       </c>
     </row>
     <row r="34">
@@ -1969,7 +1969,7 @@
         <v>46433</v>
       </c>
       <c r="I34" s="14" t="n">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="J34" s="10" t="n">
         <v>46608</v>
@@ -1980,7 +1980,7 @@
         </is>
       </c>
       <c r="L34" s="9" t="n">
-        <v>0.03422494284562026</v>
+        <v>0.03558086960144769</v>
       </c>
     </row>
     <row r="35">
@@ -2015,7 +2015,7 @@
         <v>46440</v>
       </c>
       <c r="I35" s="14" t="n">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="J35" s="10" t="n">
         <v>46450</v>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="L35" s="9" t="n">
-        <v>0.01017633144783744</v>
+        <v>0.01000906021484749</v>
       </c>
     </row>
     <row r="36">
@@ -2061,7 +2061,7 @@
         <v>46441</v>
       </c>
       <c r="I36" s="14" t="n">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="J36" s="10" t="n">
         <v>46456</v>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="L36" s="9" t="n">
-        <v>0.03197583639308245</v>
+        <v>0.03327086122266845</v>
       </c>
     </row>
     <row r="37">
@@ -2107,7 +2107,7 @@
         <v>46452</v>
       </c>
       <c r="I37" s="14" t="n">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="J37" s="10" t="n">
         <v>46487</v>
@@ -2118,7 +2118,7 @@
         </is>
       </c>
       <c r="L37" s="9" t="n">
-        <v>0.018949438093953</v>
+        <v>0.01926572184075763</v>
       </c>
     </row>
     <row r="38">
@@ -2153,7 +2153,7 @@
         <v>46461</v>
       </c>
       <c r="I38" s="14" t="n">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="J38" s="10" t="n">
         <v>46665</v>
@@ -2164,7 +2164,7 @@
         </is>
       </c>
       <c r="L38" s="9" t="n">
-        <v>0.01768920061562391</v>
+        <v>0.01813072291056532</v>
       </c>
     </row>
     <row r="39">
@@ -2184,13 +2184,13 @@
         </is>
       </c>
       <c r="D39" s="7" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="E39" s="7" t="n">
         <v>0.271</v>
       </c>
-      <c r="E39" s="7" t="n">
-        <v>0.27</v>
-      </c>
       <c r="F39" s="8" t="n">
-        <v>0.003703703703703707</v>
+        <v>0.003690036900369007</v>
       </c>
       <c r="G39" s="9" t="n">
         <v>0.02</v>
@@ -2199,7 +2199,7 @@
         <v>46461</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="J39" s="10" t="n">
         <v>46386</v>
@@ -2210,7 +2210,7 @@
         </is>
       </c>
       <c r="L39" s="9" t="n">
-        <v>0.05867388443418352</v>
+        <v>0.06097515550966866</v>
       </c>
     </row>
     <row r="40">
@@ -2245,7 +2245,7 @@
         <v>46488</v>
       </c>
       <c r="I40" s="14" t="n">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="J40" s="10" t="n">
         <v>46498</v>
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="L40" s="9" t="n">
-        <v>0.02960948806953896</v>
+        <v>0.03003827202933425</v>
       </c>
     </row>
     <row r="41">
@@ -2291,7 +2291,7 @@
         <v>46492</v>
       </c>
       <c r="I41" s="14" t="n">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="J41" s="10" t="n">
         <v>46501</v>
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="L41" s="9" t="n">
-        <v>0.02055733268831431</v>
+        <v>0.02102116058315701</v>
       </c>
     </row>
     <row r="42">
@@ -2322,13 +2322,13 @@
         </is>
       </c>
       <c r="D42" s="7" t="n">
+        <v>1.021</v>
+      </c>
+      <c r="E42" s="7" t="n">
         <v>0.974</v>
       </c>
-      <c r="E42" s="7" t="n">
-        <v>0.994</v>
-      </c>
       <c r="F42" s="8" t="n">
-        <v>0.001006036217303824</v>
+        <v>0.04825462012320322</v>
       </c>
       <c r="G42" s="9" t="n">
         <v>0.02</v>
@@ -2337,7 +2337,7 @@
         <v>46492</v>
       </c>
       <c r="I42" s="14" t="n">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="J42" s="10" t="n">
         <v>46376</v>
@@ -2348,7 +2348,7 @@
         </is>
       </c>
       <c r="L42" s="9" t="n">
-        <v>0.04263981485045694</v>
+        <v>0.04847765287972164</v>
       </c>
     </row>
     <row r="43">
@@ -2383,7 +2383,7 @@
         <v>46493</v>
       </c>
       <c r="I43" s="14" t="n">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="J43" s="10" t="n">
         <v>46531</v>
@@ -2394,7 +2394,7 @@
         </is>
       </c>
       <c r="L43" s="9" t="n">
-        <v>0.01969936444610691</v>
+        <v>0.02101466341764813</v>
       </c>
     </row>
     <row r="44">
@@ -2429,7 +2429,7 @@
         <v>46504</v>
       </c>
       <c r="I44" s="14" t="n">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="J44" s="10" t="n">
         <v>46562</v>
@@ -2440,7 +2440,7 @@
         </is>
       </c>
       <c r="L44" s="9" t="n">
-        <v>0.04796517874658265</v>
+        <v>0.04941704204942651</v>
       </c>
     </row>
     <row r="45">
@@ -2473,7 +2473,7 @@
         <v>46505</v>
       </c>
       <c r="I45" s="21" t="n">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="J45" s="20" t="n">
         <v>46526</v>
@@ -2484,7 +2484,7 @@
         </is>
       </c>
       <c r="L45" s="19" t="n">
-        <v>0.01969831987068282</v>
+        <v>0.01903762580466897</v>
       </c>
     </row>
     <row r="46">
@@ -2519,7 +2519,7 @@
         <v>46508</v>
       </c>
       <c r="I46" s="14" t="n">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="J46" s="10" t="n">
         <v>46518</v>
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="L46" s="9" t="n">
-        <v>0.04749076963560451</v>
+        <v>0.04781997143077665</v>
       </c>
     </row>
     <row r="47">
@@ -2565,7 +2565,7 @@
         <v>46515</v>
       </c>
       <c r="I47" s="14" t="n">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="J47" s="10" t="n">
         <v>46542</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="L47" s="9" t="n">
-        <v>0.04644933337595475</v>
+        <v>0.04754065390450687</v>
       </c>
     </row>
     <row r="48">
@@ -2611,7 +2611,7 @@
         <v>46532</v>
       </c>
       <c r="I48" s="14" t="n">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="J48" s="10" t="n">
         <v>46563</v>
@@ -2622,7 +2622,7 @@
         </is>
       </c>
       <c r="L48" s="9" t="n">
-        <v>0.03276637021439819</v>
+        <v>0.03316635032377153</v>
       </c>
     </row>
     <row r="49">
@@ -2657,7 +2657,7 @@
         <v>46589</v>
       </c>
       <c r="I49" s="14" t="n">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="J49" s="10" t="n">
         <v>46629</v>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="L49" s="9" t="n">
-        <v>0.02066506695303406</v>
+        <v>0.02059799423192274</v>
       </c>
     </row>
     <row r="50">
@@ -2703,7 +2703,7 @@
         <v>46591</v>
       </c>
       <c r="I50" s="14" t="n">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="J50" s="10" t="n">
         <v>46633</v>
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="L50" s="9" t="n">
-        <v>0.03726707923163132</v>
+        <v>0.0376935160759064</v>
       </c>
     </row>
     <row r="51">
@@ -2749,7 +2749,7 @@
         <v>46594</v>
       </c>
       <c r="I51" s="14" t="n">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="J51" s="10" t="n">
         <v>46613</v>
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="L51" s="9" t="n">
-        <v>0.01576354660457816</v>
+        <v>0.01569066954036555</v>
       </c>
     </row>
     <row r="52">
@@ -2795,7 +2795,7 @@
         <v>46595</v>
       </c>
       <c r="I52" s="14" t="n">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="J52" s="10" t="n">
         <v>46614</v>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="L52" s="9" t="n">
-        <v>0.0264903876291373</v>
+        <v>0.02679754601226994</v>
       </c>
     </row>
     <row r="53">
@@ -2841,7 +2841,7 @@
         <v>46597</v>
       </c>
       <c r="I53" s="14" t="n">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="J53" s="10" t="n">
         <v>46611</v>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="L53" s="9" t="n">
-        <v>0.06110975334452722</v>
+        <v>0.0615498241205511</v>
       </c>
     </row>
     <row r="54">
@@ -2887,7 +2887,7 @@
         <v>46598</v>
       </c>
       <c r="I54" s="14" t="n">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="J54" s="10" t="n">
         <v>46629</v>
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="L54" s="9" t="n">
-        <v>0.02627132204797521</v>
+        <v>0.02686576971590722</v>
       </c>
     </row>
     <row r="55">
@@ -2918,22 +2918,22 @@
         </is>
       </c>
       <c r="D55" s="7" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E55" s="7" t="n">
         <v>0.82</v>
       </c>
-      <c r="E55" s="7" t="n">
-        <v>0.8</v>
-      </c>
       <c r="F55" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.01219512195121952</v>
       </c>
       <c r="G55" s="9" t="n">
         <v>0.04</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>46628</v>
+        <v>46614</v>
       </c>
       <c r="I55" s="14" t="n">
-        <v>335</v>
+        <v>314</v>
       </c>
       <c r="J55" s="10" t="n">
         <v>46662</v>
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="L55" s="9" t="n">
-        <v>0.03395269278011557</v>
+        <v>0.03503772989535116</v>
       </c>
     </row>
     <row r="56">
@@ -2979,7 +2979,7 @@
         <v>46643</v>
       </c>
       <c r="I56" s="14" t="n">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="J56" s="10" t="n">
         <v>46709</v>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="L56" s="9" t="n">
-        <v>0.007144434529232485</v>
+        <v>0.006893939393939394</v>
       </c>
     </row>
     <row r="57">
@@ -3025,7 +3025,7 @@
         <v>46645</v>
       </c>
       <c r="I57" s="14" t="n">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="J57" s="10" t="n">
         <v>46668</v>
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L57" s="9" t="n">
-        <v>0.06022328353230328</v>
+        <v>0.06189487343217447</v>
       </c>
     </row>
     <row r="58">
@@ -3071,7 +3071,7 @@
         <v>46650</v>
       </c>
       <c r="I58" s="14" t="n">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="J58" s="10" t="n">
         <v>46690</v>
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="L58" s="9" t="n">
-        <v>0.0205462099807986</v>
+        <v>0.0196041137387245</v>
       </c>
     </row>
   </sheetData>
@@ -3117,7 +3117,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Expected Increase Announcements by Month - 09/28/2026</t>
+          <t>Expected Increase Announcements by Month - 10/05/2026</t>
         </is>
       </c>
     </row>
@@ -4199,10 +4199,10 @@
         <v>46386</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>0.271</v>
+        <v>0.272</v>
       </c>
       <c r="E57" s="8" t="n">
-        <v>0.003703703703703707</v>
+        <v>0.003690036900369007</v>
       </c>
       <c r="F57" s="12" t="inlineStr">
         <is>
@@ -4310,10 +4310,10 @@
         <v>46376</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>0.974</v>
+        <v>1.021</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>0.001006036217303824</v>
+        <v>0.04825462012320322</v>
       </c>
       <c r="F63" s="12" t="inlineStr">
         <is>
@@ -4733,16 +4733,16 @@
         </is>
       </c>
       <c r="B85" s="10" t="n">
-        <v>46628</v>
+        <v>46614</v>
       </c>
       <c r="C85" s="10" t="n">
         <v>46662</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.01219512195121952</v>
       </c>
       <c r="F85" s="12" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Complete Holdings Dividend Summary - 09/28/2026</t>
+          <t>Complete Holdings Dividend Summary - 10/05/2026</t>
         </is>
       </c>
     </row>
@@ -5004,7 +5004,7 @@
         <v>1.16</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.01017633144783744</v>
+        <v>0.01000906021484749</v>
       </c>
       <c r="I5" s="10" t="n">
         <v>46255</v>
@@ -5057,7 +5057,7 @@
         <v>10.08</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.02434900172108285</v>
+        <v>0.0250733801190597</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>46255</v>
@@ -5110,7 +5110,7 @@
         <v>8.552</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.004863235712254763</v>
+        <v>0.004618563878007072</v>
       </c>
       <c r="I7" s="10" t="n">
         <v>46231</v>
@@ -5163,7 +5163,7 @@
         <v>2.184</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>0.0264903876291373</v>
+        <v>0.02679754601226994</v>
       </c>
       <c r="I8" s="10" t="n">
         <v>46251</v>
@@ -5216,7 +5216,7 @@
         <v>2.812</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.04049539028131194</v>
+        <v>0.03974558303886926</v>
       </c>
       <c r="I9" s="10" t="n">
         <v>46251</v>
@@ -5269,7 +5269,7 @@
         <v>4.12</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.02627132204797521</v>
+        <v>0.02686576971590722</v>
       </c>
       <c r="I10" s="10" t="n">
         <v>46265</v>
@@ -5322,7 +5322,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.06110975334452722</v>
+        <v>0.0615498241205511</v>
       </c>
       <c r="I11" s="10" t="n">
         <v>46246</v>
@@ -5375,7 +5375,7 @@
         <v>5.2</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0.01946180602749289</v>
+        <v>0.01960488686266767</v>
       </c>
       <c r="I12" s="10" t="n">
         <v>46274</v>
@@ -5428,7 +5428,7 @@
         <v>0.96</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0.026044492243725</v>
+        <v>0.02546081297917674</v>
       </c>
       <c r="I13" s="10" t="n">
         <v>46254</v>
@@ -5481,7 +5481,7 @@
         <v>2.4</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>0.00785828876337411</v>
+        <v>0.007742684745454336</v>
       </c>
       <c r="I14" s="10" t="n">
         <v>46248</v>
@@ -5534,10 +5534,10 @@
         <v>1.68</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0.01573991652591106</v>
+        <v>0.01496259367888212</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>46209</v>
+        <v>46297</v>
       </c>
       <c r="J15" s="8" t="n">
         <v>0.02439024390243905</v>
@@ -5587,7 +5587,7 @@
         <v>7.12</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>0.03436293486905094</v>
+        <v>0.03491993354817895</v>
       </c>
       <c r="I16" s="10" t="n">
         <v>46253</v>
@@ -5640,7 +5640,7 @@
         <v>3.44</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0.01466044423432771</v>
+        <v>0.01482915257546235</v>
       </c>
       <c r="I17" s="10" t="n">
         <v>46211</v>
@@ -5693,7 +5693,7 @@
         <v>1.28</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0.02705845030636119</v>
+        <v>0.02692469447517261</v>
       </c>
       <c r="I18" s="10" t="n">
         <v>46280</v>
@@ -5746,7 +5746,7 @@
         <v>3.36</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0.05089367117307898</v>
+        <v>0.05169230769230769</v>
       </c>
       <c r="I19" s="10" t="n">
         <v>46280</v>
@@ -5799,7 +5799,7 @@
         <v>2.56</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0.02619193836660545</v>
+        <v>0.02542835780877885</v>
       </c>
       <c r="I20" s="10" t="n">
         <v>46247</v>
@@ -5852,7 +5852,7 @@
         <v>6.36</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0.018949438093953</v>
+        <v>0.01926572184075763</v>
       </c>
       <c r="I21" s="10" t="n">
         <v>46205</v>
@@ -5905,7 +5905,7 @@
         <v>1.18</v>
       </c>
       <c r="H22" s="19" t="n">
-        <v>0.01510303393679408</v>
+        <v>0.0152012882447665</v>
       </c>
       <c r="I22" s="20" t="n">
         <v>46223</v>
@@ -5958,7 +5958,7 @@
         <v>9.32</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>0.03197583639308245</v>
+        <v>0.03327086122266845</v>
       </c>
       <c r="I23" s="10" t="n">
         <v>46268</v>
@@ -6011,7 +6011,7 @@
         <v>5.52</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>0.02119327413458831</v>
+        <v>0.02049834685596653</v>
       </c>
       <c r="I24" s="10" t="n">
         <v>46262</v>
@@ -6064,7 +6064,7 @@
         <v>1.172</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0.05962859115015496</v>
+        <v>0.05796241542035767</v>
       </c>
       <c r="I25" s="10" t="n">
         <v>46216</v>
@@ -6117,7 +6117,7 @@
         <v>2</v>
       </c>
       <c r="H26" s="19" t="n">
-        <v>0.02734481838515112</v>
+        <v>0.0275824016146412</v>
       </c>
       <c r="I26" s="20" t="n">
         <v>46269</v>
@@ -6164,22 +6164,22 @@
         </is>
       </c>
       <c r="F27" s="7" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="G27" s="26" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0.03395269278011557</v>
+        <v>0.03503772989535116</v>
       </c>
       <c r="I27" s="10" t="n">
-        <v>46204</v>
+        <v>46296</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.01219512195121952</v>
       </c>
       <c r="K27" s="10" t="n">
-        <v>46628</v>
+        <v>46614</v>
       </c>
       <c r="L27" s="10" t="n">
         <v>46662</v>
@@ -6223,7 +6223,7 @@
         <v>2.44</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>0.01661898840947346</v>
+        <v>0.01707069676200025</v>
       </c>
       <c r="I28" s="10" t="n">
         <v>46269</v>
@@ -6276,7 +6276,7 @@
         <v>5.36</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.01969936444610691</v>
+        <v>0.02101466341764813</v>
       </c>
       <c r="I29" s="10" t="n">
         <v>46259</v>
@@ -6329,7 +6329,7 @@
         <v>6</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>0.01768920061562391</v>
+        <v>0.01813072291056532</v>
       </c>
       <c r="I30" s="10" t="n">
         <v>46209</v>
@@ -6382,7 +6382,7 @@
         <v>2.25</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0.02055733268831431</v>
+        <v>0.02102116058315701</v>
       </c>
       <c r="I31" s="10" t="n">
         <v>46216</v>
@@ -6435,10 +6435,10 @@
         <v>3.16</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>0.01157763600694031</v>
+        <v>0.0116302613355222</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>46203</v>
+        <v>46295</v>
       </c>
       <c r="J32" s="8" t="n">
         <v>0.05333333333333338</v>
@@ -6488,7 +6488,7 @@
         <v>2.88</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0.03276637021439819</v>
+        <v>0.03316635032377153</v>
       </c>
       <c r="I33" s="10" t="n">
         <v>46290</v>
@@ -6541,7 +6541,7 @@
         <v>1.92</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0.03987953020551666</v>
+        <v>0.04340945104841216</v>
       </c>
       <c r="I34" s="10" t="n">
         <v>46209</v>
@@ -6594,7 +6594,7 @@
         <v>3.64</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>0.007144434529232485</v>
+        <v>0.006893939393939394</v>
       </c>
       <c r="I35" s="10" t="n">
         <v>46254</v>
@@ -6647,7 +6647,7 @@
         <v>3.48</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>0.02871523995292049</v>
+        <v>0.0269120722736316</v>
       </c>
       <c r="I36" s="10" t="n">
         <v>46211</v>
@@ -6700,7 +6700,7 @@
         <v>1.64</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>0.04558087884561619</v>
+        <v>0.0497045022909573</v>
       </c>
       <c r="I37" s="10" t="n">
         <v>46266</v>
@@ -6753,7 +6753,7 @@
         <v>1.158</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0.03028242544905738</v>
+        <v>0.03123398452246422</v>
       </c>
       <c r="I38" s="10" t="n">
         <v>46251</v>
@@ -6800,19 +6800,19 @@
         </is>
       </c>
       <c r="F39" s="7" t="n">
-        <v>0.271</v>
+        <v>0.272</v>
       </c>
       <c r="G39" s="26" t="n">
-        <v>3.252</v>
+        <v>3.264</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>0.05867388443418352</v>
+        <v>0.06097515550966866</v>
       </c>
       <c r="I39" s="10" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>0.003703703703703707</v>
+        <v>0.003690036900369007</v>
       </c>
       <c r="K39" s="10" t="n">
         <v>46461</v>
@@ -6859,7 +6859,7 @@
         <v>4.76</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0.04749076963560451</v>
+        <v>0.04781997143077665</v>
       </c>
       <c r="I40" s="10" t="n">
         <v>46231</v>
@@ -6912,7 +6912,7 @@
         <v>2.68</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>0.04014379739729774</v>
+        <v>0.03948725344843111</v>
       </c>
       <c r="I41" s="10" t="n">
         <v>46274</v>
@@ -6965,7 +6965,7 @@
         <v>5.92</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>0.04644933337595475</v>
+        <v>0.04754065390450687</v>
       </c>
       <c r="I42" s="10" t="n">
         <v>46269</v>
@@ -7018,7 +7018,7 @@
         <v>1.72</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>0.06040386222854276</v>
+        <v>0.06260236491789237</v>
       </c>
       <c r="I43" s="10" t="n">
         <v>46227</v>
@@ -7071,7 +7071,7 @@
         <v>3.36</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>0.0289443082784107</v>
+        <v>0.02993185232025556</v>
       </c>
       <c r="I44" s="10" t="n">
         <v>46268</v>
@@ -7124,7 +7124,7 @@
         <v>4.356</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>0.02960948806953896</v>
+        <v>0.03003827202933425</v>
       </c>
       <c r="I45" s="10" t="n">
         <v>46227</v>
@@ -7177,7 +7177,7 @@
         <v>2.204</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>0.04796517874658265</v>
+        <v>0.04941704204942651</v>
       </c>
       <c r="I46" s="10" t="n">
         <v>46290</v>
@@ -7230,7 +7230,7 @@
         <v>5.08</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>0.01969831987068282</v>
+        <v>0.01903762580466897</v>
       </c>
       <c r="I47" s="20" t="n">
         <v>46252</v>
@@ -7283,7 +7283,7 @@
         <v>3.92</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>0.01576354660457816</v>
+        <v>0.01569066954036555</v>
       </c>
       <c r="I48" s="10" t="n">
         <v>46252</v>
@@ -7336,7 +7336,7 @@
         <v>9.76</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>0.02629593680273037</v>
+        <v>0.02675878779765391</v>
       </c>
       <c r="I49" s="10" t="n">
         <v>46253</v>
@@ -7389,7 +7389,7 @@
         <v>3.36</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>0.03726707923163132</v>
+        <v>0.0376935160759064</v>
       </c>
       <c r="I50" s="10" t="n">
         <v>46273</v>
@@ -7442,7 +7442,7 @@
         <v>5.2</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>0.04955920751734383</v>
+        <v>0.05039736368113923</v>
       </c>
       <c r="I51" s="10" t="n">
         <v>46280</v>
@@ -7489,19 +7489,19 @@
         </is>
       </c>
       <c r="F52" s="7" t="n">
-        <v>0.974</v>
+        <v>1.021</v>
       </c>
       <c r="G52" s="26" t="n">
-        <v>3.896</v>
+        <v>4.084</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>0.04263981485045694</v>
+        <v>0.04847765287972164</v>
       </c>
       <c r="I52" s="10" t="n">
-        <v>46112</v>
+        <v>46295</v>
       </c>
       <c r="J52" s="8" t="n">
-        <v>0.001006036217303824</v>
+        <v>0.04825462012320322</v>
       </c>
       <c r="K52" s="10" t="n">
         <v>46492</v>
@@ -7548,7 +7548,7 @@
         <v>5.68</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>0.0205462099807986</v>
+        <v>0.0196041137387245</v>
       </c>
       <c r="I53" s="10" t="n">
         <v>46234</v>
@@ -7601,7 +7601,7 @@
         <v>2.124</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>0.03422494284562026</v>
+        <v>0.03558086960144769</v>
       </c>
       <c r="I54" s="10" t="n">
         <v>46241</v>
@@ -7654,7 +7654,7 @@
         <v>5.68</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>0.02066506695303406</v>
+        <v>0.02059799423192274</v>
       </c>
       <c r="I55" s="10" t="n">
         <v>46265</v>
@@ -7707,7 +7707,7 @@
         <v>2.832</v>
       </c>
       <c r="H56" s="9" t="n">
-        <v>0.06022328353230328</v>
+        <v>0.06189487343217447</v>
       </c>
       <c r="I56" s="10" t="n">
         <v>46213</v>
@@ -7760,7 +7760,7 @@
         <v>4.12</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>0.02525206111259398</v>
+        <v>0.025221915188599</v>
       </c>
       <c r="I57" s="10" t="n">
         <v>46251</v>

--- a/data/dividend_calendar.xlsx
+++ b/data/dividend_calendar.xlsx
@@ -576,7 +576,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Estimated Dividend Calendar: Anticipated Announcements - 10/05/2026</t>
+          <t>Estimated Dividend Calendar: Anticipated Announcements - 10/12/2026</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
         <v>46048</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>-252</v>
+        <v>-259</v>
       </c>
       <c r="J6" s="10" t="n">
         <v>46413</v>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0.06260236491789237</v>
+        <v>0.060584714229587</v>
       </c>
     </row>
     <row r="7">
@@ -726,11 +726,11 @@
       <c r="H7" s="10" t="n">
         <v>46305</v>
       </c>
-      <c r="I7" s="13" t="n">
-        <v>5</v>
+      <c r="I7" s="11" t="n">
+        <v>-2</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>46339</v>
+        <v>46704</v>
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0.0269120722736316</v>
+        <v>0.02696629149713606</v>
       </c>
     </row>
     <row r="8">
@@ -773,7 +773,7 @@
         <v>46311</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J8" s="10" t="n">
         <v>46386</v>
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L8" s="9" t="n">
-        <v>0.0116302613355222</v>
+        <v>0.01212074758762932</v>
       </c>
     </row>
     <row r="9">
@@ -818,8 +818,8 @@
       <c r="H9" s="10" t="n">
         <v>46318</v>
       </c>
-      <c r="I9" s="14" t="n">
-        <v>18</v>
+      <c r="I9" s="13" t="n">
+        <v>11</v>
       </c>
       <c r="J9" s="10" t="n">
         <v>46352</v>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="L9" s="9" t="n">
-        <v>0.02049834685596653</v>
+        <v>0.02065597808138082</v>
       </c>
     </row>
     <row r="10">
@@ -865,7 +865,7 @@
         <v>46322</v>
       </c>
       <c r="I10" s="14" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J10" s="10" t="n">
         <v>46338</v>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0.02542835780877885</v>
+        <v>0.02477139648518534</v>
       </c>
     </row>
     <row r="11">
@@ -911,7 +911,7 @@
         <v>46329</v>
       </c>
       <c r="I11" s="14" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J11" s="10" t="n">
         <v>46338</v>
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0.007742684745454336</v>
+        <v>0.007395538275760539</v>
       </c>
     </row>
     <row r="12">
@@ -957,7 +957,7 @@
         <v>46332</v>
       </c>
       <c r="I12" s="14" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J12" s="10" t="n">
         <v>46346</v>
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="L12" s="9" t="n">
-        <v>0.02675878779765391</v>
+        <v>0.0270262782600054</v>
       </c>
     </row>
     <row r="13">
@@ -1003,7 +1003,7 @@
         <v>46341</v>
       </c>
       <c r="I13" s="14" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="J13" s="10" t="n">
         <v>46340</v>
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="L13" s="9" t="n">
-        <v>0.025221915188599</v>
+        <v>0.02392427756445954</v>
       </c>
     </row>
     <row r="14">
@@ -1049,7 +1049,7 @@
         <v>46344</v>
       </c>
       <c r="I14" s="14" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="J14" s="10" t="n">
         <v>46385</v>
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="L14" s="9" t="n">
-        <v>0.04340945104841216</v>
+        <v>0.04253433819142445</v>
       </c>
     </row>
     <row r="15">
@@ -1095,7 +1095,7 @@
         <v>46347</v>
       </c>
       <c r="I15" s="14" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="J15" s="10" t="n">
         <v>46358</v>
@@ -1106,7 +1106,7 @@
         </is>
       </c>
       <c r="L15" s="9" t="n">
-        <v>0.0497045022909573</v>
+        <v>0.04726905935798738</v>
       </c>
     </row>
     <row r="16">
@@ -1141,7 +1141,7 @@
         <v>46352</v>
       </c>
       <c r="I16" s="14" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="J16" s="10" t="n">
         <v>46400</v>
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0.05796241542035767</v>
+        <v>0.06113719328824217</v>
       </c>
     </row>
     <row r="17">
@@ -1181,13 +1181,13 @@
         <v>0.01204819277108435</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="H17" s="10" t="n">
         <v>46360</v>
       </c>
       <c r="I17" s="14" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="J17" s="10" t="n">
         <v>46371</v>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.05169230769230769</v>
+        <v>0.05388501362627859</v>
       </c>
     </row>
     <row r="18">
@@ -1233,7 +1233,7 @@
         <v>46366</v>
       </c>
       <c r="I18" s="14" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="J18" s="10" t="n">
         <v>46432</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0.0250733801190597</v>
+        <v>0.02435106070044935</v>
       </c>
     </row>
     <row r="19">
@@ -1279,7 +1279,7 @@
         <v>46380</v>
       </c>
       <c r="I19" s="14" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="J19" s="10" t="n">
         <v>46436</v>
@@ -1290,7 +1290,7 @@
         </is>
       </c>
       <c r="L19" s="9" t="n">
-        <v>0.02546081297917674</v>
+        <v>0.02474864597427012</v>
       </c>
     </row>
     <row r="20">
@@ -1325,7 +1325,7 @@
         <v>46383</v>
       </c>
       <c r="I20" s="21" t="n">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="J20" s="20" t="n">
         <v>46404</v>
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="L20" s="19" t="n">
-        <v>0.0152012882447665</v>
+        <v>0.01507024206908392</v>
       </c>
     </row>
     <row r="21">
@@ -1371,7 +1371,7 @@
         <v>46402</v>
       </c>
       <c r="I21" s="14" t="n">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="J21" s="10" t="n">
         <v>46483</v>
@@ -1382,7 +1382,7 @@
         </is>
       </c>
       <c r="L21" s="9" t="n">
-        <v>0.01482915257546235</v>
+        <v>0.01480142827673315</v>
       </c>
     </row>
     <row r="22">
@@ -1417,7 +1417,7 @@
         <v>46411</v>
       </c>
       <c r="I22" s="14" t="n">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="J22" s="10" t="n">
         <v>46435</v>
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="L22" s="9" t="n">
-        <v>0.03974558303886926</v>
+        <v>0.0369854010936235</v>
       </c>
     </row>
     <row r="23">
@@ -1463,7 +1463,7 @@
         <v>46417</v>
       </c>
       <c r="I23" s="14" t="n">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="J23" s="10" t="n">
         <v>46433</v>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0.03491993354817895</v>
+        <v>0.03298357685968453</v>
       </c>
     </row>
     <row r="24">
@@ -1509,7 +1509,7 @@
         <v>46423</v>
       </c>
       <c r="I24" s="14" t="n">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="J24" s="10" t="n">
         <v>46473</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="L24" s="9" t="n">
-        <v>0.03123398452246422</v>
+        <v>0.03014055323240503</v>
       </c>
     </row>
     <row r="25">
@@ -1555,7 +1555,7 @@
         <v>46428</v>
       </c>
       <c r="I25" s="14" t="n">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="J25" s="10" t="n">
         <v>46452</v>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="L25" s="9" t="n">
-        <v>0.01707069676200025</v>
+        <v>0.01631015976237089</v>
       </c>
     </row>
     <row r="26">
@@ -1601,7 +1601,7 @@
         <v>46428</v>
       </c>
       <c r="I26" s="14" t="n">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="J26" s="10" t="n">
         <v>46460</v>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="L26" s="9" t="n">
-        <v>0.05039736368113923</v>
+        <v>0.05061812352845635</v>
       </c>
     </row>
     <row r="27">
@@ -1647,7 +1647,7 @@
         <v>46429</v>
       </c>
       <c r="I27" s="21" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="J27" s="20" t="n">
         <v>46450</v>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="L27" s="19" t="n">
-        <v>0.0275824016146412</v>
+        <v>0.02748952065840456</v>
       </c>
     </row>
     <row r="28">
@@ -1693,7 +1693,7 @@
         <v>46431</v>
       </c>
       <c r="I28" s="14" t="n">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J28" s="10" t="n">
         <v>46480</v>
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="L28" s="9" t="n">
-        <v>0.01496259367888212</v>
+        <v>0.01454306253370746</v>
       </c>
     </row>
     <row r="29">
@@ -1739,7 +1739,7 @@
         <v>46432</v>
       </c>
       <c r="I29" s="14" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="J29" s="10" t="n">
         <v>46455</v>
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="L29" s="9" t="n">
-        <v>0.03948725344843111</v>
+        <v>0.03777308125827056</v>
       </c>
     </row>
     <row r="30">
@@ -1785,7 +1785,7 @@
         <v>46433</v>
       </c>
       <c r="I30" s="14" t="n">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="J30" s="10" t="n">
         <v>46425</v>
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="L30" s="9" t="n">
-        <v>0.004618563878007072</v>
+        <v>0.004833085693226959</v>
       </c>
     </row>
     <row r="31">
@@ -1831,7 +1831,7 @@
         <v>46433</v>
       </c>
       <c r="I31" s="14" t="n">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="J31" s="10" t="n">
         <v>46383</v>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="L31" s="9" t="n">
-        <v>0.01960488686266767</v>
+        <v>0.01841164230021915</v>
       </c>
     </row>
     <row r="32">
@@ -1877,7 +1877,7 @@
         <v>46433</v>
       </c>
       <c r="I32" s="14" t="n">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="J32" s="10" t="n">
         <v>46458</v>
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="L32" s="9" t="n">
-        <v>0.02692469447517261</v>
+        <v>0.02608518459263433</v>
       </c>
     </row>
     <row r="33">
@@ -1923,7 +1923,7 @@
         <v>46433</v>
       </c>
       <c r="I33" s="14" t="n">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="J33" s="10" t="n">
         <v>46634</v>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="L33" s="9" t="n">
-        <v>0.02993185232025556</v>
+        <v>0.03130677936678974</v>
       </c>
     </row>
     <row r="34">
@@ -1969,7 +1969,7 @@
         <v>46433</v>
       </c>
       <c r="I34" s="14" t="n">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="J34" s="10" t="n">
         <v>46608</v>
@@ -1980,7 +1980,7 @@
         </is>
       </c>
       <c r="L34" s="9" t="n">
-        <v>0.03558086960144769</v>
+        <v>0.03395140590432928</v>
       </c>
     </row>
     <row r="35">
@@ -2015,7 +2015,7 @@
         <v>46440</v>
       </c>
       <c r="I35" s="14" t="n">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="J35" s="10" t="n">
         <v>46450</v>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="L35" s="9" t="n">
-        <v>0.01000906021484749</v>
+        <v>0.01032212162618396</v>
       </c>
     </row>
     <row r="36">
@@ -2061,7 +2061,7 @@
         <v>46441</v>
       </c>
       <c r="I36" s="14" t="n">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="J36" s="10" t="n">
         <v>46456</v>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="L36" s="9" t="n">
-        <v>0.03327086122266845</v>
+        <v>0.03219121426382717</v>
       </c>
     </row>
     <row r="37">
@@ -2107,7 +2107,7 @@
         <v>46452</v>
       </c>
       <c r="I37" s="14" t="n">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J37" s="10" t="n">
         <v>46487</v>
@@ -2118,7 +2118,7 @@
         </is>
       </c>
       <c r="L37" s="9" t="n">
-        <v>0.01926572184075763</v>
+        <v>0.01906817724130214</v>
       </c>
     </row>
     <row r="38">
@@ -2138,13 +2138,13 @@
         </is>
       </c>
       <c r="D38" s="7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E38" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="E38" s="7" t="n">
-        <v>1.4</v>
-      </c>
       <c r="F38" s="8" t="n">
-        <v>0.07142857142857149</v>
+        <v>0.09999999999999994</v>
       </c>
       <c r="G38" s="9" t="n">
         <v>0.06</v>
@@ -2153,7 +2153,7 @@
         <v>46461</v>
       </c>
       <c r="I38" s="14" t="n">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="J38" s="10" t="n">
         <v>46665</v>
@@ -2164,7 +2164,7 @@
         </is>
       </c>
       <c r="L38" s="9" t="n">
-        <v>0.01813072291056532</v>
+        <v>0.01974688024131375</v>
       </c>
     </row>
     <row r="39">
@@ -2199,7 +2199,7 @@
         <v>46461</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="J39" s="10" t="n">
         <v>46386</v>
@@ -2210,7 +2210,7 @@
         </is>
       </c>
       <c r="L39" s="9" t="n">
-        <v>0.06097515550966866</v>
+        <v>0.06026977174155138</v>
       </c>
     </row>
     <row r="40">
@@ -2245,7 +2245,7 @@
         <v>46488</v>
       </c>
       <c r="I40" s="14" t="n">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="J40" s="10" t="n">
         <v>46498</v>
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="L40" s="9" t="n">
-        <v>0.03003827202933425</v>
+        <v>0.02866072298257646</v>
       </c>
     </row>
     <row r="41">
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>1.125</v>
+        <v>1.084</v>
       </c>
       <c r="E41" s="7" t="n">
         <v>1.087</v>
@@ -2291,7 +2291,7 @@
         <v>46492</v>
       </c>
       <c r="I41" s="14" t="n">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="J41" s="10" t="n">
         <v>46501</v>
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="L41" s="9" t="n">
-        <v>0.02102116058315701</v>
+        <v>0.01961369636922693</v>
       </c>
     </row>
     <row r="42">
@@ -2337,7 +2337,7 @@
         <v>46492</v>
       </c>
       <c r="I42" s="14" t="n">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="J42" s="10" t="n">
         <v>46376</v>
@@ -2348,7 +2348,7 @@
         </is>
       </c>
       <c r="L42" s="9" t="n">
-        <v>0.04847765287972164</v>
+        <v>0.04612083409655995</v>
       </c>
     </row>
     <row r="43">
@@ -2383,7 +2383,7 @@
         <v>46493</v>
       </c>
       <c r="I43" s="14" t="n">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="J43" s="10" t="n">
         <v>46531</v>
@@ -2394,7 +2394,7 @@
         </is>
       </c>
       <c r="L43" s="9" t="n">
-        <v>0.02101466341764813</v>
+        <v>0.02043461780192916</v>
       </c>
     </row>
     <row r="44">
@@ -2429,7 +2429,7 @@
         <v>46504</v>
       </c>
       <c r="I44" s="14" t="n">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="J44" s="10" t="n">
         <v>46562</v>
@@ -2440,7 +2440,7 @@
         </is>
       </c>
       <c r="L44" s="9" t="n">
-        <v>0.04941704204942651</v>
+        <v>0.04832803469187192</v>
       </c>
     </row>
     <row r="45">
@@ -2473,7 +2473,7 @@
         <v>46505</v>
       </c>
       <c r="I45" s="21" t="n">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="J45" s="20" t="n">
         <v>46526</v>
@@ -2484,7 +2484,7 @@
         </is>
       </c>
       <c r="L45" s="19" t="n">
-        <v>0.01903762580466897</v>
+        <v>0.01786279313034211</v>
       </c>
     </row>
     <row r="46">
@@ -2519,7 +2519,7 @@
         <v>46508</v>
       </c>
       <c r="I46" s="14" t="n">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="J46" s="10" t="n">
         <v>46518</v>
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="L46" s="9" t="n">
-        <v>0.04781997143077665</v>
+        <v>0.04579785550402819</v>
       </c>
     </row>
     <row r="47">
@@ -2565,7 +2565,7 @@
         <v>46515</v>
       </c>
       <c r="I47" s="14" t="n">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="J47" s="10" t="n">
         <v>46542</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="L47" s="9" t="n">
-        <v>0.04754065390450687</v>
+        <v>0.04691896062464589</v>
       </c>
     </row>
     <row r="48">
@@ -2611,7 +2611,7 @@
         <v>46532</v>
       </c>
       <c r="I48" s="14" t="n">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="J48" s="10" t="n">
         <v>46563</v>
@@ -2622,7 +2622,7 @@
         </is>
       </c>
       <c r="L48" s="9" t="n">
-        <v>0.03316635032377153</v>
+        <v>0.03109143998051593</v>
       </c>
     </row>
     <row r="49">
@@ -2657,7 +2657,7 @@
         <v>46589</v>
       </c>
       <c r="I49" s="14" t="n">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="J49" s="10" t="n">
         <v>46629</v>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="L49" s="9" t="n">
-        <v>0.02059799423192274</v>
+        <v>0.02034092608022438</v>
       </c>
     </row>
     <row r="50">
@@ -2703,7 +2703,7 @@
         <v>46591</v>
       </c>
       <c r="I50" s="14" t="n">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="J50" s="10" t="n">
         <v>46633</v>
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="L50" s="9" t="n">
-        <v>0.0376935160759064</v>
+        <v>0.03798756490592253</v>
       </c>
     </row>
     <row r="51">
@@ -2749,7 +2749,7 @@
         <v>46594</v>
       </c>
       <c r="I51" s="14" t="n">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="J51" s="10" t="n">
         <v>46613</v>
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="L51" s="9" t="n">
-        <v>0.01569066954036555</v>
+        <v>0.01515180818849923</v>
       </c>
     </row>
     <row r="52">
@@ -2795,7 +2795,7 @@
         <v>46595</v>
       </c>
       <c r="I52" s="14" t="n">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="J52" s="10" t="n">
         <v>46614</v>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="L52" s="9" t="n">
-        <v>0.02679754601226994</v>
+        <v>0.02660656666088859</v>
       </c>
     </row>
     <row r="53">
@@ -2841,7 +2841,7 @@
         <v>46597</v>
       </c>
       <c r="I53" s="14" t="n">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="J53" s="10" t="n">
         <v>46611</v>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="L53" s="9" t="n">
-        <v>0.0615498241205511</v>
+        <v>0.05990893907079166</v>
       </c>
     </row>
     <row r="54">
@@ -2887,7 +2887,7 @@
         <v>46598</v>
       </c>
       <c r="I54" s="14" t="n">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="J54" s="10" t="n">
         <v>46629</v>
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="L54" s="9" t="n">
-        <v>0.02686576971590722</v>
+        <v>0.02719112911712621</v>
       </c>
     </row>
     <row r="55">
@@ -2933,7 +2933,7 @@
         <v>46614</v>
       </c>
       <c r="I55" s="14" t="n">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="J55" s="10" t="n">
         <v>46662</v>
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="L55" s="9" t="n">
-        <v>0.03503772989535116</v>
+        <v>0.03471713997023395</v>
       </c>
     </row>
     <row r="56">
@@ -2979,7 +2979,7 @@
         <v>46643</v>
       </c>
       <c r="I56" s="14" t="n">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="J56" s="10" t="n">
         <v>46709</v>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="L56" s="9" t="n">
-        <v>0.006893939393939394</v>
+        <v>0.006744487525791792</v>
       </c>
     </row>
     <row r="57">
@@ -3025,7 +3025,7 @@
         <v>46645</v>
       </c>
       <c r="I57" s="14" t="n">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="J57" s="10" t="n">
         <v>46668</v>
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L57" s="9" t="n">
-        <v>0.06189487343217447</v>
+        <v>0.06643208841292222</v>
       </c>
     </row>
     <row r="58">
@@ -3071,7 +3071,7 @@
         <v>46650</v>
       </c>
       <c r="I58" s="14" t="n">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="J58" s="10" t="n">
         <v>46690</v>
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="L58" s="9" t="n">
-        <v>0.0196041137387245</v>
+        <v>0.02024161753504176</v>
       </c>
     </row>
   </sheetData>
@@ -3117,7 +3117,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Expected Increase Announcements by Month - 10/05/2026</t>
+          <t>Expected Increase Announcements by Month - 10/12/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
         <v>46305</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>46339</v>
+        <v>46704</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>0.87</v>
@@ -4175,10 +4175,10 @@
         <v>46665</v>
       </c>
       <c r="D56" s="7" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="E56" s="8" t="n">
-        <v>0.07142857142857149</v>
+        <v>0.09999999999999994</v>
       </c>
       <c r="F56" s="12" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>46501</v>
       </c>
       <c r="D62" s="7" t="n">
-        <v>1.125</v>
+        <v>1.084</v>
       </c>
       <c r="E62" s="8" t="n">
         <v>0.03495860165593379</v>
@@ -4900,7 +4900,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Complete Holdings Dividend Summary - 10/05/2026</t>
+          <t>Complete Holdings Dividend Summary - 10/12/2026</t>
         </is>
       </c>
     </row>
@@ -5004,7 +5004,7 @@
         <v>1.16</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.01000906021484749</v>
+        <v>0.01032212162618396</v>
       </c>
       <c r="I5" s="10" t="n">
         <v>46255</v>
@@ -5057,7 +5057,7 @@
         <v>10.08</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.0250733801190597</v>
+        <v>0.02435106070044935</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>46255</v>
@@ -5110,7 +5110,7 @@
         <v>8.552</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.004618563878007072</v>
+        <v>0.004833085693226959</v>
       </c>
       <c r="I7" s="10" t="n">
         <v>46231</v>
@@ -5163,7 +5163,7 @@
         <v>2.184</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>0.02679754601226994</v>
+        <v>0.02660656666088859</v>
       </c>
       <c r="I8" s="10" t="n">
         <v>46251</v>
@@ -5216,7 +5216,7 @@
         <v>2.812</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.03974558303886926</v>
+        <v>0.0369854010936235</v>
       </c>
       <c r="I9" s="10" t="n">
         <v>46251</v>
@@ -5269,7 +5269,7 @@
         <v>4.12</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.02686576971590722</v>
+        <v>0.02719112911712621</v>
       </c>
       <c r="I10" s="10" t="n">
         <v>46265</v>
@@ -5322,7 +5322,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.0615498241205511</v>
+        <v>0.05990893907079166</v>
       </c>
       <c r="I11" s="10" t="n">
         <v>46246</v>
@@ -5375,7 +5375,7 @@
         <v>5.2</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0.01960488686266767</v>
+        <v>0.01841164230021915</v>
       </c>
       <c r="I12" s="10" t="n">
         <v>46274</v>
@@ -5428,7 +5428,7 @@
         <v>0.96</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0.02546081297917674</v>
+        <v>0.02474864597427012</v>
       </c>
       <c r="I13" s="10" t="n">
         <v>46254</v>
@@ -5481,7 +5481,7 @@
         <v>2.4</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>0.007742684745454336</v>
+        <v>0.007395538275760539</v>
       </c>
       <c r="I14" s="10" t="n">
         <v>46248</v>
@@ -5534,7 +5534,7 @@
         <v>1.68</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0.01496259367888212</v>
+        <v>0.01454306253370746</v>
       </c>
       <c r="I15" s="10" t="n">
         <v>46297</v>
@@ -5587,7 +5587,7 @@
         <v>7.12</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>0.03491993354817895</v>
+        <v>0.03298357685968453</v>
       </c>
       <c r="I16" s="10" t="n">
         <v>46253</v>
@@ -5640,10 +5640,10 @@
         <v>3.44</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0.01482915257546235</v>
+        <v>0.01480142827673315</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>46211</v>
+        <v>46301</v>
       </c>
       <c r="J17" s="8" t="n">
         <v>0.07499999999999993</v>
@@ -5693,7 +5693,7 @@
         <v>1.28</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0.02692469447517261</v>
+        <v>0.02608518459263433</v>
       </c>
       <c r="I18" s="10" t="n">
         <v>46280</v>
@@ -5746,7 +5746,7 @@
         <v>3.36</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0.05169230769230769</v>
+        <v>0.05388501362627859</v>
       </c>
       <c r="I19" s="10" t="n">
         <v>46280</v>
@@ -5799,7 +5799,7 @@
         <v>2.56</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0.02542835780877885</v>
+        <v>0.02477139648518534</v>
       </c>
       <c r="I20" s="10" t="n">
         <v>46247</v>
@@ -5852,10 +5852,10 @@
         <v>6.36</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0.01926572184075763</v>
+        <v>0.01906817724130214</v>
       </c>
       <c r="I21" s="10" t="n">
-        <v>46205</v>
+        <v>46304</v>
       </c>
       <c r="J21" s="8" t="n">
         <v>0.06000000000000005</v>
@@ -5905,7 +5905,7 @@
         <v>1.18</v>
       </c>
       <c r="H22" s="19" t="n">
-        <v>0.0152012882447665</v>
+        <v>0.01507024206908392</v>
       </c>
       <c r="I22" s="20" t="n">
         <v>46223</v>
@@ -5958,7 +5958,7 @@
         <v>9.32</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>0.03327086122266845</v>
+        <v>0.03219121426382717</v>
       </c>
       <c r="I23" s="10" t="n">
         <v>46268</v>
@@ -6011,7 +6011,7 @@
         <v>5.52</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>0.02049834685596653</v>
+        <v>0.02065597808138082</v>
       </c>
       <c r="I24" s="10" t="n">
         <v>46262</v>
@@ -6064,7 +6064,7 @@
         <v>1.172</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0.05796241542035767</v>
+        <v>0.06113719328824217</v>
       </c>
       <c r="I25" s="10" t="n">
         <v>46216</v>
@@ -6117,7 +6117,7 @@
         <v>2</v>
       </c>
       <c r="H26" s="19" t="n">
-        <v>0.0275824016146412</v>
+        <v>0.02748952065840456</v>
       </c>
       <c r="I26" s="20" t="n">
         <v>46269</v>
@@ -6170,7 +6170,7 @@
         <v>3.32</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0.03503772989535116</v>
+        <v>0.03471713997023395</v>
       </c>
       <c r="I27" s="10" t="n">
         <v>46296</v>
@@ -6223,7 +6223,7 @@
         <v>2.44</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>0.01707069676200025</v>
+        <v>0.01631015976237089</v>
       </c>
       <c r="I28" s="10" t="n">
         <v>46269</v>
@@ -6276,7 +6276,7 @@
         <v>5.36</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.02101466341764813</v>
+        <v>0.02043461780192916</v>
       </c>
       <c r="I29" s="10" t="n">
         <v>46259</v>
@@ -6323,19 +6323,19 @@
         </is>
       </c>
       <c r="F30" s="7" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="G30" s="26" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>0.01813072291056532</v>
+        <v>0.01974688024131375</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>46209</v>
+        <v>46301</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>0.07142857142857149</v>
+        <v>0.09999999999999994</v>
       </c>
       <c r="K30" s="10" t="n">
         <v>46461</v>
@@ -6376,16 +6376,16 @@
         </is>
       </c>
       <c r="F31" s="7" t="n">
-        <v>1.125</v>
+        <v>1.084</v>
       </c>
       <c r="G31" s="26" t="n">
-        <v>2.25</v>
+        <v>2.168</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0.02102116058315701</v>
+        <v>0.01961369636922693</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>46216</v>
+        <v>46304</v>
       </c>
       <c r="J31" s="8" t="n">
         <v>0.03495860165593379</v>
@@ -6435,7 +6435,7 @@
         <v>3.16</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>0.0116302613355222</v>
+        <v>0.01212074758762932</v>
       </c>
       <c r="I32" s="10" t="n">
         <v>46295</v>
@@ -6488,7 +6488,7 @@
         <v>2.88</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0.03316635032377153</v>
+        <v>0.03109143998051593</v>
       </c>
       <c r="I33" s="10" t="n">
         <v>46290</v>
@@ -6541,7 +6541,7 @@
         <v>1.92</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0.04340945104841216</v>
+        <v>0.04253433819142445</v>
       </c>
       <c r="I34" s="10" t="n">
         <v>46209</v>
@@ -6594,7 +6594,7 @@
         <v>3.64</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>0.006893939393939394</v>
+        <v>0.006744487525791792</v>
       </c>
       <c r="I35" s="10" t="n">
         <v>46254</v>
@@ -6647,7 +6647,7 @@
         <v>3.48</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>0.0269120722736316</v>
+        <v>0.02696629149713606</v>
       </c>
       <c r="I36" s="10" t="n">
         <v>46211</v>
@@ -6659,7 +6659,7 @@
         <v>46305</v>
       </c>
       <c r="L36" s="10" t="n">
-        <v>46339</v>
+        <v>46704</v>
       </c>
       <c r="M36" s="12" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>1.64</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>0.0497045022909573</v>
+        <v>0.04726905935798738</v>
       </c>
       <c r="I37" s="10" t="n">
         <v>46266</v>
@@ -6753,7 +6753,7 @@
         <v>1.158</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0.03123398452246422</v>
+        <v>0.03014055323240503</v>
       </c>
       <c r="I38" s="10" t="n">
         <v>46251</v>
@@ -6806,7 +6806,7 @@
         <v>3.264</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>0.06097515550966866</v>
+        <v>0.06026977174155138</v>
       </c>
       <c r="I39" s="10" t="n">
         <v>46295</v>
@@ -6859,7 +6859,7 @@
         <v>4.76</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0.04781997143077665</v>
+        <v>0.04579785550402819</v>
       </c>
       <c r="I40" s="10" t="n">
         <v>46231</v>
@@ -6912,7 +6912,7 @@
         <v>2.68</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>0.03948725344843111</v>
+        <v>0.03777308125827056</v>
       </c>
       <c r="I41" s="10" t="n">
         <v>46274</v>
@@ -6965,7 +6965,7 @@
         <v>5.92</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>0.04754065390450687</v>
+        <v>0.04691896062464589</v>
       </c>
       <c r="I42" s="10" t="n">
         <v>46269</v>
@@ -7018,7 +7018,7 @@
         <v>1.72</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>0.06260236491789237</v>
+        <v>0.060584714229587</v>
       </c>
       <c r="I43" s="10" t="n">
         <v>46227</v>
@@ -7071,7 +7071,7 @@
         <v>3.36</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>0.02993185232025556</v>
+        <v>0.03130677936678974</v>
       </c>
       <c r="I44" s="10" t="n">
         <v>46268</v>
@@ -7124,7 +7124,7 @@
         <v>4.356</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>0.03003827202933425</v>
+        <v>0.02866072298257646</v>
       </c>
       <c r="I45" s="10" t="n">
         <v>46227</v>
@@ -7177,7 +7177,7 @@
         <v>2.204</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>0.04941704204942651</v>
+        <v>0.04832803469187192</v>
       </c>
       <c r="I46" s="10" t="n">
         <v>46290</v>
@@ -7230,7 +7230,7 @@
         <v>5.08</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>0.01903762580466897</v>
+        <v>0.01786279313034211</v>
       </c>
       <c r="I47" s="20" t="n">
         <v>46252</v>
@@ -7283,7 +7283,7 @@
         <v>3.92</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>0.01569066954036555</v>
+        <v>0.01515180818849923</v>
       </c>
       <c r="I48" s="10" t="n">
         <v>46252</v>
@@ -7336,7 +7336,7 @@
         <v>9.76</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>0.02675878779765391</v>
+        <v>0.0270262782600054</v>
       </c>
       <c r="I49" s="10" t="n">
         <v>46253</v>
@@ -7389,7 +7389,7 @@
         <v>3.36</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>0.0376935160759064</v>
+        <v>0.03798756490592253</v>
       </c>
       <c r="I50" s="10" t="n">
         <v>46273</v>
@@ -7442,7 +7442,7 @@
         <v>5.2</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>0.05039736368113923</v>
+        <v>0.05061812352845635</v>
       </c>
       <c r="I51" s="10" t="n">
         <v>46280</v>
@@ -7495,7 +7495,7 @@
         <v>4.084</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>0.04847765287972164</v>
+        <v>0.04612083409655995</v>
       </c>
       <c r="I52" s="10" t="n">
         <v>46295</v>
@@ -7548,7 +7548,7 @@
         <v>5.68</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>0.0196041137387245</v>
+        <v>0.02024161753504176</v>
       </c>
       <c r="I53" s="10" t="n">
         <v>46234</v>
@@ -7601,7 +7601,7 @@
         <v>2.124</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>0.03558086960144769</v>
+        <v>0.03395140590432928</v>
       </c>
       <c r="I54" s="10" t="n">
         <v>46241</v>
@@ -7654,7 +7654,7 @@
         <v>5.68</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>0.02059799423192274</v>
+        <v>0.02034092608022438</v>
       </c>
       <c r="I55" s="10" t="n">
         <v>46265</v>
@@ -7707,10 +7707,10 @@
         <v>2.832</v>
       </c>
       <c r="H56" s="9" t="n">
-        <v>0.06189487343217447</v>
+        <v>0.06643208841292222</v>
       </c>
       <c r="I56" s="10" t="n">
-        <v>46213</v>
+        <v>46304</v>
       </c>
       <c r="J56" s="8" t="n">
         <v>0.02608695652173916</v>
@@ -7760,7 +7760,7 @@
         <v>4.12</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>0.025221915188599</v>
+        <v>0.02392427756445954</v>
       </c>
       <c r="I57" s="10" t="n">
         <v>46251</v>

--- a/data/dividend_calendar.xlsx
+++ b/data/dividend_calendar.xlsx
@@ -145,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -166,20 +166,23 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -576,7 +579,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Estimated Dividend Calendar: Anticipated Announcements - 10/12/2026</t>
+          <t>Estimated Dividend Calendar: Anticipated Announcements - 10/19/2026</t>
         </is>
       </c>
     </row>
@@ -681,7 +684,7 @@
         <v>46048</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>-259</v>
+        <v>-266</v>
       </c>
       <c r="J6" s="10" t="n">
         <v>46413</v>
@@ -692,13 +695,13 @@
         </is>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0.060584714229587</v>
+        <v>0.05809829510539736</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>HII</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -712,25 +715,25 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>0.87</v>
+        <v>1.38</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>0.85</v>
+        <v>1.35</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>0.0235294117647059</v>
+        <v>0.02222222222222208</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>46305</v>
-      </c>
-      <c r="I7" s="11" t="n">
-        <v>-2</v>
+        <v>46318</v>
+      </c>
+      <c r="I7" s="13" t="n">
+        <v>4</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>46704</v>
+        <v>46352</v>
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
@@ -738,59 +741,57 @@
         </is>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0.02696629149713606</v>
+        <v>0.02062048170108176</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>LECO</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>0.05333333333333338</v>
-      </c>
-      <c r="G8" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H8" s="10" t="n">
-        <v>46311</v>
-      </c>
-      <c r="I8" s="13" t="n">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>MSM</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F8" s="17" t="n">
+        <v>0.0235294117647059</v>
+      </c>
+      <c r="G8" s="18" t="n"/>
+      <c r="H8" s="19" t="n">
+        <v>46318</v>
+      </c>
+      <c r="I8" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="J8" s="10" t="n">
-        <v>46386</v>
-      </c>
-      <c r="K8" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L8" s="9" t="n">
-        <v>0.01212074758762932</v>
+      <c r="J8" s="19" t="n">
+        <v>46339</v>
+      </c>
+      <c r="K8" s="21" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="L8" s="22" t="n">
+        <v>0.02687466099600802</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -804,25 +805,25 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>1.38</v>
+        <v>0.64</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>1.35</v>
+        <v>0.6</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>0.02222222222222208</v>
+        <v>0.06666666666666674</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>46318</v>
+        <v>46322</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>46352</v>
+        <v>46338</v>
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
@@ -830,13 +831,13 @@
         </is>
       </c>
       <c r="L9" s="9" t="n">
-        <v>0.02065597808138082</v>
+        <v>0.02452812046212039</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -850,21 +851,21 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.06666666666666674</v>
+        <v>0.09090909090909079</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>46322</v>
-      </c>
-      <c r="I10" s="14" t="n">
+        <v>46329</v>
+      </c>
+      <c r="I10" s="23" t="n">
         <v>15</v>
       </c>
       <c r="J10" s="10" t="n">
@@ -876,13 +877,13 @@
         </is>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0.02477139648518534</v>
+        <v>0.007036008061734701</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -896,25 +897,25 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.6</v>
+        <v>2.44</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>0.55</v>
+        <v>2.14</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>0.09090909090909079</v>
+        <v>0.1401869158878504</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>0.08</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>46329</v>
-      </c>
-      <c r="I11" s="14" t="n">
-        <v>22</v>
+        <v>46332</v>
+      </c>
+      <c r="I11" s="23" t="n">
+        <v>18</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>46338</v>
+        <v>46346</v>
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
@@ -922,13 +923,13 @@
         </is>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0.007395538275760539</v>
+        <v>0.02684619212402568</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -942,25 +943,25 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.44</v>
+        <v>1.03</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>2.14</v>
+        <v>0.99</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.1401869158878504</v>
+        <v>0.04040404040404044</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>46332</v>
-      </c>
-      <c r="I12" s="14" t="n">
-        <v>25</v>
+        <v>46341</v>
+      </c>
+      <c r="I12" s="23" t="n">
+        <v>27</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>46346</v>
+        <v>46340</v>
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
@@ -968,13 +969,13 @@
         </is>
       </c>
       <c r="L12" s="9" t="n">
-        <v>0.0270262782600054</v>
+        <v>0.02299684646296404</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -984,29 +985,29 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1.03</v>
+        <v>0.48</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>0.99</v>
+        <v>0.45</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0.04040404040404044</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>46341</v>
-      </c>
-      <c r="I13" s="14" t="n">
-        <v>34</v>
+        <v>46344</v>
+      </c>
+      <c r="I13" s="23" t="n">
+        <v>30</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>46340</v>
+        <v>46385</v>
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
@@ -1014,13 +1015,13 @@
         </is>
       </c>
       <c r="L13" s="9" t="n">
-        <v>0.02392427756445954</v>
+        <v>0.0418647250543317</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -1034,25 +1035,25 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.48</v>
+        <v>0.41</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>46344</v>
-      </c>
-      <c r="I14" s="14" t="n">
-        <v>37</v>
+        <v>46347</v>
+      </c>
+      <c r="I14" s="23" t="n">
+        <v>33</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>46385</v>
+        <v>46358</v>
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
@@ -1060,13 +1061,13 @@
         </is>
       </c>
       <c r="L14" s="9" t="n">
-        <v>0.04253433819142445</v>
+        <v>0.04446252066229808</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -1076,29 +1077,29 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.41</v>
+        <v>0.293</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>0.4</v>
+        <v>0.29</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.01034482758620691</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>46347</v>
-      </c>
-      <c r="I15" s="14" t="n">
-        <v>40</v>
+        <v>46351</v>
+      </c>
+      <c r="I15" s="23" t="n">
+        <v>37</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>46358</v>
+        <v>46399</v>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
@@ -1106,13 +1107,13 @@
         </is>
       </c>
       <c r="L15" s="9" t="n">
-        <v>0.04726905935798738</v>
+        <v>0.05780204234676849</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>EMN</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -1122,29 +1123,29 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.293</v>
+        <v>0.84</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>0.29</v>
+        <v>0.83</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0.01034482758620691</v>
+        <v>0.01204819277108435</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>46352</v>
-      </c>
-      <c r="I16" s="14" t="n">
-        <v>45</v>
+        <v>46360</v>
+      </c>
+      <c r="I16" s="23" t="n">
+        <v>46</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>46400</v>
+        <v>46371</v>
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
@@ -1152,13 +1153,13 @@
         </is>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0.06113719328824217</v>
+        <v>0.05387205479463784</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>EMN</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -1168,29 +1169,29 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.84</v>
+        <v>2.52</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>0.83</v>
+        <v>2.38</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0.01204819277108435</v>
+        <v>0.05882352941176476</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>46360</v>
-      </c>
-      <c r="I17" s="14" t="n">
-        <v>53</v>
+        <v>46366</v>
+      </c>
+      <c r="I17" s="23" t="n">
+        <v>52</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>46371</v>
+        <v>46432</v>
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
@@ -1198,13 +1199,13 @@
         </is>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.05388501362627859</v>
+        <v>0.02329343307176349</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -1218,25 +1219,25 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>2.52</v>
+        <v>0.24</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>2.38</v>
+        <v>0.23</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0.05882352941176476</v>
+        <v>0.04347826086956513</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>46366</v>
-      </c>
-      <c r="I18" s="14" t="n">
-        <v>59</v>
+        <v>46380</v>
+      </c>
+      <c r="I18" s="23" t="n">
+        <v>66</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>46432</v>
+        <v>46436</v>
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
@@ -1244,105 +1245,105 @@
         </is>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0.02435106070044935</v>
+        <v>0.02386278923498678</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>CNP</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="F19" s="8" t="n">
-        <v>0.04347826086956513</v>
-      </c>
-      <c r="G19" s="9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H19" s="10" t="n">
-        <v>46380</v>
-      </c>
-      <c r="I19" s="14" t="n">
-        <v>73</v>
-      </c>
-      <c r="J19" s="10" t="n">
-        <v>46436</v>
-      </c>
-      <c r="K19" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L19" s="9" t="n">
-        <v>0.02474864597427012</v>
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>GGG</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="F19" s="17" t="n">
+        <v>0.07272727272727258</v>
+      </c>
+      <c r="G19" s="22" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H19" s="19" t="n">
+        <v>46383</v>
+      </c>
+      <c r="I19" s="24" t="n">
+        <v>69</v>
+      </c>
+      <c r="J19" s="19" t="n">
+        <v>46404</v>
+      </c>
+      <c r="K19" s="21" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="L19" s="22" t="n">
+        <v>0.0146057678750838</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>GGG</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>Jan</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E20" s="17" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="F20" s="18" t="n">
-        <v>0.07272727272727258</v>
-      </c>
-      <c r="G20" s="19" t="n">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>0.07499999999999993</v>
+      </c>
+      <c r="G20" s="9" t="n">
         <v>0.06</v>
       </c>
-      <c r="H20" s="20" t="n">
-        <v>46383</v>
-      </c>
-      <c r="I20" s="21" t="n">
-        <v>76</v>
-      </c>
-      <c r="J20" s="20" t="n">
-        <v>46404</v>
-      </c>
-      <c r="K20" s="22" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
-      <c r="L20" s="19" t="n">
-        <v>0.01507024206908392</v>
+      <c r="H20" s="10" t="n">
+        <v>46402</v>
+      </c>
+      <c r="I20" s="23" t="n">
+        <v>88</v>
+      </c>
+      <c r="J20" s="10" t="n">
+        <v>46483</v>
+      </c>
+      <c r="K20" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="n">
+        <v>0.01468798690508526</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>BKH</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -1352,29 +1353,29 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.86</v>
+        <v>0.703</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>0.8</v>
+        <v>0.676</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>0.07499999999999993</v>
+        <v>0.03994082840236673</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>46402</v>
-      </c>
-      <c r="I21" s="14" t="n">
-        <v>95</v>
+        <v>46411</v>
+      </c>
+      <c r="I21" s="23" t="n">
+        <v>97</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>46483</v>
+        <v>46435</v>
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
@@ -1382,13 +1383,13 @@
         </is>
       </c>
       <c r="L21" s="9" t="n">
-        <v>0.01480142827673315</v>
+        <v>0.03667786059118737</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>BKH</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -1402,25 +1403,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.703</v>
+        <v>1.78</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>0.676</v>
+        <v>1.71</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>0.03994082840236673</v>
+        <v>0.04093567251461992</v>
       </c>
       <c r="G22" s="9" t="n">
         <v>0.04</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>46411</v>
-      </c>
-      <c r="I22" s="14" t="n">
-        <v>104</v>
+        <v>46417</v>
+      </c>
+      <c r="I22" s="23" t="n">
+        <v>103</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>46435</v>
+        <v>46433</v>
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
@@ -1428,45 +1429,45 @@
         </is>
       </c>
       <c r="L22" s="9" t="n">
-        <v>0.0369854010936235</v>
+        <v>0.03156028283409273</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>1.78</v>
+        <v>0.579</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>1.71</v>
+        <v>0.584</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>0.04093567251461992</v>
+        <v>1.183219178082192</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>46417</v>
-      </c>
-      <c r="I23" s="14" t="n">
-        <v>110</v>
+        <v>46423</v>
+      </c>
+      <c r="I23" s="23" t="n">
+        <v>109</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>46433</v>
+        <v>46473</v>
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
@@ -1474,18 +1475,18 @@
         </is>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0.03298357685968453</v>
+        <v>0.0300600424991833</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Semi-Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -1494,25 +1495,25 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.579</v>
+        <v>0.61</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>0.584</v>
+        <v>0.58</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>1.183219178082192</v>
+        <v>0.05172413793103453</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>46423</v>
-      </c>
-      <c r="I24" s="14" t="n">
-        <v>116</v>
+        <v>46428</v>
+      </c>
+      <c r="I24" s="23" t="n">
+        <v>114</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>46473</v>
+        <v>46452</v>
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
@@ -1520,13 +1521,13 @@
         </is>
       </c>
       <c r="L24" s="9" t="n">
-        <v>0.03014055323240503</v>
+        <v>0.01601680490124256</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -1540,25 +1541,25 @@
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>0.61</v>
+        <v>1.3</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>0.58</v>
+        <v>1.27</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>0.05172413793103453</v>
+        <v>0.02362204724409451</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H25" s="10" t="n">
         <v>46428</v>
       </c>
-      <c r="I25" s="14" t="n">
-        <v>121</v>
+      <c r="I25" s="23" t="n">
+        <v>114</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>46452</v>
+        <v>46460</v>
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
@@ -1566,105 +1567,105 @@
         </is>
       </c>
       <c r="L25" s="9" t="n">
-        <v>0.01631015976237089</v>
+        <v>0.05203642533893469</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>TROW</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>HWC</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="D26" s="7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E26" s="7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="F26" s="8" t="n">
-        <v>0.02362204724409451</v>
-      </c>
-      <c r="G26" s="9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="H26" s="10" t="n">
-        <v>46428</v>
-      </c>
-      <c r="I26" s="14" t="n">
-        <v>121</v>
-      </c>
-      <c r="J26" s="10" t="n">
-        <v>46460</v>
-      </c>
-      <c r="K26" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L26" s="9" t="n">
-        <v>0.05061812352845635</v>
+      <c r="D26" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F26" s="17" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="G26" s="22" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H26" s="19" t="n">
+        <v>46429</v>
+      </c>
+      <c r="I26" s="24" t="n">
+        <v>115</v>
+      </c>
+      <c r="J26" s="19" t="n">
+        <v>46450</v>
+      </c>
+      <c r="K26" s="21" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="L26" s="22" t="n">
+        <v>0.02740852359246717</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>HWC</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E27" s="17" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="F27" s="18" t="n">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="G27" s="19" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H27" s="20" t="n">
-        <v>46429</v>
-      </c>
-      <c r="I27" s="21" t="n">
-        <v>122</v>
-      </c>
-      <c r="J27" s="20" t="n">
-        <v>46450</v>
-      </c>
-      <c r="K27" s="22" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
-      <c r="L27" s="19" t="n">
-        <v>0.02748952065840456</v>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>CSCO</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>0.02439024390243905</v>
+      </c>
+      <c r="G27" s="9" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H27" s="10" t="n">
+        <v>46431</v>
+      </c>
+      <c r="I27" s="23" t="n">
+        <v>117</v>
+      </c>
+      <c r="J27" s="10" t="n">
+        <v>46480</v>
+      </c>
+      <c r="K27" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+      <c r="L27" s="9" t="n">
+        <v>0.01569140206127972</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>PEG</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -1674,29 +1675,29 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>0.42</v>
+        <v>0.67</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>0.41</v>
+        <v>0.63</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>0.02439024390243905</v>
+        <v>0.06349206349206354</v>
       </c>
       <c r="G28" s="9" t="n">
         <v>0.04</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>46431</v>
-      </c>
-      <c r="I28" s="14" t="n">
-        <v>124</v>
+        <v>46432</v>
+      </c>
+      <c r="I28" s="23" t="n">
+        <v>118</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>46480</v>
+        <v>46455</v>
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
@@ -1704,13 +1705,13 @@
         </is>
       </c>
       <c r="L28" s="9" t="n">
-        <v>0.01454306253370746</v>
+        <v>0.03813318222181694</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -1720,29 +1721,29 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>0.67</v>
+        <v>2.138</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>0.63</v>
+        <v>1.883</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>0.06349206349206354</v>
+        <v>0.6872012745618694</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>46432</v>
-      </c>
-      <c r="I29" s="14" t="n">
-        <v>125</v>
+        <v>46433</v>
+      </c>
+      <c r="I29" s="23" t="n">
+        <v>119</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>46455</v>
+        <v>46425</v>
       </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
@@ -1750,13 +1751,13 @@
         </is>
       </c>
       <c r="L29" s="9" t="n">
-        <v>0.03777308125827056</v>
+        <v>0.005155099221223549</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -1766,29 +1767,29 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>2.138</v>
+        <v>1.3</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>1.883</v>
+        <v>1.25</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>0.6872012745618694</v>
+        <v>4.96</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="H30" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I30" s="14" t="n">
-        <v>126</v>
+      <c r="I30" s="23" t="n">
+        <v>119</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>46425</v>
+        <v>46383</v>
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
@@ -1796,13 +1797,13 @@
         </is>
       </c>
       <c r="L30" s="9" t="n">
-        <v>0.004833085693226959</v>
+        <v>0.01779115923675148</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -1812,17 +1813,17 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>1.3</v>
+        <v>0.32</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>1.25</v>
+        <v>0.24</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>4.96</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="G31" s="9" t="n">
         <v>0.06</v>
@@ -1830,11 +1831,11 @@
       <c r="H31" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I31" s="14" t="n">
-        <v>126</v>
+      <c r="I31" s="23" t="n">
+        <v>119</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>46383</v>
+        <v>46458</v>
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
@@ -1842,13 +1843,13 @@
         </is>
       </c>
       <c r="L31" s="9" t="n">
-        <v>0.01841164230021915</v>
+        <v>0.02526149686708471</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -1858,29 +1859,29 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>0.32</v>
+        <v>0.84</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>0.24</v>
+        <v>0.82</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.02439024390243905</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H32" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I32" s="14" t="n">
-        <v>126</v>
+      <c r="I32" s="23" t="n">
+        <v>119</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>46458</v>
+        <v>46634</v>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
@@ -1888,13 +1889,13 @@
         </is>
       </c>
       <c r="L32" s="9" t="n">
-        <v>0.02608518459263433</v>
+        <v>0.03105934544760066</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -1904,17 +1905,17 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>0.84</v>
+        <v>0.531</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>0.82</v>
+        <v>0.588964</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>0.02439024390243905</v>
+        <v>0.005735494868956323</v>
       </c>
       <c r="G33" s="9" t="n">
         <v>0.04</v>
@@ -1922,11 +1923,11 @@
       <c r="H33" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I33" s="14" t="n">
-        <v>126</v>
+      <c r="I33" s="23" t="n">
+        <v>119</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>46634</v>
+        <v>46608</v>
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
@@ -1934,13 +1935,13 @@
         </is>
       </c>
       <c r="L33" s="9" t="n">
-        <v>0.03130677936678974</v>
+        <v>0.03252679786732145</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -1950,29 +1951,29 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>0.531</v>
+        <v>0.29</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>0.588964</v>
+        <v>0.27</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>0.005735494868956323</v>
+        <v>0.07407407407407393</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="I34" s="14" t="n">
+        <v>46440</v>
+      </c>
+      <c r="I34" s="23" t="n">
         <v>126</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>46608</v>
+        <v>46450</v>
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
@@ -1980,13 +1981,13 @@
         </is>
       </c>
       <c r="L34" s="9" t="n">
-        <v>0.03395140590432928</v>
+        <v>0.01045327554509916</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -2000,25 +2001,25 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>0.29</v>
+        <v>2.33</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>0.27</v>
+        <v>2.3</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>0.07407407407407393</v>
+        <v>0.01304347826086967</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>46440</v>
-      </c>
-      <c r="I35" s="14" t="n">
-        <v>133</v>
+        <v>46441</v>
+      </c>
+      <c r="I35" s="23" t="n">
+        <v>127</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>46450</v>
+        <v>46456</v>
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
@@ -2026,13 +2027,13 @@
         </is>
       </c>
       <c r="L35" s="9" t="n">
-        <v>0.01032212162618396</v>
+        <v>0.03030312976869731</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -2042,29 +2043,29 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D36" s="7" t="n">
-        <v>2.33</v>
+        <v>1.59</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>0.01304347826086967</v>
+        <v>0.06000000000000005</v>
       </c>
       <c r="G36" s="9" t="n">
         <v>0.08</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>46441</v>
-      </c>
-      <c r="I36" s="14" t="n">
-        <v>134</v>
+        <v>46452</v>
+      </c>
+      <c r="I36" s="23" t="n">
+        <v>138</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>46456</v>
+        <v>46487</v>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
@@ -2072,13 +2073,13 @@
         </is>
       </c>
       <c r="L36" s="9" t="n">
-        <v>0.03219121426382717</v>
+        <v>0.01856934306569343</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -2088,29 +2089,29 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="E37" s="7" t="n">
         <v>1.5</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>0.06000000000000005</v>
+        <v>0.09999999999999994</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>46452</v>
-      </c>
-      <c r="I37" s="14" t="n">
-        <v>145</v>
+        <v>46461</v>
+      </c>
+      <c r="I37" s="23" t="n">
+        <v>147</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>46487</v>
+        <v>46665</v>
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
@@ -2118,45 +2119,45 @@
         </is>
       </c>
       <c r="L37" s="9" t="n">
-        <v>0.01906817724130214</v>
+        <v>0.01956773053691266</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D38" s="7" t="n">
-        <v>1.65</v>
+        <v>0.272</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>1.5</v>
+        <v>0.271</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>0.09999999999999994</v>
+        <v>0.003690036900369007</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="H38" s="10" t="n">
         <v>46461</v>
       </c>
-      <c r="I38" s="14" t="n">
-        <v>154</v>
+      <c r="I38" s="23" t="n">
+        <v>147</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>46665</v>
+        <v>46386</v>
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
@@ -2164,45 +2165,45 @@
         </is>
       </c>
       <c r="L38" s="9" t="n">
-        <v>0.01974688024131375</v>
+        <v>0.05860490201786151</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>0.272</v>
+        <v>1.089</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>0.271</v>
+        <v>1.057</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>0.003690036900369007</v>
+        <v>0.03027436140018924</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>46461</v>
-      </c>
-      <c r="I39" s="14" t="n">
-        <v>154</v>
+        <v>46488</v>
+      </c>
+      <c r="I39" s="23" t="n">
+        <v>174</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>46386</v>
+        <v>46498</v>
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
@@ -2210,18 +2211,18 @@
         </is>
       </c>
       <c r="L39" s="9" t="n">
-        <v>0.06026977174155138</v>
+        <v>0.0275277889821852</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -2230,25 +2231,25 @@
         </is>
       </c>
       <c r="D40" s="7" t="n">
-        <v>1.089</v>
+        <v>1.084</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>1.057</v>
+        <v>1.087</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>0.03027436140018924</v>
+        <v>0.03495860165593379</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>46488</v>
-      </c>
-      <c r="I40" s="14" t="n">
-        <v>181</v>
+        <v>46492</v>
+      </c>
+      <c r="I40" s="23" t="n">
+        <v>178</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>46498</v>
+        <v>46501</v>
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
@@ -2256,45 +2257,45 @@
         </is>
       </c>
       <c r="L40" s="9" t="n">
-        <v>0.02866072298257646</v>
+        <v>0.01795251849684193</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Semi-Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>1.084</v>
+        <v>1.021</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>1.087</v>
+        <v>0.974</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>0.03495860165593379</v>
+        <v>0.04825462012320322</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="H41" s="10" t="n">
         <v>46492</v>
       </c>
-      <c r="I41" s="14" t="n">
-        <v>185</v>
+      <c r="I41" s="23" t="n">
+        <v>178</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>46501</v>
+        <v>46376</v>
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
@@ -2302,13 +2303,13 @@
         </is>
       </c>
       <c r="L41" s="9" t="n">
-        <v>0.01961369636922693</v>
+        <v>0.04487665648324178</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
@@ -2318,29 +2319,29 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D42" s="7" t="n">
-        <v>1.021</v>
+        <v>1.34</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>0.974</v>
+        <v>1.3</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>0.04825462012320322</v>
+        <v>0.0307692307692308</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>46492</v>
-      </c>
-      <c r="I42" s="14" t="n">
-        <v>185</v>
+        <v>46493</v>
+      </c>
+      <c r="I42" s="23" t="n">
+        <v>179</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>46376</v>
+        <v>46531</v>
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
@@ -2348,13 +2349,13 @@
         </is>
       </c>
       <c r="L42" s="9" t="n">
-        <v>0.04612083409655995</v>
+        <v>0.02108990804140305</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
@@ -2364,133 +2365,133 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>0.551</v>
+      </c>
+      <c r="E43" s="7" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>0.04952380952380957</v>
+      </c>
+      <c r="G43" s="9" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H43" s="10" t="n">
+        <v>46504</v>
+      </c>
+      <c r="I43" s="23" t="n">
+        <v>190</v>
+      </c>
+      <c r="J43" s="10" t="n">
+        <v>46562</v>
+      </c>
+      <c r="K43" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+      <c r="L43" s="9" t="n">
+        <v>0.0501250838938402</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>PSX</t>
+        </is>
+      </c>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="inlineStr">
+        <is>
           <t>May</t>
         </is>
       </c>
-      <c r="D43" s="7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="E43" s="7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F43" s="8" t="n">
-        <v>0.0307692307692308</v>
-      </c>
-      <c r="G43" s="9" t="n">
+      <c r="D44" s="16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E44" s="16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F44" s="17" t="n">
+        <v>0.05833333333333339</v>
+      </c>
+      <c r="G44" s="18" t="n"/>
+      <c r="H44" s="19" t="n">
+        <v>46505</v>
+      </c>
+      <c r="I44" s="24" t="n">
+        <v>191</v>
+      </c>
+      <c r="J44" s="19" t="n">
+        <v>46526</v>
+      </c>
+      <c r="K44" s="21" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="L44" s="22" t="n">
+        <v>0.01698655802003307</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>PAYX</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E45" s="7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="F45" s="8" t="n">
+        <v>0.1018518518518517</v>
+      </c>
+      <c r="G45" s="9" t="n">
         <v>0.06</v>
       </c>
-      <c r="H43" s="10" t="n">
-        <v>46493</v>
-      </c>
-      <c r="I43" s="14" t="n">
-        <v>186</v>
-      </c>
-      <c r="J43" s="10" t="n">
-        <v>46531</v>
-      </c>
-      <c r="K43" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L43" s="9" t="n">
-        <v>0.02043461780192916</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="n">
-        <v>0.551</v>
-      </c>
-      <c r="E44" s="7" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="F44" s="8" t="n">
-        <v>0.04952380952380957</v>
-      </c>
-      <c r="G44" s="9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H44" s="10" t="n">
-        <v>46504</v>
-      </c>
-      <c r="I44" s="14" t="n">
-        <v>197</v>
-      </c>
-      <c r="J44" s="10" t="n">
-        <v>46562</v>
-      </c>
-      <c r="K44" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L44" s="9" t="n">
-        <v>0.04832803469187192</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="15" t="inlineStr">
-        <is>
-          <t>PSX</t>
-        </is>
-      </c>
-      <c r="B45" s="16" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C45" s="16" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="D45" s="17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E45" s="17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F45" s="18" t="n">
-        <v>0.05833333333333339</v>
-      </c>
-      <c r="G45" s="23" t="n"/>
-      <c r="H45" s="20" t="n">
-        <v>46505</v>
-      </c>
-      <c r="I45" s="21" t="n">
-        <v>198</v>
-      </c>
-      <c r="J45" s="20" t="n">
-        <v>46526</v>
-      </c>
-      <c r="K45" s="22" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
-      <c r="L45" s="19" t="n">
-        <v>0.01786279313034211</v>
+      <c r="H45" s="10" t="n">
+        <v>46508</v>
+      </c>
+      <c r="I45" s="23" t="n">
+        <v>194</v>
+      </c>
+      <c r="J45" s="10" t="n">
+        <v>46518</v>
+      </c>
+      <c r="K45" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+      <c r="L45" s="9" t="n">
+        <v>0.04296028762541161</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
@@ -2500,29 +2501,29 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>1.19</v>
+        <v>1.48</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>1.08</v>
+        <v>1.423</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>0.1018518518518517</v>
+        <v>0.04005621925509482</v>
       </c>
       <c r="G46" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>46508</v>
-      </c>
-      <c r="I46" s="14" t="n">
+        <v>46515</v>
+      </c>
+      <c r="I46" s="23" t="n">
         <v>201</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>46518</v>
+        <v>46542</v>
       </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
@@ -2530,13 +2531,13 @@
         </is>
       </c>
       <c r="L46" s="9" t="n">
-        <v>0.04579785550402819</v>
+        <v>0.04479418762075352</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
@@ -2550,25 +2551,25 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>1.48</v>
+        <v>0.72</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>1.423</v>
+        <v>0.71</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>0.04005621925509482</v>
+        <v>0.01408450704225353</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>46515</v>
-      </c>
-      <c r="I47" s="14" t="n">
-        <v>208</v>
+        <v>46532</v>
+      </c>
+      <c r="I47" s="23" t="n">
+        <v>218</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>46542</v>
+        <v>46563</v>
       </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
@@ -2576,13 +2577,13 @@
         </is>
       </c>
       <c r="L47" s="9" t="n">
-        <v>0.04691896062464589</v>
+        <v>0.03067262567036151</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
@@ -2592,29 +2593,29 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D48" s="7" t="n">
-        <v>0.72</v>
+        <v>1.42</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>0.71</v>
+        <v>1.38</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>0.01408450704225353</v>
+        <v>0.02898550724637684</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>46532</v>
-      </c>
-      <c r="I48" s="14" t="n">
-        <v>225</v>
+        <v>46589</v>
+      </c>
+      <c r="I48" s="23" t="n">
+        <v>275</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>46563</v>
+        <v>46629</v>
       </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
@@ -2622,13 +2623,13 @@
         </is>
       </c>
       <c r="L48" s="9" t="n">
-        <v>0.03109143998051593</v>
+        <v>0.01977647076699418</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
@@ -2638,29 +2639,29 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>1.42</v>
+        <v>0.84</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>1.38</v>
+        <v>0.83</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>0.02898550724637684</v>
+        <v>0.01204819277108435</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>46589</v>
-      </c>
-      <c r="I49" s="14" t="n">
-        <v>282</v>
+        <v>46591</v>
+      </c>
+      <c r="I49" s="23" t="n">
+        <v>277</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>46629</v>
+        <v>46633</v>
       </c>
       <c r="K49" s="12" t="inlineStr">
         <is>
@@ -2668,13 +2669,13 @@
         </is>
       </c>
       <c r="L49" s="9" t="n">
-        <v>0.02034092608022438</v>
+        <v>0.03676269334137368</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
@@ -2684,29 +2685,29 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D50" s="7" t="n">
-        <v>0.84</v>
+        <v>0.98</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>0.83</v>
+        <v>0.93</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>0.01204819277108435</v>
+        <v>0.05376344086021498</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>46591</v>
-      </c>
-      <c r="I50" s="14" t="n">
-        <v>284</v>
+        <v>46594</v>
+      </c>
+      <c r="I50" s="23" t="n">
+        <v>280</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>46633</v>
+        <v>46613</v>
       </c>
       <c r="K50" s="12" t="inlineStr">
         <is>
@@ -2714,13 +2715,13 @@
         </is>
       </c>
       <c r="L50" s="9" t="n">
-        <v>0.03798756490592253</v>
+        <v>0.01472908914196234</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>AWR</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -2734,25 +2735,25 @@
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>0.98</v>
+        <v>0.546</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>0.93</v>
+        <v>0.504</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>0.05376344086021498</v>
+        <v>0.08333333333333341</v>
       </c>
       <c r="G51" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>46594</v>
-      </c>
-      <c r="I51" s="14" t="n">
-        <v>287</v>
+        <v>46595</v>
+      </c>
+      <c r="I51" s="23" t="n">
+        <v>281</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>46613</v>
+        <v>46614</v>
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
@@ -2760,13 +2761,13 @@
         </is>
       </c>
       <c r="L51" s="9" t="n">
-        <v>0.01515180818849923</v>
+        <v>0.02646150000721019</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>AWR</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -2780,25 +2781,25 @@
         </is>
       </c>
       <c r="D52" s="7" t="n">
-        <v>0.546</v>
+        <v>1.25</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>0.504</v>
+        <v>1.24</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>0.08333333333333341</v>
+        <v>0.008064516129032265</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>46595</v>
-      </c>
-      <c r="I52" s="14" t="n">
-        <v>288</v>
+        <v>46597</v>
+      </c>
+      <c r="I52" s="23" t="n">
+        <v>283</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>46614</v>
+        <v>46611</v>
       </c>
       <c r="K52" s="12" t="inlineStr">
         <is>
@@ -2806,13 +2807,13 @@
         </is>
       </c>
       <c r="L52" s="9" t="n">
-        <v>0.02660656666088859</v>
+        <v>0.05855829331739755</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>CFR</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -2826,25 +2827,25 @@
         </is>
       </c>
       <c r="D53" s="7" t="n">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>1.24</v>
+        <v>1</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>0.008064516129032265</v>
+        <v>0.03000000000000003</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>46597</v>
-      </c>
-      <c r="I53" s="14" t="n">
-        <v>290</v>
+        <v>46598</v>
+      </c>
+      <c r="I53" s="23" t="n">
+        <v>284</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>46611</v>
+        <v>46629</v>
       </c>
       <c r="K53" s="12" t="inlineStr">
         <is>
@@ -2852,13 +2853,13 @@
         </is>
       </c>
       <c r="L53" s="9" t="n">
-        <v>0.05990893907079166</v>
+        <v>0.02663391256691318</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>CFR</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -2868,29 +2869,29 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D54" s="7" t="n">
-        <v>1.03</v>
+        <v>0.83</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>0.03000000000000003</v>
+        <v>0.01219512195121952</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>46598</v>
-      </c>
-      <c r="I54" s="14" t="n">
-        <v>291</v>
+        <v>46614</v>
+      </c>
+      <c r="I54" s="23" t="n">
+        <v>300</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>46629</v>
+        <v>46662</v>
       </c>
       <c r="K54" s="12" t="inlineStr">
         <is>
@@ -2898,13 +2899,13 @@
         </is>
       </c>
       <c r="L54" s="9" t="n">
-        <v>0.02719112911712621</v>
+        <v>0.03416692459155611</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -2914,29 +2915,29 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D55" s="7" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E55" s="7" t="n">
         <v>0.83</v>
       </c>
-      <c r="E55" s="7" t="n">
-        <v>0.82</v>
-      </c>
       <c r="F55" s="8" t="n">
-        <v>0.01219512195121952</v>
+        <v>0.09638554216867479</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>46614</v>
-      </c>
-      <c r="I55" s="14" t="n">
-        <v>307</v>
+        <v>46643</v>
+      </c>
+      <c r="I55" s="23" t="n">
+        <v>329</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>46662</v>
+        <v>46709</v>
       </c>
       <c r="K55" s="12" t="inlineStr">
         <is>
@@ -2944,13 +2945,13 @@
         </is>
       </c>
       <c r="L55" s="9" t="n">
-        <v>0.03471713997023395</v>
+        <v>0.006843878990992571</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
@@ -2960,29 +2961,29 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D56" s="7" t="n">
-        <v>0.91</v>
+        <v>0.708</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>0.83</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>0.09638554216867479</v>
+        <v>0.02608695652173916</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>46643</v>
-      </c>
-      <c r="I56" s="14" t="n">
-        <v>336</v>
+        <v>46645</v>
+      </c>
+      <c r="I56" s="23" t="n">
+        <v>331</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>46709</v>
+        <v>46668</v>
       </c>
       <c r="K56" s="12" t="inlineStr">
         <is>
@@ -2990,13 +2991,13 @@
         </is>
       </c>
       <c r="L56" s="9" t="n">
-        <v>0.006744487525791792</v>
+        <v>0.06363329810206279</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
@@ -3010,25 +3011,25 @@
         </is>
       </c>
       <c r="D57" s="7" t="n">
-        <v>0.708</v>
+        <v>1.42</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.36</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>0.02608695652173916</v>
+        <v>0.0441176470588234</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>46645</v>
-      </c>
-      <c r="I57" s="14" t="n">
-        <v>338</v>
+        <v>46650</v>
+      </c>
+      <c r="I57" s="23" t="n">
+        <v>336</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>46668</v>
+        <v>46690</v>
       </c>
       <c r="K57" s="12" t="inlineStr">
         <is>
@@ -3036,13 +3037,13 @@
         </is>
       </c>
       <c r="L57" s="9" t="n">
-        <v>0.06643208841292222</v>
+        <v>0.02051059888861486</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
@@ -3052,29 +3053,29 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D58" s="7" t="n">
-        <v>1.42</v>
+        <v>0.79</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>1.36</v>
+        <v>0.75</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>0.0441176470588234</v>
+        <v>0.05333333333333338</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>46650</v>
-      </c>
-      <c r="I58" s="14" t="n">
-        <v>343</v>
+        <v>46676</v>
+      </c>
+      <c r="I58" s="23" t="n">
+        <v>362</v>
       </c>
       <c r="J58" s="10" t="n">
-        <v>46690</v>
+        <v>46751</v>
       </c>
       <c r="K58" s="12" t="inlineStr">
         <is>
@@ -3082,7 +3083,7 @@
         </is>
       </c>
       <c r="L58" s="9" t="n">
-        <v>0.02024161753504176</v>
+        <v>0.01212586310817193</v>
       </c>
     </row>
   </sheetData>
@@ -3096,7 +3097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3117,44 +3118,44 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Expected Increase Announcements by Month - 10/12/2026</t>
+          <t>Expected Increase Announcements by Month - 10/19/2026</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>January 2026</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="26" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3185,39 +3186,39 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>October 2026</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="26" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="26" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D9" s="25" t="inlineStr">
+      <c r="D9" s="26" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="E9" s="26" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F9" s="25" t="inlineStr">
+      <c r="F9" s="26" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3226,68 +3227,68 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
+          <t>HII</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>46318</v>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>46352</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>0.02222222222222208</v>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
           <t>MSM</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n">
-        <v>46305</v>
-      </c>
-      <c r="C10" s="10" t="n">
-        <v>46704</v>
-      </c>
-      <c r="D10" s="7" t="n">
+      <c r="B11" s="19" t="n">
+        <v>46318</v>
+      </c>
+      <c r="C11" s="19" t="n">
+        <v>46339</v>
+      </c>
+      <c r="D11" s="16" t="n">
         <v>0.87</v>
       </c>
-      <c r="E10" s="8" t="n">
+      <c r="E11" s="17" t="n">
         <v>0.0235294117647059</v>
       </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>LECO</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="n">
-        <v>46311</v>
-      </c>
-      <c r="C11" s="10" t="n">
-        <v>46386</v>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>0.05333333333333338</v>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>yfinance</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="B12" s="10" t="n">
-        <v>46318</v>
+        <v>46322</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>46352</v>
+        <v>46338</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>1.38</v>
+        <v>0.64</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>0.02222222222222208</v>
+        <v>0.06666666666666674</v>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
@@ -3295,86 +3296,86 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>ETR</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="n">
-        <v>46322</v>
-      </c>
-      <c r="C13" s="10" t="n">
+    <row r="14">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>November 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F15" s="26" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>COR</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n">
+        <v>46329</v>
+      </c>
+      <c r="C16" s="10" t="n">
         <v>46338</v>
       </c>
-      <c r="D13" s="7" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>0.06666666666666674</v>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="24" t="inlineStr">
-        <is>
-          <t>November 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="25" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B16" s="25" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C16" s="25" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D16" s="25" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E16" s="25" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F16" s="25" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="D16" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>0.09090909090909079</v>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B17" s="10" t="n">
-        <v>46329</v>
+        <v>46332</v>
       </c>
       <c r="C17" s="10" t="n">
-        <v>46338</v>
+        <v>46346</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.6</v>
+        <v>2.44</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>0.09090909090909079</v>
+        <v>0.1401869158878504</v>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
@@ -3385,20 +3386,20 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B18" s="10" t="n">
-        <v>46332</v>
+        <v>46341</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>46346</v>
+        <v>46340</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>2.44</v>
+        <v>1.03</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>0.1401869158878504</v>
+        <v>0.04040404040404044</v>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
@@ -3409,20 +3410,20 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>46341</v>
+        <v>46344</v>
       </c>
       <c r="C19" s="10" t="n">
-        <v>46340</v>
+        <v>46385</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1.03</v>
+        <v>0.48</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>0.04040404040404044</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
@@ -3433,20 +3434,20 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B20" s="10" t="n">
-        <v>46344</v>
+        <v>46347</v>
       </c>
       <c r="C20" s="10" t="n">
-        <v>46385</v>
+        <v>46358</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.48</v>
+        <v>0.41</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
@@ -3457,20 +3458,20 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="B21" s="10" t="n">
-        <v>46347</v>
+        <v>46351</v>
       </c>
       <c r="C21" s="10" t="n">
-        <v>46358</v>
+        <v>46399</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.41</v>
+        <v>0.293</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.01034482758620691</v>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
@@ -3478,86 +3479,86 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>HRL</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="n">
-        <v>46352</v>
-      </c>
-      <c r="C22" s="10" t="n">
-        <v>46400</v>
-      </c>
-      <c r="D22" s="7" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>0.01034482758620691</v>
-      </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="23">
+      <c r="A23" s="25" t="inlineStr">
+        <is>
+          <t>December 2026</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="24" t="inlineStr">
-        <is>
-          <t>December 2026</t>
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B24" s="26" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D24" s="26" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E24" s="26" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F24" s="26" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="25" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B25" s="25" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C25" s="25" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D25" s="25" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E25" s="25" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F25" s="25" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>EMN</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="n">
+        <v>46360</v>
+      </c>
+      <c r="C25" s="10" t="n">
+        <v>46371</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>0.01204819277108435</v>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>EMN</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B26" s="10" t="n">
-        <v>46360</v>
+        <v>46366</v>
       </c>
       <c r="C26" s="10" t="n">
-        <v>46371</v>
+        <v>46432</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>0.84</v>
+        <v>2.52</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>0.01204819277108435</v>
+        <v>0.05882352941176476</v>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
@@ -3568,20 +3569,20 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="B27" s="10" t="n">
-        <v>46366</v>
+        <v>46380</v>
       </c>
       <c r="C27" s="10" t="n">
-        <v>46432</v>
+        <v>46436</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>2.52</v>
+        <v>0.24</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>0.05882352941176476</v>
+        <v>0.04347826086956513</v>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
@@ -3590,109 +3591,109 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>CNP</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="n">
-        <v>46380</v>
-      </c>
-      <c r="C28" s="10" t="n">
-        <v>46436</v>
-      </c>
-      <c r="D28" s="7" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>0.04347826086956513</v>
-      </c>
-      <c r="F28" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>GGG</t>
         </is>
       </c>
-      <c r="B29" s="20" t="n">
+      <c r="B28" s="19" t="n">
         <v>46383</v>
       </c>
-      <c r="C29" s="20" t="n">
+      <c r="C28" s="19" t="n">
         <v>46404</v>
       </c>
-      <c r="D29" s="17" t="n">
+      <c r="D28" s="16" t="n">
         <v>0.295</v>
       </c>
-      <c r="E29" s="18" t="n">
+      <c r="E28" s="17" t="n">
         <v>0.07272727272727258</v>
       </c>
-      <c r="F29" s="22" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>January 2027</t>
+        </is>
+      </c>
+    </row>
     <row r="31">
-      <c r="A31" s="24" t="inlineStr">
-        <is>
-          <t>January 2027</t>
+      <c r="A31" s="26" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C31" s="26" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D31" s="26" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E31" s="26" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F31" s="26" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="25" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B32" s="25" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C32" s="25" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D32" s="25" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E32" s="25" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F32" s="25" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n">
+        <v>46402</v>
+      </c>
+      <c r="C32" s="10" t="n">
+        <v>46483</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>0.07499999999999993</v>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>BKH</t>
         </is>
       </c>
       <c r="B33" s="10" t="n">
-        <v>46402</v>
+        <v>46411</v>
       </c>
       <c r="C33" s="10" t="n">
-        <v>46483</v>
+        <v>46435</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>0.86</v>
+        <v>0.703</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>0.07499999999999993</v>
+        <v>0.03994082840236673</v>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
@@ -3703,20 +3704,20 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>BKH</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B34" s="10" t="n">
-        <v>46411</v>
+        <v>46417</v>
       </c>
       <c r="C34" s="10" t="n">
-        <v>46435</v>
+        <v>46433</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>0.703</v>
+        <v>1.78</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>0.03994082840236673</v>
+        <v>0.04093567251461992</v>
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
@@ -3724,86 +3725,86 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>CVX</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="n">
-        <v>46417</v>
-      </c>
-      <c r="C35" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="D35" s="7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="E35" s="8" t="n">
-        <v>0.04093567251461992</v>
-      </c>
-      <c r="F35" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="36">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>February 2027</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="24" t="inlineStr">
-        <is>
-          <t>February 2027</t>
+      <c r="A37" s="26" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C37" s="26" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D37" s="26" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E37" s="26" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F37" s="26" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="25" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B38" s="25" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C38" s="25" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D38" s="25" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E38" s="25" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F38" s="25" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>NVO</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n">
+        <v>46423</v>
+      </c>
+      <c r="C38" s="10" t="n">
+        <v>46473</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>1.183219178082192</v>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B39" s="10" t="n">
-        <v>46423</v>
+        <v>46428</v>
       </c>
       <c r="C39" s="10" t="n">
-        <v>46473</v>
+        <v>46452</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>0.579</v>
+        <v>0.61</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>1.183219178082192</v>
+        <v>0.05172413793103453</v>
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
@@ -3814,20 +3815,20 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B40" s="10" t="n">
         <v>46428</v>
       </c>
       <c r="C40" s="10" t="n">
-        <v>46452</v>
+        <v>46460</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>0.61</v>
+        <v>1.3</v>
       </c>
       <c r="E40" s="8" t="n">
-        <v>0.05172413793103453</v>
+        <v>0.02362204724409451</v>
       </c>
       <c r="F40" s="12" t="inlineStr">
         <is>
@@ -3836,70 +3837,70 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>TROW</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="n">
-        <v>46428</v>
-      </c>
-      <c r="C41" s="10" t="n">
-        <v>46460</v>
-      </c>
-      <c r="D41" s="7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E41" s="8" t="n">
-        <v>0.02362204724409451</v>
-      </c>
-      <c r="F41" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>HWC</t>
+        </is>
+      </c>
+      <c r="B41" s="19" t="n">
+        <v>46429</v>
+      </c>
+      <c r="C41" s="19" t="n">
+        <v>46450</v>
+      </c>
+      <c r="D41" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="F41" s="21" t="inlineStr">
+        <is>
+          <t>yfinance</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
-        <is>
-          <t>HWC</t>
-        </is>
-      </c>
-      <c r="B42" s="20" t="n">
-        <v>46429</v>
-      </c>
-      <c r="C42" s="20" t="n">
-        <v>46450</v>
-      </c>
-      <c r="D42" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E42" s="18" t="n">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="F42" s="22" t="inlineStr">
-        <is>
-          <t>yfinance</t>
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>CSCO</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="n">
+        <v>46431</v>
+      </c>
+      <c r="C42" s="10" t="n">
+        <v>46480</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>0.02439024390243905</v>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>PEG</t>
         </is>
       </c>
       <c r="B43" s="10" t="n">
-        <v>46431</v>
+        <v>46432</v>
       </c>
       <c r="C43" s="10" t="n">
-        <v>46480</v>
+        <v>46455</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>0.42</v>
+        <v>0.67</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>0.02439024390243905</v>
+        <v>0.06349206349206354</v>
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
@@ -3910,20 +3911,20 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B44" s="10" t="n">
-        <v>46432</v>
+        <v>46433</v>
       </c>
       <c r="C44" s="10" t="n">
-        <v>46455</v>
+        <v>46425</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>0.67</v>
+        <v>2.138</v>
       </c>
       <c r="E44" s="8" t="n">
-        <v>0.06349206349206354</v>
+        <v>0.6872012745618694</v>
       </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
@@ -3934,20 +3935,20 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B45" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C45" s="10" t="n">
-        <v>46425</v>
+        <v>46383</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>2.138</v>
+        <v>1.3</v>
       </c>
       <c r="E45" s="8" t="n">
-        <v>0.6872012745618694</v>
+        <v>4.96</v>
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
@@ -3958,20 +3959,20 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B46" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C46" s="10" t="n">
-        <v>46383</v>
+        <v>46458</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>1.3</v>
+        <v>0.32</v>
       </c>
       <c r="E46" s="8" t="n">
-        <v>4.96</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="F46" s="12" t="inlineStr">
         <is>
@@ -3982,20 +3983,20 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B47" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C47" s="10" t="n">
-        <v>46458</v>
+        <v>46634</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>0.32</v>
+        <v>0.84</v>
       </c>
       <c r="E47" s="8" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.02439024390243905</v>
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
@@ -4006,20 +4007,20 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B48" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C48" s="10" t="n">
-        <v>46634</v>
+        <v>46608</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>0.84</v>
+        <v>0.531</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>0.02439024390243905</v>
+        <v>0.005735494868956323</v>
       </c>
       <c r="F48" s="12" t="inlineStr">
         <is>
@@ -4030,20 +4031,20 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="B49" s="10" t="n">
-        <v>46433</v>
+        <v>46440</v>
       </c>
       <c r="C49" s="10" t="n">
-        <v>46608</v>
+        <v>46450</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>0.531</v>
+        <v>0.29</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>0.005735494868956323</v>
+        <v>0.07407407407407393</v>
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
@@ -4054,20 +4055,20 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B50" s="10" t="n">
-        <v>46440</v>
+        <v>46441</v>
       </c>
       <c r="C50" s="10" t="n">
-        <v>46450</v>
+        <v>46456</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>0.29</v>
+        <v>2.33</v>
       </c>
       <c r="E50" s="8" t="n">
-        <v>0.07407407407407393</v>
+        <v>0.01304347826086967</v>
       </c>
       <c r="F50" s="12" t="inlineStr">
         <is>
@@ -4075,86 +4076,86 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>HD</t>
-        </is>
-      </c>
-      <c r="B51" s="10" t="n">
-        <v>46441</v>
-      </c>
-      <c r="C51" s="10" t="n">
-        <v>46456</v>
-      </c>
-      <c r="D51" s="7" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="E51" s="8" t="n">
-        <v>0.01304347826086967</v>
-      </c>
-      <c r="F51" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="52">
+      <c r="A52" s="25" t="inlineStr">
+        <is>
+          <t>March 2027</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="24" t="inlineStr">
-        <is>
-          <t>March 2027</t>
+      <c r="A53" s="26" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B53" s="26" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C53" s="26" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D53" s="26" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E53" s="26" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F53" s="26" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="25" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B54" s="25" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C54" s="25" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D54" s="25" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E54" s="25" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F54" s="25" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="n">
+        <v>46452</v>
+      </c>
+      <c r="C54" s="10" t="n">
+        <v>46487</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="E54" s="8" t="n">
+        <v>0.06000000000000005</v>
+      </c>
+      <c r="F54" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B55" s="10" t="n">
-        <v>46452</v>
+        <v>46461</v>
       </c>
       <c r="C55" s="10" t="n">
-        <v>46487</v>
+        <v>46665</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="E55" s="8" t="n">
-        <v>0.06000000000000005</v>
+        <v>0.09999999999999994</v>
       </c>
       <c r="F55" s="12" t="inlineStr">
         <is>
@@ -4165,20 +4166,20 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B56" s="10" t="n">
         <v>46461</v>
       </c>
       <c r="C56" s="10" t="n">
-        <v>46665</v>
+        <v>46386</v>
       </c>
       <c r="D56" s="7" t="n">
-        <v>1.65</v>
+        <v>0.272</v>
       </c>
       <c r="E56" s="8" t="n">
-        <v>0.09999999999999994</v>
+        <v>0.003690036900369007</v>
       </c>
       <c r="F56" s="12" t="inlineStr">
         <is>
@@ -4186,86 +4187,86 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B57" s="10" t="n">
-        <v>46461</v>
-      </c>
-      <c r="C57" s="10" t="n">
-        <v>46386</v>
-      </c>
-      <c r="D57" s="7" t="n">
-        <v>0.272</v>
-      </c>
-      <c r="E57" s="8" t="n">
-        <v>0.003690036900369007</v>
-      </c>
-      <c r="F57" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="58">
+      <c r="A58" s="25" t="inlineStr">
+        <is>
+          <t>April 2027</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="24" t="inlineStr">
-        <is>
-          <t>April 2027</t>
+      <c r="A59" s="26" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B59" s="26" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C59" s="26" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D59" s="26" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E59" s="26" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F59" s="26" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="25" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B60" s="25" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C60" s="25" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D60" s="25" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E60" s="25" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F60" s="25" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="n">
+        <v>46488</v>
+      </c>
+      <c r="C60" s="10" t="n">
+        <v>46498</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="E60" s="8" t="n">
+        <v>0.03027436140018924</v>
+      </c>
+      <c r="F60" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="B61" s="10" t="n">
-        <v>46488</v>
+        <v>46492</v>
       </c>
       <c r="C61" s="10" t="n">
-        <v>46498</v>
+        <v>46501</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>1.089</v>
+        <v>1.084</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>0.03027436140018924</v>
+        <v>0.03495860165593379</v>
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
@@ -4276,20 +4277,20 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B62" s="10" t="n">
         <v>46492</v>
       </c>
       <c r="C62" s="10" t="n">
-        <v>46501</v>
+        <v>46376</v>
       </c>
       <c r="D62" s="7" t="n">
-        <v>1.084</v>
+        <v>1.021</v>
       </c>
       <c r="E62" s="8" t="n">
-        <v>0.03495860165593379</v>
+        <v>0.04825462012320322</v>
       </c>
       <c r="F62" s="12" t="inlineStr">
         <is>
@@ -4300,20 +4301,20 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B63" s="10" t="n">
-        <v>46492</v>
+        <v>46493</v>
       </c>
       <c r="C63" s="10" t="n">
-        <v>46376</v>
+        <v>46531</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>1.021</v>
+        <v>1.34</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>0.04825462012320322</v>
+        <v>0.0307692307692308</v>
       </c>
       <c r="F63" s="12" t="inlineStr">
         <is>
@@ -4324,20 +4325,20 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B64" s="10" t="n">
-        <v>46493</v>
+        <v>46504</v>
       </c>
       <c r="C64" s="10" t="n">
-        <v>46531</v>
+        <v>46562</v>
       </c>
       <c r="D64" s="7" t="n">
-        <v>1.34</v>
+        <v>0.551</v>
       </c>
       <c r="E64" s="8" t="n">
-        <v>0.0307692307692308</v>
+        <v>0.04952380952380957</v>
       </c>
       <c r="F64" s="12" t="inlineStr">
         <is>
@@ -4346,109 +4347,109 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
-      </c>
-      <c r="B65" s="10" t="n">
-        <v>46504</v>
-      </c>
-      <c r="C65" s="10" t="n">
-        <v>46562</v>
-      </c>
-      <c r="D65" s="7" t="n">
-        <v>0.551</v>
-      </c>
-      <c r="E65" s="8" t="n">
-        <v>0.04952380952380957</v>
-      </c>
-      <c r="F65" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="15" t="inlineStr">
+      <c r="A65" s="14" t="inlineStr">
         <is>
           <t>PSX</t>
         </is>
       </c>
-      <c r="B66" s="20" t="n">
+      <c r="B65" s="19" t="n">
         <v>46505</v>
       </c>
-      <c r="C66" s="20" t="n">
+      <c r="C65" s="19" t="n">
         <v>46526</v>
       </c>
-      <c r="D66" s="17" t="n">
+      <c r="D65" s="16" t="n">
         <v>1.27</v>
       </c>
-      <c r="E66" s="18" t="n">
+      <c r="E65" s="17" t="n">
         <v>0.05833333333333339</v>
       </c>
-      <c r="F66" s="22" t="inlineStr">
+      <c r="F65" s="21" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="25" t="inlineStr">
+        <is>
+          <t>May 2027</t>
+        </is>
+      </c>
+    </row>
     <row r="68">
-      <c r="A68" s="24" t="inlineStr">
-        <is>
-          <t>May 2027</t>
+      <c r="A68" s="26" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B68" s="26" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C68" s="26" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D68" s="26" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E68" s="26" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F68" s="26" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="25" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B69" s="25" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C69" s="25" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D69" s="25" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E69" s="25" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F69" s="25" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>PAYX</t>
+        </is>
+      </c>
+      <c r="B69" s="10" t="n">
+        <v>46508</v>
+      </c>
+      <c r="C69" s="10" t="n">
+        <v>46518</v>
+      </c>
+      <c r="D69" s="7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E69" s="8" t="n">
+        <v>0.1018518518518517</v>
+      </c>
+      <c r="F69" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B70" s="10" t="n">
-        <v>46508</v>
+        <v>46515</v>
       </c>
       <c r="C70" s="10" t="n">
-        <v>46518</v>
+        <v>46542</v>
       </c>
       <c r="D70" s="7" t="n">
-        <v>1.19</v>
+        <v>1.48</v>
       </c>
       <c r="E70" s="8" t="n">
-        <v>0.1018518518518517</v>
+        <v>0.04005621925509482</v>
       </c>
       <c r="F70" s="12" t="inlineStr">
         <is>
@@ -4459,20 +4460,20 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B71" s="10" t="n">
-        <v>46515</v>
+        <v>46532</v>
       </c>
       <c r="C71" s="10" t="n">
-        <v>46542</v>
+        <v>46563</v>
       </c>
       <c r="D71" s="7" t="n">
-        <v>1.48</v>
+        <v>0.72</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>0.04005621925509482</v>
+        <v>0.01408450704225353</v>
       </c>
       <c r="F71" s="12" t="inlineStr">
         <is>
@@ -4480,86 +4481,86 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>MDT</t>
-        </is>
-      </c>
-      <c r="B72" s="10" t="n">
-        <v>46532</v>
-      </c>
-      <c r="C72" s="10" t="n">
-        <v>46563</v>
-      </c>
-      <c r="D72" s="7" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E72" s="8" t="n">
-        <v>0.01408450704225353</v>
-      </c>
-      <c r="F72" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="73">
+      <c r="A73" s="25" t="inlineStr">
+        <is>
+          <t>July 2027</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="24" t="inlineStr">
-        <is>
-          <t>July 2027</t>
+      <c r="A74" s="26" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B74" s="26" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C74" s="26" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D74" s="26" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E74" s="26" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F74" s="26" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="25" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B75" s="25" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C75" s="25" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D75" s="25" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E75" s="25" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F75" s="25" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>UNP</t>
+        </is>
+      </c>
+      <c r="B75" s="10" t="n">
+        <v>46589</v>
+      </c>
+      <c r="C75" s="10" t="n">
+        <v>46629</v>
+      </c>
+      <c r="D75" s="7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="E75" s="8" t="n">
+        <v>0.02898550724637684</v>
+      </c>
+      <c r="F75" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="B76" s="10" t="n">
-        <v>46589</v>
+        <v>46591</v>
       </c>
       <c r="C76" s="10" t="n">
-        <v>46629</v>
+        <v>46633</v>
       </c>
       <c r="D76" s="7" t="n">
-        <v>1.42</v>
+        <v>0.84</v>
       </c>
       <c r="E76" s="8" t="n">
-        <v>0.02898550724637684</v>
+        <v>0.01204819277108435</v>
       </c>
       <c r="F76" s="12" t="inlineStr">
         <is>
@@ -4570,20 +4571,20 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="B77" s="10" t="n">
-        <v>46591</v>
+        <v>46594</v>
       </c>
       <c r="C77" s="10" t="n">
-        <v>46633</v>
+        <v>46613</v>
       </c>
       <c r="D77" s="7" t="n">
-        <v>0.84</v>
+        <v>0.98</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>0.01204819277108435</v>
+        <v>0.05376344086021498</v>
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
@@ -4594,20 +4595,20 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>AWR</t>
         </is>
       </c>
       <c r="B78" s="10" t="n">
-        <v>46594</v>
+        <v>46595</v>
       </c>
       <c r="C78" s="10" t="n">
-        <v>46613</v>
+        <v>46614</v>
       </c>
       <c r="D78" s="7" t="n">
-        <v>0.98</v>
+        <v>0.546</v>
       </c>
       <c r="E78" s="8" t="n">
-        <v>0.05376344086021498</v>
+        <v>0.08333333333333341</v>
       </c>
       <c r="F78" s="12" t="inlineStr">
         <is>
@@ -4618,20 +4619,20 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>AWR</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="B79" s="10" t="n">
-        <v>46595</v>
+        <v>46597</v>
       </c>
       <c r="C79" s="10" t="n">
-        <v>46614</v>
+        <v>46611</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>0.546</v>
+        <v>1.25</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>0.08333333333333341</v>
+        <v>0.008064516129032265</v>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
@@ -4642,20 +4643,20 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>CFR</t>
         </is>
       </c>
       <c r="B80" s="10" t="n">
-        <v>46597</v>
+        <v>46598</v>
       </c>
       <c r="C80" s="10" t="n">
-        <v>46611</v>
+        <v>46629</v>
       </c>
       <c r="D80" s="7" t="n">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>0.008064516129032265</v>
+        <v>0.03000000000000003</v>
       </c>
       <c r="F80" s="12" t="inlineStr">
         <is>
@@ -4663,149 +4664,149 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>CFR</t>
-        </is>
-      </c>
-      <c r="B81" s="10" t="n">
-        <v>46598</v>
-      </c>
-      <c r="C81" s="10" t="n">
-        <v>46629</v>
-      </c>
-      <c r="D81" s="7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E81" s="8" t="n">
-        <v>0.03000000000000003</v>
-      </c>
-      <c r="F81" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="82">
+      <c r="A82" s="25" t="inlineStr">
+        <is>
+          <t>August 2027</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="24" t="inlineStr">
-        <is>
-          <t>August 2027</t>
+      <c r="A83" s="26" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B83" s="26" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C83" s="26" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D83" s="26" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E83" s="26" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F83" s="26" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="25" t="inlineStr">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>INGR</t>
+        </is>
+      </c>
+      <c r="B84" s="10" t="n">
+        <v>46614</v>
+      </c>
+      <c r="C84" s="10" t="n">
+        <v>46662</v>
+      </c>
+      <c r="D84" s="7" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E84" s="8" t="n">
+        <v>0.01219512195121952</v>
+      </c>
+      <c r="F84" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="25" t="inlineStr">
+        <is>
+          <t>September 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="26" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B84" s="25" t="inlineStr">
+      <c r="B87" s="26" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C84" s="25" t="inlineStr">
+      <c r="C87" s="26" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D84" s="25" t="inlineStr">
+      <c r="D87" s="26" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E84" s="25" t="inlineStr">
+      <c r="E87" s="26" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F84" s="25" t="inlineStr">
+      <c r="F87" s="26" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>INGR</t>
-        </is>
-      </c>
-      <c r="B85" s="10" t="n">
-        <v>46614</v>
-      </c>
-      <c r="C85" s="10" t="n">
-        <v>46662</v>
-      </c>
-      <c r="D85" s="7" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E85" s="8" t="n">
-        <v>0.01219512195121952</v>
-      </c>
-      <c r="F85" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="24" t="inlineStr">
-        <is>
-          <t>September 2027</t>
-        </is>
-      </c>
-    </row>
     <row r="88">
-      <c r="A88" s="25" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B88" s="25" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C88" s="25" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D88" s="25" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E88" s="25" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F88" s="25" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B88" s="10" t="n">
+        <v>46643</v>
+      </c>
+      <c r="C88" s="10" t="n">
+        <v>46709</v>
+      </c>
+      <c r="D88" s="7" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E88" s="8" t="n">
+        <v>0.09638554216867479</v>
+      </c>
+      <c r="F88" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B89" s="10" t="n">
-        <v>46643</v>
+        <v>46645</v>
       </c>
       <c r="C89" s="10" t="n">
-        <v>46709</v>
+        <v>46668</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>0.91</v>
+        <v>0.708</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>0.09638554216867479</v>
+        <v>0.02608695652173916</v>
       </c>
       <c r="F89" s="12" t="inlineStr">
         <is>
@@ -4816,20 +4817,20 @@
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B90" s="10" t="n">
-        <v>46645</v>
+        <v>46650</v>
       </c>
       <c r="C90" s="10" t="n">
-        <v>46668</v>
+        <v>46690</v>
       </c>
       <c r="D90" s="7" t="n">
-        <v>0.708</v>
+        <v>1.42</v>
       </c>
       <c r="E90" s="8" t="n">
-        <v>0.02608695652173916</v>
+        <v>0.0441176470588234</v>
       </c>
       <c r="F90" s="12" t="inlineStr">
         <is>
@@ -4837,25 +4838,64 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="5" t="inlineStr">
-        <is>
-          <t>TXN</t>
-        </is>
-      </c>
-      <c r="B91" s="10" t="n">
-        <v>46650</v>
-      </c>
-      <c r="C91" s="10" t="n">
-        <v>46690</v>
-      </c>
-      <c r="D91" s="7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="E91" s="8" t="n">
-        <v>0.0441176470588234</v>
-      </c>
-      <c r="F91" s="12" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="25" t="inlineStr">
+        <is>
+          <t>October 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="26" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B93" s="26" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C93" s="26" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D93" s="26" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E93" s="26" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F93" s="26" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>LECO</t>
+        </is>
+      </c>
+      <c r="B94" s="10" t="n">
+        <v>46676</v>
+      </c>
+      <c r="C94" s="10" t="n">
+        <v>46751</v>
+      </c>
+      <c r="D94" s="7" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E94" s="8" t="n">
+        <v>0.05333333333333338</v>
+      </c>
+      <c r="F94" s="12" t="inlineStr">
         <is>
           <t>Notion + yfinance</t>
         </is>
@@ -4900,7 +4940,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Complete Holdings Dividend Summary - 10/12/2026</t>
+          <t>Complete Holdings Dividend Summary - 10/19/2026</t>
         </is>
       </c>
     </row>
@@ -5000,11 +5040,11 @@
       <c r="F5" s="7" t="n">
         <v>0.29</v>
       </c>
-      <c r="G5" s="26" t="n">
+      <c r="G5" s="27" t="n">
         <v>1.16</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.01032212162618396</v>
+        <v>0.01045327554509916</v>
       </c>
       <c r="I5" s="10" t="n">
         <v>46255</v>
@@ -5053,11 +5093,11 @@
       <c r="F6" s="7" t="n">
         <v>2.52</v>
       </c>
-      <c r="G6" s="26" t="n">
+      <c r="G6" s="27" t="n">
         <v>10.08</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.02435106070044935</v>
+        <v>0.02329343307176349</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>46255</v>
@@ -5106,11 +5146,11 @@
       <c r="F7" s="7" t="n">
         <v>2.138</v>
       </c>
-      <c r="G7" s="26" t="n">
+      <c r="G7" s="27" t="n">
         <v>8.552</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.004833085693226959</v>
+        <v>0.005155099221223549</v>
       </c>
       <c r="I7" s="10" t="n">
         <v>46231</v>
@@ -5159,11 +5199,11 @@
       <c r="F8" s="7" t="n">
         <v>0.546</v>
       </c>
-      <c r="G8" s="26" t="n">
+      <c r="G8" s="27" t="n">
         <v>2.184</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>0.02660656666088859</v>
+        <v>0.02646150000721019</v>
       </c>
       <c r="I8" s="10" t="n">
         <v>46251</v>
@@ -5212,11 +5252,11 @@
       <c r="F9" s="7" t="n">
         <v>0.703</v>
       </c>
-      <c r="G9" s="26" t="n">
+      <c r="G9" s="27" t="n">
         <v>2.812</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.0369854010936235</v>
+        <v>0.03667786059118737</v>
       </c>
       <c r="I9" s="10" t="n">
         <v>46251</v>
@@ -5265,11 +5305,11 @@
       <c r="F10" s="7" t="n">
         <v>1.03</v>
       </c>
-      <c r="G10" s="26" t="n">
+      <c r="G10" s="27" t="n">
         <v>4.12</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.02719112911712621</v>
+        <v>0.02663391256691318</v>
       </c>
       <c r="I10" s="10" t="n">
         <v>46265</v>
@@ -5318,11 +5358,11 @@
       <c r="F11" s="7" t="n">
         <v>1.25</v>
       </c>
-      <c r="G11" s="26" t="n">
+      <c r="G11" s="27" t="n">
         <v>5</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.05990893907079166</v>
+        <v>0.05855829331739755</v>
       </c>
       <c r="I11" s="10" t="n">
         <v>46246</v>
@@ -5371,11 +5411,11 @@
       <c r="F12" s="7" t="n">
         <v>1.3</v>
       </c>
-      <c r="G12" s="26" t="n">
+      <c r="G12" s="27" t="n">
         <v>5.2</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0.01841164230021915</v>
+        <v>0.01779115923675148</v>
       </c>
       <c r="I12" s="10" t="n">
         <v>46274</v>
@@ -5424,11 +5464,11 @@
       <c r="F13" s="7" t="n">
         <v>0.24</v>
       </c>
-      <c r="G13" s="26" t="n">
+      <c r="G13" s="27" t="n">
         <v>0.96</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0.02474864597427012</v>
+        <v>0.02386278923498678</v>
       </c>
       <c r="I13" s="10" t="n">
         <v>46254</v>
@@ -5477,11 +5517,11 @@
       <c r="F14" s="7" t="n">
         <v>0.6</v>
       </c>
-      <c r="G14" s="26" t="n">
+      <c r="G14" s="27" t="n">
         <v>2.4</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>0.007395538275760539</v>
+        <v>0.007036008061734701</v>
       </c>
       <c r="I14" s="10" t="n">
         <v>46248</v>
@@ -5530,11 +5570,11 @@
       <c r="F15" s="7" t="n">
         <v>0.42</v>
       </c>
-      <c r="G15" s="26" t="n">
+      <c r="G15" s="27" t="n">
         <v>1.68</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0.01454306253370746</v>
+        <v>0.01569140206127972</v>
       </c>
       <c r="I15" s="10" t="n">
         <v>46297</v>
@@ -5583,11 +5623,11 @@
       <c r="F16" s="7" t="n">
         <v>1.78</v>
       </c>
-      <c r="G16" s="26" t="n">
+      <c r="G16" s="27" t="n">
         <v>7.12</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>0.03298357685968453</v>
+        <v>0.03156028283409273</v>
       </c>
       <c r="I16" s="10" t="n">
         <v>46253</v>
@@ -5636,11 +5676,11 @@
       <c r="F17" s="7" t="n">
         <v>0.86</v>
       </c>
-      <c r="G17" s="26" t="n">
+      <c r="G17" s="27" t="n">
         <v>3.44</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0.01480142827673315</v>
+        <v>0.01468798690508526</v>
       </c>
       <c r="I17" s="10" t="n">
         <v>46301</v>
@@ -5689,11 +5729,11 @@
       <c r="F18" s="7" t="n">
         <v>0.32</v>
       </c>
-      <c r="G18" s="26" t="n">
+      <c r="G18" s="27" t="n">
         <v>1.28</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0.02608518459263433</v>
+        <v>0.02526149686708471</v>
       </c>
       <c r="I18" s="10" t="n">
         <v>46280</v>
@@ -5742,11 +5782,11 @@
       <c r="F19" s="7" t="n">
         <v>0.84</v>
       </c>
-      <c r="G19" s="26" t="n">
+      <c r="G19" s="27" t="n">
         <v>3.36</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0.05388501362627859</v>
+        <v>0.05387205479463784</v>
       </c>
       <c r="I19" s="10" t="n">
         <v>46280</v>
@@ -5795,11 +5835,11 @@
       <c r="F20" s="7" t="n">
         <v>0.64</v>
       </c>
-      <c r="G20" s="26" t="n">
+      <c r="G20" s="27" t="n">
         <v>2.56</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0.02477139648518534</v>
+        <v>0.02452812046212039</v>
       </c>
       <c r="I20" s="10" t="n">
         <v>46247</v>
@@ -5848,11 +5888,11 @@
       <c r="F21" s="7" t="n">
         <v>1.59</v>
       </c>
-      <c r="G21" s="26" t="n">
+      <c r="G21" s="27" t="n">
         <v>6.36</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0.01906817724130214</v>
+        <v>0.01856934306569343</v>
       </c>
       <c r="I21" s="10" t="n">
         <v>46304</v>
@@ -5873,53 +5913,53 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>GGG</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>SMID/DAC</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
         <is>
           <t>Jan/Apr/Jul/Oct</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E22" s="15" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="F22" s="17" t="n">
+      <c r="F22" s="16" t="n">
         <v>0.295</v>
       </c>
-      <c r="G22" s="27" t="n">
+      <c r="G22" s="28" t="n">
         <v>1.18</v>
       </c>
-      <c r="H22" s="19" t="n">
-        <v>0.01507024206908392</v>
-      </c>
-      <c r="I22" s="20" t="n">
+      <c r="H22" s="22" t="n">
+        <v>0.0146057678750838</v>
+      </c>
+      <c r="I22" s="19" t="n">
         <v>46223</v>
       </c>
-      <c r="J22" s="18" t="n">
+      <c r="J22" s="17" t="n">
         <v>0.07272727272727258</v>
       </c>
-      <c r="K22" s="20" t="n">
+      <c r="K22" s="19" t="n">
         <v>46383</v>
       </c>
-      <c r="L22" s="20" t="n">
+      <c r="L22" s="19" t="n">
         <v>46404</v>
       </c>
-      <c r="M22" s="22" t="inlineStr">
+      <c r="M22" s="21" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
@@ -5954,11 +5994,11 @@
       <c r="F23" s="7" t="n">
         <v>2.33</v>
       </c>
-      <c r="G23" s="26" t="n">
+      <c r="G23" s="27" t="n">
         <v>9.32</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>0.03219121426382717</v>
+        <v>0.03030312976869731</v>
       </c>
       <c r="I23" s="10" t="n">
         <v>46268</v>
@@ -6007,11 +6047,11 @@
       <c r="F24" s="7" t="n">
         <v>1.38</v>
       </c>
-      <c r="G24" s="26" t="n">
+      <c r="G24" s="27" t="n">
         <v>5.52</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>0.02065597808138082</v>
+        <v>0.02062048170108176</v>
       </c>
       <c r="I24" s="10" t="n">
         <v>46262</v>
@@ -6060,23 +6100,23 @@
       <c r="F25" s="7" t="n">
         <v>0.293</v>
       </c>
-      <c r="G25" s="26" t="n">
+      <c r="G25" s="27" t="n">
         <v>1.172</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0.06113719328824217</v>
+        <v>0.05780204234676849</v>
       </c>
       <c r="I25" s="10" t="n">
-        <v>46216</v>
+        <v>46308</v>
       </c>
       <c r="J25" s="8" t="n">
         <v>0.01034482758620691</v>
       </c>
       <c r="K25" s="10" t="n">
-        <v>46352</v>
+        <v>46351</v>
       </c>
       <c r="L25" s="10" t="n">
-        <v>46400</v>
+        <v>46399</v>
       </c>
       <c r="M25" s="12" t="inlineStr">
         <is>
@@ -6085,53 +6125,53 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>HWC</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>SMID/DAC</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
         <is>
           <t>Mar/Jun/Sep/Dec</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E26" s="15" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="F26" s="17" t="n">
+      <c r="F26" s="16" t="n">
         <v>0.5</v>
       </c>
-      <c r="G26" s="27" t="n">
+      <c r="G26" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="H26" s="19" t="n">
-        <v>0.02748952065840456</v>
-      </c>
-      <c r="I26" s="20" t="n">
+      <c r="H26" s="22" t="n">
+        <v>0.02740852359246717</v>
+      </c>
+      <c r="I26" s="19" t="n">
         <v>46269</v>
       </c>
-      <c r="J26" s="18" t="n">
+      <c r="J26" s="17" t="n">
         <v>0.1111111111111111</v>
       </c>
-      <c r="K26" s="20" t="n">
+      <c r="K26" s="19" t="n">
         <v>46429</v>
       </c>
-      <c r="L26" s="20" t="n">
+      <c r="L26" s="19" t="n">
         <v>46450</v>
       </c>
-      <c r="M26" s="22" t="inlineStr">
+      <c r="M26" s="21" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
@@ -6166,11 +6206,11 @@
       <c r="F27" s="7" t="n">
         <v>0.83</v>
       </c>
-      <c r="G27" s="26" t="n">
+      <c r="G27" s="27" t="n">
         <v>3.32</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0.03471713997023395</v>
+        <v>0.03416692459155611</v>
       </c>
       <c r="I27" s="10" t="n">
         <v>46296</v>
@@ -6219,11 +6259,11 @@
       <c r="F28" s="7" t="n">
         <v>0.61</v>
       </c>
-      <c r="G28" s="26" t="n">
+      <c r="G28" s="27" t="n">
         <v>2.44</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>0.01631015976237089</v>
+        <v>0.01601680490124256</v>
       </c>
       <c r="I28" s="10" t="n">
         <v>46269</v>
@@ -6272,11 +6312,11 @@
       <c r="F29" s="7" t="n">
         <v>1.34</v>
       </c>
-      <c r="G29" s="26" t="n">
+      <c r="G29" s="27" t="n">
         <v>5.36</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.02043461780192916</v>
+        <v>0.02108990804140305</v>
       </c>
       <c r="I29" s="10" t="n">
         <v>46259</v>
@@ -6325,11 +6365,11 @@
       <c r="F30" s="7" t="n">
         <v>1.65</v>
       </c>
-      <c r="G30" s="26" t="n">
+      <c r="G30" s="27" t="n">
         <v>6.6</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>0.01974688024131375</v>
+        <v>0.01956773053691266</v>
       </c>
       <c r="I30" s="10" t="n">
         <v>46301</v>
@@ -6378,11 +6418,11 @@
       <c r="F31" s="7" t="n">
         <v>1.084</v>
       </c>
-      <c r="G31" s="26" t="n">
+      <c r="G31" s="27" t="n">
         <v>2.168</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0.01961369636922693</v>
+        <v>0.01795251849684193</v>
       </c>
       <c r="I31" s="10" t="n">
         <v>46304</v>
@@ -6431,11 +6471,11 @@
       <c r="F32" s="7" t="n">
         <v>0.79</v>
       </c>
-      <c r="G32" s="26" t="n">
+      <c r="G32" s="27" t="n">
         <v>3.16</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>0.01212074758762932</v>
+        <v>0.01212586310817193</v>
       </c>
       <c r="I32" s="10" t="n">
         <v>46295</v>
@@ -6444,10 +6484,10 @@
         <v>0.05333333333333338</v>
       </c>
       <c r="K32" s="10" t="n">
-        <v>46311</v>
+        <v>46676</v>
       </c>
       <c r="L32" s="10" t="n">
-        <v>46386</v>
+        <v>46751</v>
       </c>
       <c r="M32" s="12" t="inlineStr">
         <is>
@@ -6484,11 +6524,11 @@
       <c r="F33" s="7" t="n">
         <v>0.72</v>
       </c>
-      <c r="G33" s="26" t="n">
+      <c r="G33" s="27" t="n">
         <v>2.88</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0.03109143998051593</v>
+        <v>0.03067262567036151</v>
       </c>
       <c r="I33" s="10" t="n">
         <v>46290</v>
@@ -6537,14 +6577,14 @@
       <c r="F34" s="7" t="n">
         <v>0.48</v>
       </c>
-      <c r="G34" s="26" t="n">
+      <c r="G34" s="27" t="n">
         <v>1.92</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0.04253433819142445</v>
+        <v>0.0418647250543317</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>46209</v>
+        <v>46308</v>
       </c>
       <c r="J34" s="8" t="n">
         <v>0.0666666666666666</v>
@@ -6590,11 +6630,11 @@
       <c r="F35" s="7" t="n">
         <v>0.91</v>
       </c>
-      <c r="G35" s="26" t="n">
+      <c r="G35" s="27" t="n">
         <v>3.64</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>0.006744487525791792</v>
+        <v>0.006843878990992571</v>
       </c>
       <c r="I35" s="10" t="n">
         <v>46254</v>
@@ -6615,55 +6655,55 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" s="14" t="inlineStr">
         <is>
           <t>MSM</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B36" s="15" t="inlineStr">
         <is>
           <t>SMID/DAC</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
         <is>
           <t>Jan/Apr/Jul/Nov</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="E36" s="15" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="F36" s="7" t="n">
+      <c r="F36" s="16" t="n">
         <v>0.87</v>
       </c>
-      <c r="G36" s="26" t="n">
+      <c r="G36" s="28" t="n">
         <v>3.48</v>
       </c>
-      <c r="H36" s="9" t="n">
-        <v>0.02696629149713606</v>
-      </c>
-      <c r="I36" s="10" t="n">
+      <c r="H36" s="22" t="n">
+        <v>0.02687466099600802</v>
+      </c>
+      <c r="I36" s="19" t="n">
         <v>46211</v>
       </c>
-      <c r="J36" s="8" t="n">
+      <c r="J36" s="17" t="n">
         <v>0.0235294117647059</v>
       </c>
-      <c r="K36" s="10" t="n">
-        <v>46305</v>
-      </c>
-      <c r="L36" s="10" t="n">
-        <v>46704</v>
-      </c>
-      <c r="M36" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="K36" s="19" t="n">
+        <v>46318</v>
+      </c>
+      <c r="L36" s="19" t="n">
+        <v>46339</v>
+      </c>
+      <c r="M36" s="21" t="inlineStr">
+        <is>
+          <t>yfinance</t>
         </is>
       </c>
     </row>
@@ -6696,11 +6736,11 @@
       <c r="F37" s="7" t="n">
         <v>0.41</v>
       </c>
-      <c r="G37" s="26" t="n">
+      <c r="G37" s="27" t="n">
         <v>1.64</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>0.04726905935798738</v>
+        <v>0.04446252066229808</v>
       </c>
       <c r="I37" s="10" t="n">
         <v>46266</v>
@@ -6749,11 +6789,11 @@
       <c r="F38" s="7" t="n">
         <v>0.579</v>
       </c>
-      <c r="G38" s="26" t="n">
+      <c r="G38" s="27" t="n">
         <v>1.158</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0.03014055323240503</v>
+        <v>0.0300600424991833</v>
       </c>
       <c r="I38" s="10" t="n">
         <v>46251</v>
@@ -6802,11 +6842,11 @@
       <c r="F39" s="7" t="n">
         <v>0.272</v>
       </c>
-      <c r="G39" s="26" t="n">
+      <c r="G39" s="27" t="n">
         <v>3.264</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>0.06026977174155138</v>
+        <v>0.05860490201786151</v>
       </c>
       <c r="I39" s="10" t="n">
         <v>46295</v>
@@ -6855,11 +6895,11 @@
       <c r="F40" s="7" t="n">
         <v>1.19</v>
       </c>
-      <c r="G40" s="26" t="n">
+      <c r="G40" s="27" t="n">
         <v>4.76</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0.04579785550402819</v>
+        <v>0.04296028762541161</v>
       </c>
       <c r="I40" s="10" t="n">
         <v>46231</v>
@@ -6908,11 +6948,11 @@
       <c r="F41" s="7" t="n">
         <v>0.67</v>
       </c>
-      <c r="G41" s="26" t="n">
+      <c r="G41" s="27" t="n">
         <v>2.68</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>0.03777308125827056</v>
+        <v>0.03813318222181694</v>
       </c>
       <c r="I41" s="10" t="n">
         <v>46274</v>
@@ -6961,11 +7001,11 @@
       <c r="F42" s="7" t="n">
         <v>1.48</v>
       </c>
-      <c r="G42" s="26" t="n">
+      <c r="G42" s="27" t="n">
         <v>5.92</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>0.04691896062464589</v>
+        <v>0.04479418762075352</v>
       </c>
       <c r="I42" s="10" t="n">
         <v>46269</v>
@@ -7014,11 +7054,11 @@
       <c r="F43" s="7" t="n">
         <v>0.43</v>
       </c>
-      <c r="G43" s="26" t="n">
+      <c r="G43" s="27" t="n">
         <v>1.72</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>0.060584714229587</v>
+        <v>0.05809829510539736</v>
       </c>
       <c r="I43" s="10" t="n">
         <v>46227</v>
@@ -7067,11 +7107,11 @@
       <c r="F44" s="7" t="n">
         <v>0.84</v>
       </c>
-      <c r="G44" s="26" t="n">
+      <c r="G44" s="27" t="n">
         <v>3.36</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>0.03130677936678974</v>
+        <v>0.03105934544760066</v>
       </c>
       <c r="I44" s="10" t="n">
         <v>46268</v>
@@ -7120,11 +7160,11 @@
       <c r="F45" s="7" t="n">
         <v>1.089</v>
       </c>
-      <c r="G45" s="26" t="n">
+      <c r="G45" s="27" t="n">
         <v>4.356</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>0.02866072298257646</v>
+        <v>0.0275277889821852</v>
       </c>
       <c r="I45" s="10" t="n">
         <v>46227</v>
@@ -7173,11 +7213,11 @@
       <c r="F46" s="7" t="n">
         <v>0.551</v>
       </c>
-      <c r="G46" s="26" t="n">
+      <c r="G46" s="27" t="n">
         <v>2.204</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>0.04832803469187192</v>
+        <v>0.0501250838938402</v>
       </c>
       <c r="I46" s="10" t="n">
         <v>46290</v>
@@ -7198,53 +7238,53 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="A47" s="14" t="inlineStr">
         <is>
           <t>PSX</t>
         </is>
       </c>
-      <c r="B47" s="16" t="inlineStr">
+      <c r="B47" s="15" t="inlineStr">
         <is>
           <t>QDVD/DAC</t>
         </is>
       </c>
-      <c r="C47" s="16" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D47" s="16" t="inlineStr">
+      <c r="C47" s="15" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D47" s="15" t="inlineStr">
         <is>
           <t>Feb/May/Aug/Nov</t>
         </is>
       </c>
-      <c r="E47" s="16" t="inlineStr">
+      <c r="E47" s="15" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="F47" s="17" t="n">
+      <c r="F47" s="16" t="n">
         <v>1.27</v>
       </c>
-      <c r="G47" s="27" t="n">
+      <c r="G47" s="28" t="n">
         <v>5.08</v>
       </c>
-      <c r="H47" s="19" t="n">
-        <v>0.01786279313034211</v>
-      </c>
-      <c r="I47" s="20" t="n">
+      <c r="H47" s="22" t="n">
+        <v>0.01698655802003307</v>
+      </c>
+      <c r="I47" s="19" t="n">
         <v>46252</v>
       </c>
-      <c r="J47" s="18" t="n">
+      <c r="J47" s="17" t="n">
         <v>0.05833333333333339</v>
       </c>
-      <c r="K47" s="20" t="n">
+      <c r="K47" s="19" t="n">
         <v>46505</v>
       </c>
-      <c r="L47" s="20" t="n">
+      <c r="L47" s="19" t="n">
         <v>46526</v>
       </c>
-      <c r="M47" s="22" t="inlineStr">
+      <c r="M47" s="21" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
@@ -7279,11 +7319,11 @@
       <c r="F48" s="7" t="n">
         <v>0.98</v>
       </c>
-      <c r="G48" s="26" t="n">
+      <c r="G48" s="27" t="n">
         <v>3.92</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>0.01515180818849923</v>
+        <v>0.01472908914196234</v>
       </c>
       <c r="I48" s="10" t="n">
         <v>46252</v>
@@ -7332,11 +7372,11 @@
       <c r="F49" s="7" t="n">
         <v>2.44</v>
       </c>
-      <c r="G49" s="26" t="n">
+      <c r="G49" s="27" t="n">
         <v>9.76</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>0.0270262782600054</v>
+        <v>0.02684619212402568</v>
       </c>
       <c r="I49" s="10" t="n">
         <v>46253</v>
@@ -7385,11 +7425,11 @@
       <c r="F50" s="7" t="n">
         <v>0.84</v>
       </c>
-      <c r="G50" s="26" t="n">
+      <c r="G50" s="27" t="n">
         <v>3.36</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>0.03798756490592253</v>
+        <v>0.03676269334137368</v>
       </c>
       <c r="I50" s="10" t="n">
         <v>46273</v>
@@ -7438,11 +7478,11 @@
       <c r="F51" s="7" t="n">
         <v>1.3</v>
       </c>
-      <c r="G51" s="26" t="n">
+      <c r="G51" s="27" t="n">
         <v>5.2</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>0.05061812352845635</v>
+        <v>0.05203642533893469</v>
       </c>
       <c r="I51" s="10" t="n">
         <v>46280</v>
@@ -7491,11 +7531,11 @@
       <c r="F52" s="7" t="n">
         <v>1.021</v>
       </c>
-      <c r="G52" s="26" t="n">
+      <c r="G52" s="27" t="n">
         <v>4.084</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>0.04612083409655995</v>
+        <v>0.04487665648324178</v>
       </c>
       <c r="I52" s="10" t="n">
         <v>46295</v>
@@ -7544,11 +7584,11 @@
       <c r="F53" s="7" t="n">
         <v>1.42</v>
       </c>
-      <c r="G53" s="26" t="n">
+      <c r="G53" s="27" t="n">
         <v>5.68</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>0.02024161753504176</v>
+        <v>0.02051059888861486</v>
       </c>
       <c r="I53" s="10" t="n">
         <v>46234</v>
@@ -7597,11 +7637,11 @@
       <c r="F54" s="7" t="n">
         <v>0.531</v>
       </c>
-      <c r="G54" s="26" t="n">
+      <c r="G54" s="27" t="n">
         <v>2.124</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>0.03395140590432928</v>
+        <v>0.03252679786732145</v>
       </c>
       <c r="I54" s="10" t="n">
         <v>46241</v>
@@ -7650,11 +7690,11 @@
       <c r="F55" s="7" t="n">
         <v>1.42</v>
       </c>
-      <c r="G55" s="26" t="n">
+      <c r="G55" s="27" t="n">
         <v>5.68</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>0.02034092608022438</v>
+        <v>0.01977647076699418</v>
       </c>
       <c r="I55" s="10" t="n">
         <v>46265</v>
@@ -7703,11 +7743,11 @@
       <c r="F56" s="7" t="n">
         <v>0.708</v>
       </c>
-      <c r="G56" s="26" t="n">
+      <c r="G56" s="27" t="n">
         <v>2.832</v>
       </c>
       <c r="H56" s="9" t="n">
-        <v>0.06643208841292222</v>
+        <v>0.06363329810206279</v>
       </c>
       <c r="I56" s="10" t="n">
         <v>46304</v>
@@ -7756,11 +7796,11 @@
       <c r="F57" s="7" t="n">
         <v>1.03</v>
       </c>
-      <c r="G57" s="26" t="n">
+      <c r="G57" s="27" t="n">
         <v>4.12</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>0.02392427756445954</v>
+        <v>0.02299684646296404</v>
       </c>
       <c r="I57" s="10" t="n">
         <v>46251</v>

--- a/data/dividend_calendar.xlsx
+++ b/data/dividend_calendar.xlsx
@@ -145,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -166,23 +166,19 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -552,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L58"/>
+  <dimension ref="A1:L57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -579,7 +575,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Estimated Dividend Calendar: Anticipated Announcements - 10/19/2026</t>
+          <t>Estimated Dividend Calendar: Anticipated Announcements - 10/26/2026</t>
         </is>
       </c>
     </row>
@@ -684,7 +680,7 @@
         <v>46048</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>-266</v>
+        <v>-273</v>
       </c>
       <c r="J6" s="10" t="n">
         <v>46413</v>
@@ -695,13 +691,13 @@
         </is>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0.05809829510539736</v>
+        <v>0.0569065336076718</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -715,25 +711,25 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>1.38</v>
+        <v>0.64</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1.35</v>
+        <v>0.6</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>0.02222222222222208</v>
+        <v>0.06666666666666674</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>46318</v>
+        <v>46322</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>46352</v>
+        <v>46338</v>
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
@@ -741,57 +737,59 @@
         </is>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0.02062048170108176</v>
+        <v>0.02369273417580299</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>MSM</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>COR</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="D8" s="16" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="F8" s="17" t="n">
-        <v>0.0235294117647059</v>
-      </c>
-      <c r="G8" s="18" t="n"/>
-      <c r="H8" s="19" t="n">
-        <v>46318</v>
-      </c>
-      <c r="I8" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="J8" s="19" t="n">
-        <v>46339</v>
-      </c>
-      <c r="K8" s="21" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
-      <c r="L8" s="22" t="n">
-        <v>0.02687466099600802</v>
+      <c r="D8" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>0.09090909090909079</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>46329</v>
+      </c>
+      <c r="I8" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>46338</v>
+      </c>
+      <c r="K8" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="n">
+        <v>0.007181758491234575</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -805,25 +803,25 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>0.64</v>
+        <v>2.44</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>0.6</v>
+        <v>2.14</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>0.06666666666666674</v>
+        <v>0.1401869158878504</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>46322</v>
+        <v>46332</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>46338</v>
+        <v>46346</v>
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
@@ -831,13 +829,13 @@
         </is>
       </c>
       <c r="L9" s="9" t="n">
-        <v>0.02452812046212039</v>
+        <v>0.02711864452769955</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -851,25 +849,25 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>0.6</v>
+        <v>1.03</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>0.55</v>
+        <v>0.99</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.09090909090909079</v>
+        <v>0.04040404040404044</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>46329</v>
-      </c>
-      <c r="I10" s="23" t="n">
-        <v>15</v>
+        <v>46341</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>20</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>46338</v>
+        <v>46340</v>
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
@@ -877,13 +875,13 @@
         </is>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0.007036008061734701</v>
+        <v>0.02236638505494382</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -893,29 +891,29 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2.44</v>
+        <v>0.48</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>2.14</v>
+        <v>0.45</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>0.1401869158878504</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>46332</v>
-      </c>
-      <c r="I11" s="23" t="n">
-        <v>18</v>
+        <v>46344</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>23</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>46346</v>
+        <v>46385</v>
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
@@ -923,13 +921,13 @@
         </is>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0.02684619212402568</v>
+        <v>0.03972687621059211</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -939,29 +937,29 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>1.03</v>
+        <v>0.41</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>0.99</v>
+        <v>0.4</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.04040404040404044</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>46341</v>
-      </c>
-      <c r="I12" s="23" t="n">
-        <v>27</v>
+        <v>46347</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>26</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>46340</v>
+        <v>46358</v>
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
@@ -969,13 +967,13 @@
         </is>
       </c>
       <c r="L12" s="9" t="n">
-        <v>0.02299684646296404</v>
+        <v>0.04288702740626434</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -985,29 +983,29 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.48</v>
+        <v>0.293</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>0.45</v>
+        <v>0.29</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.01034482758620691</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>46344</v>
-      </c>
-      <c r="I13" s="23" t="n">
+        <v>46351</v>
+      </c>
+      <c r="I13" s="14" t="n">
         <v>30</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>46385</v>
+        <v>46399</v>
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
@@ -1015,13 +1013,13 @@
         </is>
       </c>
       <c r="L13" s="9" t="n">
-        <v>0.0418647250543317</v>
+        <v>0.05554502269247655</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>EMN</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -1035,25 +1033,25 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.41</v>
+        <v>0.84</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.01204819277108435</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>46347</v>
-      </c>
-      <c r="I14" s="23" t="n">
-        <v>33</v>
+        <v>46360</v>
+      </c>
+      <c r="I14" s="14" t="n">
+        <v>39</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>46358</v>
+        <v>46371</v>
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
@@ -1061,13 +1059,13 @@
         </is>
       </c>
       <c r="L14" s="9" t="n">
-        <v>0.04446252066229808</v>
+        <v>0.05093224098570341</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -1077,29 +1075,29 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.293</v>
+        <v>2.52</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>0.29</v>
+        <v>2.38</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0.01034482758620691</v>
+        <v>0.05882352941176476</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>46351</v>
-      </c>
-      <c r="I15" s="23" t="n">
-        <v>37</v>
+        <v>46366</v>
+      </c>
+      <c r="I15" s="14" t="n">
+        <v>45</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>46399</v>
+        <v>46432</v>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
@@ -1107,13 +1105,13 @@
         </is>
       </c>
       <c r="L15" s="9" t="n">
-        <v>0.05780204234676849</v>
+        <v>0.02243989253356084</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>EMN</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -1123,29 +1121,29 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.84</v>
+        <v>0.24</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>0.83</v>
+        <v>0.23</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0.01204819277108435</v>
+        <v>0.04347826086956513</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>46360</v>
-      </c>
-      <c r="I16" s="23" t="n">
-        <v>46</v>
+        <v>46380</v>
+      </c>
+      <c r="I16" s="14" t="n">
+        <v>59</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>46371</v>
+        <v>46436</v>
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
@@ -1153,59 +1151,59 @@
         </is>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0.05387205479463784</v>
+        <v>0.02323892442716519</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>AMGN</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>0.05882352941176476</v>
-      </c>
-      <c r="G17" s="9" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H17" s="10" t="n">
-        <v>46366</v>
-      </c>
-      <c r="I17" s="23" t="n">
-        <v>52</v>
-      </c>
-      <c r="J17" s="10" t="n">
-        <v>46432</v>
-      </c>
-      <c r="K17" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L17" s="9" t="n">
-        <v>0.02329343307176349</v>
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>GGG</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>0.07272727272727258</v>
+      </c>
+      <c r="G17" s="19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H17" s="20" t="n">
+        <v>46383</v>
+      </c>
+      <c r="I17" s="21" t="n">
+        <v>62</v>
+      </c>
+      <c r="J17" s="20" t="n">
+        <v>46404</v>
+      </c>
+      <c r="K17" s="22" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="L17" s="19" t="n">
+        <v>0.01758962534253235</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>CNP</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -1215,89 +1213,89 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>0.07499999999999993</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>46402</v>
+      </c>
+      <c r="I18" s="14" t="n">
+        <v>81</v>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v>46483</v>
+      </c>
+      <c r="K18" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+      <c r="L18" s="9" t="n">
+        <v>0.01418088867191861</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>BKH</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
           <t>Feb</t>
         </is>
       </c>
-      <c r="D18" s="7" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>0.04347826086956513</v>
-      </c>
-      <c r="G18" s="9" t="n">
+      <c r="D19" s="7" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>0.03994082840236673</v>
+      </c>
+      <c r="G19" s="9" t="n">
         <v>0.04</v>
       </c>
-      <c r="H18" s="10" t="n">
-        <v>46380</v>
-      </c>
-      <c r="I18" s="23" t="n">
-        <v>66</v>
-      </c>
-      <c r="J18" s="10" t="n">
-        <v>46436</v>
-      </c>
-      <c r="K18" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L18" s="9" t="n">
-        <v>0.02386278923498678</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>GGG</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C19" s="15" t="inlineStr">
-        <is>
-          <t>Jan</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E19" s="16" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="F19" s="17" t="n">
-        <v>0.07272727272727258</v>
-      </c>
-      <c r="G19" s="22" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="H19" s="19" t="n">
-        <v>46383</v>
-      </c>
-      <c r="I19" s="24" t="n">
-        <v>69</v>
-      </c>
-      <c r="J19" s="19" t="n">
-        <v>46404</v>
-      </c>
-      <c r="K19" s="21" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
-      <c r="L19" s="22" t="n">
-        <v>0.0146057678750838</v>
+      <c r="H19" s="10" t="n">
+        <v>46411</v>
+      </c>
+      <c r="I19" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="J19" s="10" t="n">
+        <v>46435</v>
+      </c>
+      <c r="K19" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="n">
+        <v>0.03531332534209399</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -1307,29 +1305,29 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.86</v>
+        <v>1.78</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>0.8</v>
+        <v>1.71</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>0.07499999999999993</v>
+        <v>0.04093567251461992</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>46402</v>
-      </c>
-      <c r="I20" s="23" t="n">
-        <v>88</v>
+        <v>46417</v>
+      </c>
+      <c r="I20" s="14" t="n">
+        <v>96</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>46483</v>
+        <v>46433</v>
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
@@ -1337,45 +1335,45 @@
         </is>
       </c>
       <c r="L20" s="9" t="n">
-        <v>0.01468798690508526</v>
+        <v>0.030444264542924</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>BKH</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.703</v>
+        <v>0.579</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>0.676</v>
+        <v>0.584</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>0.03994082840236673</v>
+        <v>1.183219178082192</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>46411</v>
-      </c>
-      <c r="I21" s="23" t="n">
-        <v>97</v>
+        <v>46423</v>
+      </c>
+      <c r="I21" s="14" t="n">
+        <v>102</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>46435</v>
+        <v>46473</v>
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
@@ -1383,13 +1381,13 @@
         </is>
       </c>
       <c r="L21" s="9" t="n">
-        <v>0.03667786059118737</v>
+        <v>0.02968089242895755</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -1399,29 +1397,29 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>1.78</v>
+        <v>0.61</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>1.71</v>
+        <v>0.58</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>0.04093567251461992</v>
+        <v>0.05172413793103453</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>46417</v>
-      </c>
-      <c r="I22" s="23" t="n">
-        <v>103</v>
+        <v>46428</v>
+      </c>
+      <c r="I22" s="14" t="n">
+        <v>107</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>46433</v>
+        <v>46452</v>
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
@@ -1429,18 +1427,18 @@
         </is>
       </c>
       <c r="L22" s="9" t="n">
-        <v>0.03156028283409273</v>
+        <v>0.0150659132006637</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Semi-Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1449,25 +1447,25 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.579</v>
+        <v>1.3</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>0.584</v>
+        <v>1.27</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>1.183219178082192</v>
+        <v>0.02362204724409451</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>46423</v>
-      </c>
-      <c r="I23" s="23" t="n">
-        <v>109</v>
+        <v>46428</v>
+      </c>
+      <c r="I23" s="14" t="n">
+        <v>107</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>46473</v>
+        <v>46460</v>
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
@@ -1475,59 +1473,59 @@
         </is>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0.0300600424991833</v>
+        <v>0.04933820547108572</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>JKHY</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>HWC</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="D24" s="7" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E24" s="7" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="F24" s="8" t="n">
-        <v>0.05172413793103453</v>
-      </c>
-      <c r="G24" s="9" t="n">
+      <c r="D24" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F24" s="18" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="G24" s="19" t="n">
         <v>0.08</v>
       </c>
-      <c r="H24" s="10" t="n">
-        <v>46428</v>
-      </c>
-      <c r="I24" s="23" t="n">
-        <v>114</v>
-      </c>
-      <c r="J24" s="10" t="n">
-        <v>46452</v>
-      </c>
-      <c r="K24" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L24" s="9" t="n">
-        <v>0.01601680490124256</v>
+      <c r="H24" s="20" t="n">
+        <v>46429</v>
+      </c>
+      <c r="I24" s="21" t="n">
+        <v>108</v>
+      </c>
+      <c r="J24" s="20" t="n">
+        <v>46450</v>
+      </c>
+      <c r="K24" s="22" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="L24" s="19" t="n">
+        <v>0.02699419758207186</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -1537,89 +1535,89 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>0.02439024390243905</v>
+      </c>
+      <c r="G25" s="9" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H25" s="10" t="n">
+        <v>46431</v>
+      </c>
+      <c r="I25" s="14" t="n">
+        <v>110</v>
+      </c>
+      <c r="J25" s="10" t="n">
+        <v>46480</v>
+      </c>
+      <c r="K25" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+      <c r="L25" s="9" t="n">
+        <v>0.01550173010380623</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>PEG</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="D25" s="7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E25" s="7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="F25" s="8" t="n">
-        <v>0.02362204724409451</v>
-      </c>
-      <c r="G25" s="9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="H25" s="10" t="n">
-        <v>46428</v>
-      </c>
-      <c r="I25" s="23" t="n">
-        <v>114</v>
-      </c>
-      <c r="J25" s="10" t="n">
-        <v>46460</v>
-      </c>
-      <c r="K25" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L25" s="9" t="n">
-        <v>0.05203642533893469</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr">
-        <is>
-          <t>HWC</t>
-        </is>
-      </c>
-      <c r="B26" s="15" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C26" s="15" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E26" s="16" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="F26" s="17" t="n">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="G26" s="22" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H26" s="19" t="n">
-        <v>46429</v>
-      </c>
-      <c r="I26" s="24" t="n">
-        <v>115</v>
-      </c>
-      <c r="J26" s="19" t="n">
-        <v>46450</v>
-      </c>
-      <c r="K26" s="21" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
-      <c r="L26" s="22" t="n">
-        <v>0.02740852359246717</v>
+      <c r="D26" s="7" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>0.06349206349206354</v>
+      </c>
+      <c r="G26" s="9" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H26" s="10" t="n">
+        <v>46432</v>
+      </c>
+      <c r="I26" s="14" t="n">
+        <v>111</v>
+      </c>
+      <c r="J26" s="10" t="n">
+        <v>46455</v>
+      </c>
+      <c r="K26" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+      <c r="L26" s="9" t="n">
+        <v>0.03696551724137932</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -1629,29 +1627,29 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>0.42</v>
+        <v>2.138</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>0.41</v>
+        <v>1.883</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>0.02439024390243905</v>
+        <v>0.6872012745618694</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>46431</v>
-      </c>
-      <c r="I27" s="23" t="n">
-        <v>117</v>
+        <v>46433</v>
+      </c>
+      <c r="I27" s="14" t="n">
+        <v>112</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>46480</v>
+        <v>46425</v>
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
@@ -1659,13 +1657,13 @@
         </is>
       </c>
       <c r="L27" s="9" t="n">
-        <v>0.01569140206127972</v>
+        <v>0.005378819524740057</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -1675,29 +1673,29 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>0.67</v>
+        <v>1.3</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>0.63</v>
+        <v>1.25</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>0.06349206349206354</v>
+        <v>4.96</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>46432</v>
-      </c>
-      <c r="I28" s="23" t="n">
-        <v>118</v>
+        <v>46433</v>
+      </c>
+      <c r="I28" s="14" t="n">
+        <v>112</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>46455</v>
+        <v>46383</v>
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
@@ -1705,13 +1703,13 @@
         </is>
       </c>
       <c r="L28" s="9" t="n">
-        <v>0.03813318222181694</v>
+        <v>0.01682385150932105</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -1721,29 +1719,29 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>2.138</v>
+        <v>0.32</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>1.883</v>
+        <v>0.24</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>0.6872012745618694</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="H29" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I29" s="23" t="n">
-        <v>119</v>
+      <c r="I29" s="14" t="n">
+        <v>112</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>46425</v>
+        <v>46458</v>
       </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
@@ -1751,13 +1749,13 @@
         </is>
       </c>
       <c r="L29" s="9" t="n">
-        <v>0.005155099221223549</v>
+        <v>0.0246807407010214</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -1767,29 +1765,29 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>1.3</v>
+        <v>0.84</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>1.25</v>
+        <v>0.82</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>4.96</v>
+        <v>0.02439024390243905</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H30" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I30" s="23" t="n">
-        <v>119</v>
+      <c r="I30" s="14" t="n">
+        <v>112</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>46383</v>
+        <v>46634</v>
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
@@ -1797,13 +1795,13 @@
         </is>
       </c>
       <c r="L30" s="9" t="n">
-        <v>0.01779115923675148</v>
+        <v>0.03036876372501466</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -1813,29 +1811,29 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>0.32</v>
+        <v>0.531</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>0.24</v>
+        <v>0.588964</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.005735494868956323</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H31" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I31" s="23" t="n">
-        <v>119</v>
+      <c r="I31" s="14" t="n">
+        <v>112</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>46458</v>
+        <v>46608</v>
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
@@ -1843,13 +1841,13 @@
         </is>
       </c>
       <c r="L31" s="9" t="n">
-        <v>0.02526149686708471</v>
+        <v>0.03209913947068581</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -1859,29 +1857,29 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>0.84</v>
+        <v>0.29</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>0.82</v>
+        <v>0.27</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>0.02439024390243905</v>
+        <v>0.07407407407407393</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="I32" s="23" t="n">
+        <v>46440</v>
+      </c>
+      <c r="I32" s="14" t="n">
         <v>119</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>46634</v>
+        <v>46450</v>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
@@ -1889,13 +1887,13 @@
         </is>
       </c>
       <c r="L32" s="9" t="n">
-        <v>0.03105934544760066</v>
+        <v>0.01085024750037608</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -1905,29 +1903,29 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>0.531</v>
+        <v>2.33</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>0.588964</v>
+        <v>2.3</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>0.005735494868956323</v>
+        <v>0.01304347826086967</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="I33" s="23" t="n">
-        <v>119</v>
+        <v>46441</v>
+      </c>
+      <c r="I33" s="14" t="n">
+        <v>120</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>46608</v>
+        <v>46456</v>
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
@@ -1935,13 +1933,13 @@
         </is>
       </c>
       <c r="L33" s="9" t="n">
-        <v>0.03252679786732145</v>
+        <v>0.02907820093926896</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -1951,89 +1949,89 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>0.06000000000000005</v>
+      </c>
+      <c r="G34" s="9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H34" s="10" t="n">
+        <v>46452</v>
+      </c>
+      <c r="I34" s="14" t="n">
+        <v>131</v>
+      </c>
+      <c r="J34" s="10" t="n">
+        <v>46487</v>
+      </c>
+      <c r="K34" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+      <c r="L34" s="9" t="n">
+        <v>0.01795342272406493</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>DOX</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="D34" s="7" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E34" s="7" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="F34" s="8" t="n">
-        <v>0.07407407407407393</v>
-      </c>
-      <c r="G34" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H34" s="10" t="n">
-        <v>46440</v>
-      </c>
-      <c r="I34" s="23" t="n">
-        <v>126</v>
-      </c>
-      <c r="J34" s="10" t="n">
-        <v>46450</v>
-      </c>
-      <c r="K34" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L34" s="9" t="n">
-        <v>0.01045327554509916</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>HD</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="E35" s="7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="F35" s="8" t="n">
-        <v>0.01304347826086967</v>
-      </c>
-      <c r="G35" s="9" t="n">
+      <c r="D35" s="17" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="F35" s="18" t="n">
+        <v>0.07969639468690688</v>
+      </c>
+      <c r="G35" s="19" t="n">
         <v>0.08</v>
       </c>
-      <c r="H35" s="10" t="n">
-        <v>46441</v>
-      </c>
-      <c r="I35" s="23" t="n">
-        <v>127</v>
-      </c>
-      <c r="J35" s="10" t="n">
-        <v>46456</v>
-      </c>
-      <c r="K35" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L35" s="9" t="n">
-        <v>0.03030312976869731</v>
+      <c r="H35" s="20" t="n">
+        <v>46455</v>
+      </c>
+      <c r="I35" s="21" t="n">
+        <v>134</v>
+      </c>
+      <c r="J35" s="20" t="n">
+        <v>46476</v>
+      </c>
+      <c r="K35" s="22" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="L35" s="19" t="n">
+        <v>0.03597850237731143</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -2043,29 +2041,29 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D36" s="7" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="E36" s="7" t="n">
         <v>1.5</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>0.06000000000000005</v>
+        <v>0.09999999999999994</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>46452</v>
-      </c>
-      <c r="I36" s="23" t="n">
-        <v>138</v>
+        <v>46461</v>
+      </c>
+      <c r="I36" s="14" t="n">
+        <v>140</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>46487</v>
+        <v>46665</v>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
@@ -2073,45 +2071,45 @@
         </is>
       </c>
       <c r="L36" s="9" t="n">
-        <v>0.01856934306569343</v>
+        <v>0.01966685560362995</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>1.65</v>
+        <v>0.272</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>1.5</v>
+        <v>0.271</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>0.09999999999999994</v>
+        <v>0.003690036900369007</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="H37" s="10" t="n">
         <v>46461</v>
       </c>
-      <c r="I37" s="23" t="n">
-        <v>147</v>
+      <c r="I37" s="14" t="n">
+        <v>140</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>46665</v>
+        <v>46386</v>
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
@@ -2119,45 +2117,45 @@
         </is>
       </c>
       <c r="L37" s="9" t="n">
-        <v>0.01956773053691266</v>
+        <v>0.05691368939570006</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D38" s="7" t="n">
-        <v>0.272</v>
+        <v>1.089</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>0.271</v>
+        <v>1.057</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>0.003690036900369007</v>
+        <v>0.03027436140018924</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>46461</v>
-      </c>
-      <c r="I38" s="23" t="n">
-        <v>147</v>
+        <v>46488</v>
+      </c>
+      <c r="I38" s="14" t="n">
+        <v>167</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>46386</v>
+        <v>46498</v>
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
@@ -2165,18 +2163,18 @@
         </is>
       </c>
       <c r="L38" s="9" t="n">
-        <v>0.05860490201786151</v>
+        <v>0.02703742774190096</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -2185,25 +2183,25 @@
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>1.089</v>
+        <v>1.084</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>1.057</v>
+        <v>1.087</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>0.03027436140018924</v>
+        <v>0.03495860165593379</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>46488</v>
-      </c>
-      <c r="I39" s="23" t="n">
-        <v>174</v>
+        <v>46492</v>
+      </c>
+      <c r="I39" s="14" t="n">
+        <v>171</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>46498</v>
+        <v>46501</v>
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
@@ -2211,45 +2209,45 @@
         </is>
       </c>
       <c r="L39" s="9" t="n">
-        <v>0.0275277889821852</v>
+        <v>0.01940044742729307</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Semi-Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D40" s="7" t="n">
-        <v>1.084</v>
+        <v>1.021</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>1.087</v>
+        <v>0.974</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>0.03495860165593379</v>
+        <v>0.04825462012320322</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="H40" s="10" t="n">
         <v>46492</v>
       </c>
-      <c r="I40" s="23" t="n">
-        <v>178</v>
+      <c r="I40" s="14" t="n">
+        <v>171</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>46501</v>
+        <v>46376</v>
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
@@ -2257,13 +2255,13 @@
         </is>
       </c>
       <c r="L40" s="9" t="n">
-        <v>0.01795251849684193</v>
+        <v>0.04359521762057851</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
@@ -2273,29 +2271,29 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>1.021</v>
+        <v>1.34</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>0.974</v>
+        <v>1.3</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>0.04825462012320322</v>
+        <v>0.0307692307692308</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>46492</v>
-      </c>
-      <c r="I41" s="23" t="n">
-        <v>178</v>
+        <v>46493</v>
+      </c>
+      <c r="I41" s="14" t="n">
+        <v>172</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>46376</v>
+        <v>46531</v>
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
@@ -2303,13 +2301,13 @@
         </is>
       </c>
       <c r="L41" s="9" t="n">
-        <v>0.04487665648324178</v>
+        <v>0.01971312363195655</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
@@ -2319,29 +2317,29 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D42" s="7" t="n">
-        <v>1.34</v>
+        <v>0.551</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>1.3</v>
+        <v>0.525</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>0.0307692307692308</v>
+        <v>0.04952380952380957</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>46493</v>
-      </c>
-      <c r="I42" s="23" t="n">
-        <v>179</v>
+        <v>46504</v>
+      </c>
+      <c r="I42" s="14" t="n">
+        <v>183</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>46531</v>
+        <v>46562</v>
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
@@ -2349,13 +2347,13 @@
         </is>
       </c>
       <c r="L42" s="9" t="n">
-        <v>0.02108990804140305</v>
+        <v>0.04930648685418649</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
@@ -2365,87 +2363,89 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E43" s="7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>0.1018518518518517</v>
+      </c>
+      <c r="G43" s="9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H43" s="10" t="n">
+        <v>46508</v>
+      </c>
+      <c r="I43" s="14" t="n">
+        <v>187</v>
+      </c>
+      <c r="J43" s="10" t="n">
+        <v>46518</v>
+      </c>
+      <c r="K43" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+      <c r="L43" s="9" t="n">
+        <v>0.04081807732450217</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="D43" s="7" t="n">
-        <v>0.551</v>
-      </c>
-      <c r="E43" s="7" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="F43" s="8" t="n">
-        <v>0.04952380952380957</v>
-      </c>
-      <c r="G43" s="9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H43" s="10" t="n">
-        <v>46504</v>
-      </c>
-      <c r="I43" s="23" t="n">
-        <v>190</v>
-      </c>
-      <c r="J43" s="10" t="n">
-        <v>46562</v>
-      </c>
-      <c r="K43" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L43" s="9" t="n">
-        <v>0.0501250838938402</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="14" t="inlineStr">
-        <is>
-          <t>PSX</t>
-        </is>
-      </c>
-      <c r="B44" s="15" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C44" s="15" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="D44" s="16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E44" s="16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F44" s="17" t="n">
-        <v>0.05833333333333339</v>
-      </c>
-      <c r="G44" s="18" t="n"/>
-      <c r="H44" s="19" t="n">
-        <v>46505</v>
-      </c>
-      <c r="I44" s="24" t="n">
-        <v>191</v>
-      </c>
-      <c r="J44" s="19" t="n">
-        <v>46526</v>
-      </c>
-      <c r="K44" s="21" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
-      <c r="L44" s="22" t="n">
-        <v>0.01698655802003307</v>
+      <c r="D44" s="7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>1.423</v>
+      </c>
+      <c r="F44" s="8" t="n">
+        <v>0.04005621925509482</v>
+      </c>
+      <c r="G44" s="9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H44" s="10" t="n">
+        <v>46515</v>
+      </c>
+      <c r="I44" s="14" t="n">
+        <v>194</v>
+      </c>
+      <c r="J44" s="10" t="n">
+        <v>46542</v>
+      </c>
+      <c r="K44" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+      <c r="L44" s="9" t="n">
+        <v>0.04307647759224001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
@@ -2455,29 +2455,29 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>1.19</v>
+        <v>0.72</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>1.08</v>
+        <v>0.71</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>0.1018518518518517</v>
+        <v>0.01408450704225353</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>46508</v>
-      </c>
-      <c r="I45" s="23" t="n">
-        <v>194</v>
+        <v>46532</v>
+      </c>
+      <c r="I45" s="14" t="n">
+        <v>211</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>46518</v>
+        <v>46563</v>
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
@@ -2485,13 +2485,13 @@
         </is>
       </c>
       <c r="L45" s="9" t="n">
-        <v>0.04296028762541161</v>
+        <v>0.03014917512688835</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
@@ -2501,29 +2501,29 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>1.423</v>
+        <v>1.38</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>0.04005621925509482</v>
+        <v>0.02898550724637684</v>
       </c>
       <c r="G46" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>46515</v>
-      </c>
-      <c r="I46" s="23" t="n">
-        <v>201</v>
+        <v>46589</v>
+      </c>
+      <c r="I46" s="14" t="n">
+        <v>268</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>46542</v>
+        <v>46629</v>
       </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
@@ -2531,13 +2531,13 @@
         </is>
       </c>
       <c r="L46" s="9" t="n">
-        <v>0.04479418762075352</v>
+        <v>0.01920930688593553</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
@@ -2547,29 +2547,29 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>0.72</v>
+        <v>0.84</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>0.71</v>
+        <v>0.83</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>0.01408450704225353</v>
+        <v>0.01204819277108435</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>46532</v>
-      </c>
-      <c r="I47" s="23" t="n">
-        <v>218</v>
+        <v>46591</v>
+      </c>
+      <c r="I47" s="14" t="n">
+        <v>270</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>46563</v>
+        <v>46633</v>
       </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
@@ -2577,13 +2577,13 @@
         </is>
       </c>
       <c r="L47" s="9" t="n">
-        <v>0.03067262567036151</v>
+        <v>0.03380621813697231</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
@@ -2597,25 +2597,25 @@
         </is>
       </c>
       <c r="D48" s="7" t="n">
-        <v>1.42</v>
+        <v>0.98</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>1.38</v>
+        <v>0.93</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>0.02898550724637684</v>
+        <v>0.05376344086021498</v>
       </c>
       <c r="G48" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>46589</v>
-      </c>
-      <c r="I48" s="23" t="n">
-        <v>275</v>
+        <v>46594</v>
+      </c>
+      <c r="I48" s="14" t="n">
+        <v>273</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>46629</v>
+        <v>46613</v>
       </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
@@ -2623,13 +2623,13 @@
         </is>
       </c>
       <c r="L48" s="9" t="n">
-        <v>0.01977647076699418</v>
+        <v>0.01460833291159467</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>AWR</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
@@ -2639,29 +2639,29 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>0.84</v>
+        <v>0.546</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>0.83</v>
+        <v>0.504</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>0.01204819277108435</v>
+        <v>0.08333333333333341</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>46591</v>
-      </c>
-      <c r="I49" s="23" t="n">
-        <v>277</v>
+        <v>46595</v>
+      </c>
+      <c r="I49" s="14" t="n">
+        <v>274</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>46633</v>
+        <v>46614</v>
       </c>
       <c r="K49" s="12" t="inlineStr">
         <is>
@@ -2669,13 +2669,13 @@
         </is>
       </c>
       <c r="L49" s="9" t="n">
-        <v>0.03676269334137368</v>
+        <v>0.02559175174267394</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
@@ -2689,25 +2689,25 @@
         </is>
       </c>
       <c r="D50" s="7" t="n">
-        <v>0.98</v>
+        <v>1.25</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>0.93</v>
+        <v>1.24</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>0.05376344086021498</v>
+        <v>0.008064516129032265</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>46594</v>
-      </c>
-      <c r="I50" s="23" t="n">
-        <v>280</v>
+        <v>46597</v>
+      </c>
+      <c r="I50" s="14" t="n">
+        <v>276</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>46613</v>
+        <v>46611</v>
       </c>
       <c r="K50" s="12" t="inlineStr">
         <is>
@@ -2715,13 +2715,13 @@
         </is>
       </c>
       <c r="L50" s="9" t="n">
-        <v>0.01472908914196234</v>
+        <v>0.05710370191198418</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>AWR</t>
+          <t>CFR</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -2735,25 +2735,25 @@
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>0.546</v>
+        <v>1.03</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>0.504</v>
+        <v>1</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>0.08333333333333341</v>
+        <v>0.03000000000000003</v>
       </c>
       <c r="G51" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>46595</v>
-      </c>
-      <c r="I51" s="23" t="n">
-        <v>281</v>
+        <v>46598</v>
+      </c>
+      <c r="I51" s="14" t="n">
+        <v>277</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>46614</v>
+        <v>46629</v>
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
@@ -2761,13 +2761,13 @@
         </is>
       </c>
       <c r="L51" s="9" t="n">
-        <v>0.02646150000721019</v>
+        <v>0.02594540160274221</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -2777,29 +2777,29 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D52" s="7" t="n">
-        <v>1.25</v>
+        <v>0.83</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>1.24</v>
+        <v>0.82</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>0.008064516129032265</v>
+        <v>0.01219512195121952</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>46597</v>
-      </c>
-      <c r="I52" s="23" t="n">
-        <v>283</v>
+        <v>46614</v>
+      </c>
+      <c r="I52" s="14" t="n">
+        <v>293</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>46611</v>
+        <v>46662</v>
       </c>
       <c r="K52" s="12" t="inlineStr">
         <is>
@@ -2807,13 +2807,13 @@
         </is>
       </c>
       <c r="L52" s="9" t="n">
-        <v>0.05855829331739755</v>
+        <v>0.03450784774548257</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>CFR</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -2823,29 +2823,29 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
-        <v>1.03</v>
+        <v>0.91</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>0.03000000000000003</v>
+        <v>0.09638554216867479</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>46598</v>
-      </c>
-      <c r="I53" s="23" t="n">
-        <v>284</v>
+        <v>46643</v>
+      </c>
+      <c r="I53" s="14" t="n">
+        <v>322</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>46629</v>
+        <v>46709</v>
       </c>
       <c r="K53" s="12" t="inlineStr">
         <is>
@@ -2853,13 +2853,13 @@
         </is>
       </c>
       <c r="L53" s="9" t="n">
-        <v>0.02663391256691318</v>
+        <v>0.006938487832176294</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -2873,25 +2873,25 @@
         </is>
       </c>
       <c r="D54" s="7" t="n">
-        <v>0.83</v>
+        <v>0.708</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>0.82</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>0.01219512195121952</v>
+        <v>0.02608695652173916</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>46614</v>
-      </c>
-      <c r="I54" s="23" t="n">
-        <v>300</v>
+        <v>46645</v>
+      </c>
+      <c r="I54" s="14" t="n">
+        <v>324</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>46662</v>
+        <v>46668</v>
       </c>
       <c r="K54" s="12" t="inlineStr">
         <is>
@@ -2899,13 +2899,13 @@
         </is>
       </c>
       <c r="L54" s="9" t="n">
-        <v>0.03416692459155611</v>
+        <v>0.065351334021713</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -2915,29 +2915,29 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D55" s="7" t="n">
-        <v>0.91</v>
+        <v>1.42</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>0.83</v>
+        <v>1.36</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>0.09638554216867479</v>
+        <v>0.0441176470588234</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>46643</v>
-      </c>
-      <c r="I55" s="23" t="n">
+        <v>46650</v>
+      </c>
+      <c r="I55" s="14" t="n">
         <v>329</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>46709</v>
+        <v>46690</v>
       </c>
       <c r="K55" s="12" t="inlineStr">
         <is>
@@ -2945,13 +2945,13 @@
         </is>
       </c>
       <c r="L55" s="9" t="n">
-        <v>0.006843878990992571</v>
+        <v>0.0198317095330963</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
@@ -2961,29 +2961,29 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D56" s="7" t="n">
-        <v>0.708</v>
+        <v>0.79</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>0.02608695652173916</v>
+        <v>0.05333333333333338</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>46645</v>
-      </c>
-      <c r="I56" s="23" t="n">
-        <v>331</v>
+        <v>46676</v>
+      </c>
+      <c r="I56" s="14" t="n">
+        <v>355</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>46668</v>
+        <v>46751</v>
       </c>
       <c r="K56" s="12" t="inlineStr">
         <is>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L56" s="9" t="n">
-        <v>0.06363329810206279</v>
+        <v>0.01216179872726553</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>HII</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
@@ -3007,29 +3007,29 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D57" s="7" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>0.0441176470588234</v>
+        <v>0.02222222222222208</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>46650</v>
-      </c>
-      <c r="I57" s="23" t="n">
-        <v>336</v>
+        <v>46683</v>
+      </c>
+      <c r="I57" s="14" t="n">
+        <v>362</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>46690</v>
+        <v>46717</v>
       </c>
       <c r="K57" s="12" t="inlineStr">
         <is>
@@ -3037,53 +3037,7 @@
         </is>
       </c>
       <c r="L57" s="9" t="n">
-        <v>0.02051059888861486</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>LECO</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="D58" s="7" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E58" s="7" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F58" s="8" t="n">
-        <v>0.05333333333333338</v>
-      </c>
-      <c r="G58" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H58" s="10" t="n">
-        <v>46676</v>
-      </c>
-      <c r="I58" s="23" t="n">
-        <v>362</v>
-      </c>
-      <c r="J58" s="10" t="n">
-        <v>46751</v>
-      </c>
-      <c r="K58" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L58" s="9" t="n">
-        <v>0.01212586310817193</v>
+        <v>0.01982367084874391</v>
       </c>
     </row>
   </sheetData>
@@ -3097,7 +3051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F94"/>
+  <dimension ref="A1:F93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3118,44 +3072,44 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Expected Increase Announcements by Month - 10/19/2026</t>
+          <t>Expected Increase Announcements by Month - 10/26/2026</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>January 2026</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="24" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="24" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="24" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F5" s="26" t="inlineStr">
+      <c r="F5" s="24" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3186,39 +3140,39 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>October 2026</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="24" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D9" s="26" t="inlineStr">
+      <c r="D9" s="24" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E9" s="26" t="inlineStr">
+      <c r="E9" s="24" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F9" s="26" t="inlineStr">
+      <c r="F9" s="24" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3227,20 +3181,20 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>46318</v>
+        <v>46322</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>46352</v>
+        <v>46338</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>1.38</v>
+        <v>0.64</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>0.02222222222222208</v>
+        <v>0.06666666666666674</v>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
@@ -3248,110 +3202,110 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>MSM</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="n">
-        <v>46318</v>
-      </c>
-      <c r="C11" s="19" t="n">
-        <v>46339</v>
-      </c>
-      <c r="D11" s="16" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="E11" s="17" t="n">
-        <v>0.0235294117647059</v>
-      </c>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
-    </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>ETR</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="n">
-        <v>46322</v>
-      </c>
-      <c r="C12" s="10" t="n">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>November 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>COR</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n">
+        <v>46329</v>
+      </c>
+      <c r="C14" s="10" t="n">
         <v>46338</v>
       </c>
-      <c r="D12" s="7" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>0.06666666666666674</v>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="25" t="inlineStr">
-        <is>
-          <t>November 2026</t>
+      <c r="D14" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>0.09090909090909079</v>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B15" s="26" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C15" s="26" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D15" s="26" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E15" s="26" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F15" s="26" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>SNA</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n">
+        <v>46332</v>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>46346</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>0.1401869158878504</v>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B16" s="10" t="n">
-        <v>46329</v>
+        <v>46341</v>
       </c>
       <c r="C16" s="10" t="n">
-        <v>46338</v>
+        <v>46340</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.6</v>
+        <v>1.03</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>0.09090909090909079</v>
+        <v>0.04040404040404044</v>
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
@@ -3362,20 +3316,20 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="B17" s="10" t="n">
-        <v>46332</v>
+        <v>46344</v>
       </c>
       <c r="C17" s="10" t="n">
-        <v>46346</v>
+        <v>46385</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>2.44</v>
+        <v>0.48</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>0.1401869158878504</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
@@ -3386,20 +3340,20 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B18" s="10" t="n">
-        <v>46341</v>
+        <v>46347</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>46340</v>
+        <v>46358</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>1.03</v>
+        <v>0.41</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>0.04040404040404044</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
@@ -3410,20 +3364,20 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>46344</v>
+        <v>46351</v>
       </c>
       <c r="C19" s="10" t="n">
-        <v>46385</v>
+        <v>46399</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.48</v>
+        <v>0.293</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.01034482758620691</v>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
@@ -3431,110 +3385,110 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>NKE</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="n">
-        <v>46347</v>
-      </c>
-      <c r="C20" s="10" t="n">
-        <v>46358</v>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>0.02499999999999988</v>
-      </c>
-      <c r="F20" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>HRL</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="n">
-        <v>46351</v>
-      </c>
-      <c r="C21" s="10" t="n">
-        <v>46399</v>
-      </c>
-      <c r="D21" s="7" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>0.01034482758620691</v>
-      </c>
-      <c r="F21" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>December 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="25" t="inlineStr">
-        <is>
-          <t>December 2026</t>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>EMN</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n">
+        <v>46360</v>
+      </c>
+      <c r="C23" s="10" t="n">
+        <v>46371</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>0.01204819277108435</v>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="26" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B24" s="26" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C24" s="26" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D24" s="26" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E24" s="26" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F24" s="26" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>AMGN</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="n">
+        <v>46366</v>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>46432</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>0.05882352941176476</v>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>EMN</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="B25" s="10" t="n">
-        <v>46360</v>
+        <v>46380</v>
       </c>
       <c r="C25" s="10" t="n">
-        <v>46371</v>
+        <v>46436</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>0.84</v>
+        <v>0.24</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>0.01204819277108435</v>
+        <v>0.04347826086956513</v>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
@@ -3543,133 +3497,133 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>AMGN</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="n">
-        <v>46366</v>
-      </c>
-      <c r="C26" s="10" t="n">
-        <v>46432</v>
-      </c>
-      <c r="D26" s="7" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="E26" s="8" t="n">
-        <v>0.05882352941176476</v>
-      </c>
-      <c r="F26" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>CNP</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="n">
-        <v>46380</v>
-      </c>
-      <c r="C27" s="10" t="n">
-        <v>46436</v>
-      </c>
-      <c r="D27" s="7" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E27" s="8" t="n">
-        <v>0.04347826086956513</v>
-      </c>
-      <c r="F27" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>GGG</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="n">
+        <v>46383</v>
+      </c>
+      <c r="C26" s="20" t="n">
+        <v>46404</v>
+      </c>
+      <c r="D26" s="17" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="E26" s="18" t="n">
+        <v>0.07272727272727258</v>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>yfinance</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="inlineStr">
-        <is>
-          <t>GGG</t>
-        </is>
-      </c>
-      <c r="B28" s="19" t="n">
-        <v>46383</v>
-      </c>
-      <c r="C28" s="19" t="n">
-        <v>46404</v>
-      </c>
-      <c r="D28" s="16" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E28" s="17" t="n">
-        <v>0.07272727272727258</v>
-      </c>
-      <c r="F28" s="21" t="inlineStr">
-        <is>
-          <t>yfinance</t>
+      <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>January 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="25" t="inlineStr">
-        <is>
-          <t>January 2027</t>
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="n">
+        <v>46402</v>
+      </c>
+      <c r="C30" s="10" t="n">
+        <v>46483</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>0.07499999999999993</v>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="26" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B31" s="26" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C31" s="26" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D31" s="26" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E31" s="26" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F31" s="26" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>BKH</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="n">
+        <v>46411</v>
+      </c>
+      <c r="C31" s="10" t="n">
+        <v>46435</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>0.03994082840236673</v>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B32" s="10" t="n">
-        <v>46402</v>
+        <v>46417</v>
       </c>
       <c r="C32" s="10" t="n">
-        <v>46483</v>
+        <v>46433</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>0.86</v>
+        <v>1.78</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>0.07499999999999993</v>
+        <v>0.04093567251461992</v>
       </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
@@ -3677,110 +3631,110 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>BKH</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="n">
-        <v>46411</v>
-      </c>
-      <c r="C33" s="10" t="n">
-        <v>46435</v>
-      </c>
-      <c r="D33" s="7" t="n">
-        <v>0.703</v>
-      </c>
-      <c r="E33" s="8" t="n">
-        <v>0.03994082840236673</v>
-      </c>
-      <c r="F33" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>CVX</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="n">
-        <v>46417</v>
-      </c>
-      <c r="C34" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="E34" s="8" t="n">
-        <v>0.04093567251461992</v>
-      </c>
-      <c r="F34" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A34" s="23" t="inlineStr">
+        <is>
+          <t>February 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E35" s="24" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F35" s="24" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="25" t="inlineStr">
-        <is>
-          <t>February 2027</t>
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>NVO</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="n">
+        <v>46423</v>
+      </c>
+      <c r="C36" s="10" t="n">
+        <v>46473</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>1.183219178082192</v>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="26" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B37" s="26" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C37" s="26" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D37" s="26" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E37" s="26" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F37" s="26" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>JKHY</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="n">
+        <v>46428</v>
+      </c>
+      <c r="C37" s="10" t="n">
+        <v>46452</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>0.05172413793103453</v>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B38" s="10" t="n">
-        <v>46423</v>
+        <v>46428</v>
       </c>
       <c r="C38" s="10" t="n">
-        <v>46473</v>
+        <v>46460</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>0.579</v>
+        <v>1.3</v>
       </c>
       <c r="E38" s="8" t="n">
-        <v>1.183219178082192</v>
+        <v>0.02362204724409451</v>
       </c>
       <c r="F38" s="12" t="inlineStr">
         <is>
@@ -3789,46 +3743,46 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>JKHY</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="n">
-        <v>46428</v>
-      </c>
-      <c r="C39" s="10" t="n">
-        <v>46452</v>
-      </c>
-      <c r="D39" s="7" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E39" s="8" t="n">
-        <v>0.05172413793103453</v>
-      </c>
-      <c r="F39" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>HWC</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="n">
+        <v>46429</v>
+      </c>
+      <c r="C39" s="20" t="n">
+        <v>46450</v>
+      </c>
+      <c r="D39" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E39" s="18" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="F39" s="22" t="inlineStr">
+        <is>
+          <t>yfinance</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B40" s="10" t="n">
-        <v>46428</v>
+        <v>46431</v>
       </c>
       <c r="C40" s="10" t="n">
-        <v>46460</v>
+        <v>46480</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>1.3</v>
+        <v>0.42</v>
       </c>
       <c r="E40" s="8" t="n">
-        <v>0.02362204724409451</v>
+        <v>0.02439024390243905</v>
       </c>
       <c r="F40" s="12" t="inlineStr">
         <is>
@@ -3837,46 +3791,46 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="14" t="inlineStr">
-        <is>
-          <t>HWC</t>
-        </is>
-      </c>
-      <c r="B41" s="19" t="n">
-        <v>46429</v>
-      </c>
-      <c r="C41" s="19" t="n">
-        <v>46450</v>
-      </c>
-      <c r="D41" s="16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E41" s="17" t="n">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="F41" s="21" t="inlineStr">
-        <is>
-          <t>yfinance</t>
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>PEG</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="n">
+        <v>46432</v>
+      </c>
+      <c r="C41" s="10" t="n">
+        <v>46455</v>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>0.06349206349206354</v>
+      </c>
+      <c r="F41" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B42" s="10" t="n">
-        <v>46431</v>
+        <v>46433</v>
       </c>
       <c r="C42" s="10" t="n">
-        <v>46480</v>
+        <v>46425</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>0.42</v>
+        <v>2.138</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>0.02439024390243905</v>
+        <v>0.6872012745618694</v>
       </c>
       <c r="F42" s="12" t="inlineStr">
         <is>
@@ -3887,20 +3841,20 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B43" s="10" t="n">
-        <v>46432</v>
+        <v>46433</v>
       </c>
       <c r="C43" s="10" t="n">
-        <v>46455</v>
+        <v>46383</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>0.67</v>
+        <v>1.3</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>0.06349206349206354</v>
+        <v>4.96</v>
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
@@ -3911,20 +3865,20 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B44" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C44" s="10" t="n">
-        <v>46425</v>
+        <v>46458</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>2.138</v>
+        <v>0.32</v>
       </c>
       <c r="E44" s="8" t="n">
-        <v>0.6872012745618694</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
@@ -3935,20 +3889,20 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B45" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C45" s="10" t="n">
-        <v>46383</v>
+        <v>46634</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>1.3</v>
+        <v>0.84</v>
       </c>
       <c r="E45" s="8" t="n">
-        <v>4.96</v>
+        <v>0.02439024390243905</v>
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
@@ -3959,20 +3913,20 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B46" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C46" s="10" t="n">
-        <v>46458</v>
+        <v>46608</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>0.32</v>
+        <v>0.531</v>
       </c>
       <c r="E46" s="8" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.005735494868956323</v>
       </c>
       <c r="F46" s="12" t="inlineStr">
         <is>
@@ -3983,20 +3937,20 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="B47" s="10" t="n">
-        <v>46433</v>
+        <v>46440</v>
       </c>
       <c r="C47" s="10" t="n">
-        <v>46634</v>
+        <v>46450</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>0.84</v>
+        <v>0.29</v>
       </c>
       <c r="E47" s="8" t="n">
-        <v>0.02439024390243905</v>
+        <v>0.07407407407407393</v>
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
@@ -4007,20 +3961,20 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B48" s="10" t="n">
-        <v>46433</v>
+        <v>46441</v>
       </c>
       <c r="C48" s="10" t="n">
-        <v>46608</v>
+        <v>46456</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>0.531</v>
+        <v>2.33</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>0.005735494868956323</v>
+        <v>0.01304347826086967</v>
       </c>
       <c r="F48" s="12" t="inlineStr">
         <is>
@@ -4028,110 +3982,110 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>ALSN</t>
-        </is>
-      </c>
-      <c r="B49" s="10" t="n">
-        <v>46440</v>
-      </c>
-      <c r="C49" s="10" t="n">
-        <v>46450</v>
-      </c>
-      <c r="D49" s="7" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E49" s="8" t="n">
-        <v>0.07407407407407393</v>
-      </c>
-      <c r="F49" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>HD</t>
-        </is>
-      </c>
-      <c r="B50" s="10" t="n">
-        <v>46441</v>
-      </c>
-      <c r="C50" s="10" t="n">
-        <v>46456</v>
-      </c>
-      <c r="D50" s="7" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="E50" s="8" t="n">
-        <v>0.01304347826086967</v>
-      </c>
-      <c r="F50" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A50" s="23" t="inlineStr">
+        <is>
+          <t>March 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="24" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B51" s="24" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C51" s="24" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D51" s="24" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E51" s="24" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F51" s="24" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="25" t="inlineStr">
-        <is>
-          <t>March 2027</t>
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="n">
+        <v>46452</v>
+      </c>
+      <c r="C52" s="10" t="n">
+        <v>46487</v>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>0.06000000000000005</v>
+      </c>
+      <c r="F52" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="26" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B53" s="26" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C53" s="26" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D53" s="26" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E53" s="26" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F53" s="26" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t>DOX</t>
+        </is>
+      </c>
+      <c r="B53" s="20" t="n">
+        <v>46455</v>
+      </c>
+      <c r="C53" s="20" t="n">
+        <v>46476</v>
+      </c>
+      <c r="D53" s="17" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="E53" s="18" t="n">
+        <v>0.07969639468690688</v>
+      </c>
+      <c r="F53" s="22" t="inlineStr">
+        <is>
+          <t>yfinance</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B54" s="10" t="n">
-        <v>46452</v>
+        <v>46461</v>
       </c>
       <c r="C54" s="10" t="n">
-        <v>46487</v>
+        <v>46665</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="E54" s="8" t="n">
-        <v>0.06000000000000005</v>
+        <v>0.09999999999999994</v>
       </c>
       <c r="F54" s="12" t="inlineStr">
         <is>
@@ -4142,20 +4096,20 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B55" s="10" t="n">
         <v>46461</v>
       </c>
       <c r="C55" s="10" t="n">
-        <v>46665</v>
+        <v>46386</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>1.65</v>
+        <v>0.272</v>
       </c>
       <c r="E55" s="8" t="n">
-        <v>0.09999999999999994</v>
+        <v>0.003690036900369007</v>
       </c>
       <c r="F55" s="12" t="inlineStr">
         <is>
@@ -4163,86 +4117,86 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B56" s="10" t="n">
-        <v>46461</v>
-      </c>
-      <c r="C56" s="10" t="n">
-        <v>46386</v>
-      </c>
-      <c r="D56" s="7" t="n">
-        <v>0.272</v>
-      </c>
-      <c r="E56" s="8" t="n">
-        <v>0.003690036900369007</v>
-      </c>
-      <c r="F56" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="57">
+      <c r="A57" s="23" t="inlineStr">
+        <is>
+          <t>April 2027</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="25" t="inlineStr">
-        <is>
-          <t>April 2027</t>
+      <c r="A58" s="24" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B58" s="24" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C58" s="24" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D58" s="24" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E58" s="24" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F58" s="24" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="26" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B59" s="26" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C59" s="26" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D59" s="26" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E59" s="26" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F59" s="26" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="n">
+        <v>46488</v>
+      </c>
+      <c r="C59" s="10" t="n">
+        <v>46498</v>
+      </c>
+      <c r="D59" s="7" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="E59" s="8" t="n">
+        <v>0.03027436140018924</v>
+      </c>
+      <c r="F59" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="B60" s="10" t="n">
-        <v>46488</v>
+        <v>46492</v>
       </c>
       <c r="C60" s="10" t="n">
-        <v>46498</v>
+        <v>46501</v>
       </c>
       <c r="D60" s="7" t="n">
-        <v>1.089</v>
+        <v>1.084</v>
       </c>
       <c r="E60" s="8" t="n">
-        <v>0.03027436140018924</v>
+        <v>0.03495860165593379</v>
       </c>
       <c r="F60" s="12" t="inlineStr">
         <is>
@@ -4253,20 +4207,20 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B61" s="10" t="n">
         <v>46492</v>
       </c>
       <c r="C61" s="10" t="n">
-        <v>46501</v>
+        <v>46376</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>1.084</v>
+        <v>1.021</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>0.03495860165593379</v>
+        <v>0.04825462012320322</v>
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
@@ -4277,20 +4231,20 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B62" s="10" t="n">
-        <v>46492</v>
+        <v>46493</v>
       </c>
       <c r="C62" s="10" t="n">
-        <v>46376</v>
+        <v>46531</v>
       </c>
       <c r="D62" s="7" t="n">
-        <v>1.021</v>
+        <v>1.34</v>
       </c>
       <c r="E62" s="8" t="n">
-        <v>0.04825462012320322</v>
+        <v>0.0307692307692308</v>
       </c>
       <c r="F62" s="12" t="inlineStr">
         <is>
@@ -4301,20 +4255,20 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B63" s="10" t="n">
-        <v>46493</v>
+        <v>46504</v>
       </c>
       <c r="C63" s="10" t="n">
-        <v>46531</v>
+        <v>46562</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>1.34</v>
+        <v>0.551</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>0.0307692307692308</v>
+        <v>0.04952380952380957</v>
       </c>
       <c r="F63" s="12" t="inlineStr">
         <is>
@@ -4322,110 +4276,110 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
-      </c>
-      <c r="B64" s="10" t="n">
-        <v>46504</v>
-      </c>
-      <c r="C64" s="10" t="n">
-        <v>46562</v>
-      </c>
-      <c r="D64" s="7" t="n">
-        <v>0.551</v>
-      </c>
-      <c r="E64" s="8" t="n">
-        <v>0.04952380952380957</v>
-      </c>
-      <c r="F64" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
     <row r="65">
-      <c r="A65" s="14" t="inlineStr">
-        <is>
-          <t>PSX</t>
-        </is>
-      </c>
-      <c r="B65" s="19" t="n">
-        <v>46505</v>
-      </c>
-      <c r="C65" s="19" t="n">
-        <v>46526</v>
-      </c>
-      <c r="D65" s="16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E65" s="17" t="n">
-        <v>0.05833333333333339</v>
-      </c>
-      <c r="F65" s="21" t="inlineStr">
-        <is>
-          <t>yfinance</t>
+      <c r="A65" s="23" t="inlineStr">
+        <is>
+          <t>May 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="24" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B66" s="24" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C66" s="24" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D66" s="24" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E66" s="24" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F66" s="24" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="25" t="inlineStr">
-        <is>
-          <t>May 2027</t>
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>PAYX</t>
+        </is>
+      </c>
+      <c r="B67" s="10" t="n">
+        <v>46508</v>
+      </c>
+      <c r="C67" s="10" t="n">
+        <v>46518</v>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E67" s="8" t="n">
+        <v>0.1018518518518517</v>
+      </c>
+      <c r="F67" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="26" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B68" s="26" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C68" s="26" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D68" s="26" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E68" s="26" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F68" s="26" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="B68" s="10" t="n">
+        <v>46515</v>
+      </c>
+      <c r="C68" s="10" t="n">
+        <v>46542</v>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="E68" s="8" t="n">
+        <v>0.04005621925509482</v>
+      </c>
+      <c r="F68" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B69" s="10" t="n">
-        <v>46508</v>
+        <v>46532</v>
       </c>
       <c r="C69" s="10" t="n">
-        <v>46518</v>
+        <v>46563</v>
       </c>
       <c r="D69" s="7" t="n">
-        <v>1.19</v>
+        <v>0.72</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>0.1018518518518517</v>
+        <v>0.01408450704225353</v>
       </c>
       <c r="F69" s="12" t="inlineStr">
         <is>
@@ -4433,110 +4387,110 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>PEP</t>
-        </is>
-      </c>
-      <c r="B70" s="10" t="n">
-        <v>46515</v>
-      </c>
-      <c r="C70" s="10" t="n">
-        <v>46542</v>
-      </c>
-      <c r="D70" s="7" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="E70" s="8" t="n">
-        <v>0.04005621925509482</v>
-      </c>
-      <c r="F70" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
     <row r="71">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>MDT</t>
-        </is>
-      </c>
-      <c r="B71" s="10" t="n">
-        <v>46532</v>
-      </c>
-      <c r="C71" s="10" t="n">
-        <v>46563</v>
-      </c>
-      <c r="D71" s="7" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E71" s="8" t="n">
-        <v>0.01408450704225353</v>
-      </c>
-      <c r="F71" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A71" s="23" t="inlineStr">
+        <is>
+          <t>July 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="24" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B72" s="24" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C72" s="24" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D72" s="24" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E72" s="24" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F72" s="24" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="25" t="inlineStr">
-        <is>
-          <t>July 2027</t>
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>UNP</t>
+        </is>
+      </c>
+      <c r="B73" s="10" t="n">
+        <v>46589</v>
+      </c>
+      <c r="C73" s="10" t="n">
+        <v>46629</v>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="E73" s="8" t="n">
+        <v>0.02898550724637684</v>
+      </c>
+      <c r="F73" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="26" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B74" s="26" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C74" s="26" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D74" s="26" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E74" s="26" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F74" s="26" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>SWK</t>
+        </is>
+      </c>
+      <c r="B74" s="10" t="n">
+        <v>46591</v>
+      </c>
+      <c r="C74" s="10" t="n">
+        <v>46633</v>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E74" s="8" t="n">
+        <v>0.01204819277108435</v>
+      </c>
+      <c r="F74" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="B75" s="10" t="n">
-        <v>46589</v>
+        <v>46594</v>
       </c>
       <c r="C75" s="10" t="n">
-        <v>46629</v>
+        <v>46613</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>1.42</v>
+        <v>0.98</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>0.02898550724637684</v>
+        <v>0.05376344086021498</v>
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
@@ -4547,20 +4501,20 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>AWR</t>
         </is>
       </c>
       <c r="B76" s="10" t="n">
-        <v>46591</v>
+        <v>46595</v>
       </c>
       <c r="C76" s="10" t="n">
-        <v>46633</v>
+        <v>46614</v>
       </c>
       <c r="D76" s="7" t="n">
-        <v>0.84</v>
+        <v>0.546</v>
       </c>
       <c r="E76" s="8" t="n">
-        <v>0.01204819277108435</v>
+        <v>0.08333333333333341</v>
       </c>
       <c r="F76" s="12" t="inlineStr">
         <is>
@@ -4571,20 +4525,20 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="B77" s="10" t="n">
-        <v>46594</v>
+        <v>46597</v>
       </c>
       <c r="C77" s="10" t="n">
-        <v>46613</v>
+        <v>46611</v>
       </c>
       <c r="D77" s="7" t="n">
-        <v>0.98</v>
+        <v>1.25</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>0.05376344086021498</v>
+        <v>0.008064516129032265</v>
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
@@ -4595,194 +4549,194 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>AWR</t>
+          <t>CFR</t>
         </is>
       </c>
       <c r="B78" s="10" t="n">
-        <v>46595</v>
+        <v>46598</v>
       </c>
       <c r="C78" s="10" t="n">
+        <v>46629</v>
+      </c>
+      <c r="D78" s="7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E78" s="8" t="n">
+        <v>0.03000000000000003</v>
+      </c>
+      <c r="F78" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="23" t="inlineStr">
+        <is>
+          <t>August 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="24" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B81" s="24" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C81" s="24" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D81" s="24" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E81" s="24" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F81" s="24" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>INGR</t>
+        </is>
+      </c>
+      <c r="B82" s="10" t="n">
         <v>46614</v>
       </c>
-      <c r="D78" s="7" t="n">
-        <v>0.546</v>
-      </c>
-      <c r="E78" s="8" t="n">
-        <v>0.08333333333333341</v>
-      </c>
-      <c r="F78" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>CLX</t>
-        </is>
-      </c>
-      <c r="B79" s="10" t="n">
-        <v>46597</v>
-      </c>
-      <c r="C79" s="10" t="n">
-        <v>46611</v>
-      </c>
-      <c r="D79" s="7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E79" s="8" t="n">
-        <v>0.008064516129032265</v>
-      </c>
-      <c r="F79" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>CFR</t>
-        </is>
-      </c>
-      <c r="B80" s="10" t="n">
-        <v>46598</v>
-      </c>
-      <c r="C80" s="10" t="n">
-        <v>46629</v>
-      </c>
-      <c r="D80" s="7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E80" s="8" t="n">
-        <v>0.03000000000000003</v>
-      </c>
-      <c r="F80" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="25" t="inlineStr">
-        <is>
-          <t>August 2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="26" t="inlineStr">
+      <c r="C82" s="10" t="n">
+        <v>46662</v>
+      </c>
+      <c r="D82" s="7" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E82" s="8" t="n">
+        <v>0.01219512195121952</v>
+      </c>
+      <c r="F82" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="23" t="inlineStr">
+        <is>
+          <t>September 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="24" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B83" s="26" t="inlineStr">
+      <c r="B85" s="24" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C83" s="26" t="inlineStr">
+      <c r="C85" s="24" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D83" s="26" t="inlineStr">
+      <c r="D85" s="24" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E83" s="26" t="inlineStr">
+      <c r="E85" s="24" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F83" s="26" t="inlineStr">
+      <c r="F85" s="24" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>INGR</t>
-        </is>
-      </c>
-      <c r="B84" s="10" t="n">
-        <v>46614</v>
-      </c>
-      <c r="C84" s="10" t="n">
-        <v>46662</v>
-      </c>
-      <c r="D84" s="7" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E84" s="8" t="n">
-        <v>0.01219512195121952</v>
-      </c>
-      <c r="F84" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
     <row r="86">
-      <c r="A86" s="25" t="inlineStr">
-        <is>
-          <t>September 2027</t>
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B86" s="10" t="n">
+        <v>46643</v>
+      </c>
+      <c r="C86" s="10" t="n">
+        <v>46709</v>
+      </c>
+      <c r="D86" s="7" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E86" s="8" t="n">
+        <v>0.09638554216867479</v>
+      </c>
+      <c r="F86" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="26" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B87" s="26" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C87" s="26" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D87" s="26" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E87" s="26" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F87" s="26" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>VZ</t>
+        </is>
+      </c>
+      <c r="B87" s="10" t="n">
+        <v>46645</v>
+      </c>
+      <c r="C87" s="10" t="n">
+        <v>46668</v>
+      </c>
+      <c r="D87" s="7" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="E87" s="8" t="n">
+        <v>0.02608695652173916</v>
+      </c>
+      <c r="F87" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B88" s="10" t="n">
-        <v>46643</v>
+        <v>46650</v>
       </c>
       <c r="C88" s="10" t="n">
-        <v>46709</v>
+        <v>46690</v>
       </c>
       <c r="D88" s="7" t="n">
-        <v>0.91</v>
+        <v>1.42</v>
       </c>
       <c r="E88" s="8" t="n">
-        <v>0.09638554216867479</v>
+        <v>0.0441176470588234</v>
       </c>
       <c r="F88" s="12" t="inlineStr">
         <is>
@@ -4790,112 +4744,88 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="5" t="inlineStr">
-        <is>
-          <t>VZ</t>
-        </is>
-      </c>
-      <c r="B89" s="10" t="n">
-        <v>46645</v>
-      </c>
-      <c r="C89" s="10" t="n">
-        <v>46668</v>
-      </c>
-      <c r="D89" s="7" t="n">
-        <v>0.708</v>
-      </c>
-      <c r="E89" s="8" t="n">
-        <v>0.02608695652173916</v>
-      </c>
-      <c r="F89" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
     <row r="90">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>TXN</t>
-        </is>
-      </c>
-      <c r="B90" s="10" t="n">
-        <v>46650</v>
-      </c>
-      <c r="C90" s="10" t="n">
-        <v>46690</v>
-      </c>
-      <c r="D90" s="7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="E90" s="8" t="n">
-        <v>0.0441176470588234</v>
-      </c>
-      <c r="F90" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A90" s="23" t="inlineStr">
+        <is>
+          <t>October 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="24" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B91" s="24" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C91" s="24" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D91" s="24" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E91" s="24" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F91" s="24" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="25" t="inlineStr">
-        <is>
-          <t>October 2027</t>
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>LECO</t>
+        </is>
+      </c>
+      <c r="B92" s="10" t="n">
+        <v>46676</v>
+      </c>
+      <c r="C92" s="10" t="n">
+        <v>46751</v>
+      </c>
+      <c r="D92" s="7" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E92" s="8" t="n">
+        <v>0.05333333333333338</v>
+      </c>
+      <c r="F92" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="26" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B93" s="26" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C93" s="26" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D93" s="26" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E93" s="26" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F93" s="26" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t>LECO</t>
-        </is>
-      </c>
-      <c r="B94" s="10" t="n">
-        <v>46676</v>
-      </c>
-      <c r="C94" s="10" t="n">
-        <v>46751</v>
-      </c>
-      <c r="D94" s="7" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E94" s="8" t="n">
-        <v>0.05333333333333338</v>
-      </c>
-      <c r="F94" s="12" t="inlineStr">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>HII</t>
+        </is>
+      </c>
+      <c r="B93" s="10" t="n">
+        <v>46683</v>
+      </c>
+      <c r="C93" s="10" t="n">
+        <v>46717</v>
+      </c>
+      <c r="D93" s="7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E93" s="8" t="n">
+        <v>0.02222222222222208</v>
+      </c>
+      <c r="F93" s="12" t="inlineStr">
         <is>
           <t>Notion + yfinance</t>
         </is>
@@ -4912,7 +4842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4940,7 +4870,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Complete Holdings Dividend Summary - 10/19/2026</t>
+          <t>Complete Holdings Dividend Summary - 10/26/2026</t>
         </is>
       </c>
     </row>
@@ -5040,11 +4970,11 @@
       <c r="F5" s="7" t="n">
         <v>0.29</v>
       </c>
-      <c r="G5" s="27" t="n">
+      <c r="G5" s="25" t="n">
         <v>1.16</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.01045327554509916</v>
+        <v>0.01085024750037608</v>
       </c>
       <c r="I5" s="10" t="n">
         <v>46255</v>
@@ -5072,7 +5002,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>QDVD/DAC</t>
+          <t>QDVD/DAC/OR</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -5093,11 +5023,11 @@
       <c r="F6" s="7" t="n">
         <v>2.52</v>
       </c>
-      <c r="G6" s="27" t="n">
+      <c r="G6" s="25" t="n">
         <v>10.08</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.02329343307176349</v>
+        <v>0.02243989253356084</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>46255</v>
@@ -5146,11 +5076,11 @@
       <c r="F7" s="7" t="n">
         <v>2.138</v>
       </c>
-      <c r="G7" s="27" t="n">
+      <c r="G7" s="25" t="n">
         <v>8.552</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.005155099221223549</v>
+        <v>0.005378819524740057</v>
       </c>
       <c r="I7" s="10" t="n">
         <v>46231</v>
@@ -5199,11 +5129,11 @@
       <c r="F8" s="7" t="n">
         <v>0.546</v>
       </c>
-      <c r="G8" s="27" t="n">
+      <c r="G8" s="25" t="n">
         <v>2.184</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>0.02646150000721019</v>
+        <v>0.02559175174267394</v>
       </c>
       <c r="I8" s="10" t="n">
         <v>46251</v>
@@ -5252,11 +5182,11 @@
       <c r="F9" s="7" t="n">
         <v>0.703</v>
       </c>
-      <c r="G9" s="27" t="n">
+      <c r="G9" s="25" t="n">
         <v>2.812</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.03667786059118737</v>
+        <v>0.03531332534209399</v>
       </c>
       <c r="I9" s="10" t="n">
         <v>46251</v>
@@ -5284,7 +5214,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>QDVD/SMID/DAC</t>
+          <t>QDVD/SMID/DAC/OR</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -5305,11 +5235,11 @@
       <c r="F10" s="7" t="n">
         <v>1.03</v>
       </c>
-      <c r="G10" s="27" t="n">
+      <c r="G10" s="25" t="n">
         <v>4.12</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.02663391256691318</v>
+        <v>0.02594540160274221</v>
       </c>
       <c r="I10" s="10" t="n">
         <v>46265</v>
@@ -5337,7 +5267,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>QDVD/SMID/DAC</t>
+          <t>QDVD/SMID/DAC/OR</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -5358,11 +5288,11 @@
       <c r="F11" s="7" t="n">
         <v>1.25</v>
       </c>
-      <c r="G11" s="27" t="n">
+      <c r="G11" s="25" t="n">
         <v>5</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.05855829331739755</v>
+        <v>0.05710370191198418</v>
       </c>
       <c r="I11" s="10" t="n">
         <v>46246</v>
@@ -5390,7 +5320,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>QDVD/DAC</t>
+          <t>QDVD/DAC/OR</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -5411,11 +5341,11 @@
       <c r="F12" s="7" t="n">
         <v>1.3</v>
       </c>
-      <c r="G12" s="27" t="n">
+      <c r="G12" s="25" t="n">
         <v>5.2</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0.01779115923675148</v>
+        <v>0.01682385150932105</v>
       </c>
       <c r="I12" s="10" t="n">
         <v>46274</v>
@@ -5464,11 +5394,11 @@
       <c r="F13" s="7" t="n">
         <v>0.24</v>
       </c>
-      <c r="G13" s="27" t="n">
+      <c r="G13" s="25" t="n">
         <v>0.96</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0.02386278923498678</v>
+        <v>0.02323892442716519</v>
       </c>
       <c r="I13" s="10" t="n">
         <v>46254</v>
@@ -5496,7 +5426,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>SMID/DAC</t>
+          <t>SMID/DAC/OR</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -5517,11 +5447,11 @@
       <c r="F14" s="7" t="n">
         <v>0.6</v>
       </c>
-      <c r="G14" s="27" t="n">
+      <c r="G14" s="25" t="n">
         <v>2.4</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>0.007036008061734701</v>
+        <v>0.007181758491234575</v>
       </c>
       <c r="I14" s="10" t="n">
         <v>46248</v>
@@ -5549,7 +5479,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>QDVD/DAC</t>
+          <t>QDVD/DAC/OR</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -5570,11 +5500,11 @@
       <c r="F15" s="7" t="n">
         <v>0.42</v>
       </c>
-      <c r="G15" s="27" t="n">
+      <c r="G15" s="25" t="n">
         <v>1.68</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0.01569140206127972</v>
+        <v>0.01550173010380623</v>
       </c>
       <c r="I15" s="10" t="n">
         <v>46297</v>
@@ -5623,11 +5553,11 @@
       <c r="F16" s="7" t="n">
         <v>1.78</v>
       </c>
-      <c r="G16" s="27" t="n">
+      <c r="G16" s="25" t="n">
         <v>7.12</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>0.03156028283409273</v>
+        <v>0.030444264542924</v>
       </c>
       <c r="I16" s="10" t="n">
         <v>46253</v>
@@ -5655,7 +5585,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>SMID/DAC</t>
+          <t>SMID/DAC/OR</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -5676,11 +5606,11 @@
       <c r="F17" s="7" t="n">
         <v>0.86</v>
       </c>
-      <c r="G17" s="27" t="n">
+      <c r="G17" s="25" t="n">
         <v>3.44</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0.01468798690508526</v>
+        <v>0.01418088867191861</v>
       </c>
       <c r="I17" s="10" t="n">
         <v>46301</v>
@@ -5701,67 +5631,67 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>DVN</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>QDVD/SMID/DAC</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>DOX</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>SMID/DAC</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>Mar/Jun/Sep/Dec</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="16" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="F18" s="7" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="G18" s="27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="H18" s="9" t="n">
-        <v>0.02526149686708471</v>
-      </c>
-      <c r="I18" s="10" t="n">
-        <v>46280</v>
-      </c>
-      <c r="J18" s="8" t="n">
-        <v>0.3333333333333334</v>
-      </c>
-      <c r="K18" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="L18" s="10" t="n">
-        <v>46458</v>
-      </c>
-      <c r="M18" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="F18" s="17" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="G18" s="26" t="n">
+        <v>2.276</v>
+      </c>
+      <c r="H18" s="19" t="n">
+        <v>0.03597850237731143</v>
+      </c>
+      <c r="I18" s="20" t="n">
+        <v>46295</v>
+      </c>
+      <c r="J18" s="18" t="n">
+        <v>0.07969639468690688</v>
+      </c>
+      <c r="K18" s="20" t="n">
+        <v>46455</v>
+      </c>
+      <c r="L18" s="20" t="n">
+        <v>46476</v>
+      </c>
+      <c r="M18" s="22" t="inlineStr">
+        <is>
+          <t>yfinance</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>EMN</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>SMID/DAC</t>
+          <t>QDVD/SMID/DAC</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -5776,29 +5706,29 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="F19" s="7" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="G19" s="27" t="n">
-        <v>3.36</v>
+        <v>0.32</v>
+      </c>
+      <c r="G19" s="25" t="n">
+        <v>1.28</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0.05387205479463784</v>
+        <v>0.0246807407010214</v>
       </c>
       <c r="I19" s="10" t="n">
         <v>46280</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>0.01204819277108435</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="K19" s="10" t="n">
-        <v>46360</v>
+        <v>46433</v>
       </c>
       <c r="L19" s="10" t="n">
-        <v>46371</v>
+        <v>46458</v>
       </c>
       <c r="M19" s="12" t="inlineStr">
         <is>
@@ -5809,12 +5739,12 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>EMN</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>QDVD/DAC</t>
+          <t>SMID/DAC</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -5824,34 +5754,34 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Feb/May/Aug/Nov</t>
+          <t>Mar/Jun/Sep/Dec</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="G20" s="27" t="n">
-        <v>2.56</v>
+        <v>0.84</v>
+      </c>
+      <c r="G20" s="25" t="n">
+        <v>3.36</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0.02452812046212039</v>
+        <v>0.05093224098570341</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>46247</v>
+        <v>46280</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>0.06666666666666674</v>
+        <v>0.01204819277108435</v>
       </c>
       <c r="K20" s="10" t="n">
-        <v>46322</v>
+        <v>46360</v>
       </c>
       <c r="L20" s="10" t="n">
-        <v>46338</v>
+        <v>46371</v>
       </c>
       <c r="M20" s="12" t="inlineStr">
         <is>
@@ -5862,171 +5792,171 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
+          <t>ETR</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>QDVD/DAC/OR</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Feb/May/Aug/Nov</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G21" s="25" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>0.02369273417580299</v>
+      </c>
+      <c r="I21" s="10" t="n">
+        <v>46247</v>
+      </c>
+      <c r="J21" s="8" t="n">
+        <v>0.06666666666666674</v>
+      </c>
+      <c r="K21" s="10" t="n">
+        <v>46322</v>
+      </c>
+      <c r="L21" s="10" t="n">
+        <v>46338</v>
+      </c>
+      <c r="M21" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
           <t>GD</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>QDVD/DAC</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>Jan/Apr/Jul/Oct</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="F21" s="7" t="n">
+      <c r="F22" s="7" t="n">
         <v>1.59</v>
       </c>
-      <c r="G21" s="27" t="n">
+      <c r="G22" s="25" t="n">
         <v>6.36</v>
       </c>
-      <c r="H21" s="9" t="n">
-        <v>0.01856934306569343</v>
-      </c>
-      <c r="I21" s="10" t="n">
+      <c r="H22" s="9" t="n">
+        <v>0.01795342272406493</v>
+      </c>
+      <c r="I22" s="10" t="n">
         <v>46304</v>
       </c>
-      <c r="J21" s="8" t="n">
+      <c r="J22" s="8" t="n">
         <v>0.06000000000000005</v>
       </c>
-      <c r="K21" s="10" t="n">
+      <c r="K22" s="10" t="n">
         <v>46452</v>
       </c>
-      <c r="L21" s="10" t="n">
+      <c r="L22" s="10" t="n">
         <v>46487</v>
       </c>
-      <c r="M21" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+      <c r="M22" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>GGG</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>SMID/DAC</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D22" s="15" t="inlineStr">
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>Jan/Apr/Jul/Oct</t>
         </is>
       </c>
-      <c r="E22" s="15" t="inlineStr">
+      <c r="E23" s="16" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="F22" s="16" t="n">
+      <c r="F23" s="17" t="n">
         <v>0.295</v>
       </c>
-      <c r="G22" s="28" t="n">
+      <c r="G23" s="26" t="n">
         <v>1.18</v>
       </c>
-      <c r="H22" s="22" t="n">
-        <v>0.0146057678750838</v>
-      </c>
-      <c r="I22" s="19" t="n">
-        <v>46223</v>
-      </c>
-      <c r="J22" s="17" t="n">
+      <c r="H23" s="19" t="n">
+        <v>0.01758962534253235</v>
+      </c>
+      <c r="I23" s="20" t="n">
+        <v>46314</v>
+      </c>
+      <c r="J23" s="18" t="n">
         <v>0.07272727272727258</v>
       </c>
-      <c r="K22" s="19" t="n">
+      <c r="K23" s="20" t="n">
         <v>46383</v>
       </c>
-      <c r="L22" s="19" t="n">
+      <c r="L23" s="20" t="n">
         <v>46404</v>
       </c>
-      <c r="M22" s="21" t="inlineStr">
+      <c r="M23" s="22" t="inlineStr">
         <is>
           <t>yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>HD</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>QDVD/DAC</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>Mar/Jun/Aug/Nov</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="G23" s="27" t="n">
-        <v>9.32</v>
-      </c>
-      <c r="H23" s="9" t="n">
-        <v>0.03030312976869731</v>
-      </c>
-      <c r="I23" s="10" t="n">
-        <v>46268</v>
-      </c>
-      <c r="J23" s="8" t="n">
-        <v>0.01304347826086967</v>
-      </c>
-      <c r="K23" s="10" t="n">
-        <v>46441</v>
-      </c>
-      <c r="L23" s="10" t="n">
-        <v>46456</v>
-      </c>
-      <c r="M23" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>SMID/DAC</t>
+          <t>QDVD/DAC/OR</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -6036,34 +5966,34 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>Feb/May/Aug/Nov</t>
+          <t>Mar/Jun/Aug/Nov</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="F24" s="7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="G24" s="27" t="n">
-        <v>5.52</v>
+        <v>2.33</v>
+      </c>
+      <c r="G24" s="25" t="n">
+        <v>9.32</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>0.02062048170108176</v>
+        <v>0.02907820093926896</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>46262</v>
+        <v>46268</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>0.02222222222222208</v>
+        <v>0.01304347826086967</v>
       </c>
       <c r="K24" s="10" t="n">
-        <v>46318</v>
+        <v>46441</v>
       </c>
       <c r="L24" s="10" t="n">
-        <v>46352</v>
+        <v>46456</v>
       </c>
       <c r="M24" s="12" t="inlineStr">
         <is>
@@ -6074,171 +6004,171 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
+          <t>HII</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>SMID/DAC</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Feb/May/Aug/Nov</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G25" s="25" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="H25" s="9" t="n">
+        <v>0.01982367084874391</v>
+      </c>
+      <c r="I25" s="10" t="n">
+        <v>46262</v>
+      </c>
+      <c r="J25" s="8" t="n">
+        <v>0.02222222222222208</v>
+      </c>
+      <c r="K25" s="10" t="n">
+        <v>46683</v>
+      </c>
+      <c r="L25" s="10" t="n">
+        <v>46717</v>
+      </c>
+      <c r="M25" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
           <t>HRL</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>SMID/DAC</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>Jan/Apr/Jul/Oct</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="F25" s="7" t="n">
+      <c r="F26" s="7" t="n">
         <v>0.293</v>
       </c>
-      <c r="G25" s="27" t="n">
+      <c r="G26" s="25" t="n">
         <v>1.172</v>
       </c>
-      <c r="H25" s="9" t="n">
-        <v>0.05780204234676849</v>
-      </c>
-      <c r="I25" s="10" t="n">
+      <c r="H26" s="9" t="n">
+        <v>0.05554502269247655</v>
+      </c>
+      <c r="I26" s="10" t="n">
         <v>46308</v>
       </c>
-      <c r="J25" s="8" t="n">
+      <c r="J26" s="8" t="n">
         <v>0.01034482758620691</v>
       </c>
-      <c r="K25" s="10" t="n">
+      <c r="K26" s="10" t="n">
         <v>46351</v>
       </c>
-      <c r="L25" s="10" t="n">
+      <c r="L26" s="10" t="n">
         <v>46399</v>
       </c>
-      <c r="M25" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="M26" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>HWC</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>SMID/DAC</t>
         </is>
       </c>
-      <c r="C26" s="15" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D26" s="15" t="inlineStr">
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>Mar/Jun/Sep/Dec</t>
         </is>
       </c>
-      <c r="E26" s="15" t="inlineStr">
+      <c r="E27" s="16" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="F26" s="16" t="n">
+      <c r="F27" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="G26" s="28" t="n">
+      <c r="G27" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="H26" s="22" t="n">
-        <v>0.02740852359246717</v>
-      </c>
-      <c r="I26" s="19" t="n">
+      <c r="H27" s="19" t="n">
+        <v>0.02699419758207186</v>
+      </c>
+      <c r="I27" s="20" t="n">
         <v>46269</v>
       </c>
-      <c r="J26" s="17" t="n">
+      <c r="J27" s="18" t="n">
         <v>0.1111111111111111</v>
       </c>
-      <c r="K26" s="19" t="n">
+      <c r="K27" s="20" t="n">
         <v>46429</v>
       </c>
-      <c r="L26" s="19" t="n">
+      <c r="L27" s="20" t="n">
         <v>46450</v>
       </c>
-      <c r="M26" s="21" t="inlineStr">
+      <c r="M27" s="22" t="inlineStr">
         <is>
           <t>yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>INGR</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>SMID/DAC</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Mar/Jul/Oct/Dec</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="G27" s="27" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="H27" s="9" t="n">
-        <v>0.03416692459155611</v>
-      </c>
-      <c r="I27" s="10" t="n">
-        <v>46296</v>
-      </c>
-      <c r="J27" s="8" t="n">
-        <v>0.01219512195121952</v>
-      </c>
-      <c r="K27" s="10" t="n">
-        <v>46614</v>
-      </c>
-      <c r="L27" s="10" t="n">
-        <v>46662</v>
-      </c>
-      <c r="M27" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>QDVD/SMID/DAC</t>
+          <t>SMID/DAC/OR</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -6248,34 +6178,34 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Mar/May/Sep/Dec</t>
+          <t>Mar/Jul/Oct/Dec</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="F28" s="7" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="G28" s="27" t="n">
-        <v>2.44</v>
+        <v>0.83</v>
+      </c>
+      <c r="G28" s="25" t="n">
+        <v>3.32</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>0.01601680490124256</v>
+        <v>0.03450784774548257</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>46269</v>
+        <v>46296</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>0.05172413793103453</v>
+        <v>0.01219512195121952</v>
       </c>
       <c r="K28" s="10" t="n">
-        <v>46428</v>
+        <v>46614</v>
       </c>
       <c r="L28" s="10" t="n">
-        <v>46452</v>
+        <v>46662</v>
       </c>
       <c r="M28" s="12" t="inlineStr">
         <is>
@@ -6286,12 +6216,12 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>QDVD/DAC</t>
+          <t>QDVD/SMID/DAC/OR</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -6301,34 +6231,34 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Feb/May/Aug/Nov</t>
+          <t>Mar/May/Sep/Dec</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="F29" s="7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="G29" s="27" t="n">
-        <v>5.36</v>
+        <v>0.61</v>
+      </c>
+      <c r="G29" s="25" t="n">
+        <v>2.44</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.02108990804140305</v>
+        <v>0.0150659132006637</v>
       </c>
       <c r="I29" s="10" t="n">
-        <v>46259</v>
+        <v>46269</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>0.0307692307692308</v>
+        <v>0.05172413793103453</v>
       </c>
       <c r="K29" s="10" t="n">
-        <v>46493</v>
+        <v>46428</v>
       </c>
       <c r="L29" s="10" t="n">
-        <v>46531</v>
+        <v>46452</v>
       </c>
       <c r="M29" s="12" t="inlineStr">
         <is>
@@ -6339,12 +6269,12 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>QDVD/DAC</t>
+          <t>QDVD/DAC/OR</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -6354,34 +6284,34 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Jan/Apr/Jul/Oct</t>
+          <t>Feb/May/Aug/Nov</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>May</t>
         </is>
       </c>
       <c r="F30" s="7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="G30" s="27" t="n">
-        <v>6.6</v>
+        <v>1.34</v>
+      </c>
+      <c r="G30" s="25" t="n">
+        <v>5.36</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>0.01956773053691266</v>
+        <v>0.01971312363195655</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>46301</v>
+        <v>46259</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>0.09999999999999994</v>
+        <v>0.0307692307692308</v>
       </c>
       <c r="K30" s="10" t="n">
-        <v>46461</v>
+        <v>46493</v>
       </c>
       <c r="L30" s="10" t="n">
-        <v>46665</v>
+        <v>46531</v>
       </c>
       <c r="M30" s="12" t="inlineStr">
         <is>
@@ -6392,49 +6322,49 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>QDVD</t>
+          <t>QDVD/DAC/OR</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Semi-Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Apr/Oct</t>
+          <t>Jan/Apr/Jul/Oct</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="F31" s="7" t="n">
-        <v>1.084</v>
-      </c>
-      <c r="G31" s="27" t="n">
-        <v>2.168</v>
+        <v>1.65</v>
+      </c>
+      <c r="G31" s="25" t="n">
+        <v>6.6</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0.01795251849684193</v>
+        <v>0.01966685560362995</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>46304</v>
+        <v>46301</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>0.03495860165593379</v>
+        <v>0.09999999999999994</v>
       </c>
       <c r="K31" s="10" t="n">
-        <v>46492</v>
+        <v>46461</v>
       </c>
       <c r="L31" s="10" t="n">
-        <v>46501</v>
+        <v>46665</v>
       </c>
       <c r="M31" s="12" t="inlineStr">
         <is>
@@ -6445,49 +6375,49 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>SMID/DAC</t>
+          <t>QDVD/OR</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>Mar/Jun/Sep/Dec</t>
+          <t>Apr/Oct</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="F32" s="7" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="G32" s="27" t="n">
-        <v>3.16</v>
+        <v>1.084</v>
+      </c>
+      <c r="G32" s="25" t="n">
+        <v>2.168</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>0.01212586310817193</v>
+        <v>0.01940044742729307</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>46295</v>
+        <v>46304</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>0.05333333333333338</v>
+        <v>0.03495860165593379</v>
       </c>
       <c r="K32" s="10" t="n">
-        <v>46676</v>
+        <v>46492</v>
       </c>
       <c r="L32" s="10" t="n">
-        <v>46751</v>
+        <v>46501</v>
       </c>
       <c r="M32" s="12" t="inlineStr">
         <is>
@@ -6498,12 +6428,12 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>QDVD/DAC</t>
+          <t>SMID/DAC/OR</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -6518,29 +6448,29 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="F33" s="7" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G33" s="27" t="n">
-        <v>2.88</v>
+        <v>0.79</v>
+      </c>
+      <c r="G33" s="25" t="n">
+        <v>3.16</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0.03067262567036151</v>
+        <v>0.01216179872726553</v>
       </c>
       <c r="I33" s="10" t="n">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>0.01408450704225353</v>
+        <v>0.05333333333333338</v>
       </c>
       <c r="K33" s="10" t="n">
-        <v>46532</v>
+        <v>46676</v>
       </c>
       <c r="L33" s="10" t="n">
-        <v>46563</v>
+        <v>46751</v>
       </c>
       <c r="M33" s="12" t="inlineStr">
         <is>
@@ -6551,12 +6481,12 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>QDVD/SMID/DAC</t>
+          <t>QDVD/DAC/OR</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -6566,34 +6496,34 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Apr/Jul/Oct/Dec</t>
+          <t>Mar/Jun/Sep/Dec</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="F34" s="7" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="G34" s="27" t="n">
-        <v>1.92</v>
+        <v>0.72</v>
+      </c>
+      <c r="G34" s="25" t="n">
+        <v>2.88</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0.0418647250543317</v>
+        <v>0.03014917512688835</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>46308</v>
+        <v>46290</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.01408450704225353</v>
       </c>
       <c r="K34" s="10" t="n">
-        <v>46344</v>
+        <v>46532</v>
       </c>
       <c r="L34" s="10" t="n">
-        <v>46385</v>
+        <v>46563</v>
       </c>
       <c r="M34" s="12" t="inlineStr">
         <is>
@@ -6604,106 +6534,106 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
+          <t>MKC</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>QDVD/SMID/DAC/OR</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Apr/Jul/Oct/Dec</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G35" s="25" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H35" s="9" t="n">
+        <v>0.03972687621059211</v>
+      </c>
+      <c r="I35" s="10" t="n">
+        <v>46308</v>
+      </c>
+      <c r="J35" s="8" t="n">
+        <v>0.0666666666666666</v>
+      </c>
+      <c r="K35" s="10" t="n">
+        <v>46344</v>
+      </c>
+      <c r="L35" s="10" t="n">
+        <v>46385</v>
+      </c>
+      <c r="M35" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>QDVD/DAC</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>QDVD/DAC/OR</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>Feb/May/Aug/Nov</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="F35" s="7" t="n">
+      <c r="F36" s="7" t="n">
         <v>0.91</v>
       </c>
-      <c r="G35" s="27" t="n">
+      <c r="G36" s="25" t="n">
         <v>3.64</v>
       </c>
-      <c r="H35" s="9" t="n">
-        <v>0.006843878990992571</v>
-      </c>
-      <c r="I35" s="10" t="n">
+      <c r="H36" s="9" t="n">
+        <v>0.006938487832176294</v>
+      </c>
+      <c r="I36" s="10" t="n">
         <v>46254</v>
       </c>
-      <c r="J35" s="8" t="n">
+      <c r="J36" s="8" t="n">
         <v>0.09638554216867479</v>
       </c>
-      <c r="K35" s="10" t="n">
+      <c r="K36" s="10" t="n">
         <v>46643</v>
       </c>
-      <c r="L35" s="10" t="n">
+      <c r="L36" s="10" t="n">
         <v>46709</v>
       </c>
-      <c r="M35" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="14" t="inlineStr">
-        <is>
-          <t>MSM</t>
-        </is>
-      </c>
-      <c r="B36" s="15" t="inlineStr">
-        <is>
-          <t>SMID/DAC</t>
-        </is>
-      </c>
-      <c r="C36" s="15" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D36" s="15" t="inlineStr">
-        <is>
-          <t>Jan/Apr/Jul/Nov</t>
-        </is>
-      </c>
-      <c r="E36" s="15" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="F36" s="16" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="G36" s="28" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="H36" s="22" t="n">
-        <v>0.02687466099600802</v>
-      </c>
-      <c r="I36" s="19" t="n">
-        <v>46211</v>
-      </c>
-      <c r="J36" s="17" t="n">
-        <v>0.0235294117647059</v>
-      </c>
-      <c r="K36" s="19" t="n">
-        <v>46318</v>
-      </c>
-      <c r="L36" s="19" t="n">
-        <v>46339</v>
-      </c>
-      <c r="M36" s="21" t="inlineStr">
-        <is>
-          <t>yfinance</t>
+      <c r="M36" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
@@ -6715,7 +6645,7 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>QDVD/DAC</t>
+          <t>QDVD/DAC/OR</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -6736,11 +6666,11 @@
       <c r="F37" s="7" t="n">
         <v>0.41</v>
       </c>
-      <c r="G37" s="27" t="n">
+      <c r="G37" s="25" t="n">
         <v>1.64</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>0.04446252066229808</v>
+        <v>0.04288702740626434</v>
       </c>
       <c r="I37" s="10" t="n">
         <v>46266</v>
@@ -6768,7 +6698,7 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>QDVD</t>
+          <t>QDVD/OR</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -6789,11 +6719,11 @@
       <c r="F38" s="7" t="n">
         <v>0.579</v>
       </c>
-      <c r="G38" s="27" t="n">
+      <c r="G38" s="25" t="n">
         <v>1.158</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0.0300600424991833</v>
+        <v>0.02968089242895755</v>
       </c>
       <c r="I38" s="10" t="n">
         <v>46251</v>
@@ -6821,7 +6751,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>QDVD/DAC</t>
+          <t>QDVD/DAC/OR</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -6842,11 +6772,11 @@
       <c r="F39" s="7" t="n">
         <v>0.272</v>
       </c>
-      <c r="G39" s="27" t="n">
+      <c r="G39" s="25" t="n">
         <v>3.264</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>0.05860490201786151</v>
+        <v>0.05691368939570006</v>
       </c>
       <c r="I39" s="10" t="n">
         <v>46295</v>
@@ -6874,7 +6804,7 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>SMID/DAC</t>
+          <t>QDVD/SMID/DAC/OR</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -6895,11 +6825,11 @@
       <c r="F40" s="7" t="n">
         <v>1.19</v>
       </c>
-      <c r="G40" s="27" t="n">
+      <c r="G40" s="25" t="n">
         <v>4.76</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0.04296028762541161</v>
+        <v>0.04081807732450217</v>
       </c>
       <c r="I40" s="10" t="n">
         <v>46231</v>
@@ -6927,7 +6857,7 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>QDVD/DAC</t>
+          <t>QDVD/DAC/OR</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -6948,11 +6878,11 @@
       <c r="F41" s="7" t="n">
         <v>0.67</v>
       </c>
-      <c r="G41" s="27" t="n">
+      <c r="G41" s="25" t="n">
         <v>2.68</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>0.03813318222181694</v>
+        <v>0.03696551724137932</v>
       </c>
       <c r="I41" s="10" t="n">
         <v>46274</v>
@@ -6980,7 +6910,7 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>QDVD/DAC</t>
+          <t>QDVD/DAC/OR</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -7001,11 +6931,11 @@
       <c r="F42" s="7" t="n">
         <v>1.48</v>
       </c>
-      <c r="G42" s="27" t="n">
+      <c r="G42" s="25" t="n">
         <v>5.92</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>0.04479418762075352</v>
+        <v>0.04307647759224001</v>
       </c>
       <c r="I42" s="10" t="n">
         <v>46269</v>
@@ -7033,7 +6963,7 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>QDVD/DAC</t>
+          <t>QDVD/DAC/OR</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -7054,11 +6984,11 @@
       <c r="F43" s="7" t="n">
         <v>0.43</v>
       </c>
-      <c r="G43" s="27" t="n">
+      <c r="G43" s="25" t="n">
         <v>1.72</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>0.05809829510539736</v>
+        <v>0.0569065336076718</v>
       </c>
       <c r="I43" s="10" t="n">
         <v>46227</v>
@@ -7086,7 +7016,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>SMID/DAC</t>
+          <t>SMID/DAC/OR</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -7107,11 +7037,11 @@
       <c r="F44" s="7" t="n">
         <v>0.84</v>
       </c>
-      <c r="G44" s="27" t="n">
+      <c r="G44" s="25" t="n">
         <v>3.36</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>0.03105934544760066</v>
+        <v>0.03036876372501466</v>
       </c>
       <c r="I44" s="10" t="n">
         <v>46268</v>
@@ -7139,7 +7069,7 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>QDVD/DAC</t>
+          <t>QDVD/DAC/OR</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -7160,14 +7090,14 @@
       <c r="F45" s="7" t="n">
         <v>1.089</v>
       </c>
-      <c r="G45" s="27" t="n">
+      <c r="G45" s="25" t="n">
         <v>4.356</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>0.0275277889821852</v>
+        <v>0.02703742774190096</v>
       </c>
       <c r="I45" s="10" t="n">
-        <v>46227</v>
+        <v>46318</v>
       </c>
       <c r="J45" s="8" t="n">
         <v>0.03027436140018924</v>
@@ -7213,11 +7143,11 @@
       <c r="F46" s="7" t="n">
         <v>0.551</v>
       </c>
-      <c r="G46" s="27" t="n">
+      <c r="G46" s="25" t="n">
         <v>2.204</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>0.0501250838938402</v>
+        <v>0.04930648685418649</v>
       </c>
       <c r="I46" s="10" t="n">
         <v>46290</v>
@@ -7238,67 +7168,67 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="14" t="inlineStr">
-        <is>
-          <t>PSX</t>
-        </is>
-      </c>
-      <c r="B47" s="15" t="inlineStr">
-        <is>
-          <t>QDVD/DAC</t>
-        </is>
-      </c>
-      <c r="C47" s="15" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D47" s="15" t="inlineStr">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>RGA</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>QDVD/SMID/DAC/OR</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>Feb/May/Aug/Nov</t>
         </is>
       </c>
-      <c r="E47" s="15" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="F47" s="16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="G47" s="28" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="H47" s="22" t="n">
-        <v>0.01698655802003307</v>
-      </c>
-      <c r="I47" s="19" t="n">
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G47" s="25" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H47" s="9" t="n">
+        <v>0.01460833291159467</v>
+      </c>
+      <c r="I47" s="10" t="n">
         <v>46252</v>
       </c>
-      <c r="J47" s="17" t="n">
-        <v>0.05833333333333339</v>
-      </c>
-      <c r="K47" s="19" t="n">
-        <v>46505</v>
-      </c>
-      <c r="L47" s="19" t="n">
-        <v>46526</v>
-      </c>
-      <c r="M47" s="21" t="inlineStr">
-        <is>
-          <t>yfinance</t>
+      <c r="J47" s="8" t="n">
+        <v>0.05376344086021498</v>
+      </c>
+      <c r="K47" s="10" t="n">
+        <v>46594</v>
+      </c>
+      <c r="L47" s="10" t="n">
+        <v>46613</v>
+      </c>
+      <c r="M47" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>QDVD/SMID/DAC</t>
+          <t>SMID/DAC</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -7313,29 +7243,29 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="F48" s="7" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="G48" s="27" t="n">
-        <v>3.92</v>
+        <v>2.44</v>
+      </c>
+      <c r="G48" s="25" t="n">
+        <v>9.76</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>0.01472908914196234</v>
+        <v>0.02711864452769955</v>
       </c>
       <c r="I48" s="10" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="J48" s="8" t="n">
-        <v>0.05376344086021498</v>
+        <v>0.1401869158878504</v>
       </c>
       <c r="K48" s="10" t="n">
-        <v>46594</v>
+        <v>46332</v>
       </c>
       <c r="L48" s="10" t="n">
-        <v>46613</v>
+        <v>46346</v>
       </c>
       <c r="M48" s="12" t="inlineStr">
         <is>
@@ -7346,7 +7276,7 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
@@ -7361,34 +7291,34 @@
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Feb/May/Aug/Nov</t>
+          <t>Mar/Jun/Sep/Nov</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="F49" s="7" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="G49" s="27" t="n">
-        <v>9.76</v>
+        <v>0.84</v>
+      </c>
+      <c r="G49" s="25" t="n">
+        <v>3.36</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>0.02684619212402568</v>
+        <v>0.03380621813697231</v>
       </c>
       <c r="I49" s="10" t="n">
-        <v>46253</v>
+        <v>46273</v>
       </c>
       <c r="J49" s="8" t="n">
-        <v>0.1401869158878504</v>
+        <v>0.01204819277108435</v>
       </c>
       <c r="K49" s="10" t="n">
-        <v>46332</v>
+        <v>46591</v>
       </c>
       <c r="L49" s="10" t="n">
-        <v>46346</v>
+        <v>46633</v>
       </c>
       <c r="M49" s="12" t="inlineStr">
         <is>
@@ -7399,12 +7329,12 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>SMID/DAC</t>
+          <t>QDVD/SMID/DAC/OR</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -7414,34 +7344,34 @@
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>Mar/Jun/Sep/Nov</t>
+          <t>Mar/Jun/Sep/Dec</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="F50" s="7" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="G50" s="27" t="n">
-        <v>3.36</v>
+        <v>1.3</v>
+      </c>
+      <c r="G50" s="25" t="n">
+        <v>5.2</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>0.03676269334137368</v>
+        <v>0.04933820547108572</v>
       </c>
       <c r="I50" s="10" t="n">
-        <v>46273</v>
+        <v>46280</v>
       </c>
       <c r="J50" s="8" t="n">
-        <v>0.01204819277108435</v>
+        <v>0.02362204724409451</v>
       </c>
       <c r="K50" s="10" t="n">
-        <v>46591</v>
+        <v>46428</v>
       </c>
       <c r="L50" s="10" t="n">
-        <v>46633</v>
+        <v>46460</v>
       </c>
       <c r="M50" s="12" t="inlineStr">
         <is>
@@ -7452,12 +7382,12 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>QDVD/SMID/DAC</t>
+          <t>QDVD</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -7472,29 +7402,29 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="F51" s="7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="G51" s="27" t="n">
-        <v>5.2</v>
+        <v>1.021</v>
+      </c>
+      <c r="G51" s="25" t="n">
+        <v>4.084</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>0.05203642533893469</v>
+        <v>0.04359521762057851</v>
       </c>
       <c r="I51" s="10" t="n">
-        <v>46280</v>
+        <v>46295</v>
       </c>
       <c r="J51" s="8" t="n">
-        <v>0.02362204724409451</v>
+        <v>0.04825462012320322</v>
       </c>
       <c r="K51" s="10" t="n">
-        <v>46428</v>
+        <v>46492</v>
       </c>
       <c r="L51" s="10" t="n">
-        <v>46460</v>
+        <v>46376</v>
       </c>
       <c r="M51" s="12" t="inlineStr">
         <is>
@@ -7505,12 +7435,12 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>QDVD</t>
+          <t>QDVD/DAC/OR</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -7520,34 +7450,34 @@
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>Mar/Jun/Sep/Dec</t>
+          <t>Jan/May/Jul/Oct</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="F52" s="7" t="n">
-        <v>1.021</v>
-      </c>
-      <c r="G52" s="27" t="n">
-        <v>4.084</v>
+        <v>1.42</v>
+      </c>
+      <c r="G52" s="25" t="n">
+        <v>5.68</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>0.04487665648324178</v>
+        <v>0.0198317095330963</v>
       </c>
       <c r="I52" s="10" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="J52" s="8" t="n">
-        <v>0.04825462012320322</v>
+        <v>0.0441176470588234</v>
       </c>
       <c r="K52" s="10" t="n">
-        <v>46492</v>
+        <v>46650</v>
       </c>
       <c r="L52" s="10" t="n">
-        <v>46376</v>
+        <v>46690</v>
       </c>
       <c r="M52" s="12" t="inlineStr">
         <is>
@@ -7558,12 +7488,12 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>QDVD/DAC</t>
+          <t>QDVD/OR</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -7573,34 +7503,34 @@
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Jan/May/Jul/Oct</t>
+          <t>Feb/May/Aug/Nov</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="F53" s="7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="G53" s="27" t="n">
-        <v>5.68</v>
+        <v>0.531</v>
+      </c>
+      <c r="G53" s="25" t="n">
+        <v>2.124</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>0.02051059888861486</v>
+        <v>0.03209913947068581</v>
       </c>
       <c r="I53" s="10" t="n">
-        <v>46234</v>
+        <v>46241</v>
       </c>
       <c r="J53" s="8" t="n">
-        <v>0.0441176470588234</v>
+        <v>0.005735494868956323</v>
       </c>
       <c r="K53" s="10" t="n">
-        <v>46650</v>
+        <v>46433</v>
       </c>
       <c r="L53" s="10" t="n">
-        <v>46690</v>
+        <v>46608</v>
       </c>
       <c r="M53" s="12" t="inlineStr">
         <is>
@@ -7611,12 +7541,12 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>QDVD</t>
+          <t>QDVD/DAC/OR</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -7626,7 +7556,7 @@
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>Feb/May/Aug/Nov</t>
+          <t>Feb/May/Aug/Dec</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -7635,25 +7565,25 @@
         </is>
       </c>
       <c r="F54" s="7" t="n">
-        <v>0.531</v>
-      </c>
-      <c r="G54" s="27" t="n">
-        <v>2.124</v>
+        <v>1.42</v>
+      </c>
+      <c r="G54" s="25" t="n">
+        <v>5.68</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>0.03252679786732145</v>
+        <v>0.01920930688593553</v>
       </c>
       <c r="I54" s="10" t="n">
-        <v>46241</v>
+        <v>46265</v>
       </c>
       <c r="J54" s="8" t="n">
-        <v>0.005735494868956323</v>
+        <v>0.02898550724637684</v>
       </c>
       <c r="K54" s="10" t="n">
-        <v>46433</v>
+        <v>46589</v>
       </c>
       <c r="L54" s="10" t="n">
-        <v>46608</v>
+        <v>46629</v>
       </c>
       <c r="M54" s="12" t="inlineStr">
         <is>
@@ -7664,12 +7594,12 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>QDVD/DAC</t>
+          <t>QDVD/DAC/OR</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -7679,34 +7609,34 @@
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Feb/May/Aug/Dec</t>
+          <t>Jan/Apr/Jul/Oct</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="F55" s="7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="G55" s="27" t="n">
-        <v>5.68</v>
+        <v>0.708</v>
+      </c>
+      <c r="G55" s="25" t="n">
+        <v>2.832</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>0.01977647076699418</v>
+        <v>0.065351334021713</v>
       </c>
       <c r="I55" s="10" t="n">
-        <v>46265</v>
+        <v>46304</v>
       </c>
       <c r="J55" s="8" t="n">
-        <v>0.02898550724637684</v>
+        <v>0.02608695652173916</v>
       </c>
       <c r="K55" s="10" t="n">
-        <v>46589</v>
+        <v>46645</v>
       </c>
       <c r="L55" s="10" t="n">
-        <v>46629</v>
+        <v>46668</v>
       </c>
       <c r="M55" s="12" t="inlineStr">
         <is>
@@ -7717,7 +7647,7 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
@@ -7732,89 +7662,36 @@
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>Jan/Apr/Jul/Oct</t>
+          <t>Feb/May/Aug/Nov</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="F56" s="7" t="n">
-        <v>0.708</v>
-      </c>
-      <c r="G56" s="27" t="n">
-        <v>2.832</v>
+        <v>1.03</v>
+      </c>
+      <c r="G56" s="25" t="n">
+        <v>4.12</v>
       </c>
       <c r="H56" s="9" t="n">
-        <v>0.06363329810206279</v>
+        <v>0.02236638505494382</v>
       </c>
       <c r="I56" s="10" t="n">
-        <v>46304</v>
+        <v>46251</v>
       </c>
       <c r="J56" s="8" t="n">
-        <v>0.02608695652173916</v>
+        <v>0.04040404040404044</v>
       </c>
       <c r="K56" s="10" t="n">
-        <v>46645</v>
+        <v>46341</v>
       </c>
       <c r="L56" s="10" t="n">
-        <v>46668</v>
+        <v>46340</v>
       </c>
       <c r="M56" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>QDVD/DAC</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>Feb/May/Aug/Nov</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="F57" s="7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="G57" s="27" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="H57" s="9" t="n">
-        <v>0.02299684646296404</v>
-      </c>
-      <c r="I57" s="10" t="n">
-        <v>46251</v>
-      </c>
-      <c r="J57" s="8" t="n">
-        <v>0.04040404040404044</v>
-      </c>
-      <c r="K57" s="10" t="n">
-        <v>46341</v>
-      </c>
-      <c r="L57" s="10" t="n">
-        <v>46340</v>
-      </c>
-      <c r="M57" s="12" t="inlineStr">
         <is>
           <t>Notion + yfinance</t>
         </is>
